--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1091,8 +1091,102 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Gempa magnitudo 5,1 guncang Bengkulu tak berpotensi tsunami</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 00:48:12 +0700</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Gempa magnitudo 5,1 mengguncang Kecamatan Enggano, Kabupaten Bengkulu Utara, pada Selasa dini hari sekitar pukul 00.08 ...</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688380/gempa-magnitudo-51-guncang-bengkulu-tak-berpotensi-tsunami</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_003935.jpg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Viral KDMP Berdiri di Tengah Pasar Papahan Karanganyar, Ternyata Ini Alasan Lokasinya Dipilih</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 00:52:07 +0700</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Viral Koperasi Desa Merah Putih (KDMP) berdiri di dalam area Pasar Desa Papahan, Kecamatan Tasikmadu, Kabupaten Karanganyar, Jawa Tengah.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866579/viral-kdmp-berdiri-di-tengah-pasar-papahan-karanganyar-ternyata-ini-alasan-lokasinya-dipilih</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/HeE3ln7veTR03JkbSYojXYqN5XA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Viral-KDMP-Berdiri-di-Tengah-Pasar-Papahan-Karanganyar-Ternyata-Ini-Alasan-Lokasinya-Dipilih.jpg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I14"/>
+  <autoFilter ref="A1:I16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1185,8 +1185,290 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PIER: Konsumsi masyarakat terjaga ditopang stimulus pemerintah</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 02:09:10 +0700</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Head of Macroeconomic &amp; Financial Market Research Permata Bank Faisal Rachman mengatakan konsumsi rumah tangga ...</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688393/pier-konsumsi-masyarakat-terjaga-ditopang-stimulus-pemerintah</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000456857.jpg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KPK masih dalami aliran uang kasus Bank BJB ke Lisa Mariana</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 02:08:56 +0700</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi (KPK) mengaku masih mendalami aliran uang kasus dugaan korupsi dalam pengadaan iklan PT ...</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688389/kpk-masih-dalami-aliran-uang-kasus-bank-bjb-ke-lisa-mariana</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/22/pemeriksaan-lisa-mariana-di-kpk-2604981.jpg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KPK duga tersangka kasus Bank BJB upayakan pengondisian audit BPK</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 02:05:07 +0700</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi (KPK) menduga tersangka kasus dugaan korupsi dalam pengadaan iklan PT Bank Pembangunan ...</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688388/kpk-duga-tersangka-kasus-bank-bjb-upayakan-pengondisian-audit-bpk</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/KPK-tahan-tersangka-kasus-korupsi-pengadaan-iklan-Bank-BJB-100826-fzn-6.jpg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KPK buka peluang periksa Ridwan Kamil setelah tahan tersangka Bank BJB</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:59:43 +0700</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi (KPK) membuka peluang untuk memeriksa kembali mantan Gubernur Jawa Barat Ridwan Kamil ...</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688385/kpk-buka-peluang-periksa-ridwan-kamil-setelah-tahan-tersangka-bank-bjb</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/02/ridwan-kamil-diperiksa-kpk-2680869_1.jpg</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Liverpool resmi pinjam bek Uruguay Ronald Araujo dari Barcelona</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:55:42 +0700</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Liverpool resmi meminjam bek tengah asal Uruguay Ronald Araujo dari Barcelona selama satu musim penuh untuk kompetisi ...</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688383/liverpool-resmi-pinjam-bek-uruguay-ronald-araujo-dari-barcelona</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000044027.jpg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pelajar Tewas Tertemper KRL di Stasiun Jurangmangu , Video TikTok Diduga Milik Korban Jadi Sorotan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:45:12 +0700</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Dugaan sengaja menjatuhkan ramai dibicarakan di media sosial setelah unggahan yang diduga berasal dari akun TikTok milik korban ikut viral</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866580/pelajar-tewas-tertemper-krl-di-stasiun-jurangmangu-video-tiktok-diduga-milik-korban-jadi-sorotan</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vnN8t7-_sNFl5avv0zV2pk7I0Tk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/tertemperKRL1.jpg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I16"/>
+  <autoFilter ref="A1:I22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1467,8 +1467,149 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sahroni Apresiasi BNN Bongkar Penyelundupan 1,3 Ton Ketamin: Mengerikan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 03:17:55 +0700</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi III DPR Sahroni apresiasi BNN dan Polri atas penggagalan penyelundupan 1,3 ton ketamin. Ia dorong larangan vape untuk lindungi generasi muda.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613006/sahroni-apresiasi-bnn-bongkar-penyelundupan-1-3-ton-ketamin-mengerikan</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/20/wakil-ketua-komisi-iii-dpr-ri-ahmad-sahroni-1771531633340_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Presiden Kolombia Sebut Setidaknya 111 Orang Tewas dalam Gempa Magnitudo 7,4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 03:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>"Per pukul 12.30 (waktu setempat), korban tewas mencapai 111 orang dan 87 orang luka-luka, dengan 1.575 rumah rusak,"</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866582/presiden-kolombia-sebut-setidaknya-111-orang-tewas-dalam-gempa-magnitudo-74</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/URaiCze4k2TRjD74O4lopRgG6kY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PRESIDEN-KOLOMBIA-Presiden-Kolombia-yang-baru-dilantik-Abelardo-de-la-Espriella.jpg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Trump Klaim Perang Iran Segera Berakhir, Teheran Pasang Syarat Buka Hormuz, Pakar: Strategi Tekan AS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 02:54:27 +0700</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Trump yakin perang Iran segera berakhir, tetapi Teheran masih mensyaratkan sejumlah hal untuk membuka kembali Selat Hormuz.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866581/trump-klaim-perang-iran-segera-berakhir-teheran-pasang-syarat-buka-hormuz-pakar-strategi-tekan-as</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/pd58Lh0QZkuUPrM04LfPl7UxG4o=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/residen-AS-Donald-Trump-Senin-27-Juli-2026-Foto-Res.jpg</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I22"/>
+  <autoFilter ref="A1:I25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1608,8 +1608,55 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Misbakhun Ingatkan Kepala Daerah Tak Main Anggaran, Singgung Audit BPK</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 04:01:26 +0700</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ketua Komisi XI DPR, Mukhamad Misbakhun, mengingatkan kepala daerah untuk bertanggung jawab dalam penggunaan anggaran demi pelayanan publik yang optimal.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613008/misbakhun-ingatkan-kepala-daerah-tak-main-anggaran-singgung-audit-bpk</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/ketua-komisi-xi-dpr-mukhamad-misbakhun-dokistimewa-1786395665642_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I25"/>
+  <autoFilter ref="A1:I26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,13 +419,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
@@ -1655,8 +1655,384 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur perpanjang kontrak Micky van de Ven</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 04:42:06 +0700</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur resmi memperpanjang kontrak bek tengah asal Belanda, Micky van de Ven di bursa transfer musim panas ...</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688399/tottenham-hotspur-perpanjang-kontrak-micky-van-de-ven</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000044029.jpg</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Federasi sepak bola AS dan Kanada dukung kritik terhadap Infantino</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 04:37:43 +0700</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Federasi sepak bola Amerika Serikat (US Soccer) dan Kanada (Canada Soccer) mendukung pernyataan tiga konfederasi yang ...</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688395/federasi-sepak-bola-as-dan-kanada-dukung-kritik-terhadap-infantino</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/06/12/Fifa.jpg</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Menhut Sebut Prabowo Dukung Penuh Upaya Restorasi Ekosistem di Indonesia</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:08:09 +0700</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Menhut Raja Juli Antoni mengungkapkan dukungan Presiden Prabowo untuk restorasi ekosistem di Indonesia, menargetkan pemulihan lahan kritis 12 juta hektare.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613011/menhut-sebut-prabowo-dukung-penuh-upaya-restorasi-ekosistem-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/12/raja-juli-antoni-1773304564547_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bigmo 2 Kali Dipolisikan Gegara Konten: Sangat Kapok!</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Bigmo mengaku kapok dua kali dipolisikan karena konten. Bigmo ngaku kapok, benar atau hanya ucapan di mulut saja?</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612978/bigmo-2-kali-dipolisikan-gegara-konten-sangat-kapok</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/youtuber-bigmo-tengah-meminta-maaf-soal-konten-promosi-vape-ajak-anak-in-frame-saat-siaran-langsung-1786363802068_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Trump Geser Strategi Hadapi Iran, Serangan Militer Diganti Tekanan Ekonomi, Pakar: AS Makin Terdesak</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 04:43:52 +0700</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Trump menggeser strategi menghadapi Iran ke tekanan ekonomi. Namun, Iran menjadikan Selat Hormuz sebagai kartu tawar untuk menekan balik AS.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866583/trump-geser-strategi-hadapi-iran-serangan-militer-diganti-tekanan-ekonomi-pakar-as-makin-terdesak</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ehJMjfAn9SH0LhD96-yXjyWtw7o=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Presiden-AS-Donald-Trump-berbicara-deF.jpg</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4 Tersangka Bank BJB Ditahan, KPK Ungkap Nasib Ridwan Kamil</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:17:47 +0700</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>KPK membuka peluang kembali memeriksa Ridwan Kamil untuk melengkapi penyidikan kasus dugaan korupsi pengadaan iklan Bank BJB.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266664/4-tersangka-bank-bjb-ditahan-kpk-ungkap-nasib-ridwan-kamil</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/neDfj15bxZKgfagFGEEQHaZsWWE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5430010/original/078632300_1764649557-Ridwan_Kamil_penuhi_panggilan_KPK.jpg</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Gempa Magnitudo 5,1 Guncang Bengkulu, Tak Berpotensi Tsunami</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 04:32:42 +0700</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Gempa yang mengguncang Kabupaten Bengkulu Utara, Provinsi Bengkulu itu berlokasi di titik koordinat 5.89 LS dan 102.43 BT.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266665/gempa-magnitudo-51-guncang-bengkulu-tak-berpotensi-tsunami</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/ruRqc-lTqT-XvDVyvgHjqgAm-Lk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320778/original/021979200_1786397556-Jepretan_Layar_2025-08-11_pukul_04.31.35.jpg</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Imbas Kebakaran Gudang Limbah di Brebes, PMI: Warga Sekitar Mulai Keluhkan Sesak Napas</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:28:31 +0700</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Kebakaran gudang limbah di Brebes memasuki hari ketiga, menyebabkan 17 warga terdampak asap pekat. PMI imbau penggunaan masker.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/10/220954978/imbas-kebakaran-gudang-limbah-di-brebes-pmi-warga-sekitar-mulai-keluhkan</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/D8y5Ijxhx87jJp8_zZsHGbAAgmc=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a79e553413c6.jpg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I26"/>
+  <autoFilter ref="A1:I34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2031,8 +2031,1277 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kenapa panjat pinang jadi tradisi 17 Agustus? Ini sejarahnya</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:23:51 +0700</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Panjat pinang menjadi salah satu perlombaan yang identik dengan perayaan Hari Ulang Tahun (HUT) Kemerdekaan Republik ...</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688427/kenapa-panjat-pinang-jadi-tradisi-17-agustus-ini-sejarahnya</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/28/Perayaan-Hut-ke-80-Bhayangkara-di-Balikpapan-280626-AP-9.jpg</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Selasa, Jakarta diperkirakan cerah berawan sepanjang hari</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:21:33 +0700</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan seluruh wilayah DKI Jakarta cerah berawan sepanjang ...</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688423/selasa-jakarta-diperkirakan-cerah-berawan-sepanjang-hari</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/cerah-berawan.jpg</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Baru mulai lari? Hindari 5 kesalahan ini agar tak mudah cedera</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:20:45 +0700</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Lari menjadi salah satu olahraga yang cukup mudah untuk dimulai. Tidak perlu banyak peralatan, bisa dilakukan di ...</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688421/baru-mulai-lari-hindari-5-kesalahan-ini-agar-tak-mudah-cedera</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/12/4a857c34-57d4-49c7-902f-a2db84fd3474.jpeg</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BMKG prakirakan cuaca di sebagian besar RI berawan tebal pada Selasa</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:20:26 +0700</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan cuaca hari ini, Selasa, di sebagian besar wilayah ...</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688417/bmkg-prakirakan-cuaca-di-sebagian-besar-ri-berawan-tebal-pada-selasa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/IMG_20260727_000432.jpg</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Kenapa lari makin populer di kota? Ini 8 alasannya</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:17:48 +0700</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Lari kini bukan lagi sekadar aktivitas olahraga yang dilakukan oleh atlet atau mereka yang sedang mempersiapkan diri ...</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688415/kenapa-lari-makin-populer-di-kota-ini-8-alasannya</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/lomba-lari-lila-wangsa-run-di-lhokseumawe-2837668.jpg</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DKI kemarin, persiapan HUT RI hingga transportasi Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:16:56 +0700</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sejumlah berita seputar DKI Jakarta yang terjadi pada Senin (10/8), mulai dari persiapan HUT ke-81 RI hingga ...</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688412/dki-kemarin-persiapan-hut-ri-hingga-transportasi-kepulauan-seribu</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/02/07/antarafoto-aktivitas-penyeberangan-kapal-kepulauan-seribu-070224-bay-7.jpg</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Lari 30 menit setiap hari, ini 7 manfaatnya bagi kesehatan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:13:32 +0700</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Di tengah rutinitas yang semakin padat, olahraga tidak selalu harus dilakukan berjam-jam di pusat kebugaran. Salah satu ...</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688411/lari-30-menit-setiap-hari-ini-7-manfaatnya-bagi-kesehatan</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/IMG_7942.jpg</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Flowdesk Mendapatkan Lisensi VARA Penuh untuk Layanan Broker-Dealer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:06:20 +0700</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>- Flowdesk merupakan penyedia likuiditas global sekaligus perusahaan teknologi perdagangan aset virtual dan hari ini ...</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688407/flowdesk-mendapatkan-lisensi-vara-penuh-untuk-layanan-broker-dealer</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/03/23/Logo-BusinessWire-800x600.jpg</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rp4 triliun BOS madrasah mulai disalurkan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Kementerian Agama (Kemenag) menyalurkan dana Bantuan Operasional Sekolah (BOS) tahap II dengan total nilai lebih dari ...</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5688175/rp4-triliun-bos-madrasah-mulai-disalurkan</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/20260810-Rp4-triliun-BOS-madrasah-mulai-disalurkan.jpg</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kriminal kemarin, ekshumasi Sutrimo hingga pemeriksaan Bigmo</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:59:42 +0700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Sejumlah peristiwa berkaitan dengan keamanan menghiasi Jakarta yang terjadi pada Senin (10/8) kemarin, mulai dari ...</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688403/kriminal-kemarin-ekshumasi-sutrimo-hingga-pemeriksaan-bigmo</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000912256.jpg</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Penjelasan DJP soal Pajak Rumah Kontrakan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:55:37 +0700</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Direktorat Jenderal Pajak (DJP) Kementerian Keuangan menjelaskan rencana pemungutan pajak kepada pemilik rumah kontrakan pada 2027.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8612434/penjelasan-djp-soal-pajak-rumah-kontrakan</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2014/10/01/aba994a2-34ed-467e-b236-0838b109f70c_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Jessica Mila Klarifikasi Tudingan ke Pulau Padar saat Pelayaran Ditutup</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:02:46 +0700</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Selebritias Jessica Mila klarifikasi tudingan ke Pulau Padar dan Komodo saat pelayaran ditutup.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613015/jessica-mila-klarifikasi-tudingan-ke-pulau-padar-saat-pelayaran-ditutup</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/jessica-mila-dan-suami-1778209378388_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Keluarga Nyalakan Lilin di Lokasi Tragedi Drag Race Maut Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:59:34 +0700</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Momen duka keluarga korban Drag Race maut Kotamobagu pasang lilin di lokasi tewasnya keluarga mereka usai ditabrak mobil pembalap Tian Ngantung.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866593/keluarga-nyalakan-lilin-di-lokasi-tragedi-drag-race-maut-kotamobagu</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5T63MMdtg-gtQnuc0Xo9vVmIECU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kolase-2-bakar-lilin-di-drag-race-kotamobagu.jpg</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Viral Promo Miras Pakai Hafalan Alquran di Festival Musik, MUI Kecam Keras : Ini Bentuk Perendahan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:51:28 +0700</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MUI mengecam keras aksi promosi minuman keras (miras) berkedok tantangan hafalan Alquran yang mendadak viral di media sosial.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866592/viral-promo-miras-pakai-hafalan-alquran-di-festival-musik-mui-kecam-keras-ini-bentuk-perendahan</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/-2d59XXwfIYkLuE0Rz5s5WSaLms=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-minuman-beralkohol-76t8.jpg</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Drama Pramusim Barcelona di 3 Negara, Penjualan Tiket Lawan Basel Berubah Kekacauan</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:46:40 +0700</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Barcelona kembali hadapi drama di pramusim. Setelah beberapa laga uji coba dibatalkan, laga lawan Basel justru membuat server penjualan klub eror.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866591/drama-pramusim-barcelona-di-3-negara-penjualan-tiket-lawan-basel-berubah-kekacauan</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/um9v51_Smi_Af51A3wMXpv34uos=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Barcelona-Copa-del-Rey-161.jpg</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Quartararo Tak Anggap MotoGP 2026 Aneh, Aprilia Cocok di Silverstone dan Ducati Dinanti di Aragon</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:41:20 +0700</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Fabio Quartararo tidak menganggap persaingan MotoGP 2026 aneh setelah Aprilia tampil dominan di Silverstone dan Ducati kesulitan.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866590/quartararo-tak-anggap-motogp-2026-aneh-aprilia-cocok-di-silverstone-dan-ducati-dinanti-di-aragon</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/iq8q0RqjkDf00LiB-ZCYSDyQ6mM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/fabio-quartararo-berbicara-kepada-media-setelah-latihan-bebas-kedua.jpg</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Sulawesi Barat Selasa, 11 Agustus 2026: Semua Cerah</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:33:48 +0700</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BMKG melaporkan prakiraan cuaca untuk wilayah Sulawesi Barat (Sulbar), Selasa (11/8/2026). Semua wilayah akan cerah.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866589/prakiraan-cuaca-sulawesi-barat-selasa-11-agustus-2026-semua-cerah</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zuUaADQ8yitcRX5Zk0F6srdEnKw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Prakiraan-Cuaca-Sulawesi-Barat-Selasa-10-Maret-2026Waspada-Hujan-Lebat-di-Wilayah-Ini.jpg</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5 Populer Regional: Drag Race Maut di Kotamobagu - Sosok 2 Tersangka Perampokan Candra Waskito</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:32:13 +0700</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Drag race Kotamobagu menewaskan 7 orang, sementara dua tersangka pembunuhan bos Royal Phone Ambarawa ditangkap polisi.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866588/5-populer-regional-drag-race-maut-di-kotamobagu-sosok-2-tersangka-perampokan-candra-waskito</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/AXdgAr9Iw3PgL4auFlOtiwlS1HI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kecelakaan-Drag-Race-dan-Drag-Bike-di-kotamobagu.jpg</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ambil Tawaran Sinetron, Betrand Peto Kini Belajar Lebih Luas Lagi soal Dunia Entertain</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:30:32 +0700</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Penyanyi Betrand Peto belajar lebih luas lagi soal dunia entertain lewat debut aktingnya di sinetron Ternyata Ini Cinta.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866587/ambil-tawaran-sinetron-betrand-peto-kini-belajar-lebih-luas-lagi-soal-dunia-entertain</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/WmDEz8uVI8MheqYNv2eV8ii5aV4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Betrand-Peto-nangis-melihat-video-Sarwendah-viral.jpg</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Hampir Setahun Cerai dari Ahmad Assegaf, Tasya Farasya Curhat soal Sisi Rapuh</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:28:18 +0700</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Hampir setahun bercerai ari Ahmad Assegaf, Tasya Farasya kepergok curhat membahas tentang sisi rapuh.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866586/hampir-setahun-cerai-dari-ahmad-assegaf-tasya-farasya-curhat-soal-sisi-rapuh</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/myn8Dx3mai8z5-ojphGgM9LQRgY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/beauty-influencer-tasya-farasya.jpg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ada Peran Sahabat Lionel Messi di Balik Kepindahan Ronald Araujo ke Liverpool, Pesan Khusus Terkirim</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:23:37 +0700</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ronald Araujo mendapatkan pesan spesial dari Luis Suarez setelah resmi membuka lembaran baru bersama Liverpool sebagai pemain pinjaman Barcelona.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866585/ada-peran-sahabat-lionel-messi-di-balik-kepindahan-ronald-araujo-ke-liverpool-pesan-khusus-terkirim</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MTQ-ST3HxsLdctGDaIeNGoHJwD8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pemain-pinjaman-Barcelona-Ronald-Araujo-saat-diperkenalkan.jpg</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kini Gandeng Kekasih Baru, Dahlia Poland Bantah Dicomblangin Dicky SMASH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:22:54 +0700</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Dahlia Poland kini gandeng pacar baru, konten kreator Rangga Azies usai bercerai dengan aktor Fandy Christian. Ia membantah dicomblangin Dicky SMASH.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866584/kini-gandeng-kekasih-baru-dahlia-poland-bantah-dicomblangin-dicky-smash</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ESge_XkWLJJAmaVL-NgpugssHB8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Dahlia-Poland-ketika-ditemui-di-kawasan-Tendean-Jakarta-Selatan.jpg</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KPK Ungkap Dugaan Pengondisian Audit BPK dalam Kasus Korupsi Bank BJB</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:17:42 +0700</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>KPK menduga uang nonbujeter dari pengadaan iklan Bank BJB digunakan untuk mengurus temuan audit BPK.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266666/kpk-ungkap-dugaan-pengondisian-audit-bpk-dalam-kasus-korupsi-bank-bjb</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/JwVem3lzYNfwyZ1ITqmvAg88XZg=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320689/original/081405900_1786367086-71944.jpg</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Penjelasan KPK soal Sisa Uang Amplop Bupati Kuansing untuk Menhut</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:06:52 +0700</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>KPK terus menelusuri sisa uang SGD 2.000 dari total SGD 14.000 dalam kasus dugaan suap Bupati Kuansing dan Kemenhut.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266678/penjelasan-kpk-soal-sisa-uang-amplop-bupati-kuansing-untuk-menhut</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/HhURMajvSW7aquQf9I_ex0-2LQg=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/7618978/original/014714900_1780405596-IMG_2704.jpg</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KPK Telusuri Aliran Uang Kasus Bank BJB ke Lisa Mariana Lewat Nomine</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:45:50 +0700</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>KPK tengah menelusuri dugaan aliran uang kasus Bank BJB ke Lisa Mariana yang disebut melalui pihak lain atau nomine.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266660/kpk-telusuri-aliran-uang-kasus-bank-bjb-ke-lisa-mariana-lewat-nomine</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/rUdL_iF94kLXxYVrzb1n0DNLu4A=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5324168/original/096678300_1755843657-20250822-Lisa_M-HEL_9.jpg</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Bigmo Minta Maaf Usai Diperiksa Polisi, Akui Kontennya Tak Pantas</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:31:18 +0700</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>YouTuber Bigmo Mengaku Kapok dan Minta Maaf Usai Diperiksa Polisi Terkait Konten Live Streaming</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266658/bigmo-minta-maaf-usai-diperiksa-polisi-akui-kontennya-tak-pantas</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/RuQNgz1b2xdlesPvESyGkeIiBiw=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320772/original/046943600_1786395707-Bigmo__1_.jpg</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MBG Tetap Jalan, Komisi XI Minta Tata Kelola Diperketat</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:16:16 +0700</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Mitra SPPG diminta mengikuti standardisasi dan pembenahan tata kelola MBG agar penggunaan APBN semakin transparan dan akuntabel.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266670/mbg-tetap-jalan-komisi-xi-minta-tata-kelola-diperketat</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/CSIKMS1zrLfH-SxfmCKYABQjZXw=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9295136/original/006741400_1783915651-mbg2.jpg</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I34"/>
+  <autoFilter ref="A1:I61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,13 +419,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
@@ -3300,8 +3300,2123 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kolombia akui kedaulatan Israel atas Dataran Tinggi Golan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:44:21 +0700</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Kementerian Luar Negeri Kolombia, Senin (10/8), mengumumkan pengakuan negaranya terhadap kedaulatan Israel atas Dataran ...</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688484/kolombia-akui-kedaulatan-israel-atas-dataran-tinggi-golan</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/31/Golan.jpg</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Gempa Kolombia tewaskan sedikitnya 111 orang</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:38:13 +0700</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Jumlah korban tewas akibat gempa bumi berkekuatan Magnitudo 7,4 yang mengguncang barat Kolombia pada Senin, 10 Agustus, ...</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688481/gempa-kolombia-tewaskan-sedikitnya-111-orang</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/AA-20260810-42182432-42182426-AT_LEAST_18_KILLED_AS_MAGNITUDE_74_EARTHQUAKE_HITS_COLOMBIA.jpg</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BPKN: Perlindungan terhadap jamaah haji-umrah harus terus diperkuat</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:25:29 +0700</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Badan Perlindungan Konsumen Nasional (BPKN) RI memandang perlindungan terhadap jamaah haji dan umrah harus terus ...</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688480/bpkn-perlindungan-terhadap-jamaah-haji-umrah-harus-terus-diperkuat</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/16/1000103036.jpg</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Desain Samsung Galaxy Tab hingga penghargaan untuk NEV di GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:21:01 +0700</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Sejumlah peristiwa berkaitan dengan teknologi, otomotif, hiburan dan gaya hidup yang terjadi pada Senin (10/8) kemarin, ...</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688476/desain-samsung-galaxy-tab-hingga-penghargaan-untuk-nev-di-giias-2026</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/InShot_20260731_101146569.jpg</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tangan kecil membuka pintu bahasa</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:08:27 +0700</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Ada jarak yang tidak selalu terlihat di ruang kelas, loket pelayanan, rumah sakit, terminal, hingga ruang publik. Jarak ...</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688473/tangan-kecil-membuka-pintu-bahasa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/tenggilis-mejoyo-11.jpg</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Beanstalk AgTech Umumkan Peluncuran Monsoon Ventures untuk Mempercepat Komersialisasi Teknologi Pertanian di Asia Tenggara</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:02:29 +0700</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>- Beanstalk AgTech pada hari ini mengumumkan peluncuran Monsoon Ventures, yaitu sebuah studio ventura baru di ...</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688469/beanstalk-agtech-umumkan-peluncuran-monsoon-ventures-untuk-mempercepat-komersialisasi-teknologi-pertanian-di-asia-tenggara</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-06.45.19.jpeg</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Sulit tidur? Hindari 7 makanan &amp; minuman ini sebelum berbaring</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:00:40 +0700</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Memilih makanan sebelum tidur perlu diperhatikan karena jenis dan waktu makan dapat memengaruhi kualitas tidur serta ...</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688465/sulit-tidur-hindari-7-makanan-minuman-ini-sebelum-berbaring</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/15/Tidur.jpg</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>8 buah yang baik untuk membantu mengontrol asam urat</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:57:24 +0700</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Mengonsumsi buah dapat menjadi bagian dari pola makan untuk membantu mengontrol kadar asam urat dan menurunkan risiko ...</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688464/8-buah-yang-baik-untuk-membantu-mengontrol-asam-urat</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/28/pisang-mas-kirana.jpg</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>8 buah untuk membantu menurunkan kolesterol secara alami</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:54:02 +0700</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Mengonsumsi buah kaya serat dapat menjadi bagian dari pola makan untuk membantu mengendalikan kadar kolesterol, ...</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688460/8-buah-untuk-membantu-menurunkan-kolesterol-secara-alami</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/23/permintaan-buah-buahan-selama-ramadhan-2736866.jpg</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>8 cara mengatasi sakit gigi di rumah, redakan nyeri sementara</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:50:58 +0700</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Sakit gigi dapat muncul akibat berbagai masalah, mulai dari gigi berlubang, infeksi, gangguan gusi hingga gigi retak. ...</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688457/8-cara-mengatasi-sakit-gigi-di-rumah-redakan-nyeri-sementara</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/pemeriksaan-kesehatan-gratis-di-rumah-sakit-2830635.jpg</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tak harus cepat, ini alasan pelari perlu melakukan easy run</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:48:00 +0700</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Dalam dunia lari, kecepatan sering kali menjadi hal yang paling menarik perhatian. Ada pelari yang mengejar pace lebih ...</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688453/tak-harus-cepat-ini-alasan-pelari-perlu-melakukan-easy-run</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/Run-for-Equality-2026_Plan-Indonesia-start.jpeg</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Lari pagi atau sore, mana yang lebih baik? Ini penjelasannya</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:44:52 +0700</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Lari bisa dilakukan hampir kapan saja. Ada yang memilih bangun lebih pagi untuk berlari sebelum memulai aktivitas, ...</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688452/lari-pagi-atau-sore-mana-yang-lebih-baik-ini-penjelasannya</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/06/IMG-20260606-WA0007.jpg</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Gaji pemain Liga Inggris dibayar mingguan? Ini faktanya</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:42:43 +0700</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Saat membaca berita sepak bola khususnya Liga Inggris, Anda mungkin sering menemukan informasi soal gaji pemain yang ...</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688449/gaji-pemain-liga-inggris-dibayar-mingguan-ini-faktanya</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/image-35.jpg</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>10 contoh prompt AI untuk buat poster bertema HUT ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:39:08 +0700</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 tidak hanya bisa diramaikan ...</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688448/10-contoh-prompt-ai-untuk-buat-poster-bertema-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-08.38.14.jpeg</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Aira Ev jadi tulang punggung penjualan Wuling di GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:38:12 +0700</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Wuling Motors (Wuling) mencatatkan penjualan sebanyak 3.290 surat pemesanan kendaraan (SPK) sepanjang pameran Gaikindo ...</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5688444/aira-ev-jadi-tulang-punggung-penjualan-wuling-di-giias-2026</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/WhatsApp-Image-2026-07-29-at-19.47.57-1.jpeg</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Peneliti kembangkan sistem beton yang dibangun dalam hitungan detik</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:38:06 +0700</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Peneliti mengembangkan sistem beton yang dapat terpasang mandiri sehingga bangun struktur dalam hitungan detik dan ...</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688443/peneliti-kembangkan-sistem-beton-yang-dibangun-dalam-hitungan-detik</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/11/Proyek-APBN-Kendari-021118-JOjon-3.jpg</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ESDM: Penetapan ICP cerminkan dinamika pasar minyak mentah global</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:33:46 +0700</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Kementerian Energi dan Sumber Daya Mineral (ESDM) mengungkapkan penetapan rata-rata Harga Minyak Mentah Indonesia atau ...</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688439/esdm-penetapan-icp-cerminkan-dinamika-pasar-minyak-mentah-global</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/arsip-berita-pasokan-global-pulih-icp-juli-2026-turun-jadi-us-8168-per-barel-3k1y3nb.jpeg</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Kemarin, penghargaan bagi periset baterai UNS hingga karhutla Bromo</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:33:31 +0700</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Sejumlah warta humaniora kemarin, Senin (10/8) masih menarik dibaca hari ini, mulai dari Guru Besar Universitas Sebelas ...</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688436/kemarin-penghargaan-bagi-periset-baterai-uns-hingga-karhutla-bromo</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000474131_1.jpg</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>50 ucapan HUT ke-81 RI yang Islami cocok untuk status sosial media</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:32:49 +0700</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 tinggal menghitung hari. ...</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688433/50-ucapan-hut-ke-81-ri-yang-islami-cocok-untuk-status-sosial-media</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1002614962.jpg</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Selasa, layanan SIM keliling tersedia di lima lokasi Jakarta</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:28:40 +0700</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Direktorat Lalu Lintas Polda Metro Jaya membuka lokasi layanan Surat Izin Mengemudi (SIM) Keliling bagi masyarakat yang ...</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688429/selasa-layanan-sim-keliling-tersedia-di-lima-lokasi-jakarta</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/13/Batas-Akhir-Dispensasi-Perpanjangan-SIM-31082020-gp-3.jpg</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Permintaan Maaf Bigmo, Ngaku Salah Ajak Anak Ngonten Promo Vape</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:07:59 +0700</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Bigmo diperiksa Polda Metro Jaya terkait dugaan eksploitasi anak dalam siaran langsung promosi vape. Bigmo gak mengelak, mengakui kesalahannya, dan minta maaf.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612984/permintaan-maaf-bigmo-ngaku-salah-ajak-anak-ngonten-promo-vape</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/bigmo-1786347973337_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Cuaca Wilayah Priangan Jawa Barat Selasa, 11 Agustus 2026: Dominan Cerah Berawan</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:29:50 +0700</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) merilis prakiraan cuaca untuk wilayah Priangan, Jawa Barat, pada Selasa (11/8/2026).</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866610/cuaca-wilayah-priangan-jawa-barat-selasa-11-agustus-2026-dominan-cerah-berawan</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/lDgUVS5zQ1sLN8t3mHbweeriZkY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-cerah-berawan-xx.jpg</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BWF Soroti 5 Ganda Campuran Jelang Kejuaraan Dunia 2026, Indonesia Tak Masuk Daftar</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:25:26 +0700</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>BWF menyoroti 5 ganda campuran yang dinilai layak diperhitungkan di Kejuaraan Dunia 2026 tetapi tidak ada wakil Indonesia.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866609/bwf-soroti-5-ganda-campuran-jelang-kejuaraan-dunia-2026-indonesia-tak-masuk-daftar</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/rrYaUa8gjXRyW3ZYEAAjBB3boks=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/feng-yan-zhehuang-dong-ping-indonesia-masters-2023.jpg</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Silverstone Mengungkap Kebiasaan Marc Marquez Selalu Berbohong saat Bahas Cedera Bahu</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:23:37 +0700</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Marc Marquez rutin berbohong soal cedera bahu saat performanya belum konsisten dan tak ingin menjadikannya sebuah alasan.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866608/silverstone-mengungkap-kebiasaan-marc-marquez-selalu-berbohong-saat-bahas-cedera-bahu</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/2Q-IEDrezBdZuSNP6-u3CSrABHg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Marc-Marquez-Practice-MotoGP-Hungaria-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pengacara Khariq Soroti Putusan MK soal Dampak Konten Digital Terhadap Demo Agustus</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:22:29 +0700</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Kuasa hukum Khariq, Afif Abdul Qoyim, mengatakan jaksa menyebut pasal itu sebagai delik formil.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866607/pengacara-khariq-soroti-putusan-mk-soal-dampak-konten-digital-terhadap-demo-agustus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/BOYWBTrp4RCOcVHTQOtiL7TLiho=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/har-di-Pengadilan-Negeri-Jakarta.jpg</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Hari ini Eks Menag Gus Yaqut Jalani Sidang Perdana di PN Jakpus</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:22:10 +0700</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Eks Menag Yaqut Cholil Qoumas (Gus Yaqut) jalani sidang perdana perkara dugaan korupsi kuota haji pada Selasa (11/8/2026) di PN Jakpus.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866606/hari-ini-eks-menag-gus-yaqut-jalani-sidang-perdana-di-pn-jakpus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ykkngW8ol49qIUGRcsC7HK5aCcg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pemeriksaan-Yaqut-Cholil-Qoumas_20260325_183337.jpg</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Peringatan Dini 6 Ibu Kota Pulau Jawa Hari Ini Selasa 11 Agustus: Jakarta Cerah, Jogja Udara Kabur</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:17:56 +0700</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Peringatan dini BMKG di 6 Ibu Kota di Pulau Jawa. Mulai dari Jakarta, Bandung, hingga Semarang pada (11/8/2026).</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866605/peringatan-dini-6-ibu-kota-pulau-jawa-hari-ini-selasa-11-agustus-jakarta-cerah-jogja-udara-kabur</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/kt7_F_i-uxwt6UCNxvVfCWowi4A=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-cerah-berawan-yogyakarta.jpg</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Waspada Alergi Skincare pada Bayi, Ini Tanda dan Cara Pilih Produk yang Tepat</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:15:39 +0700</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Dokter anak, dr. Hans mengatakan orang tua perlu mengetahui tanda alergi skincare pada bayi setelah penggunaan produk tersebut. Berikut ciri-cirinya.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866604/waspada-alergi-skincare-pada-bayi-ini-tanda-dan-cara-pilih-produk-yang-tepat</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/umKVBJF65IbfXBVjy48cT4Yds4Q=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/teknik-pijat-lembut-pada-bayi-untuk-meredakan-gejala-batuk-dan-pilek.jpg</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Qodari Ungkap Rincian Paket Stimulus Ekonomi Semester II Rp 26,34 T yang Digelontorkan Pemerintah</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:15:35 +0700</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Qodari mengatakan pertumbuhan ekonomi tidak lepas dari upaya pemerintah dalam menjaga stabilitas ekonomi di tengah gejolak eksternal.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866603/qodari-ungkap-rincian-paket-stimulus-ekonomi-semester-ii-rp-2634-t-yang-digelontorkan-pemerintah</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/kMOjJrvoru6ACSaadafwSXPw01s=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kepala-Badan-Komunikasi-Pemerintah-Muhammad-Qodari-pemadaman-listrik-Jawa-Bali.jpg</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Bandung Raya Selasa, 11 Agustus 2026: Seluruh Wilayah Cerah</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:15:23 +0700</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Simak prakiraan cuaca wilayah Bandung Raya pada Selasa (11/8/2026). Cuaca di seluruh wilayah Bandung Raya diprakirakan cerah.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866602/prakiraan-cuaca-bandung-raya-selasa-11-agustus-2026-seluruh-wilayah-cerah</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/lDgUVS5zQ1sLN8t3mHbweeriZkY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-cerah-berawan-xx.jpg</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Banyumas, Selasa 11 Agustus 2026: Sebagian Besar Cerah</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:05:23 +0700</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Pada hari Selasa, 11 Agustus 2026, sebagian besar daerah Kabupaten Banyumas, Jawa Tengah, diperkirakan akan cerah.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866601/prakiraan-cuaca-banyumas-selasa-11-agustus-2026-sebagian-besar-cerah</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/NoFE2LvWzp2AdpzhhqsTlBzJZCc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Foto-ilustrasi-cuaca-cerah.jpg</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Story TikTok Pelajar SMK Tewas Tertemper KRL di Jurangmangu :Maaf Perjalanan Kereta Anda Terlambat</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:00:38 +0700</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Pelajar SMK swasta di Bintaro, Jakarta Selatan tewas tertemper KRL Commuter Line Jabodetabek di Stasiun Jurangmangu Tangsel.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866600/story-tiktok-pelajar-smk-tewas-tertemper-krl-di-jurangmangu-maaf-perjalanan-kereta-anda-terlambat</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vnN8t7-_sNFl5avv0zV2pk7I0Tk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/tertemperKRL1.jpg</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Sepeda Motor Wartawan Hilang Usai Liputan di Kantor Kemenko Polkam</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:55:15 +0700</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Motor milik reporter digital iNews Media Group, Danandaya hilang saat bertugas meliput di Kantor Kemenko Polkam, Jakarta pada Senin (10/8/2026).</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866599/sepeda-motor-wartawan-hilang-usai-liputan-di-kantor-kemenko-polkam</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ePqHfoFf-17d9pflJPJo05qQDhM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ilustrasi-maling-motor-di-Jatinegara.jpg</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Menikah 4 Tahun, Suami Istri di Ponorogo Jatim Bongkar Toko Usai Cerai</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:48:23 +0700</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Toko yang semula dengan ukuran 5 meter kali 7 meter yang sebelumnya berdiri kokoh kini rata dengan tanah</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866598/menikah-4-tahun-suami-istri-di-ponorogo-jatim-bongkar-toko-usai-cerai</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/bL_POPEC31gctykwuyLnxm4H3t0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Alat-berat-saat-menghancurkan-toko-di-Ponorogo.jpg</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Nasib Mees Hilgers di Twente Kian Rumit, sang Sahabat Sebut Terjadi Hubungan Mengecewakan</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:39:18 +0700</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Di tengah situasi kontrak yang pelik, sahabat Mees Hilgers kedua pihak mengesampingkan masalah dan mencari solusi terbaik.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866597/nasib-mees-hilgers-di-twente-kian-rumit-sang-sahabat-sebut-terjadi-hubungan-mengecewakan</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hbfx5QCMH3Kgs58UhCLe-pJ8Vas=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Bek-Timnas-Indonesia-Mees-Hilgers-diberi-instruksi-oleh-pelatih-FC-Twente-Joseph-Oosting.jpg</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Jejak Kontroversi Bigmo Berujung ke Ranah Hukum, Dulu Dilaporkan Zize, Kini Terseret Kasus Vape</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:32:45 +0700</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Tak hanya sekali Youtber Bigmo terseret kasus hukum. Terbaru harus diperiksa gara-gara konten live promo vape libatkan anak-anak.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866596/jejak-kontroversi-bigmo-berujung-ke-ranah-hukum-dulu-dilaporkan-zize-kini-terseret-kasus-vape</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MB1ZiNQ6NK2dGnKcwEd1QqaGYkc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Bigmo-1-10082026.jpg</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Bukan Cuma An Se-young dan Kim/Seo, Korea Punya Kekuatan Baru di Kejuaraan Dunia dan Asian Games</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:29:01 +0700</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Badminton Korea Selatan mulai menunjukkan kekuatan yang lebih merata menjelang Kejuaraan Dunia BWF 2026 dan Asian Games 2026.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866595/bukan-cuma-an-se-young-dan-kimseo-korea-punya-kekuatan-baru-di-kejuaraan-dunia-dan-asian-games</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/u3aBtXb_mVRne_ARsfRNRAMcTFQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/An-Se-Young-Juara-Tunggal-Putri-Polytron-Indonesia-Open-2026_20260607_172600.jpg</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Paspampres Siapkan Senjata hingga Kendaraan Anti-Drone untuk Amankan HUT RI</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:21:21 +0700</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Ribuan personel Paspampres lengkap dengan alutsista diterjunkan dalam pengamanan rangkaian agenda kenegaraan peringatan HUT RI.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866594/paspampres-siapkan-senjata-hingga-kendaraan-anti-drone-untuk-amankan-hut-ri</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Cr9gQwcExhbsJCjs2Jf4Fi3iZbk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/paspampres-amankan-HUT-RI.jpg</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Konektivitas Kepulauan Seribu Menguat, Commuter Line Jadi Penghubung dari Daratan Jakarta</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:01:43 +0700</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Rencana Pemerintah Provinsi DKI Jakarta memperkuat layanan transportasi menuju Kepulauan Seribu mulai 2027 membuka ruang semakin besar bagi terbentuknya perjalanan antarmoda yang terhubung antara wilayah daratan dan...</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjkw2v423/konektivitas-kepulauan-seribu-menguat-commuter-line-jadi-penghubung-dari-daratan-jakarta</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/sebuah-rangkaian-kereta-rel-listrik-krl-commuter-line-melintas_220329204441-993.jpg</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Eks Menag Yaqut Sidang Perdana Kasus Korupsi Kuota Haji Hari Ini</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Eks Menteri Agama Yaqut Cholil Qoumas menjalani sidang perdana kasus dugaan korupsi kuota haji di Pengadilan Tipikor Jakarta.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266702/eks-menag-yaqut-sidang-perdana-kasus-korupsi-kuota-haji-hari-ini</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/-vg7hXrpZ8lhCuiom8MZJ3zTUuQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/7608165/original/012297800_1780392985-2.jpg</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Makam Sutrimo Akan Dibongkar, Ini yang Disiapkan Polisi</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:06:11 +0700</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Polda Jateng menyiapkan personel dan pengamanan makam Sutrimo untuk mendukung proses ekshumasi yang dijadwalkan 12 Agustus.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266677/makam-sutrimo-akan-dibongkar-ini-yang-disiapkan-polisi</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Ac0CwWSgaQOzoD0dmfbEg4_UyMk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9312458/original/059177100_1785493658-IMG_1805.jpg</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Uji KUHP di MK, Polri-KPK Beda Pandangan soal Hitung Kerugian Negara</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:30:11 +0700</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Polri dan KPK menyampaikan pandangan berbeda dalam uji Pasal 603 KUHP terkait kewenangan menghitung kerugian keuangan negara.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266675/uji-kuhp-di-mk-polri-kpk-beda-pandangan-soal-hitung-kerugian-negara</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/RSSVpMCJnSE7wqWR0JfCZVfW7cM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/7009691/original/038642700_1779781689-IMG_0511.jpeg</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Pasang Bendera Merah Putih Jelang 17-an: Kewajiban atau Bentuk Nasionalisme?</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:49:40 +0700</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Pengibaran Merah Putih setiap Agustus: antara kebiasaan warga, kewajiban nasional, dan makna mendalam sejarah perjuangan bangsa.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/07485281/pasang-bendera-merah-putih-jelang-17-an-kewajiban-atau-bentuk-nasionalisme</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/TTwqMF3CSqH8Xnz6Q3J4oWjYZEw=/0x0:780x520/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2023/08/11/64d6041a41750.jpg</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Kasus Meme Khariq Anhar: Unggahan "Timpa Teks" yang Berujung Tuntutan 6 Bulan Penjara</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:49:40 +0700</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Jaksa menilai perbuatan Khariq Anhar dilakukan tanpa hak karena tidak mengantongi izin dari media terkait maupun Said Iqbal.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/11/07233121/kasus-meme-khariq-anhar-unggahan-timpa-teks-yang-berujung-tuntutan-6</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/SrzuQPBYeyQ2pDwAbJmwsi3mejg=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a79d16534dbd.jpg</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Tren</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ramai soal Rumah Kontrakan Bakal Kena Pajak Mulai 2027, Ini Penjelasan DJP</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:49:40 +0700</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Ramai kabar rumah kontrakan bakal kena pajak pada 2027, tetapi DJP menegaskan belum ada program khusus yang menyasar pemilik rumah kontrakan.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/tren/read/2026/08/11/070000565/ramai-soal-rumah-kontrakan-bakal-kena-pajak-mulai-2027-ini-penjelasan-djp</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/jbO9EbulYplMWP-kC_i8DVVfIzc=/0x0:1536x1024/1200x675/filters:watermark(data/photo/2026/01/30/697c818d0ca91.png,0,-0,1)/data/photo/2026/08/07/6a759a0af08d7.png</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I61"/>
+  <autoFilter ref="A1:I106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$219</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5415,8 +5415,5319 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Bupati Banyumas dorong siswa SNT bangun karakter sejak dini</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:54:54 +0700</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Bupati Banyumas Sadewo Tri Lastiono mendorong siswa baru Sekolah Nasional Terintegrasi (SNT) 2 Banyumas membangun ...</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688580/bupati-banyumas-dorong-siswa-snt-bangun-karakter-sejak-dini</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001105065.jpg</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S26 FE dibekali baterai 4.900 mAh dan chip Exynos 2500</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:54:44 +0700</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Bocoran lengkap spesifikasi Samsung Galaxy S26 Fan Edition (FE) muncul jelang peluncurannya yang diperkirakan ...</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688577/samsung-galaxy-s26-fe-dibekali-baterai-4900-mah-dan-chip-exynos-2500</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000142665.jpg</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>AS cabut lebih dari 175.000 visa sejak Januari 2025</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:53:56 +0700</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Departemen Luar Negeri Amerika Serikat (AS) pada Senin (10/8) mengumumkan bahwa pihaknya telah mencabut lebih dari ...</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688576/as-cabut-lebih-dari-175000-visa-sejak-januari-2025</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/thumbs_b_c_7585b7a40076b45ff76a5da72d4e66da.jpg</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BI tingkatkan penggunaan QRIS di Tomohon International Flower Festival</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:52:23 +0700</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Bank Indonesia (BI) mendorong peningkatan penggunaan Quick Response Code Indonesian Standard (QRIS) kepada ...</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688572/bi-tingkatkan-penggunaan-qris-di-tomohon-international-flower-festival</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-09.20.16.jpeg</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Korban Tewas Gempa Bumi Kolombia Tembus 111 Orang</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:50:57 +0700</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Jumlah korban tewas akibat gempa bumi bermagnitudo 7,4 yang mengguncang wilayah barat Kolombia pada Senin (10/8) ...</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688569/korban-tewas-gempa-bumi-kolombia-tembus-111-orang</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000002_20260811_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Jeongyeon TWICE berpisah dengan JYP Entertainment</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:48:50 +0700</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Anggota girl group K-pop TWICE Jeongyeon akan berpisah dengan agensi JYP Entertainment yang menaunginya setelah 11 ...</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688565/jeongyeon-twice-berpisah-dengan-jyp-entertainment</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/92a9b7d3-af43-42ed-9ee8-783571364243.jpeg</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Penerima Beasiswa Garuda ciptakan robot deteksi kebakaran lahan gambut</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:42:42 +0700</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Penerima Beasiswa Garuda asal Tangerang Selatan, Imran berhasil menciptakan Robot Gambut, purwarupa yang dikembangkan ...</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688563/penerima-beasiswa-garuda-ciptakan-robot-deteksi-kebakaran-lahan-gambut</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-10-at-20.36.37.jpeg</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Polres Kotim pasang garis polisi di sejumlah area karhutla</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:40:25 +0700</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Polres Kotawaringin Timur (Kotim), Kalimantan Tengah, menyatakan dalam penanganan kebakaran hutan dan lahan (karhutla), ...</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688561/polres-kotim-pasang-garis-polisi-di-sejumlah-area-karhutla</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001739584.jpg</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Harga emas Antam Selasa ini naik Rp20.000 jadi Rp2,710 juta per gram</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:40:07 +0700</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Harga emas Antam yang dipantau dari laman Logam Mulia di Jakarta, Selasa, pukul 9.36 WIB, naik Rp20.000 ke angka ...</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688560/harga-emas-antam-selasa-ini-naik-rp20000-jadi-rp2710-juta-per-gram</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/harga-emas-antam-turun-2829983.jpg</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Cak Imin apresiasi Baznas perkuat pemberdayaan masyarakat miskin</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:39:12 +0700</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Pemberdayaan Masyarakat (Menko PM) Abdul Muhaimin Iskandar atau dikenal dengan Cak Imin ...</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688557/cak-imin-apresiasi-baznas-perkuat-pemberdayaan-masyarakat-miskin</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_091132.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Kelurahan Paseban kembangkan pengolahan sampah bernilai ekonomi</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:34:11 +0700</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Kelurahan Paseban, Kecamatan Senen, Jakarta Pusat mengembangkan pengolahan sampah plastik berbasis warga menjadi produk ...</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688555/kelurahan-paseban-kembangkan-pengolahan-sampah-bernilai-ekonomi</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000836107.jpg</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>KPK akan urai secara utuh konstruksi kasus haji pada sidang hari ini</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:32:59 +0700</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi (KPK) menyatakan akan menguraikan secara utuh konstruksi kasus dugaan korupsi kuota haji ...</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688553/kpk-akan-urai-secara-utuh-konstruksi-kasus-haji-pada-sidang-hari-ini</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/pemeriksaan-lanjutan-yaqut-cholil-2798231.jpg</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Mendikdasmen: Transformasi pendidikan dimulai dari pendekatan belajar</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:32:58 +0700</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Menteri Pendidikan Dasar dan Menengah (Mendikdasmen) Abdul Mu’ti mengatakan transformasi pendidikan perlu dimulai ...</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688549/mendikdasmen-transformasi-pendidikan-dimulai-dari-pendekatan-belajar</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000232226.jpg</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>AS janjikan bantuan darurat senilai 15,5 juta dolar untuk Kolombia</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:29:11 +0700</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Departemen Luar Negeri Amerika Serikat, Senin (10/8), mengumumkan bantuan darurat senilai 15,5 juta dolar AS (sekitar ...</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688545/as-janjikan-bantuan-darurat-senilai-155-juta-dolar-untuk-kolombia</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/AA-20260810-42182432-42182417-AT_LEAST_18_KILLED_AS_MAGNITUDE_74_EARTHQUAKE_HITS_COLOMBIA.jpg</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Mentan tegaskan reformasi pertanian dongkrak kesejahteraan petani</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:28:05 +0700</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Menteri Pertanian (Mentan) Andi Amran Sulaiman menegaskan reformasi sektor pertanian berhasil meningkatkan ...</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688543/mentan-tegaskan-reformasi-pertanian-dongkrak-kesejahteraan-petani</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/C44A08EA-304F-47CC-8C28-7D635D024160.jpeg</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Laporan: Korban tewas akibat gempa Kolombia capai 132 orang, 570 luka</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:24:14 +0700</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Jumlah korban tewas akibat gempa bumi kuat di Kolombia mencapai 132 orang, sementara 570 lainnya mengalami luka-luka, ...</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688539/laporan-korban-tewas-akibat-gempa-kolombia-capai-132-orang-570-luka</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Gempa-di-Kolombia.jpg</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Whitney Houston diabadikan dalam Barbie "I Wanna Dance with Somebody"</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:23:16 +0700</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Perusahaan mainan asal Amerika Serikat Mattel resmi merilis boneka Barbie edisi khusus mendiang Whitney ...</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688535/whitney-houston-diabadikan-dalam-barbie-i-wanna-dance-with-somebody</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/barbie-whitney-houston.jpg</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Penertiban Tambang Ilegal Jadi Katalis Produksi dan Kinerja TINS</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:21:38 +0700</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Penertiban tambang timah ilegal berpotensi menjadi katalis bagi PT Timah Tbk (TINS) untuk meningkatkan produksi. ...</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688533/penertiban-tambang-ilegal-jadi-katalis-produksi-dan-kinerja-tins</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/24/IMG_9178.jpeg</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Yaqut Cholil jalani sidang perdana kasus korupsi kuota haji hari ini</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:18:33 +0700</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Menteri Agama periode 2020-2024 Yaqut Cholil Qoumas akan menjalani sidang perdana kasus dugaan korupsi kuota haji di ...</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688532/yaqut-cholil-jalani-sidang-perdana-kasus-korupsi-kuota-haji-hari-ini</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/pelimpahan-tahap-dua-yaqut-cholil-qoumas-2821469.jpg</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Ribuan pemuda India demonstrasi tuntut reformasi ujian rekrutmen</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:16:26 +0700</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Ribuan pemuda yang menuntut reformasi dalam pelaksanaan ujian rekrutmen berunjuk rasa pada Senin di Negara Bagian ...</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688528/ribuan-pemuda-india-demonstrasi-tuntut-reformasi-ujian-rekrutmen</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/thumbs_b_c_8bb6798985684d7ce1fa28a86507daab.jpg</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Modus kasus iklan Bank BJB</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:13:45 +0700</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Pengadaan barang dan jasa, terutama di lingkungan pemerintah maupun badan usaha milik pemerintah, semestinya ...</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688527/modus-kasus-iklan-bank-bjb</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/KPK-tahan-tersangka-kasus-korupsi-pengadaan-iklan-Bank-BJB-100826-fzn-6.jpg</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>IHSG Selasa dibuka menguat 18,44 poin ke posisi 6.383</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:13:35 +0700</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa pagi dibuka menguat 18,44 poin atau 0,29 ...</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688525/ihsg-selasa-dibuka-menguat-1844-poin-ke-posisi-6383</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/03/11/IHSGa.jpg</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Rupiah pada Selasa pagi melemah jadi Rp17.795 per dolar AS</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:10:11 +0700</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah terhadap dolar AS pada pembukaan perdagangan Selasa (11/8), bergerak melemah 40 poin atau 0,23 ...</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688524/rupiah-pada-selasa-pagi-melemah-jadi-rp17795-per-dolar-as</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/jumlah-peredaran-uang-pada-mei-2026-2815165.jpg</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BNPB dorong penguatan program penanggulangan bencana lewat Rakortek PB</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:06:52 +0700</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) mendorong penguatan program penanggulangan bencana yang lebih tepat ...</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688520/bnpb-dorong-penguatan-program-penanggulangan-bencana-lewat-rakortek-pb</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/pemadaman-kebakaran-tpa-rasau-jaya-2835984.jpg</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>BPK: Mahkamah Konstitusi tindaklanjuti 100 persen rekomendasi BPK</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:06:09 +0700</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Anggota I Badan Pemeriksa Keuangan (BPK) Nyoman Adhi Suryadnyana menyatakan Mahkamah Konstitusi (MK) telah ...</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688516/bpk-mahkamah-konstitusi-tindaklanjuti-100-persen-rekomendasi-bpk</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-06-at-15.24.13.jpeg</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Polda Metro gagalkan peredaran sabu modus paket ekspedisi di Jakpus</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:05:27 +0700</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Direktorat Reserse Narkoba Polda Metro Jaya menggagalkan peredaran narkotika jenis sabu berkedok pengiriman paket ...</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688513/polda-metro-gagalkan-peredaran-sabu-modus-paket-ekspedisi-di-jakpus</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000912990.jpg</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Menyelamatkan Rp360 miliar dari pencurian ikan</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Kementerian Kelautan dan Perikanan (KKP) menindak puluhan kapal yang menangkap ikan secara ilegal di perairan Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5688440/menyelamatkan-rp360-miliar-dari-pencurian-ikan</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/20260811-Menyelamatkan-Rp360-miliar-dari-pencuri-ikan-ilegal.jpg</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Menjahit harapan dan kesempatan di era "Social Commerce"</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>ANTARA - Di balik setiap busana yang sampai ke tangan pelanggan, ada cerita yang ikut dijahit di dalamnya. Di Kota ...</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688217/menjahit-harapan-dan-kesempatan-di-era-social-commerce</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/MENJAHIT-HARAPAN-DAN-KESEMPATAN-DI-ERA-22SOCIAL-COMMERCE.jpg</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PIHPS: Harga cabai rawit Rp120.000kg, telur ayam Rp37.500/kg</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:50:55 +0700</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Pusat Informasi Harga Pangan Strategis (PIHPS) Nasional, yang dikelola Bank Indonesia, mencatat harga komoditas cabai ...</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688511/pihps-harga-cabai-rawit-rp120000kg-telur-ayam-rp37500-kg</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/B11A0C6B-BF60-4D0D-A0A4-76981E1F1D5F.jpeg</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>BIGBANG siapkan lagu baru “BiiiG” sambut ulang tahun debut ke-20</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:46:11 +0700</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Grup idola K-pop BIGBANG bersiap merilis single digital baru berjudul “BiiiG” untuk menyambut ulang tahun ...</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688509/bigbang-siapkan-lagu-baru-biiig-sambut-ulang-tahun-debut-ke-20</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/13/f8bdcb0b-a929-4b3c-9e9e-a0f5199b4700.jpeg</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Kemlu: Semua WNI di Kolombia dalam keadaan aman</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:35:33 +0700</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Kementerian Luar Negeri RI mengatakan sejauh ini semua warga negara Indonesia yang berada di Kolombia dalam keadaan ...</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688507/kemlu-semua-wni-di-kolombia-dalam-keadaan-aman</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/AA-20260810-42182432-42182412-AT_LEAST_18_KILLED_AS_MAGNITUDE_74_EARTHQUAKE_HITS_COLOMBIA.jpg</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Kemarin, pengajuan Gubernur BI baru dan peningkatan inklusi keuangan</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:33:20 +0700</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Terdapat berbagai peristiwa bidang ekonomi yang terjadi pada Senin (10/8/2026) yang masih hangat dan relevan untuk ...</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688505/kemarin-pengajuan-gubernur-bi-baru-dan-peningkatan-inklusi-keuangan</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000722643.jpg</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Hukum kemarin: KPK usut Bank BJB, Kejagung periksa kasus MBG</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:29:47 +0700</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Dari penguatan layanan darurat Polri melalui SuperApp hingga penahanan tersangka kasus pengadaan iklan Bank BJB, ...</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://ramadhan.antaranews.com/berita/5688501/hukum-kemarin-kpk-usut-bank-bjb-kejagung-periksa-kasus-mbg</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/02/pelayanan-smart-road-safety-policing-di-polrestabes-bandung-2681285.jpg</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Spanyol evakuasi lebih dari 1000 orang akibat kebakaran hutan</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:21:26 +0700</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Lebih dari seribu orang, Senin (10/8), diungsikan dari rumah-rumah mereka akibat kebakaran hutan besar yang melanda ...</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688499/spanyol-evakuasi-lebih-dari-1000-orang-akibat-kebakaran-hutan</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/thumbs_b_c_5ce987f57076d14115b17c9f43ba83e8.jpg</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Lima belas tewas, delapan hilang akibat banjir, longsor di Filipina</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:11:02 +0700</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Jumlah korban jiwa akibat siklon tropis Kujira dan Dolphin, serta angin muson barat daya yang memicu banjir dan tanah ...</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688496/lima-belas-tewas-delapan-hilang-akibat-banjir-longsor-di-filipina</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/07/anadolu_penha.jpg</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Wamenaker ajak daerah siapkan kompetensi SDM “green jobs”</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:09:44 +0700</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Ketenagakerjaan (Wamenaker) Afriansyah Noor mengajak pemerintah daerah mulai menyiapkan sumber daya ...</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688495/wamenaker-ajak-daerah-siapkan-kompetensi-sdm-green-jobs</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/c2278f3c-b09f-4291-8bdc-6899dcd0f118.jpeg</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Kemarin, Prabowo ajukan Destry, Muktamar NU hingga sidang tahunan</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:04:15 +0700</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Dari pencalonan Destry Damayanti sebagai Gubernur Bank Indonesia definitif hingga agenda Muktamar Ke-35 NU, dinamika ...</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688491/kemarin-prabowo-ajukan-destry-muktamar-nu-hingga-sidang-tahunan</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Narasi_sp_2814926_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>KAI Jember edukasi masyarakat terkait bahaya meletakkan benda di rel</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:01:00 +0700</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia Daerah Operasi (Daop) 9 Jember mengedukasi masyarakat, terutama anak-anak terkait dengan bahaya ...</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688488/kai-jember-edukasi-masyarakat-terkait-bahaya-meletakkan-benda-di-rel</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-10-at-15.54.44-1.jpeg</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>AS siap bantu Kolombia pascagempa yang tewaskan sedikitnya 111 orang</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:00:46 +0700</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Menteri Luar Negeri Amerika Serikat (AS) Marco Rubio, Senin (10/8), menegaskan Gedung Putih siap membantu Kolombia ...</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688487/as-siap-bantu-kolombia-pascagempa-yang-tewaskan-sedikitnya-111-orang</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/AA-20260810-42182432-42182428-AT_LEAST_18_KILLED_AS_MAGNITUDE_74_EARTHQUAKE_HITS_COLOMBIA.jpg</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Italia, Denmark tentang migrasi ilegal tak terkendali ke Eropa</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:50:11 +0700</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Perdana Menteri Italia Giorgia Meloni dan Perdana Menteri Denmark Mette Frederiksen menegaskan sikap negaranya ...</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688485/italia-denmark-tentang-migrasi-ilegal-tak-terkendali-ke-eropa</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/thumbs_b_c_61b9b5a45b45b992cb574d4b0b9e38a2.jpg</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Korban tewas gempa Kolombia dilaporkan sedikitnya 111 orang</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:38:13 +0700</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Jumlah korban tewas akibat gempa bumi berkekuatan Magnitudo 7,4 yang mengguncang barat Kolombia pada Senin, 10 Agustus, ...</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688481/korban-tewas-gempa-kolombia-dilaporkan-sedikitnya-111-orang</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/AA-20260810-42182432-42182426-AT_LEAST_18_KILLED_AS_MAGNITUDE_74_EARTHQUAKE_HITS_COLOMBIA.jpg</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Setahun Buron, Maling Pembobol Rumah Wakil Bupati OKU Selatan Ditangkap</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:49:08 +0700</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Tommy Saputra</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Polisi menangkap Nanda Diwangga, maling yang membobol rumah milik Wakil Bupati OKU Selatan H Misnadi di Kabupaten Pringsewu, Lampung.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613177/setahun-buron-maling-pembobol-rumah-wakil-bupati-oku-selatan-ditangkap</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/11/06/6da17d61-730f-4c82-8d3a-363b30d553a8_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Puslabfor Cek DNA di 3 Ruangan Terkait Ratusan Senjata di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:40:10 +0700</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Polisi melakukan olah TKP di sekolah swasta Jakarta, menemukan 996 senjata. Penyelidikan berlanjut untuk memastikan tidak ada barang berbahaya lainnya.</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613162/puslabfor-cek-dna-di-3-ruangan-terkait-ratusan-senjata-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/ruangan-mantan-kepala-yayasan-ditemukannya-senjata-di-sekolah-swasta-jaksel-taufiqdetikcom-1786104460813_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Anggaran Revitalisasi Alun-alun Kota Serang Rp 48 M, Bakal Ada Patung Golok</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:33:24 +0700</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Serang menganggarkan Rp 48,2 M untuk revitalisasi alun-alun, termasuk untuk pembangunan patung golok dan fasilitas air siap minum.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613146/anggaran-revitalisasi-alun-alun-kota-serang-rp-48-m-bakal-ada-patung-golok</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/alun-alun-kota-serang-1786415561607_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Pemotor Patah Tulang Usai Tabrak Bus di Bekasi, Brimob Bantu Evakuasi</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:25:08 +0700</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Kecelakaan bus dan motor di Bekasi melibatkan pengendara yang mengalami patah tulang. Brimob membantu evakuasi dan mengimbau keselamatan berkendara.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613141/pemotor-patah-tulang-usai-tabrak-bus-di-bekasi-brimob-bantu-evakuasi</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/tim-patroli-brimob-polda-metro-jaya-menyisir-sejumlah-titik-rawan-di-bekasi-1786415084685_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Kemlu Ungkap Kondisi Terkini WNI Usai Gempa M 7,4 Guncang Kolombia</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:13:44 +0700</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Antara News</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Kemlu mengungkap kondisi terkini warga negara Indonesia (WNI) usai gempa dengan kekuatan magnitudo (M) 7,4 mengguncang Kolombia.</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613127/kemlu-ungkap-kondisi-terkini-wni-usai-gempa-m-7-4-guncang-kolombia</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/colombia-quakepereira-1786375621681_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Polda Metro Ringkus Ayah Bejat Tega Cabuli Anak Kandung Bertahun-tahun</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:03:26 +0700</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menangkap pria berinisial H karena mencabuli anak kandungnya berulang kali. Kasus ini mengedepankan perlindungan bagi korban.</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613120/polda-metro-ringkus-ayah-bejat-tega-cabuli-anak-kandung-bertahun-tahun</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/12/09/1195205515_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Motor Tertabrak KA di Pelintasan Tanpa Palang Sergai, 2 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:51:01 +0700</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Mhd Ilham Pradila</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Sepeda motor tertabrak kereta api (KA) di pelintasan sebidang tanpa palang pintu di Dusun I, Desa Pematang Sijonam, Kabupaten Serdang Bedagai (Sergai).</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613114/motor-tertabrak-ka-di-pelintasan-tanpa-palang-sergai-2-orang-tewas</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/foto-suasana-saat-kecelakaan-di-perlintasan-rel-kereta-api-dok-polres-sergai-1786378423257_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Anggota DPRD Apresiasi Rencana TransJ Kelola Transportasi Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:47:34 +0700</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Ketua Komisi B DPRD DKI Jakarta, Nova Paloh, dukung pengelolaan transportasi Pulau Seribu oleh Transjakarta. Ia minta kajian khusus terkait PSO dan tarif kapal.</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613113/anggota-dprd-apresiasi-rencana-transj-kelola-transportasi-kepulauan-seribu</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/09/pulau-bidadari-1765259194049_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>MUI Kecam Viral Challenge Hafalan Surah Al-Qur'an Ad-Dhuha demi Miras</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:38:40 +0700</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Wilda Hayatun Nufus</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Majelis Ulama Indonesia (MUI) mengecam keras viral aksi promosi minuman keras (miras) berkedok tantangan hafalan Al-Qur'an.</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613088/mui-kecam-viral-challenge-hafalan-surah-al-quran-ad-dhuha-demi-miras</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/05/24/ilustrasi-gedung-mui_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Pemprov Siapkan Regulasi TransJ Kelola Transportasi ke Pulau Seribu Mulai 2027</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:34:14 +0700</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Pemprov DKI akan alihkan pengelolaan transportasi Kepulauan Seribu ke Transjakarta mulai 2027, untuk meningkatkan layanan dan integrasi transportasi publik.</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613083/pemprov-siapkan-regulasi-transj-kelola-transportasi-ke-pulau-seribu-mulai-2027</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/12/stafsus-gubernur-jakarta-chico-hakim-maulanidetikcom-1747049619991_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Bea Cukai Gagalkan Penyelundupan 2,7 Juta Batang Rokok Ilegal di Kalbar</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:34:00 +0700</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Wilda Hayatun Nufus</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Kanwil Ditjen Bea dan Cukai Kalimantan Bagian Barat (Kanwil DJBC Kalbagbar) menggagalkan penyelundupan 2.740.000 batang rokok ilegal.</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613082/bea-cukai-gagalkan-penyelundupan-2-7-juta-batang-rokok-ilegal-di-kalbar</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/08/30/9950fe5a-950e-41f3-9b92-db2c7d0dbb2e_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Silaturahmi ke BPK, Pimpinan MPR Puji Peningkatan Kualitas Opini WTP</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:27:00 +0700</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI Ahmad Muzani silaturahmi dengan Pimpinan BPK, membahas Sidang Tahunan MPR dan akuntabilitas pengelolaan keuangan negara.</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613080/silaturahmi-ke-bpk-pimpinan-mpr-puji-peningkatan-kualitas-opini-wtp</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/silaturahmi-ke-bpk-pimpinan-mpr-puji-peningkatan-kualitas-opini-wtp-1786411605025.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Legislator PKB Minta Teknologi Drone Dioptimalkan untuk Padamkan Karhutla Bromo</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:05:52 +0700</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Anggota DPR Daniel Johan prihatin dengan karhutla di Gunung Bromo. Dia mendorong penggunaan teknologi, seperti drone, untuk pemadaman yang lebih efektif.</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613071/legislator-pkb-minta-teknologi-drone-dioptimalkan-untuk-padamkan-karhutla-bromo</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/05/31/daniel-johan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Ulah Pria Bakar 1,5 Hektare Lahan di Inhu dengan Dalih Usir Nyamuk</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:59:04 +0700</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Seorang pria di Inhu ditangkap usai membakar 1,5 hektare lahan untuk mengusir nyamuk. Polisi menegaskan penegakan hukum terhadap karhutla akan terus dilakukan.</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613064/ulah-pria-bakar-1-5-hektare-lahan-di-inhu-dengan-dalih-usir-nyamuk</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/polres-inhu-mengamankan-seorang-kakek-yang-membakar-lahan-15-hektare-1786343491276_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Cegah Titik Api Baru, Petugas Siaga 24 Jam di Bromo</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:58:00 +0700</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Trypama Randra</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Petugas gabungan terus bersiaga selama 24 jam untuk memantau perkembangan kebakaran di kawasan Taman Nasional Bromo Tengger Semeru (TNBTS), Jawa Timur.</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612933/cegah-titik-api-baru-petugas-siaga-24-jam-di-bromo</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/detik-pagi-cegah-titik-api-baru-petugas-siaga-24-jam-di-bromo-1786407647947_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Asrama Ponpes di Kampar Terbakar Hebat Semalam, Api Padam Usai 4 Jam</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:51:39 +0700</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda Pondok Pesantren Syekh Burhanuddin di Kampar, menghanguskan gedung asrama. Api dipadamkan dalam 4 jam tanpa korban jiwa.</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613061/asrama-ponpes-di-kampar-terbakar-hebat-semalam-api-padam-usai-4-jam</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/gedung-asrama-pondok-pesantren-syekh-burhanuddin-kuntu-darussalam-kampar-kebakaran-1786409407964_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Waka DPRD DKI Dukung TransJ Kelola Transportasi Pulau Seribu: Bangun Awareness</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:44:56 +0700</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Waka DPRD DKI Wibi Andrino dukung rencana pengelolaan transportasi Pulau Seribu oleh TransJakarta dengan tarif terjangkau untuk meningkatkan mobilitas warga.</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613055/waka-dprd-dki-dukung-transj-kelola-transportasi-pulau-seribu-bangun-awareness</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/15/wakil-ketua-dprd-dki-jakarta-wibi-andrino-1781509718241_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Kebakaran Hutan Terjadi di Gunung Andong Magelang, 3,67 Hektare Lahan Hangus</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:38:16 +0700</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Eko Susanto</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan melanda Gunung Andong, Magelang, dengan luas lahan terbakar 3,67 hektare. Tim gabungan berhasil memadamkan api dalam beberapa jam.</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613049/kebakaran-hutan-terjadi-di-gunung-andong-magelang-3-67-hektare-lahan-hangus</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/gunung-andong-terkabar-1786365987827_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Dugaan Pembunuhan Berencana di Balik Kematian Sutrimo Diusut</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:37:26 +0700</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Kematian Sutrimo di Klinik Mordent kini dalam penyidikan polisi. Dugaan pembunuhan berencana diusut</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613048/dugaan-pembunuhan-berencana-di-balik-kematian-sutrimo-diusut</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/26/kondisi-klinik-kecantikan-di-kebayoran-baru-jaksel-temoat-pria-bernama-sutrimo-ditemukan-tewas-adhfardetikcom-1785073645811_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Kepala BNPB Ungkap Pemadaman Karhutla Gunung Bromo Terkendala Cuaca</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:28:45 +0700</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Kepala BNPB Suharyanto ungkap kendala pemadaman kebakaran hutan di Gunung Bromo, terutama cuaca. Kebakaran meluas hingga 520 hektare, upaya terus dilakukan.</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613044/kepala-bnpb-ungkap-pemadaman-karhutla-gunung-bromo-terkendala-cuaca</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/30/teks-foto-kepala-bnpb-letjen-tni-suharyanto-saat-konferensi-pers-foto-dok-bnpb-1764493958835_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>⁠Perpres Ojol Tinggal Tunggu Waktu</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:25:18 +0700</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Perpres ojek online (ojol) hampir rampung. Pemerintah targetkan finalisasi sebelum 17 Agustus 2026, dengan ojol diakui sebagai pelaku UMKM.</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613043/perpres-ojol-tinggal-tunggu-waktu</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/23/wakil-ketua-dpr-sufmi-dasco-ahmad-memimpin-rapat-bersama-pemerintah-di-gedung-dpr-senayan-jakarta-kamis-2372026-1784778262980_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Eks Menag Yaqut Jalani Sidang Perdana Kasus Korupsi Kuota Haji Hari Ini</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:08:14 +0700</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Sidang perdana kasus dugaan korupsi kuota haji tambahan tahun 2023-2024 dengan terdakwa mantan Menag Yaqut Cholil Qoumas (YCQ) digelar hari ini</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613040/eks-menag-yaqut-jalani-sidang-perdana-kasus-korupsi-kuota-haji-hari-ini</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/31/penahanan-yaqut-cholil-qoumas-diperpanjang-1774956425556_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Harga Emas Hari Ini Lompat!</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:49:41 +0700</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Harga emas Antam hari ini, 11 Agustus 2026, naik Rp 20.000 per gram menjadi Rp 2.710.000. Cek rincian harga dari 0,5 gram hingga 1.000 gram.</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613178/harga-emas-hari-ini-lompat</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/15/harga-emas-antam-tembus-rekor-tertinggi-sentuh-rp238-juta-per-gram-1760532607071_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>IHSG Dibuka Dua Arah Pagi Ini, Tertahan di 6.300</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:24:06 +0700</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) dibuka dua arah pagi ini. Mulanya IHSG menguat, namun langsung melemah setelah beberapa menit perdagangan dibuka.</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8613138/ihsg-dibuka-dua-arah-pagi-ini-tertahan-di-6-300</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/11/19/ihsg-ditutup-menguat-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>TAPG Bagi Dividen Rp1,19 T, CMRY dan IFSH Catat Kinerja Positif</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:21:17 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Redaksi Detik</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>IHSG turun 0,69%, sementara TAPG siapkan dividen Rp1,19 triliun. CMRY dan IFSH juga mencatat pertumbuhan kinerja pada semester I-2026.</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8613134/tapg-bagi-dividen-rp1-19-t-cmry-dan-ifsh-catat-kinerja-positif</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/bursa-dan-valas-1786411120-1786411120587.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Dolar AS Pagi Ini Menguat ke Rp 17.797</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:18:16 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Nilai tukar dolar Amerika Serikat (AS) menguat terhadap rupiah. Pagi ini mata uang Paman Sam bergerak naik mendekati level Rp 17.800.</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8613129/dolar-as-pagi-ini-menguat-ke-rp-17-797</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/rupiah-masih-tertekan-dolar-as-betah-di-level-rp18000-1783662450657_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Produk UMKM Eks Lokalisasi Dolly Didorong Tembus Pasar Ekspor</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:34:51 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Angga Aliya ZRF</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Peluang ekspor bagi pelaku UMKM Gotong Royong di kawasan Putat Jaya, eks lokalisasi Dolly, Surabaya sangat besar.</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613084/produk-umkm-eks-lokalisasi-dolly-didorong-tembus-pasar-ekspor</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/produk-umkm-eks-lokalisasi-dolly-didorong-tembus-pasar-ekspor-1786412010899_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Trump Bolehkan Kapal Berbendera Asing Angkut BBM ke AS</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:30:20 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Pemerintah AS memperpanjang pengecualian UU Jones hingga November 2026 untuk menjaga pasokan minyak. Langkah ini diambil di tengah konflik dengan Iran.</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8613045/trump-bolehkan-kapal-berbendera-asing-angkut-bbm-ke-as</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Izin KMP Mutiara Sentosa II Terancam Dicabut</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:57:38 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan Dudy Purwagandhi siapkan sanksi tegas untuk PT Atosim Lampung Pelayaran setelah insiden kebakaran KMP Mutiara Sentosa II di Madura.</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8612855/izin-kmp-mutiara-sentosa-ii-terancam-dicabut</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Penjelasan OJK &amp;amp; BEI soal Masjid Istiqlal Masuk Bursa</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:30:13 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Direktur Utama Bursa Efek Indonesia (BEI) Jeffrey Hendrik membenarkan adanya kerja sama dengan Masjid Istiqlal.</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8612841/penjelasan-ojk-bei-soal-masjid-istiqlal-masuk-bursa</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/30/ihsg-rebound-usai-dua-hari-anjlok-seiring-pengunduran-diri-dirut-bei-1769748663323_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Harga Minyak Mentah RI Turun Jadi US$ 81,68/Barel</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:15:55 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Rata-rata Harga Minyak Mentah Indonesia atau Indonesian Crude Price (ICP) pada Juli ditetapkan pemerintah menjadi sebesar US$ 81,68 per barel.</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8613036/harga-minyak-mentah-ri-turun-jadi-us-81-68-barel</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/13/emas-minyak-membara-usai-israel-serang-iran-1749816574366_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Jalan Rusak Hambat Aktivitas Ekonomi Warga Desa Terpencil di Kerinci</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:01:24 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Grandyos Zafna</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Pengendara melintasi jalan Sungai Sampun-Renah Kasah yang menjadi satu-satunya akses warga menuju pasar dan rumah sakit di Kerinci, Jambi.</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8612507/jalan-rusak-hambat-aktivitas-ekonomi-warga-desa-terpencil-di-kerinci</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/akses-jalan-desa-terpencil-di-kerinci-1786356435491.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Akses Investasi Emas Makin Luas Lewat ETF</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:41:40 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Ardan Adhi Chandra</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>ETF emas merupakan Reksa Dana berbentuk Kontrak Investasi Kolektif (KIK) berbasis emas yang Unit Penyertaannya diperdagangkan di BEI.</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8613032/akses-investasi-emas-makin-luas-lewat-etf</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/ilustrasi-emas-1768395112559_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Prabowo Usulkan Destry Damayanti Calon Tunggal Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:30:53 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto sudah menentukan Gubernur Bank Indonesia pilihannya.</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8612554/prabowo-usulkan-destry-damayanti-calon-tunggal-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/20/deputi-gubernur-senior-bi-destry-damayanti-1747729609306_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Tradisigila Tebar Cinta di Album Ketiga</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:30:45 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Band Tradisigila luncurkan album ketiga Street Love Memories dengan 10 lagu bertema cinta. Album ini tampilkan kolaborasi unik dan proses produksi yang menarik.</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/music/d-8613140/tradisigila-tebar-cinta-di-album-ketiga</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/tradisigila-1786415036540_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Bigmo Umbar Janji Usai Konten Bermasalah Lagi hingga Dipolisikan</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:09:35 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Bigmo mengakui kesalahan dan berkomitmen untuk memperbaiki konten di masa depan. Ini bukan pertama kali Bigmo janji.</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613069/bigmo-umbar-janji-usai-konten-bermasalah-lagi-hingga-dipolisikan</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/bigmo-1786347973337_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Double Happy Kevin Sanjaya: Ultah Ke-31 dan Bakal Punya Anak Perempuan Lagi</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:09:53 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Pebulutangkis Kevin Sanjaya merayakan ulang tahun ke-31. Ia bakal dikaruniai seorang putri lagi, sebab istrinya, Valencia Tanoesoedibjo hamil anak kedua, yeay!</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611905/double-happy-kevin-sanjaya-ultah-ke-31-dan-bakal-punya-anak-perempuan-lagi</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kevin-sanjaya-1786339357537_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Momen Bigmo Klarifikasi soal Dugaan Promosi Vape Libatkan Anak, Janji Buat Konten Positif</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:49:50 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Bigmo jalani klarifikasi di Polda Metro Jaya soal dugaan eksploitasi anak dalam live streaming, akui kapok dan janji evaluasi konten.</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866692/momen-bigmo-klarifikasi-soal-dugaan-promosi-vape-libatkan-anak-janji-buat-konten-positif</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MB1ZiNQ6NK2dGnKcwEd1QqaGYkc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Bigmo-1-10082026.jpg</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Harga Emas Antam Hari Ini, Selasa 11 Agustus 2026: Naik di Level Rp2.710.000 per Gram</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:48:16 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Harga emas pada hari ini, Selasa (11/8/2026), naik di level Rp 2.710.000, simak rincian harga emas terbarunya.</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866691/harga-emas-antam-hari-ini-selasa-11-agustus-2026-naik-di-level-rp2710000-per-gram</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yXSSWAbqyzd4eU7_V1vMMlCefPo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Harga-Emas-Antam-Mulai-Naik_20250409_204103.jpg</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Pemain Libur Latihan, Laga Uji Coba Timnas Voli Putri Indonesia vs Korea Belum Ada Titik Terang</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:47:29 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Laga uji coba Timnas Voli Putri Indonesia vs Korea Selatan belum temui titik terang setelah SEA V Cup 2026 rampung.</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866690/pemain-libur-latihan-laga-uji-coba-timnas-voli-putri-indonesia-vs-korea-belum-ada-titik-terang</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ji5jh_awPmeoo7bKdWFIChFnymU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pemain-Timnas-Voli-Putri-Indonesia-melakukan-perayaan-setelah-mencetak-poin-saat.jpg</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Kesaksian Keluarga Korban Penyekapan di Sumedang, Dipicu Sewa Mobil dan Jaminan STNK</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:47:09 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Kasus penyekapan di markas ormas Sumedang menewaskan penyewa mobil asal Bandung akibat dugaan penganiayaan dan perselisihan jaminan STNK.</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866689/kesaksian-keluarga-korban-penyekapan-di-sumedang-dipicu-sewa-mobil-dan-jaminan-stnk</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/A1YYPLRilH3I4xpPq3AfPCEpo4M=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PENYEKAPAN-sumedang.jpg</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Wasit Somalia Omar Artan Dulu Ditolak Pimpin Piala Dunia, Kini Cetak Sejarah di Piala Super Eropa</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:44:56 +0700</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Wasit Somalia Omar Artan gagal bertugas di Piala Dunia 2026. Tapi kini ia akan cetak sejarah pimpin Piala Super Eropa antara PSG vs Aston Villa.</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866688/wasit-somalia-omar-artan-dulu-ditolak-pimpin-piala-dunia-kini-cetak-sejarah-di-piala-super-eropa</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/cu4kjqtdwmzziPnaYLrm3iqdpmI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wasit-Omar-Artan-asal-Somalia.jpg</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Baru Juara Korea Masters 2026, Herry IP Minta Anak Didik Fokus ke Kejuaraan Dunia BWF 2026</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:42:19 +0700</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Herry IP tidak membiarkan anak didiknya terlena karena juara Korea Masters 2026 sebab Kejuaraan Dunia BWF 2026 sudah menanti.</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866687/baru-juara-korea-masters-2026-herry-ip-minta-anak-didik-fokus-ke-kejuaraan-dunia-bwf-2026</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yoV87cuvFbibknPtbgk8pRanBAQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/aaron-chiasoh-wooi-yik-kalah_20240608_210449.jpg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Ayah Kandung Tega Cabuli Darah Dagingnya Sendiri, Terbongkar Usai Sang Anak Cerita ke Guru</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:40:41 +0700</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Dalam kasus tersebut, penyidik menetapkan ayah kandung korban berinisial H (48) sebagai tersangka pada 15 Juli 2026.</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866686/ayah-kandung-tega-cabuli-darah-dagingnya-sendiri-terbongkar-usai-sang-anak-cerita-ke-guru</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/lgquujyi8tNMzKMS2WaHIPuzDRY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-borgol-polisi-ok.jpg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>41 Bidang Pelatihan Vokasi Nasional Batch 4 Tahun 2026 Kemnaker</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:38:22 +0700</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Kemnaker membuka Pelatihan Vokasi Nasional Batch 4 di berbagai bidang. Pendaftaran akan ditutup pada 12 Agustus 2026. Berikut persyaratannya.</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866685/41-bidang-pelatihan-vokasi-nasional-batch-4-tahun-2026-kemnaker</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/R3FIzepNAON4esJLLu0A57BlU0U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PELATIHAN-VOKASI-NASIONAL-34534534t534.jpg</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Dokter Ungkap Pilihan Pengobatan Sinusitis hingga Kapan Perlu Operasi</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:36:51 +0700</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Dokter ungkap sinusitis dapat ditangani dengan obat-obatan dan cuci hidung, sedangkan operasi dipertimbangkan jika kondisi sudah kronis.</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866684/dokter-ungkap-pilihan-pengobatan-sinusitis-hingga-kapan-perlu-operasi</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/v5mx-RLREFQ7JtIFrF09sjE1Rc0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/sinusitis-54644.jpg</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Bintangi Film Seni Merayu Tuhan, Lutesha Ungkap Tantangan Perankan Karakter Sophia</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:33:45 +0700</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Aktris Lutesha mengungkap tantangan memerankan karakter Sophia dalam film Seni Merayu Tuhan. Ia pun melakukan riset tentang pacaran beda agama.</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866683/bintangi-film-seni-merayu-tuhan-lutesha-ungkap-tantangan-perankan-karakter-sophia</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/6QDU-A5OOgZKMGf3STeqKDQEYbs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Lutesha-1-12062026.jpg</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Fuji Komentari Fotonya yang Di-crop oleh Violenzia Jeanette: Stop Besarkan Masalah</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:32:19 +0700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Fuji An buka suara soal fotonya yang di-crop Violenzia Jeanette. Ia meminta warganet tak membesar-besarkan persoalan tersebut.</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866682/fuji-komentari-fotonya-yang-di-crop-oleh-violenzia-jeanette-stop-besarkan-masalah</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/eSLahIyeHZ_FnrQKUYoE89HqelM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Fuji-23012026.jpg</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Video Lawas Ruben Onsu Akui Memang Pilih-pilih Datang ke Podcast, Ungkit Alasan Takut Cerita</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:31:58 +0700</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Ruben Onsu mengungkapkan alasannya pilih-pilih datang undangan podcast atau wawancara dalam sebuah video lawas enam tahun lalu.</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866681/video-lawas-ruben-onsu-akui-memang-pilih-pilih-datang-ke-podcast-ungkit-alasan-takut-cerita</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/B0PjO6TU4zWsvX1GGG1dLTB_lgA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/mediasi-ruben-onsu.jpg</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Perkuat Sistem Sanitasi Perkotaan, Jaringan Air Limbah JSDP Terus Dikebut</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:30:23 +0700</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>JSDP bertujuan untuk meningkatkan kualitas lingkungan perairan dan akses sanitasi di DKI Jakarta.</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866680/perkuat-sistem-sanitasi-perkotaan-jaringan-air-limbah-jsdp-terus-dikebut</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/6bOF8h2WTEB_426N_0ft1_I0Kqk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/JSDP-Pemerintah-Provinsi-DKI-Jakarta.jpg</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Diterpa Isu Makelar Jabatan, Raffi Ahmad: Semoga Keluarga Saya Dijaga Allah</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:30:10 +0700</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Diterpa isu makelar jabatan, presenter kondang Raffi Ahmad berdoa agar keluarganya selalu dilindungi oleh Allah SWT.</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866679/diterpa-isu-makelar-jabatan-raffi-ahmad-semoga-keluarga-saya-dijaga-allah</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/lC6bl6-fHAgnWmXsBq02OmcoJ9k=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Raffi-Ahmad-akui-narkoba.jpg</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Hasil Drawing Ronde Kedua Carabao Cup 2026/2027: Chelsea vs Luton Town, Tottenham Jumpa Charlton</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:27:46 +0700</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Hasil drawing ronde kedua Carabao Cup 2026/2027 menghadirkan duel Chelsea vs Luton Town dan Tottenham Hotspur vs Charlton Athletic.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866678/hasil-drawing-ronde-kedua-carabao-cup-20262027-chelsea-vs-luton-town-tottenham-jumpa-charlton</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/wIj2Ieyz8SVHT4ouMvoXV76dqMU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Chelsea-Bantai-AC-Milan-3-0-di-SUGBK_20260808_235528.jpg</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Jaecoo Australia Recall Model J7 karena Kabel Kelistrikan yang Berisiko Mesin Mati</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:27:16 +0700</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Jaecoo me-recall 171 unit SUV Jaecoo J7 model tahun 2025-2026 dari tangan konsumen di Australia akibat masalah pada kabel kelistrikan.</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/otomotif/7866677/jaecoo-australia-recall-model-j7-karena-kabel-kelistrikan-yang-berisiko-mesin-mati</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/nnwb0rGPK9t7XV4NI4cEjd442pk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Jaecoo-J7-Australia-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Awal Mula Kasus Penyekapan di Sumedang Terungkap, Korban Tewas saat Dirawat di Rumah Sakit</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:26:53 +0700</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Seorang pria asal Bandung meninggal dunia setelah disekap dan dianiaya secara terencana di markas ormas wilayah Sumedang Utara.</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866676/awal-mula-kasus-penyekapan-di-sumedang-terungkap-korban-tewas-saat-dirawat-di-rumah-sakit</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/A1YYPLRilH3I4xpPq3AfPCEpo4M=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PENYEKAPAN-sumedang.jpg</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Sidang Perdana Korupsi Kuota Haji, KPK Ajak Masyarakat Kawal Pembuktian Dakwaan Eks Menag Yaqut</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:26:41 +0700</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>KPK mengajak seluruh elemen masyarakat untuk mengawal ketat jalannya sidang perdana perkara dugaan korupsi kuota haji tambahan tahun 2023–2024.</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866675/sidang-perdana-korupsi-kuota-haji-kpk-ajak-masyarakat-kawal-pembuktian-dakwaan-eks-menag-yaqut</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/JWY_zXSr_92WtYMCqp_1sySb4SU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Yaqut-Cholil-Qoumas-alias-Gus-Yaqut-diperiksa-lagi-selasa.jpg</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>TB Hasanuddin Ingatkan TNI Boleh Bantu Polri, Bukan Ambil Alih Kamtibmas Jelang HUT ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:23:22 +0700</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>TB Hasanuddin menjelaskan Pasal 30 UUD 1945 menempatkan TNI sebagai alat negara di bidang pertahanan.</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866674/tb-hasanuddin-ingatkan-tni-boleh-bantu-polri-bukan-ambil-alih-kamtibmas-jelang-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/DK04Z5Zl2o9lJjQ4NWbNacQarXk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/tb-hasanuddin-usai-sesi-wawancara-khusus-dengan-direktur-pemberitaan-tribun-network.jpg</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>BPJS Ketenagakerjaan Gandeng Universitas Brawijaya, Buka Akses Kuliah bagi Anak Ahli Waris</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:23:15 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>BPJS Ketenagakerjaan bersama Universitas Brawijaya (UB) melalui Perjanjian Kerja Sama (PKS) perluas manfaat jaminan sosial ke bidang pendidikan.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866673/bpjs-ketenagakerjaan-gandeng-universitas-brawijaya-buka-akses-kuliah-bagi-anak-ahli-waris</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1jInZKMcpSZPe_ym4t_VvYsU7j4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/BPJS-TK-di-Ospek-UB.jpg</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Bandung Barat Makin Berkembang, Aktivitas Ekonomi Kawasan Ikut Tumbuh</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, BANDUNG -- Perkembangan kawasan hunian di Bandung Barat mulai mendorong pertumbuhan aktivitas ekonomi dan kebutuhan ruang usaha. Bertambahnya jumlah penghuni, fasilitas kawasan, serta konektivitas membuat permintaan terhadap ruang komersial...</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjl0zb416/bandung-barat-makin-berkembang-aktivitas-ekonomi-kawasan-ikut-tumbuh</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/investasi-esg_230919115622-936.jpg</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ShopeePay Merchant Bantu UMKM Go Digital, Begini Cara Daftar QRIS Online</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Dwi Murdaningsih</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA - Transformasi digital mengubah cara masyarakat bertransaksi. Kini, pembayaran menggunakan QRIS semakin menjadi pilihan utama karena praktis, cepat, dan dapat digunakan oleh berbagai aplikasi pembayaran digital. Kondisi ini...</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjtjp368/shopeepay-merchant-bantu-umkm-go-digital-begini-cara-daftar-qris-online</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/melalui-shopeepay-merchant-pelaku-usaha-dapat-memulai-digitalisasi-pembayaran_260810170554-416.jpg</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Destry Calon Tunggal Gubernur BI, Rupiah Jadi Ujian</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:26:57 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Tekanan terhadap rupiah menjadi salah satu tantangan yang akan dihadapi Destry Damayanti jika terpilih sebagai Gubernur Bank Indonesia (BI). Chief Economist Permata Bank Josua Pardede menilai Destry...</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjl00x416/destry-calon-tunggal-gubernur-bi-rupiah-jadi-ujian</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260731110729-944.png</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Konsumsi Masyarakat Terjaga Ditopang Stimulus Pemerintah</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:01:00 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Head of Macroeconomic &amp; Financial Market Research Permata Bank Faisal Rachman mengatakan konsumsi rumah tangga Indonesia masih menunjukkan ketahanan di tengah dinamika ekonomi global dan kenaikan harga...</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjkx3i423/konsumsi-masyarakat-terjaga-ditopang-stimulus-pemerintah</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/019116900-1770627294-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Gempa Kolombia M 7,4 dan Ancaman yang Juga Mengintai Indonesia</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:49:51 +0700</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Gempa ini menewaskan sedikitnya 132 orang dan menyebabkan kerusakan pada sejumlah bangunan.</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266766/gempa-kolombia-m-74-dan-ancaman-yang-juga-mengintai-indonesia</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/myyFUTBwzzkhnCw9JQGSfvKGClo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320742/original/096695800_1786380115-col4.jpg</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Anak Cerita ke Guru, Bongkar Kekerasan Seksual Ayah Kandung</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya tangani kasus kekerasan seksual anak yang dibongkar korban kepada guru.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266736/anak-cerita-ke-guru-bongkar-kekerasan-seksual-ayah-kandung</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/6ZnERNrXCveARYtk90IJDED3T6w=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320810/original/009858000_1786413762-email-attachment_2026_08_11_adyanugrahadi_bapak-kandung-cabuli-anak-terungkap-dari-curhatan-ke-guru_93f1c7a4-f1d7-49d1-a16b-cbafc6f16029.jpeg</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Menteri LH Dorong Wonosobo Kembangkan Pariwisata Berbasis Lingkungan</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:30:53 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Pariwisata berbasis lingkungan didorong di Wonosobo untuk meningkatkan kesejahteraan masyarakat sekaligus menjaga kelestarian alam.</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266311/menteri-lh-dorong-wonosobo-kembangkan-pariwisata-berbasis-lingkungan</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/AaM9wa-gA-oOdWkoNHdqVBx0ZlU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5536124/original/096555900_1774250305-3.jpg</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Satpol PP Depok Bongkar 350 Bangunan Pedagang Pasar Cisalak Depok</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:25:54 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Penertiban dilakukan setelah lapak pedagang dikeluhkan mengganggu akses jalan dan menutup saluran drainase.</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266713/satpol-pp-depok-bongkar-350-bangunan-pedagang-pasar-cisalak-depok</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/hlamGskIC0lkULIRHgiwZcrU4lc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320786/original/040974200_1786410221-1001445600.jpg</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Pengiriman Sabu Berkedok Paket Ekspedisi , Polisi Sita 31,48 Gram</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:37:06 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Paket ekspedisi ternyata menyimpan sabu puluhan gram yang siap diedarkan.</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266746/pengiriman-sabu-berkedok-paket-ekspedisi-polisi-sita-3148-gram</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/rAeQ9HVd0yIr2ZM3V81WlpGcbPU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320819/original/008308900_1786414825-6f603265-6909-4f32-a3d0-62824e626ef8.jpg</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Jelang HUT RI, Kepala Bakom Imbau Warga Bijak Bermedsos</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Menjelang HUT RI, Kepala Bakom RI Muhammad Qodari meminta masyarakat tenang dan bijak menerima informasi, terutama di medsos.</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266742/jelang-hut-ri-kepala-bakom-imbau-warga-bijak-bermedsos</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/co8KS1aagel0CU0X9XtCIoCxZWQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/8686422/original/016959600_1782742010-Kepala_Badan_Komunikasi_Pemerintah__Bakom__Muhammad_Qodari-29_Juni_2026a.jpg</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Berapa Lama Proses Pembebasan PBB-P2? Ini Estimasi Waktu dan Cara Memantaunya</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Ingin mengajukan pembebasan PBB-P2? Cek berapa lama prosesnya dan cara mengajukan agar tahapan yang dilakukan sesuai dengan aturan yang ada.</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266203/berapa-lama-proses-pembebasan-pbb-p2-ini-estimasi-waktu-dan-cara-memantaunya</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/tt1N9ic4WtxZwzhOoPplRv8RFrw=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5571556/original/032225200_1777635945-Depositphotos_634728534_L.jpg</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Sidang Perdana Eks Menag Yaqut Digelar Hari Ini</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:04:42 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Eks Menteri Agama Yaqut Cholil Qoumas menjalani sidang perdana kasus dugaan korupsi kuota haji di Pengadilan Tipikor Jakarta.</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266702/sidang-perdana-eks-menag-yaqut-digelar-hari-ini</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/-vg7hXrpZ8lhCuiom8MZJ3zTUuQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/7608165/original/012297800_1780392985-2.jpg</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Hype</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Anggota Boyband Asal Thailand, Tae Ditemukan Meninggal di Sungai Chao Phraya</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:02:09 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Penyanyi Thailand Tae atau Thaman Taephan ditemukan meninggal di sungai dalam kondisi mengambang</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://entertainment.kompas.com/read/2026/08/11/100121766/anggota-boyband-asal-thailand-tae-ditemukan-meninggal-di-sungai-chao</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/7Lvw_-mvyg0dZX3wSwWUnKl4eH0=/0x110:1200x910/1200x675/filters:watermark(data/photo/2026/01/30/697c81706c5a3.png,0,-0,1)/data/photo/2026/08/11/6a7a8efa2522d.jpg</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Update Harga Ban Mobil Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:02:09 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Sebelum menempuh perjalanan jauh, pemilik mobil wajib mengecek kondisi ban, mulai dari tekanan angin hingga tingkat keausan.</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://otomotif.kompas.com/read/2026/08/11/094200615/update-harga-ban-mobil-bulan-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/2XuQ_IBQ6JMFyequVWNueYkNFQo=/306x204:6192x4128/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/03/07/69ac0bf44063e.jpg</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Kapolda Sebut Pebalap Drag Race Kotamobagu Berpotensi Jadi Tersangka, 8 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:02:09 +0700</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Kapolda Sulut sebut pebalap drag race di Kotamobagu berpotensi jadi tersangka. Kecelakaan tewaskan 8 orang.</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/11/091727678/kapolda-sebut-pebalap-drag-race-kotamobagu-berpotensi-jadi-tersangka-8</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/GZTzVXqiUz38ndaLRV9lyUQKis8=/0x20:944x650/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a79958c59300.jpg</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I106"/>
+  <autoFilter ref="A1:I219"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$335</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I219"/>
+  <dimension ref="A1:I335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10726,8 +10726,5461 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Gerakan bersih-bersih masjid libatkan 50 ribu masjid dan mushala</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:13:17 +0700</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Kementerian Agama melaporkan Gerakan Bersih-Bersih Masjid (Geber Mas) 2026 secara nasional diikuti lebih dari 50 masjid ...</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688669/gerakan-bersih-bersih-masjid-libatkan-50-ribu-masjid-dan-mushala</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000177445.jpg</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Mantan Menag Yaqut jalani sidang perdana dugaan korupsi kuota haji</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:12:44 +0700</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Terdakwa kasus dugaan korupsi kuota haji Yaqut Cholil Qoumas melambaikan tangan saat bersiap menjalani sidang pembacaan ...</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5688668/mantan-menag-yaqut-jalani-sidang-perdana-dugaan-korupsi-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/sidang-dakwaan-yaqut-110826-bay-1A.jpg</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>​Polisi selidiki tewasnya siswi 14 tahun di Stasiun Jurangmangu</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:11:39 +0700</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Kepolisian Sektor (Polsek) Ciputat Timur tengah menyelidiki insiden tewasnya seorang pelajar perempuan berinisial ...</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688667/polisi-selidiki-tewasnya-siswi-14-tahun-di-stasiun-jurangmangu</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/06/07/IMG-20210607-WA0007_1_1.jpg</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Kontribusi perahu listrik bagi kawasan wisata Rammang-Rammang</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:07:39 +0700</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Sebuah perahu berlayar membelah perairan sungai di kawasan Wisata Karst Rammang-Rammang yang berstatus warisan dunia ...</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688665/kontribusi-perahu-listrik-bagi-kawasan-wisata-rammang-rammang</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-10.17.50_edited.jpg</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>DKI didorong miliki BUMD yang kelola sampah untuk tingkatkan PAD</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:04:09 +0700</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) DKI Jakarta didorong untuk memiliki Badan Usaha Milik Daerah (BUMD) yang secara khusus ...</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688664/dki-didorong-miliki-bumd-yang-kelola-sampah-untuk-tingkatkan-pad</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/optimalisasi-pengelolaan-sampah-tps-3r-2833135.jpg</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Upaya, kepercayaan, dan dukungan menjinakan api di Bromo</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:03:30 +0700</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Terhitung sudah tujuh hari, sejak Senin (3/8) hingga Senin (10/8), kawasan Gunung Bromo di Jawa Timur dilanda kebakaran ...</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688660/upaya-kepercayaan-dan-dukungan-menjinakan-api-di-bromo</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001412650.jpg</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>China bangun kemitraan global untuk kemajuan bersama</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:00:24 +0700</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Di Pelabuhan Piraeus, Yunani, salah satu pusat maritim tersibuk di Eropa, kapal-kapal keluar dan masuk sepanjang waktu, ...</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688656/china-bangun-kemitraan-global-untuk-kemajuan-bersama</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000005_20260811_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Harga emas Galeri24-Antam-UBS di Pegadaian kompak naik</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:58:05 +0700</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Harga emas di laman Pegadaian yang dikutip di Jakarta, Selasa, pukul 10.20 WIB, sama-sama menunjukkan kenaikan ...</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688653/harga-emas-galeri24-antam-ubs-di-pegadaian-kompak-naik</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/03/inflasi-kalimantan-tengah-mei-2026-2798829.jpg</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Apple siapkan fitur untuk verifikasi keaslian foto di iOS 27</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:54:45 +0700</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Apple dikabarkan tengah mengembangkan fitur bernama Reference Image yang memungkinkan pengguna memverifikasi apakah ...</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688649/apple-siapkan-fitur-untuk-verifikasi-keaslian-foto-di-ios-27</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_145658063.jpg</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Polisi tahan ayah kandung tersangka kekerasan seksual anak di Jaktim</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:52:31 +0700</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Direktorat Reserse Perlindungan Perempuan dan Anak serta Pemberantasan Perdagangan Orang (Ditres PPA dan PPO) Polda ...</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688645/polisi-tahan-ayah-kandung-tersangka-kekerasan-seksual-anak-di-jaktim</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000913066.jpg</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Sejumlah wilayah diguyur hujan lebat akibat topan Dolphin di China</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:52:08 +0700</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Topan Dolphin bergerak ke arah pedalaman setelah dua kali menghantam daratan di sepanjang pesisir Provinsi Zhejiang, ...</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688641/sejumlah-wilayah-diguyur-hujan-lebat-akibat-topan-dolphin-di-china</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000006_20260811_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>IHSG berpotensi melemah, pasar "wait and see" sentimen global-domestik</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:48:55 +0700</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa berpotensi bergerak melemah di tengah pelaku ...</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688640/ihsg-berpotensi-melemah-pasar-wait-and-see-sentimen-global-domestik</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-02.jpg</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Baznas gandeng LPAI kolaborasi perlindungan anak keluarga prasejahtera</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:45:27 +0700</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Badan Amil Zakat Nasional (Baznas) RI bersama Lembaga Perlindungan Anak Indonesia (LPAI) bersinergi memperkuat ...</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688636/baznas-gandeng-lpai-kolaborasi-perlindungan-anak-keluarga-prasejahtera</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_091114.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Rupiah melemah seiring ketidakpastian geopolitik di Timur Tengah</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:39:12 +0700</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Analis mata uang Doo Financial Futures Lukman Leong mengatakan rupiah melemah seiring ketidakpastian geopolitik di ...</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688635/rupiah-melemah-seiring-ketidakpastian-geopolitik-di-timur-tengah</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/nilai-tukar-rupiah-melemah-44-poin-2821211.jpg</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Chris Evans bocorkan cerita Captain America pada film baru "Avengers"</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:34:35 +0700</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Aktor Chris Evans memberikan sedikit bocoran karakter dan cerita Steve Rogers alias Captain America ...</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688631/chris-evans-bocorkan-cerita-captain-america-pada-film-baru-avengers</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/11/09/Screenshot_2022-11-08-22-05-36-00_1c337646f29875672b5a61192b9010f9_copy_1024x683.jpg</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Pemimpin tertinggi Iran tunjuk 6 komandan militer baru</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:34:24 +0700</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Pemimpin Tertinggi Iran Mojtaba Khamenei telah menunjuk enam komandan militer baru untuk angkatan bersenjata negara ...</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688627/pemimpin-tertinggi-iran-tunjuk-6-komandan-militer-baru</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/19/CjkinzN000005_20260719_CBMFN0A001a.jpg</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Menaker: Budaya inovasi tingkatkan kualitas layanan ketenagakerjaan</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:30:38 +0700</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli mengatakan pembangunan budaya inovasi merupakan upaya penting untuk ...</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688623/menaker-budaya-inovasi-tingkatkan-kualitas-layanan-ketenagakerjaan</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/8247be16-8661-43de-ac65-33cb22ac4d85.jpeg</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Brimob Polda Metro Jaya evakuasi korban kecelakaan di Bekasi</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:30:06 +0700</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Tim Patroli Mobil (Patmob) Satuan Brigade Mobil (Brimob) Polda Metro Jaya mengevakuasi korban kecelakaan lalu lintas ...</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688620/brimob-polda-metro-jaya-evakuasi-korban-kecelakaan-di-bekasi</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000913040.jpg</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Terpopuler, Surpres Destry jadi Gubernur BI hingga gempa Kolombia</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:28:13 +0700</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Sejumlah berita unggulan Selasa untuk disimak, Prabowo kirim Surpres ke DPR ajukan Destry jadi Gubernur BI definitif ...</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688617/terpopuler-surpres-destry-jadi-gubernur-bi-hingga-gempa-kolombia</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Narasi_sp_2814926_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>ThinkPalm dan Singapore Polytechnic Kembangkan IIoT Berkelanjutan bagi UKM dan Perusahaan Rintisan</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:27:37 +0700</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>ThinkPalm Technologies adalah penyedia solusi teknologi dengan spesialisasi Industrial Internet of Things ...</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688616/thinkpalm-dan-singapore-polytechnic-kembangkan-iiot-berkelanjutan-bagi-ukm-dan-perusahaan-rintisan</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/ThinkPalm-and-Singapore-Polytechnic.jpg</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Trump isyaratkan AS masih siap tingkatkan eskalasi militer kepada Iran</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:26:47 +0700</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat (AS) Donald Trump, Senin (10/8) menolak mengatakan apa yang akan terjadi selanjutnya ...</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688612/trump-isyaratkan-as-masih-siap-tingkatkan-eskalasi-militer-kepada-iran</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/thumbs_b_c_2263c951fe4876ab38332a738c829d57-1.jpg</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Trump tuntut Iran bayar kompensasi atas "kekejaman" 50 tahun</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:26:32 +0700</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump, Senin (10/8), mengajukan tuntutan balik berupa kompensasi keuangan dari ...</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688611/trump-tuntut-iran-bayar-kompensasi-atas-kekejaman-50-tahun</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/thumbs_b_c_0faf781db807e5288836e40ddc754e72.jpg</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Anggota DPD dorong Pemprov DKI perkuat fiskal usai pemotongan DBH</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:25:48 +0700</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Anggota Dewan Perwakilan Daerah (DPD) RI dari Daerah Pemilihan (Dapil) DKI Jakarta, Dailami Firdaus mendorong ...</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688608/anggota-dpd-dorong-pemprov-dki-perkuat-fiskal-usai-pemotongan-dbh</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/06/Anggota_DPD_RI_Dailami_Firdaus.jpg</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Hadapi sidang perdana, Yaqut: Semua yang benar akan kelihatan</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:24:17 +0700</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Menteri Agama periode 2020-2024 Yaqut Cholil Qoumas mengaku sudah siap menjalani sidang perdana kasus dugaan korupsi ...</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688604/hadapi-sidang-perdana-yaqut-semua-yang-benar-akan-kelihatan</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/03/pemeriksaan-tersangka-ishfah-abidal-aziz-2816143.jpg</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>BGN berlakukan batas waktu konsumsi MBG maksimal 4 jam setelah matang</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:20:36 +0700</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) resmi memberlakukan batas waktu konsumsi Makan Bergizi Gratis (MBG) paling lambat empat jam ...</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688601/bgn-berlakukan-batas-waktu-konsumsi-mbg-maksimal-4-jam-setelah-matang</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Kepala-BGN-Sudaryono-MBG.jpg</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Panda raksasa Xing Mei rayakan ulang tahun ke-15 di Tianjin</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:17:27 +0700</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Kebun binatang di Resor Wisata Lembah Fotosintesis (Photosynthesis Valley Tourist Resort) di Kota Tianjin, China utara, ...</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688597/panda-raksasa-xing-mei-rayakan-ulang-tahun-ke-15-di-tianjin</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000004_20260811_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>China jadi pasar pariwisata dengan pertumbuhan tercepat di Turkiye</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:15:10 +0700</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Turkiye menerima hampir 245.000 pengunjung dari China pada paruh pertama (H1) tahun ini, menjadikan China sebagai pasar ...</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688595/china-jadi-pasar-pariwisata-dengan-pertumbuhan-tercepat-di-turkiye</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000003_20260811_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Pengamat nilai revisi UU PKH strategis perkuat keberlanjutan dana haji</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:11:10 +0700</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Revisi Undang-Undang Pengelolaan Keuangan Haji menjadi langkah strategis memperkuat keberlanjutan dana haji melalui ...</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688592/pengamat-nilai-revisi-uu-pkh-strategis-perkuat-keberlanjutan-dana-haji</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/1000445396.jpg</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Anggota DPR kecam promosi miras "Newport" dengan baca ayat Al Quran</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:08:41 +0700</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Anggota Komisi VI DPR RI Kawendra Lukistian mengecam keras promosi minuman keras (miras) beralkohol bermerek Newport ...</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688591/anggota-dpr-kecam-promosi-miras-newport-dengan-baca-ayat-al-quran</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/1000436529.jpg</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Mintoak Mengumumkan Akuisisi terhadap Perusahaan Fintech ICC Loyalty yang Berkantor Pusat di Timur Tengah</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:06:36 +0700</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Mintoak, sistem operasi (OS) pembayaran dan keterlibatan bagi acquirer, hari ini mengumumkan akuisisi ICC Loyalty, ...</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688587/mintoak-mengumumkan-akuisisi-terhadap-perusahaan-fintech-icc-loyalty-yang-berkantor-pusat-di-timur-tengah</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Mintoak-logo.jpg</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Netcore berganti nama menjadi Netcore.ai dan menjadi platform pemasaran berbasis AI agen pertama</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:03:36 +0700</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Netcore Cloud adalah perusahaan terdepan di dunia di bidang Teknologi Pemasaran (MarTech), Keterlibatan ...</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688583/netcore-berganti-nama-menjadi-netcoreai-dan-menjadi-platform-pemasaran-berbasis-ai-agen-pertama</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Netcore.ai.jpg</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Xiaomi 18 akan hadir dengan lima pilihan warna dan kamera ganda 200MP</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:58:15 +0700</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Xiaomi 18 dikabarkan akan hadir dengan lima pilihan warna, yakni hitam, putih, merah muda, biru, dan merah, berdasarkan ...</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688581/xiaomi-18-akan-hadir-dengan-lima-pilihan-warna-dan-kamera-ganda-200mp</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000142687.jpg</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Bukan Bunker, Ruangan TKP Temuan Senjata di Sekolah Jaksel Basemen</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:04:56 +0700</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Polisi mengungkap isi basement di sekolah swasta Jakarta, tempat ratusan senjata ditemukan. Penemuan ini terkait konflik internal yayasan.</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613292/bukan-bunker-ruangan-tkp-temuan-senjata-di-sekolah-jaksel-basemen</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363566_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Viral DC Gebuk Warga Bekasi Pakai Kursi Besi, Polisi Turun Tangan</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:03:21 +0700</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Video debt collector (DC) memukul warga di Bekasi menggunakan kursi besi viral di medsos. Polisi bergerak menangkap pelaku.</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613287/viral-dc-gebuk-warga-bekasi-pakai-kursi-besi-polisi-turun-tangan</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/video-debt-collector-dc-memukul-warga-di-bekasi-menggunakan-kursi-besi-viral-di-medsos-polisi-bergerak-menangkap-pelaku-dok-is-1786420915048_169.webp?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Demokrat Sebut SBY Tak Bisa Hadiri Sidang Tahunan: Sedang di Luar Negeri</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:54:49 +0700</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>SBY tak bisa menghadiri Sidang Tahunan MPR dan Sidang Bersama (STSB) DPR RI-DPD RI pada 14 Agustus 2026. Hal itu lantaran SBY tengah berada di luar negeri.</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613272/demokrat-sebut-sby-tak-bisa-hadiri-sidang-tahunan-sedang-di-luar-negeri</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/28/presiden-ke-6-ri-susilo-bambang-yudhoyono-dokistimewa-1782644586904_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Eks Menag Yaqut Didakwa Rugikan Negara Rp 622 M di Kasus Korupsi Kuota Haji</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:50:24 +0700</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Yaqut Cholil Qoumas didakwa merugikan keuangan negara sebesar Rp 622.090.207.166,41 (622 miliar) dalam kasus dugaan korupsi kuota haji tambahan tahun 2023-2024.</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613270/eks-menag-yaqut-didakwa-rugikan-negara-rp-622-m-di-kasus-korupsi-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/sidang-dakwaan-mantan-menteri-agama-yaqut-cholil-qoumas-di-kasus-korupsi-kuota-haji-muliadetikcom-1786420189458_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Pengedar Obat Keras Ilegal di Bogor Ditangkap, Simpan Ratusan Butir di Saung</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:41:07 +0700</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Polisi menangkap pria berinisial Y (22) di Kecamatan Gunung Putri, Bogor, Jawa Barat. Y ditangkap usai mengedarkan obat keras tanpa izin edar atau ilegal.</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613243/pengedar-obat-keras-ilegal-di-bogor-ditangkap-simpan-ratusan-butir-di-saung</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/polisi-menangkap-peria-berinisial-y-22-di-kecamatan-gunung-putri-bogor-jawa-barat-y-ditangkap-usai-mengedarkan-obat-keras-tanp-1786419565320_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Polisi: Sejumlah Airsoft Gun di Sekolah Jaksel dalam Kondisi Rusak-Tak Utuh</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:40:56 +0700</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Puslabfor Polri menyelidiki penemuan 996 senjata di sekolah swasta Jakarta. Temuan mencakup airsoft gun dan senapan angin, terkait konflik yayasan.</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613242/polisi-sejumlah-airsoft-gun-di-sekolah-jaksel-dalam-kondisi-rusak-tak-utuh</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363566_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Sempat Mangkir, Rudy Tanoesoedibjo Diperiksa KPK Terkait Korupsi Bansos 2020</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:40:23 +0700</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Adrial akbar</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Rudy Tanoesoedibjo, Komisaris Utama PT Dosni Roha, diperiksa KPK terkait dugaan korupsi bansos 2020 setelah sebelumnya absen</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613241/sempat-mangkir-rudy-tanoesoedibjo-diperiksa-kpk-terkait-korupsi-bansos-2020</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rudy-tanoesoedibjo-adrial-akbardetikcom-1786419607993_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>KPK Ungkap Selisih SGD 2 Ribu di Amplop Bupati Kuansing untuk Menhut</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:19:20 +0700</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>KPK menyelidiki selisih uang SGD 2 ribu dalam amplop dari Bupati Kuansing Suhardiman Amby untuk Menteri Kehutanan Raja Juli Antoni</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613216/kpk-ungkap-selisih-sgd-2-ribu-di-amplop-bupati-kuansing-untuk-menhut</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/22/jumpa-pers-kpk-1784716930554_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Ugal-ugalan Naik Motor di Bogor, Gerombolan Pemuda Diamankan Polisi</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:17:03 +0700</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Polisi mengamankan sejumlah pemuda yang mengendarai motor ugal-ugalan di wilayah Cileungsi, Bogor, Jabar. Mereka diamankan saat polisi menggelar patroli malam.</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613214/ugal-ugalan-naik-motor-di-bogor-gerombolan-pemuda-diamankan-polisi</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/gerombolan-pemuda-dan-sepeda-motornya-diamankan-polisi-usai-kedapatan-ugal-ugalan-di-bogor-1786418148723_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Yaqut Mohon Doa Jelang Sidang Dakwaan: Semua yang Benar Akan Kelihatan</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:07:52 +0700</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Mantan Menag Yaqut Cholil Qoumas siap menjalani sidang dakwaan korupsi kuota haji 2023-2024. Dia berharap keadilan dan memohon doa untuk proses hukum ini.</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613201/yaqut-mohon-doa-jelang-sidang-dakwaan-semua-yang-benar-akan-kelihatan</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/mantan-menag-yaqut-cholil-qoumas-1786417604158_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Efek El Nino, Juli Tahun Ini Suhunya Paling Tinggi Sejak 1991</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:56:18 +0700</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Rakhmad Hidayatulloh Permana</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menyatakan bahwa suhu di bulan Juli tahun ini menjadi yang terpanas sejak 1991.</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613183/efek-el-nino-juli-tahun-ini-suhunya-paling-tinggi-sejak-1991</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/16/ilustrasi-kekeringan-sebagai-dampak-el-nino-freepik-1776310365501_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>UMKM Sudah Dikasih Modal, Kok Bisa Mati? Menteri UMKM: Pasar RI Becek</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:10:26 +0700</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Menteri UMKM Maman Abdurrahman mengungkapkan tantangan produk UMKM di pasar domestik yang 'becek'. Akses pembiayaan meningkat, namun penjualan tetap rendah.</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613295/umkm-sudah-dikasih-modal-kok-bisa-mati-menteri-umkm-pasar-ri-becek</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/maman-abdurrahman-1786421014136_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Kemnaker Umumkan 46 Ribu Peserta Lolos Program Magang Nasional</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:40:07 +0700</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) resmi menetapkan 46.160 lulusan perguruan tinggi sebagai peserta Program Pemagangan Nasional 2026 batch 1 angkatan kedua.</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613240/kemnaker-umumkan-46-ribu-peserta-lolos-program-magang-nasional</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/24/ilustrasi-jam-kerja-1771920794834_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Pembiayaan UMKM Tembus Rp 1.948 T, Tapi Banyak yang Masih Sulit Dapat Kredit</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:03:03 +0700</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>OJK mencatat pembiayaan UMKM mencapai Rp 1.948 triliun pada Juni 2026, tumbuh 2,16% yoy. Sektor jasa keuangan berperan penting dalam pertumbuhan ini.</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8613196/pembiayaan-umkm-tembus-rp-1-948-t-tapi-banyak-yang-masih-sulit-dapat-kredit</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/ojk-1786417223889_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Batang Pinang Mulai Diburu Jelang Perayaan HUT RI</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:53:04 +0700</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Ari Saputra</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Menjelang HUT ke-81 Kemerdekaan RI, permintaan batang pinang untuk perlombaan mulai meningkat. Satu batang sepanjang 9 meter dijual mulai Rp800 ribu.</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8612692/batang-pinang-mulai-diburu-jelang-perayaan-hut-ri</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/batang-pinang-mulai-diburu-jelang-perayaan-hut-ri-1786362154601.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Aldi Taher Ngaku Aksi Peluk Vokalis Jet Norak: Saya Minta Maaf</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:01:47 +0700</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Aldi Taher akhirnya minta maaf usai memeluk vokalis Jet, Nic Cester, menjadi sorotan dan viral.</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613263/aldi-taher-ngaku-aksi-peluk-vokalis-jet-norak-saya-minta-maaf</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/aldi-taher-1786345749787_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Jangan Diganggu! Ayu Ting Ting Benar-benar Lagi Kasmaran dengan Kevin</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:12:11 +0700</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Ayu Ting Ting mulai terbuka soal hubungan dengan kekasihnya, Kevin Gusnadi. Ayu gak sungkan mengumbar chat pribadi dengan Kevin ke TikTok miliknya.</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612348/jangan-diganggu-ayu-ting-ting-benar-benar-lagi-kasmaran-dengan-kevin</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/22/ayu-ting-ting-dan-kevin-gusnadi-1784708477228_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Kasus Kematian Sutrimo Naik ke Penyidikan, Pakar Hukum Pidana: Belum Tentu Ada Tersangka</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:11:11 +0700</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Kasus kematian Sutrimo telah naik dari tahap penyelidikan ke penyidikan setelah polisi menemukan dugaan kuat adanya tindak pidana.</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866737/kasus-kematian-sutrimo-naik-ke-penyidikan-pakar-hukum-pidana-belum-tentu-ada-tersangka</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/CwMUyzUp6Ng_C-qMpDr5muWU_Ls=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/klinik-Mordent-Esthetic-Clinic-TKP-Sutrimo-Tewas.jpg</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Update Transfer Al Nassr: Cuma Satu Pemain yang Masuk, Lima Pemain Dilepas</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:08:46 +0700</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Hingga jelang bergulirnya Liga Arab Saudi musim 2026/2027, Al Nassr baru mendatangkan satu pemain, sementara lima pemain tercatat meninggalkan tim.</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866736/update-transfer-al-nassr-cuma-satu-pemain-yang-masuk-lima-pemain-dilepas</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Cyib7FLfUSF10TPgO8ouC9PoF_0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Logo-klub-Liga-Arab-Saudi-Al-Nassr.jpg</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPS Kelas 7 Halaman 87 Kurikulum Merdeka Edisi Revisi: Aktivitas 7</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:07:07 +0700</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Berikut ini kunci jawaban mata pelajaran IPS Kelas 7 Halaman 87 Kurikulum Merdeka terdapat tugas Aktivitas 7 pada Tema 2.</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7866735/kunci-jawaban-ips-kelas-7-halaman-87-kurikulum-merdeka-edisi-revisi-aktivitas-7</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/FBmkDqYmlx5UM0pD7_3NuyX3Hwc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/SISWA-SMP-BELAJAR-10.jpg</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Profil dan Jejak Karier Brigjen Pol Sumy Hastry, Pakar DNA Forensik Polri untuk Penegakan Hukum</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:02:40 +0700</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>DNA forensik jadi metode penting penegakan hukum modern, akurasi 99,99 persen dalam identifikasi pelaku, korban, dan bukti.</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866734/profil-dan-jejak-karier-brigjen-pol-sumy-hastry-pakar-dna-forensik-polri-untuk-penegakan-hukum</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/aGQjJ57jktI54Ie7U72wM1e6cxc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/foto-Brigjen-Pol-dr-Sumy-Hastry-Purwanti.jpg</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Kunci Gitar Ini Laguku - Mahalini, Viral TikTok: Bukalah Hatimu Lihat Diriku Ku Takkan Mampu Tanpamu</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:01:16 +0700</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Simak kunci gitar dan lirik lagu berjudul Ini Laguku oleh penyanyi Mahalini dalam artikel berikut ini.</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7866733/kunci-gitar-ini-laguku-mahalini-viral-tiktok-bukalah-hatimu-lihat-diriku-ku-takkan-mampu-tanpamu</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ZHxbO-t47vCc01kbLIoktyItJ_Y=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Bukan-diet-Mahalini-jelaskan-penyebab-berat-badannya-turun-drastis-pasca-melahirkan.jpg</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Ashmita Chaliha Balikkan Nasib di Negeri Ginseng, Cedera 2024 Dibayar dengan Gelar Korea Masters</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:01:07 +0700</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Ashmita Chaliha mengubah tempat yang pernah menjadi saksi cedera parahnya menjadi panggung gelar BWF World Tour pertamanya.</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866732/ashmita-chaliha-balikkan-nasib-di-negeri-ginseng-cedera-2024-dibayar-dengan-gelar-korea-masters</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/QhDxIQRuYpyCtNPwG67A0UB4SsM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ashmita-Chaliha-Juara-Korea-Masters-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Momen Seskab Teddy Indra Wijaya Janji Belikan Sepatu dan Baju Baru untuk Peserta Magang</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:59:31 +0700</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Momen Seskab Teddy Indra Wijaya memberikan bantuan perlengkapan kerja baru kepada satu di antara peserta magang bernama Ferdian.</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866731/momen-seskab-teddy-indra-wijaya-janji-belikan-sepatu-dan-baju-baru-untuk-peserta-magang</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/cZ_Aselag556l70Wywk3ybxXiVM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Letkol-Teddy-Indra-Wijaya-JANJI-BERI-SEPATU.jpg</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Segera Dibersihkan, Sekolah Penyimpanan Ratusan Senjata di Jaksel Akan Digunakan untuk Belajar</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:57:32 +0700</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Menurut Kepala Staf Ahli Pembina Yayasan, Untung Sangaji, pembersihan akan dilakukan dalam satu hingga dua hari ke depan.</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866730/segera-dibersihkansekolah-penyimpan-ratusan-senjata-di-jaksel-akan-digunakan-untuk-belajar</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c23bmk4PHY76ZCmOECtNP5j3wK4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ratusan-senjata-api-di-sekolah-swasta-Pondok-Pinang-Kebayoran-Lama-Jakarta-Selatan.jpg</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Brand Miras hingga EO Dilaporkan ke Polda Metro Jaya usai Viral Challenge Baca Alquran Dapat Miras</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:56:58 +0700</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Advokat melaporkan lima pihak pasca viralnya video challenge membaca Alquran dengan imbalan miras gratis yaitu dari EO, brand miras, hingga MC.</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866729/brand-miras-hingga-eo-dilaporkan-ke-polda-metro-jaya-usai-viral-challenge-baca-alquran-dapat-miras</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/jAjjvGFhY8GK348a-BKvSxJo6MU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Gedung-Polda-Metro-Jaya-di-Kuningan.jpg</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Film Kung Fu Soccer Tayang Perdana di Bioskop Mulai 12 Agustus 2026, Ini Sinopsis dan Pemainnya</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:56:23 +0700</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Film Kung Fu Soccer tayang perdana di bioskop mulai 12 Agustus 2026, berikut sinopsis, daftar pemain, dan jadwal tayangnya di bioskop.</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866728/film-kung-fu-soccer-tayang-perdana-di-bioskop-mulai-12-agustus-2026-ini-sinopsis-dan-pemainnya</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/741UGGMgGbJJbaYqHX_Ljju216w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Film-Bioskop-Ilustrasi.jpg</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Bigmo Janji Evaluasi Konten Usai Diperiksa Polisi, Ingin Lebih Positif dan Edukatif</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:54:37 +0700</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Youtuber Muhammad Jannah atau Bigmo berjanji melakukan evaluasi terhadap konten-konten yang selama ini dibuatnya.</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866727/bigmo-janji-evaluasi-konten-usai-diperiksa-polisi-ingin-lebih-positif-dan-edukatif</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/kVJ1JVg63OmX06VPzX6uBJAdK7g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bigmo-apa.jpg</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Suami Tersandung Kasus Korupsi Kuota Haji, Istri Yaqut: Ikhtiar Lahir dan Batin Beri Dukungan</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:52:35 +0700</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Istri dari eks Menag Yaqut Cholil Qoumas, Eny Retno Purwaningtyas ngaku memberi dukungan ke suami yang terjerat kasus dugaan korupsi kuota haji.</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866726/suami-tersandung-kasus-korupsi-kuota-haji-istri-yaqut-ikhtiar-lahir-dan-batin-beri-dukungan</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/B1Y_MhHIR5JtMcW4AJWoh8pmaTI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Yaqut-Cholil-Qoumas-bersama-istrinya.jpg</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Lenovo Rilis Lecoo P900A, Bawa Layar 8 Inci 4G dengan Harga Rp2 Jutaan</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:50:57 +0700</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Lenovo merilis tablet Lecoo P900A di China. Tablet ini membawa layar 8 Inci dan konektivitas 4G dengan harga Rp2 jutaan. Berikut spesifikasi lainnya.</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/techno/7866725/lenovo-rilis-lecoo-p900a-bawa-layar-8-inci-4g-dengan-harga-rp2-jutaan</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yEjAfnVNk07YDUX0lvWbgvwTiN0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/TABLET-LENOVO-TERBARU-456546543.jpg</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Ratu Voli Korea Kim Yeon-koung Raih Penghargaan AVC, Idola Megawati Tetap Eksis Meski Sudah Pensiun</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:50:35 +0700</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Kim Yeon-koung tetap eksis usai pensiun dengan meraih penghargaan AVC, legenda voli Korea itu merupakan idola Megawati Hangestri.</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866724/ratu-voli-korea-kim-yeon-koung-raih-penghargaan-avc-idola-megawati-tetap-eksis-meski-sudah-pensiun</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/myY8FQfwoxHyKgtANUnLHSCnE-8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kim-yeon-koung-vs-red-sparks-play-off-liga-voli-korea.jpg</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Pakar Soroti Kemungkinan Relasi Sutrimo Selain dengan Febrie Adriansyah, Singgung Santunan Rp20 Juta</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:49:35 +0700</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Pakar Hukum Pidana, Abdul Fickar Hadjar, menyoroti kemungkinan relasi Sutrimo dengan pihak lain.</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866723/pakar-soroti-kemungkinan-relasi-sutrimo-selain-dengan-febrie-adriansyah-singgung-santunan-rp20-juta</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/CwMUyzUp6Ng_C-qMpDr5muWU_Ls=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/klinik-Mordent-Esthetic-Clinic-TKP-Sutrimo-Tewas.jpg</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Belanja Makin Hemat Pakai Cicilan BRI Kartu Kredit: Bunga Mulai 0 Persen Transaksi Minimal 100 Ribu</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:46:28 +0700</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Program Cicilan BRI Kartu Kredit hadirkan bunga mulai 0 persen dengan transaksi minimal Rp100 ribu, dan tenor hingga 36 bulan.</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866722/belanja-makin-hemat-pakai-cicilan-bri-kartu-kredit-bunga-mulai-0-persen-transaksi-minimal-100-ribu</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yWO7joEKOirtd82XLQdurmemWA4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Program-Cicilan-BRI-Kartu-Kredit-Kini-Tawarkan-Bunga-Lebih-Ringan.jpg</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Tak Lagi Antre di Kantor, Dhia Rasakan Praktisnya Layanan Digital JKN</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:46:19 +0700</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Melalui aplikasi Mobile JKN, mengurus administrasi kepesertaan kini semakin mudah karena tidak harus mengunjungi kantor cabang.</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866721/tak-lagi-antre-di-kantor-dhia-rasakan-praktisnya-layanan-digital-jkn</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/3C8fI2mXM1RO-fMK1Ubz4ybQybI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Dhia-peserta-JKN-asal-Jember.jpg</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Polisi di Palembang Dibegal saat Kerja Sampingan Ngojek, Alami 4 Luka Tusuk, 3 Pelaku Ditangkap</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:45:53 +0700</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Polrestabes Palembang menangkap tiga pelaku pembegalan terhadap anggota Biddokkes Polda Sumsel, Aiptu JE, yang nyambi sebagai tukang ojek pangkalan.</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866720/polisi-di-palembang-dibegal-saat-kerja-sampingan-ngojek-alami-4-luka-tusuk-3-pelaku-ditangkap</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/XfV5WTRcxonxe_AAIRL1RRXJanY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pelaku-begal-polisi-di-palembang.jpg</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Aurel Hermansyah Dikabarkan Hamil Anak Ketiga, Atta Halilintar: Ada Saatnya Kita Kasih Tahu</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:43:36 +0700</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Aurel Hermansyah dikabarkan hamil anak ketiga, sang suami Atta Halilintar mengaku akan mengumumkan kabar bahagia tersebut pada waktu yang tepat.</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866719/aurel-hermansyah-dikabarkan-hamil-anak-ketiga-atta-halilintar-ada-saatnya-kita-kasih-tahu</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/xeFwaIRJoXXe7Bqd6QzU_Ho2P54=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/aurel-hermansyah-1-120724.jpg</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Trump Balik Tuntut Iran Bayar Ganti Rugi Perang, Negosiasi Perdamaian Timur Tengah Terancam Gagal</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:43:04 +0700</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Trump balik menuntut Iran membayar ganti rugi perang sebagai balasan atas tuntutan Teheran. Langkah ini dinilai membuat negosiasi damai makin sulit</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866718/trump-balik-tuntut-iran-bayar-ganti-rugi-perang-negosiasi-perdamaian-timur-tengah-terancam-gagal</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/pd58Lh0QZkuUPrM04LfPl7UxG4o=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/residen-AS-Donald-Trump-Senin-27-Juli-2026-Foto-Res.jpg</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Calon Raja Jalanan Baru RI, Mobil Ini Laku Keras di GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>GIIAS 2026 sukses, mobil ini paling laku dengan raih 3.290 SPK, jadi primadona dan calon raja jalanan RI.</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811102329-4-758182/calon-raja-jalanan-baru-ri-mobil-ini-laku-keras-di-giias-2026</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/29/aira-ev-1785334266165_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Video: Ramai Isu Pungutan Pajak untuk Rumah Kontrakan, DJP Buka Suara</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:59:17 +0700</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Direktorat Jenderal Pajak, Kementerian Keuangan, menjelaskan rencana pemungutan pajak kepada pemilik rumah kontrakan pada 2027.</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811100617-8-758170/video-ramai-isu-pungutan-pajak-untuk-rumah-kontrakan-djp-buka-suara</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/ramai-isu-pungutan-pajak-untuk-rumah-kontrakan-djp-buka-suara-1786417655217_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Video: Ompreng MBG Akan Ditempeli Label Batas Konsumsi Pekan Depan</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:49:38 +0700</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) akan memberikan label batas waktu konsumsi pada setiap ompreng Makan Bergizi Gratis (MBG) mulai pekan depan.</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811100438-8-758168/video-ompreng-mbg-akan-ditempeli-label-batas-konsumsi-pekan-depan</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/ompreng-mbg-akan-ditempeli-label-batas-konsumsi-pekan-depan-1786417546167_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Mendagri Blak-blakan Soal 3 Jurus Penyelamat ASN di Daerah</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:45:56 +0700</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Emir Yanwardhana</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Pemerintah siapkan tiga skema untuk bantu Pemda bayar gaji PPPK. Efisiensi anggaran, penyaluran DBH, dan tambahan DAU jadi solusi untuk masalah fiskal.</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811103556-4-758183/mendagri-blak-blakan-soal-3-jurus-penyelamat-asn-di-daerah</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/22/menteri-dalam-negeri-mendagri-muhammad-tito-karnavian-1784725668894_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Freeport Punya Proyek Tambang Bawah Tanah Baru, Beroperasi di 2029</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:40:05 +0700</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>PT Freeport Indonesia menargetkan tambang Kucing Liar beroperasi tahun 2029.</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811100902-4-758172/freeport-punya-proyek-tambang-bawah-tanah-baru-beroperasi-di-2029</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/presiden-direktur-pt-freeport-indonesia-ptfi-tony-wenas-1786101675207_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Video: Calon Deputi Gubernur Senior BI Akan Diumumkan Oleh DPR</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:39:34 +0700</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Prasetyo Hadi mengungkapkan nama Deputi Gubernur Senior Bank Indonesia akan diumumkan langsung oleh DPR RI.</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811084152-8-758150/video-calon-deputi-gubernur-senior-bi-akan-diumumkan-oleh-dpr</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/calon-deputi-gubernur-senior-bi-akan-diumumkan-oleh-dpr-1786417446009_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Resmi Berlaku! MBG Wajib Habis Maksimal 4 Jam dan Dilarang Dibawa Pulang</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional memberlakukan aturan baru untuk program Makan Bergizi Gratis, mewajibkan konsumsi makanan dalam 4 jam setelah matang.</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811101436-4-758177/resmi-berlaku-mbg-wajib-habis-maksimal-4-jam-dilarang-dibawa-pulang</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/11/26/uji-coba-program-makan-bergizi-gratis-mbg-di-sds-angkasa-5-lanud-halim-perdanakusuma-jakarta-selasa-26112024-cnbc-indonesiamuh-1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>ETF Emas Resmi Meluncur, Pemerintah Kaji Pemberian Insentif Pajak</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:29:42 +0700</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Indonesia telah meluncurkan produk Exchange Traded Fund berbasis emas pada Senin, 10 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811100943-8-758173/etf-emas-resmi-meluncur-pemerintah-kaji-pemberian-insentif-pajak</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/etf-emas-resmi-meluncur-pemerintah-kaji-pemberian-insentif-pajak-1786417877724_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Video: Para Pejabat Sambut Baik Calon Tunggal Gubernur BI Definitif</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:29:26 +0700</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Sejumlah pejabat negara menyambut baik pencalonan tunggal Destry Damayanti sebagai Gubernur Bank Indonesia definitif.</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811083952-8-758149/video-para-pejabat-sambut-baik-calon-tunggal-gubernur-bi-definitif</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/para-pejabat-sambut-baik-calon-tunggal-gubernur-bi-definitif-1786417375686_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Video: Cadangan Minyak AS Tembus Level Terendah Dalam 4 Dekade</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:19:14 +0700</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Cadangan minyak strategis Amerika Serikat atau Strategic Petroleum Reserve turun di bawah 300 juta barel.</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811083847-8-758147/video-cadangan-minyak-as-tembus-level-terendah-dalam-4-dekade</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/cadangan-minyak-as-tembus-level-terendah-dalam-4-dekade-1786417240017_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Video: Trump Tunggu Ekonomi Iran Makin Tertekan</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:09:05 +0700</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Trump mengisyaratkan kesiapannya untuk membiarkan tekanan ekonomi semakin menghantam Iran ketimbang melancarkan serangan militer</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811083726-8-758146/video-trump-tunggu-ekonomi-iran-makin-tertekan</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/trump-tunggu-ekonomi-iran-makin-tertekan-1786417169776_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Eks Anggota Dewan Tembak Pejabat Pemda Gara-Gara Utang, Didor di Mobil</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Mantan anggota parlemen Thailand diduga menembak mati pejabat pemerintah Nonthaburi akibat sengketa utang. Perdana Menteri mengecam tindakan tersebut.</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811081723-4-758141/eks-anggota-dewan-tembak-pejabat-pemda-gara-gara-utang-didor-di-mobil</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/petugas-memeriksa-lokasi-penembakan-setelah-mantan-anggota-parlemen-chalong-riewrang-diduga-menembak-thongchai-yenprasert-pres-1786408168208_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Video: Gempa M7,4 Mengguncang Kolombia, 111 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:58:49 +0700</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Gempa bumi berkekuatan magnitudo 7,4 mengguncang Kolombia pada Senin waktu setempat</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811083623-8-758145/video-gempa-m74-mengguncang-kolombia-111-orang-tewas</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/gempa-m74-mengguncang-kolombia-111-orang-tewas-1786417122563_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Trump Siapkan 'Mesin Pembunuh Baru' Iran, Selat Hormuz Makin Ngeri</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>tfa</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Presiden Trump mengubah strategi terhadap Iran, mengandalkan tekanan ekonomi. Di sisi lain, apakah Selat Hormuz dibuka kembali juga belum pasti.</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811080844-4-758138/trump-siapkan-mesin-pembunuh-baru-iran-selat-hormuz-makin-ngeri</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/06/bendera-amerika-yang-dibakar-oleh-para-pelayat-berkobar-di-dekat-papan-bertuliskan-presiden-as-donald-trump-saat-orang-orang-b-1783346636932_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Bansos di 143 Daerah Mulai Pakai Sistem Digital, Begini Skemanya</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:45:10 +0700</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Pemerintah akan mulai menerapkan penyaluran program perlinsos menggunakan sistem e-governement bulan ini</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811093030-4-758161/bansos-di-143-daerah-mulai-pakai-sistem-digital-begini-skemanya</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/04/06/fakta-sidang-mk-bantuan-pangan-ri-kalah-dari-singapura-malaysia-1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>PT Garam dan ACWA Power Berkolaborasi Garap Proyek di Gresik</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Elga Nurmutia</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>PT Garam dan ACWA Power tandatangani JDA untuk proyek desalinasi dan produksi garam di Gresik. Kerja sama ini dorong transformasi industri garam nasional.</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811092640-4-758162/pt-garam-dan-acwa-power-berkolaborasi-garap-proyek-di-gresik</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/pt-garam-dan-acwa-power-kolaborasi-garap-proyek-di-gresik-1786415661845_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Heboh Fenomena Semburan Lumpur di Blora, Ini Penjelasan Badan Geologi</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Penjelasan Badan Geologi Kementerian ESDM terkait semburan lumpur di Blora</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811075059-4-758137/heboh-fenomena-semburan-lumpur-di-blora-ini-penjelasan-badan-geologi</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/07/31/bendungan-mursapa-yang-menyusut-saat-musim-kemarau-berkepanjangan-di-desa-pucung-kidul-kedungtuban-kecamatan-kedungtuban-kabup-7_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Hancur Lebur, Potret 'Gempa Terkuat Abad 21' Guncang Kolumbia</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Setidaknya 111 orang tewas setelah gempa bumi dahsyat mengguncang Kolumbia. Gempa itu disebut "terkuat selama abad-21" di negeri itu.</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811065833-7-758110/hancur-lebur-potret-gempa-terkuat-abad-21-guncang-kolumbia</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/suasana-setelah-gempa-bumi-di-dosquebradas-kolombia-senin-1082026-reutersjuan-david-duque-1786405982899_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Bukan Rp10.000 per Liter, Ini Harga Sebenarnya BBM Pertalite</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Harga asli BBM Pertalite jika tak disubsidi pemerintah</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811073427-4-758135/bukan-rp10000-per-liter-ini-harga-sebenarnya-bbm-pertalite</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/10/antrean-pembeli-bahan-bakar-minyak-bbm-jenis-pertalite-di-ciputat-raya-tangerang-selatan-rabu-1062026-malam-1781104170814_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Perhatian! Harga Minyak Mentah RI (ICP) Turun Jadi US$81,68 per Barel</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Harga minyak mentah RI atau ICP pada Juli turun jadi US$ 81,68 per barell</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811072214-4-758126/perhatian-harga-minyak-mentah-ri--icp--turun-jadi-us-8168-per-barel</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/11/17/blok-minyak-dan-gas-bumi-migas-yang-dioperasikan-pt-pertamina-hulu-energi-phe-1763344161408_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>1.147 Pasukan Siaga! Paspampres Kerahkan Alutsista Jelang HUT RI</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Paspampres siapkan 1.147 personel untuk amankan rangkaian HUT ke-81 RI, didukung alutsista dan sistem antidrone guna mengantisipasi berbagai ancaman.</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810184651-7-758072/1147-pasukan-siaga-paspampres-kerahkan-alutsista-jelang-hut-ri</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/komandan-pasukan-pengamanan-presiden-danpaspampres-mayjen-tni-dr-edwin-adrian-sumantha-memimpin-apel-gelar-kesiapan-pasukan-sa-1786362408759_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Tambang Ilegal Ditertibkan, Produksi PT Timah Jadi Meningkat</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Produksi timah PT Timah meningkat pasca penertiban tambang ilegal di Bangka Belitung</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811070732-4-758122/tambang-ilegal-ditertibkan-produksi-pt-timah-jadi-meningkat</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2019/07/27/33cc238d-2985-466b-a07c-4a48707453bf_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Verifikasi BPHTB Dipercepat Jadi 3 Hari, Balik Nama Maksimal 10 Hari</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:10:30 +0700</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Elga Nurmutia</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Menteri ATR/BPN Nusron Wahid dan Mendagri Tito Karnavian tandatangani SEB untuk percepatan verifikasi BPHTB, targetkan proses Peralihan Hak maksimal 10 hari.</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811073330-4-758128/verifikasi-bphtb-dipercepat-jadi-3-hari-balik-nama-maksimal-10-hari</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/11/17/menteri-atr-kepala-bpn-nusron-wahid-1763356989299_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Kim Jong Un Ngamuk! Korea Utara Tiba-Tiba Murka ke Jepang</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Korea Utara (Korut) mengecam buku putih pertahanan Jepang 2026, menuduhnya sebagai rencana invasi ulang. Ketegangan militer di Asia Timur semakin meningkat.</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811070731-4-758119/kim-jong-un-ngamuk-korea-utara-tiba-tiba-murka-ke-jepang</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/06/14/e841c426-5e70-4f37-8e49-5c8b23932276_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>DJP Tegaskan Tak Ada Agenda Tarik Pajak Rumah Kontrakan di 2027</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>DJP menegaskan tidak ada pajak baru untuk rumah kontrakan pada 2027. Penghasilan sewa properti sudah dikenakan Pajak Penghasilan sesuai ketentuan yang berlaku.</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811072004-4-758124/djp-tegaskan-tak-ada-agenda-tarik-pajak-rumah-kontrakan-di-2027</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/11/17/gedung-kementerian-keuangan-ri-direktorat-jenderal-pajak-selasa-17112025-1763361291730_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Reformasi Presiden Bikin Investor Gembira, tapi Rakyat Masih Menjerit</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Reformasi ekonomi Presiden Nigeria Tinubu mulai menunjukkan hasil, namun jutaan warga masih berjuang dengan lonjakan biaya hidup dan kemiskinan yang meningkat.</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810210324-4-758097/reformasi-presiden-bikin-investor-gembira-tapi-rakyat-masih-menjerit</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/12/para-demonstran-melakukan-unjuk-rasa-memperingati-hari-demokrasi-di-abuja-nigeria-jumat-1262026-1781269525927_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Hore! PNS-PPPK Daerah Cek Rekening, Gaji Sudah Ditransfer Purbaya</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Emir Yanwardhana</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Pemerintah Pusat telah resmi mengirimkan dana bantuan kepada pemerintah daerah untuk keperluan belanja pegawai</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811054843-4-758106/hore-pns-pppk-daerah-cek-rekening-gaji-sudah-ditransfer-purbaya</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/01/30/sah-jokowi-resmi-naikkan-gaji-pns_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Gempa "Terkuat Bumi Abad 21" Guncang Kolombia M 7,4, 111 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>tfa</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Gempa magnitudo 7,4 mengguncang Kolombia, menewaskan 111 orang dan melukai 87 lainnya. Banyak bangunan runtuh, pemerintah aktif dalam penanggulangan bencana.</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811004837-4-758108/gempa-terkuat-bumi-abad-21-guncang-kolombia-m-74-111-orang-tewas</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/03/28/ilustrasi-gempa-getty-imagesistockphotopetrovich9_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Turki, Arab Saudi dan Pakistan Bikin 'NATO Islam', Ada Apa?</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:38:39 +0700</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>sef</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Turki, Arab Saudi, dan Pakistan menandatangani pakta pertahanan Mekkah, menciptakan aliansi strategis baru di Timur Tengah.</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811062928-4-758107/turki-arab-saudi-pakistan-bikin-nato-islam-ada-apa</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/arab-saudi-turki-dan-pakistan-bentuk-nato-islam-1786345043372_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Ancaman China Membayangi, Sirene Serangan hingga Tank Dikerahkan</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Taiwan menggelar latihan perang Han Kuang dengan sirene serangan, tank dan simulasi gangguan internet untuk menghadapi ancaman serangan China.</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810182054-7-758060/ancaman-china-membayangi-sirene-serangan-hingga-tank-dikerahkan</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/para-prajurit-berpartisipasi-dalam-misi-pertahanan-untuk-sebuah-pelabuhan-vital-selama-latihan-militer-tahunan-han-kuang-di-yi-1786360844437_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Banjir Terjang Tetangga RI, Warga Nekat Terobos Air Setinggi Pinggang</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Banjir akibat Habagat merendam Manila hingga setinggi pinggang. Sekitar 110 ribu keluarga terdampak, sementara rumah dan toko ikut terendam.</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810210042-7-758098/banjir-terjang-tetangga-ri-warga-nekat-terobos-air-setinggi-pinggang</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/warga-yang-membawa-barang-barang-mereka-berjalan-menerjang-banjir-di-sebuah-desa-di-tengah-hujan-monsun-barat-daya-di-bagong-s-1786370053193_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Transaksi BNIdirect Tumbuh 17 Persen, Tembus Rp6.039 Triliun hingga Juni</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:09:35 +0700</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Volume transaksi BNIdirect mencapai Rp6.039 triliun hingga akhir Juni 2026, tumbuh 17 persen secara tahunan. Pertumbuhan transaksi tersebut terjadi seiring jumlah pengguna BNIdirect yang telah mencapai 280 ribu...</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjl7jz416/transaksi-bnidirect-tumbuh-17-persen-tembus-rp6039-triliun-hingga-juni</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/032112300-1653646741-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>RANS Gandeng Mayora Lagi, Nilai Kerja Sama Masih Dirahasiakan</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:02:42 +0700</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- PT RANS Entertainment Indonesia Tbk (RANS) dan Mayora Group memperpanjang kemitraan yang telah berjalan sejak 2019. Kolaborasi terbaru keduanya mencakup pengembangan berbagai kekayaan intelektual (intellectual property/IP) RANS,...</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjl5xm416/rans-gandeng-mayora-lagi-nilai-kerja-sama-masih-dirahasiakan</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/konferensi-pers-kolaborasi-strategis-rans-entertainment-indonesia-dengan-mayora_260811110152-303.jpeg</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Maknai Kemerdekaan, Danantara Melalui BRILink Agen Buka Akses dan Gerakkan Ekonomi Negeri</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:53:42 +0700</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Ferry kisihandi</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Di balik denyut nadi perekonomian yang berputar di setiap sudut desa, BRI terus menghadirkan layanan keuangan yang semakin dekat dengan masyarakat. 
+Melalui jaringan BRILink Agen, BRI...</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjl6ti472/maknai-kemerdekaan-danantara-melalui-brilink-agen-buka-akses-dan-gerakkan-ekonomi-negeri</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/transformasi-brilink-agen-terus-berkembang-kini-agen-telah-bertransformasi_260811105227-270.jpeg</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Kemenhub Luncurkan ETLE HUB Dukung Implementasi Zero ODOL 2027</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:51:30 +0700</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Direktur Jenderal Perhubungan Darat Aan Suhanan mengatakan Electronic Traffic Law Enforcement atau ETLE HUB merupakan sistem digital terintegrasi yang dikembangkan untuk menghubungkan berbagai sumber data dalam mendukung...</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjl6pu423/kemenhub-luncurkan-etle-hub-dukung-implementasi-zero-odol-2027</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/075082300-1751439158-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Prediksi Penjualan Aira EV di GIIAS 2026 Tembus 2.000 Unit Terbukti</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:30:39 +0700</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Israr Itah</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Prediksi Republika terhadap penjualan Aira EV yang diperkirakan dapat menembus 2.000 unit selama GAIKINDO Indonesia International Auto Show (GIIAS) 2026 akhirnya terbukti. City car listrik terbaru Wuling...</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjl5r3348/prediksi-penjualan-aira-ev-di-giias-2026-tembus-2000-unit-terbukti</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/marketing-director-wuling-motors-ricky-christian-saat-mengumumkan-harag_260729201044-694.JPG</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Harga Emas Antam Naik Rp 20.000, Tembus Rp 2,71 Juta per Gram</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:19:43 +0700</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Harga emas Antam yang dipantau dari laman Logam Mulia di Jakarta, Selasa (11/8/2026), pukul 9.36 WIB, naik Rp 20.000 ke angka Rp 2.710.000 dari semula Rp 2.690.000 per...</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjl58v423/harga-emas-antam-naik-rp-20000-tembus-rp-271-juta-per-gram</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/073341200-1767769494-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Siswi Tewas Tertemper KRL di Jurangmangu Sudah Dimakamkan</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Penyelidikan kasus tewasnya siswi AP, 14 tahun, yang tertemper KRL di Stasiun Jurangmangu, Tangerang Selatan, terus berlanjut.</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266834/siswi-tewas-tertemper-krl-di-jurangmangu-sudah-dimakamkan</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/Ev4ehAMF7-zR9tHbIitqZM4nMSo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320952/original/034209300_1786420367-email-attachment_2026_08_11_pramita-tristiawati_polisi-selidiki-kematian-siswi-perempuan-yang-tewas-tertemper-krl-di-stasiun-jurang-mangu_Screenshot_20260811_095558_WhatsApp_2.jpg</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Yaqut Jelang Sidang Perdana: Yang Benar akan Kelihatan</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:39:43 +0700</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Sidang digelar di Pengadilan Tindak Pidana Korupsi pada Pengadilan Negeri Jakarta Pusat.</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266815/yaqut-jelang-sidang-perdana-yang-benar-akan-kelihatan</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/-vg7hXrpZ8lhCuiom8MZJ3zTUuQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/7608165/original/012297800_1780392985-2.jpg</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca, Sejumlah Wilayah Berpotensi Hujan</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:45:12 +0700</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Cuaca hari ini didominasi awan, beberapa wilayah perlu waspada hujan.</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266808/prakiraan-cuaca-sejumlah-wilayah-berpotensi-hujan</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/YWsvg7wojVxUiUGRaJ5kTQHDClQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/729279/original/012595900_1409253702-view.jpg</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Peternak Ayam Demo, Ini Janji Mentan soal Pakan Murah hingga Serapan Telur</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:22:35 +0700</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Peternak mengeluhkan harga pakan yang tinggi dan harga telur yang anjlok hingga membuat mereka merugi.</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266801/peternak-ayam-demo-ini-janji-mentan-soal-pakan-murah-hingga-serapan-telur</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/y1R75OosqyyvDcBb8ObPEZR5tC8=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320900/original/048521000_1786418542-988244.jpg</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Yaqut Cholil Qoumas Disambut Selawat Asyghil Saat Tiba di PN Jakpus</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:26:21 +0700</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Yaqut berharap persidangannya berjalan lancar.</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266796/yaqut-cholil-qoumas-disambut-selawat-asyghil-saat-tiba-di-pn-jakpus</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/m5ElepMyC1mlHYKYeULKwHIPjUU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320897/original/037861500_1786418319-IMG-20260811-WA0011.jpg</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Puslabfor Kembali Periksa Sekolah di Jaksel, 30 Senjata Dibawa</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:15:59 +0700</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Pemeriksaan ulang Puslabfor mengungkap puluhan item terkait senjata di sekolah.</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266793/puslabfor-kembali-periksa-sekolah-di-jaksel-30-senjata-dibawa</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/CtM5XDTHJfKJmDzpcb6YMTVMeWI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317273/original/093250400_1786008225-1001014569.jpg</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>BPIP Buka Arsip Sidang BPUPK, Terungkap Dinamika Perdebatan Dasar Negara</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:53:22 +0700</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>NSA Dasar Negara II merekam dinamika perdebatan para pendiri bangsa dalam merumuskan Pancasila, UUD 1945, hingga bentuk negara Indonesia berdasarkan arsip autentik.</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266835/bpip-buka-arsip-sidang-bpupk-terungkap-dinamika-perdebatan-dasar-negara</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/3WaWDWjdfvaWMf0wcfAAApL_7Wk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320953/original/069367100_1786420394-WhatsApp_Image_2026-08-11_at_10.35.01.jpeg</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Lestari</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>875 Bibit Ditanam Serentak di Kawasan Konservasi NTT, Ada Mangrove hingga Nangka</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:19:42 +0700</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Penanaman tidak hanya ditujukan untuk menghijaukan kembali kawasan yang mengalami kerusakan, tetapi juga memulihkan fungsi ekologi.</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>https://lestari.kompas.com/read/2026/08/11/111900086/875-bibit-ditanam-serentak-di-kawasan-konservasi-ntt-ada-mangrove-hingga</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/9-67Guy1ui7LxPlUtJFfySY5hg4=/150x256:1686x1280/1200x675/data/photo/2024/11/12/6732f59febba9.jpg</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Cara Daftar Upacara HUT RI di Istana untuk Warga Jakarta dan Sekitarnya</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:19:42 +0700</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Warga Jakarta dan sekitarnya bisa mendaftar undangan khusus Upacara HUT ke-81 RI di Istana. Pendaftaran dibuka 11 Agustus pukul 10.00 WIB.</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/11/10591561/cara-daftar-upacara-hut-ri-di-istana-untuk-warga-jakarta-dan-sekitarnya</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/dS2tv78fVxjL9C2Qhmjw5WDOHPk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/08/17/68a1a2ac7c890.jpg</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Tekno</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Meta Rilis Muse Glimmer, Model AI yang Bisa Dijalankan Lokal di PC dan Mac</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:19:42 +0700</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Berbeda dari model AI berukuran besar yang perlu infrastruktur cloud, Muse Glimmer mampu menjalankan berbagai tugas agen AI langsung di perangkat.</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>https://tekno.kompas.com/read/2026/08/11/10350007/meta-rilis-muse-glimmer-model-ai-yang-bisa-dijalankan-lokal-di-pc-dan-mac</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/2rdMvp-ndO-M6iD-xzFe021gRDE=/52x0:1267x810/1200x675/filters:watermark(data/photo/2026/01/30/697c816a7af9e.png,0,-0,1)/data/photo/2026/08/11/6a7a7c301c388.webp</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I219"/>
+  <autoFilter ref="A1:I335"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$335</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$439</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I335"/>
+  <dimension ref="A1:I439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16179,8 +16179,4898 @@
         </is>
       </c>
     </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Mendikti: Pendidikan psikologi harus jadi instrumen tekan masalah jiwa</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:44:08 +0700</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Menteri Pendidikan Tinggi, Sains, dan Teknologi (Mendiktisaintek) Brian Yuliarto menekankan pendidikan psikologi harus ...</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688816/mendikti-pendidikan-psikologi-harus-jadi-instrumen-tekan-masalah-jiwa</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-03-at-18.27.21.jpeg</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Peking University siap perluas kerja sama riset dengan Kementrans</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:41:36 +0700</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Perguruan tinggi riset publik di Beijing, China, Institute of South-South Cooperation and ...</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688812/peking-university-siap-perluas-kerja-sama-riset-dengan-kementrans</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000179540.jpg</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Mentan apresiasi capaian Unhas pertahankan gelar Pimnas</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:40:14 +0700</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Menteri Pertanian Andi Amran Sulaiman memberikan apresiasi atas capaian Universitas Hasanuddin (Unhas) yang mampu ...</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688811/mentan-apresiasi-capaian-unhas-pertahankan-gelar-pimnas</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_085244.jpg</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Ekonom Danamon proyeksikan ekonomi RI tumbuh 5,2 persen pada 2026</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:39:43 +0700</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Ekonom PT Bank Danamon Indonesia Tbk memproyeksikan ekonomi Indonesia tumbuh 5,2 persen pada 2026, dengan momentum ...</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688807/ekonom-danamon-proyeksikan-ekonomi-ri-tumbuh-52-persen-pada-2026</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000169493.jpg</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Komisi III minta provokator hoaks dikategorikan sebagai musuh negara</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:34:28 +0700</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi III DPR RI Ahmad Sahroni meminta provokator hoaks di media sosial dikategorikan sebagai musuh negara ...</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688805/komisi-iii-minta-provokator-hoaks-dikategorikan-sebagai-musuh-negara</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/raker-komisi-iii-dpr-dengan-kpk-dan-bnn-2807117.jpg</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Airlangga sebut ETF Emas perkuat posisi Indonesia di investasi global</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:32:42 +0700</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Perekonomian Airlangga Hartarto mengatakan Exchange Traded Fund (ETF) Emas memperkuat posisi ...</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688804/airlangga-sebut-etf-emas-perkuat-posisi-indonesia-di-investasi-global</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/B7A00464-D39A-42DE-804D-457E77F33FB2.jpeg</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>OJK tempatkan penguatan ekosistem UMKM sebagai program utama</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:31:42 +0700</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (DK OJK) Friderica Widyasari Dewi menyatakan pihaknya menempatkan ...</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688801/ojk-tempatkan-penguatan-ekosistem-umkm-sebagai-program-utama</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-12.24.49.jpeg</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>BRImo beri diskon hingga Rp100 ribu untuk tiket Gaia Music Festival 2026</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:27:21 +0700</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Bagi pencinta festival musik, Gaia Music Festival 2026 menjadi salah satu agenda hiburan yang patut dinantikan. ...</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688797/brimo-beri-diskon-hingga-rp100-ribu-untuk-tiket-gaia-music-festival-2026</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Gaia-Music-Festival-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Wamendag: Ekspor F&amp;B masuk lima besar ASEAN</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:26:51 +0700</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Perdagangan (Wamendag) Dyah Roro Esti menyebut ekspor produk makanan dan minuman (food and ...</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688796/wamendag-ekspor-fb-masuk-lima-besar-asean</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_3743.jpeg</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>PP Pesti siapkan tujuh atlet menuju Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:20:56 +0700</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Pengurus Pusat Persatuan Soft Tennis Indonesia (PP Pesti) menyiapkan tujuh atlet putra dan putri untuk lolos ...</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688793/pp-pesti-siapkan-tujuh-atlet-menuju-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/d3f241c9-ca8b-4e11-b845-b8543dd7f9b3.jpeg</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Bea Cukai gagalkan penyelundupan 2,7 juta rokok ilegal di Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:20:10 +0700</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Kanwil Ditjen Bea dan Cukai Kalimantan Bagian Barat (Kanwil DJBC Kalbagbar) berhasil menggagalkan upaya penyelundupan ...</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688789/bea-cukai-gagalkan-penyelundupan-27-juta-rokok-ilegal-di-kubu-raya</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/28/1001382866.jpg</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Bapanas salurkan 610,3 ribu ton beras SPHP hingga 8 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:17:59 +0700</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Badan Pangan Nasional (Bapanas) menyebut penyaluran beras program Stabilisasi Pasokan dan Harga Pangan (SPHP) hingga 8 ...</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688785/bapanas-salurkan-6103-ribu-ton-beras-sphp-hingga-8-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/E9A3406D-1197-4E14-93E3-ED73348EFD19.jpeg</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Komnas HAM dorong penguatan bantuan bagi pengungsi Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:16:22 +0700</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Komisi Nasional Hak Asasi Manusia (Komnas HAM) mendorong penguatan kolaborasi lintas kementerian, pemerintah daerah, ...</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688783/komnas-ham-dorong-penguatan-bantuan-bagi-pengungsi-papua-tengah</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/08/WhatsApp-Image-2026-04-08-at-5.53.23-PM_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Visa Indonesia pegang hak penamaan stasiun MRT Blok A</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:16:03 +0700</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Visa Indonesia memegang hak penamaan (naming rights) stasiun MRT Blok A sebagai upaya memperluas akses pembayaran ...</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688779/visa-indonesia-pegang-hak-penamaan-stasiun-mrt-blok-a</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001022419.jpg</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Plus minus penggunaan AI untuk produksi film menurut Brad Pitt</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:13:56 +0700</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Aktor Hollywood, Brad Pitt menyoroti penggunaan kecerdasan artifisial (AI) untuk film yang dinilainya dapat membantu ...</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688776/plus-minus-penggunaan-ai-untuk-produksi-film-menurut-brad-pitt</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/04/29/Brad.jpeg</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>KPPPA: Sistem terpadu penanganan korban kekerasan butuh kolaborasi K/L</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:10:04 +0700</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Pemberdayaan Perempuan dan Perlindungan Anak Veronica Tan mengatakan kebijakan dan sistem yang terpadu ...</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688772/kpppa-sistem-terpadu-penanganan-korban-kekerasan-butuh-kolaborasi-k-l</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-10.32.14.jpeg</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Mazda konfirmasi CX-3 generasi terbaru akan diproduksi pada 2027</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:07:19 +0700</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Mazda mengonfirmasi bahwa generasi terbaru dari crossover CX-3 akan mulai diproduksi pada 2027 mendatang.
+Dilansir ...</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5688765/mazda-konfirmasi-cx-3-generasi-terbaru-akan-diproduksi-pada-2027</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/IMG_1246.jpeg</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Gulkarmat DKI ingatkan personel jaga keselamatan saat bertugas</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:04:54 +0700</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Kepala Dinas Penanggulangan Kebakaran dan Penyelamatan (Gulkarmat) DKI Jakarta, Bayu Meghantara meminta para personel ...</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688764/gulkarmat-dki-ingatkan-personel-jaga-keselamatan-saat-bertugas</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000319297.jpg</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Polda Jatim perkuat kesiapan personel hadapi karhutla</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:03:12 +0700</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Kepolisian Daerah Jawa Timur memperkuat kesiapan personel dan peralatan menghadapi ancaman kebakaran hutan dan lahan ...</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688760/polda-jatim-perkuat-kesiapan-personel-hadapi-karhutla</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1346126.jpg</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Kemlu terus pantau 7 ABK WNI di Kapal MV Star Janet di perairan China</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:01:30 +0700</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Kementerian Luar Negeri RI terus memantau perkembangan kasus tujuh anak buah kapal (ABK) warga negara Indonesia (WNI) ...</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688756/kemlu-terus-pantau-7-abk-wni-di-kapal-mv-star-janet-di-perairan-china</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/WhatsApp-Image-2026-07-01-at-6.44.26-PM.jpeg</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Akselerasi revitalisasi sekolah dan madrasah</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Pemerintah berupaya mengakselerasi revitalisasi sekolah dan madrasah pada 2026 dengan target lebih dari 70 ribu unit ...</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5688743/akselerasi-revitalisasi-sekolah-dan-madrasah</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/20260811-Akselerasi-revitalisasi-sekolah-dan-madrasah.jpg</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Pemprov Lampung perbaiki akses jalan percepat pembangunan PSEL</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:58:45 +0700</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) Lampung perbaiki akses jalan serta memastikan kesiapan lahan untuk mendukung percepatan ...</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688752/pemprov-lampung-perbaiki-akses-jalan-percepat-pembangunan-psel</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260810-WA0039-1.jpg</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Aksi percobaan pembobolan kotak amal di Tambora terekam CCTV</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:58:26 +0700</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Seorang pria terekam kamera pengawas (CCTV) diduga mencoba membobol kotak amal di Musala Al-Ikhlas, Jalan Siaga III, RT ...</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688748/aksi-percobaan-pembobolan-kotak-amal-di-tambora-terekam-cctv</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/01/IMG-20260301-WA0014_1.jpg</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Cahaya dari Bukit Menoreh</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:57:57 +0700</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Pembangunan infrastruktur di Kulon Progo, Yogyakarta, melaju pesat sejak awal 2000-an. Kawasan hortikultura di pantai ...</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688745/cahaya-dari-bukit-menoreh</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/25/RHD_6567.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Israel simpan 1.700 jenazah warga Palestina, kompromi tukar tawanan</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:54:19 +0700</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Israel menahan jenazah sekitar 1.700 warga Palestina untuk digunakan sebagai alat kompromi pertukaran tawanan ke ...</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688739/israel-simpan-1700-jenazah-warga-palestina-kompromi-tukar-tawanan</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/thumbs_b_ddc255f068d62800412e647c5948659a.jpg</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Pemuda di Jakut diajak sulap sampah jadi barang bernilai ekonomis</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:53:33 +0700</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Anggota DPRD DKI Jakarta, Bebizie Sri Mulyati mengajak pemuda di Jakarta Utara menyulap sampah menjadi barang yang ...</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688737/pemuda-di-jakut-diajak-sulap-sampah-jadi-barang-bernilai-ekonomis</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/ad47cbd6-b89d-467a-a6cc-f440cfa15d4e.jpeg</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Memotret ekonomi Indonesia dari Kepri</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:51:53 +0700</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Suatu pagi di pekan ketiga Juni 2026, kediaman pribadi Gubernur Kepulauan Riau (Kepri) Ansar Ahmad di Jalan Peralatan, ...</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688733/memotret-ekonomi-indonesia-dari-kepri</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Facebook_creation_F39777D3-5B89-4505-9238-16B524314731.jpeg</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Dubes Palestina: Korban tewas di Jalur Gaza lampaui 75.000 orang</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:49:15 +0700</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Duta Besar Palestina untuk Rusia Abdel Hafiz Nofal mengatakan jumlah korban tewas di Jalur Gaza telah melampaui 75.000 ...</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688731/dubes-palestina-korban-tewas-di-jalur-gaza-lampaui-75000-orang</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/thumbs_b_b39e1a6a973e661feeb3926a2ec52632.jpg</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Program Cicilan BRI Kartu Kredit hadir dengan bunga mulai 0% dan tenor hingga 36 bulan</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:49:04 +0700</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Di tengah berbagai kebutuhan dan gaya hidup yang semakin dinamis, kemampuan mengatur pengeluaran menjadi salah satu ...</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688727/program-cicilan-bri-kartu-kredit-hadir-dengan-bunga-mulai-0-dan-tenor-hingga-36-bulan</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/11/01/pexels-karolina-grabowska-5239804.jpg</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Wamentrans: China dapat jadi referensi pengembangan transmigrasi RI</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:46:14 +0700</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Transmigrasi (Wamentrans) Viva Yoga Mauladi mengatakan pengalaman China dalam pembangunan sumber daya ...</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688724/wamentrans-china-dapat-jadi-referensi-pengembangan-transmigrasi-ri</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000179538.jpg</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Anggota DPD dukung Pemprov DKI terbitkan obligasi daerah</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:44:21 +0700</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Anggota Dewan Perwakilan Daerah (DPD) RI dari Daerah Pemilihan (Dapil) DKI Jakarta, Dailami Firdaus mendukung rencana ...</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688721/anggota-dpd-dukung-pemprov-dki-terbitkan-obligasi-daerah</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/05/19/WhatsApp-Image-2022-05-19-at-10.45.33.jpeg</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>E-football jadi nomor esports teramai pada Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:41:26 +0700</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>E-football menjadi nomor pertandingan esports dengan jumlah peserta negara terbanyak pada Asian Games 2026 Aichi-Nagoya ...</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688719/e-football-jadi-nomor-esports-teramai-pada-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/04/01/img-6989-_x600.jpg</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Trump diam-diam ganti pesawat saat di Turkiye di tengah ancaman Iran</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:39:00 +0700</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat (AS) Donald Trump diam-diam meninggalkan Turkiye dengan pesawat militer bulan lalu di ...</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688717/trump-diam-diam-ganti-pesawat-saat-di-turkiye-di-tengah-ancaman-iran</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/thumbs_b_c_0faf781db807e5288836e40ddc754e72.jpg</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Gempa Kolombia beri pemahaman risikonya pada struktur bangunan kota</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:38:38 +0700</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Pakar dari Ikatan Ahli Kebencanaan Indonesia (IABI) Daryono menyatakan fenomena seismotektonik pada gempa bumi ...</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688713/gempa-kolombia-beri-pemahaman-risikonya-pada-struktur-bangunan-kota</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/thumbs_b_c_e726e95b76c6f0cd719dcf122fc06d02.jpg</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Hampir 22 ribu rumah rusak akibat gempa Kumamoto</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:36:52 +0700</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Otoritas Prefektur Kumamoto, Jepang, mencatat hampir 22.000 rumah mengalami kerusakan akibat gempa bumi ...</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688711/hampir-22-ribu-rumah-rusak-akibat-gempa-kumamoto</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/thumbs_b_c_c0a1b3ae6f28b99cdb4f19b3d325f6dc-1.jpg</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>PBB: Krisis kemanusiaan di Sudan kian memburuk akibat konflik</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:36:35 +0700</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Konflik yang berkelanjutan, pengungsian, dan kekurangan dana terus memperdalam kebutuhan kemanusiaan di seluruh Sudan, ...</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688707/pbb-krisis-kemanusiaan-di-sudan-kian-memburuk-akibat-konflik</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000009_20260811_CBMFN0A001.jpeg</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>BPBD Sulteng tangani 33 karhutla selama Januari-Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:34:40 +0700</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Badan Penanggulangan Bencana Daerah (BPBD) Sulawesi Tengah (Sulteng) telah menangani 33 kejadian kebakaran hutan dan ...</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688703/bpbd-sulteng-tangani-33-karhutla-selama-januari-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260808-WA0026.jpg</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Bakamla RI latihan bersama "coast guard" Malaysia - Singapura di Kepri</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:33:31 +0700</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Badan Keamanan Laut (Bakamla) RI menggelar latihan bersama penjaga pantai (coast guard) Malaysia dan Singapura dalam ...</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688700/bakamla-ri-latihan-bersama-coast-guard-malaysia-singapura-di-kepri</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_1754.jpeg</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Cara Jakarta menekan pengangguran dari akar rumput</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:32:13 +0700</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Dua puluh warga Pasar Rebo tidak perlu mendatangi balai pelatihan kerja untuk belajar meracik kopi atau mengedit video. ...</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688699/cara-jakarta-menekan-pengangguran-dari-akar-rumput</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/target-rasio-kewirausahaan-nasional-2834312.jpg</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Swiatek bertemu Svitolina pada semifinal WTA 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:31:15 +0700</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Iga Swiatek akan menghadapi Elina Svitolina pada semifinal National Bank Open 2026 di Toronto setelah kedua petenis ...</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688696/swiatek-bertemu-svitolina-pada-semifinal-wta-1000-toronto</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_0161.jpeg</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>AS mediasi Israel-Suriah sepakati IAEA evakuasi material nuklir</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:30:33 +0700</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Amerika Serikat telah menengahi kesepakatan antara Suriah dan Israel untuk membiarkan Badan Energi Atom Internasional ...</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688692/as-mediasi-israel-suriah-sepakati-iaea-evakuasi-material-nuklir</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/03/IAEA.jpg</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Baznas dan Ika Unpad perkuat pemberdayaan mahasiswa berbasis masjid</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:30:22 +0700</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Badan Amil Zakat Nasional (Baznas) bersama Unit Pengumpulan Zakat (UPZ) Ikatan Alumni Universitas Padjadjaran (IKA ...</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688688/baznas-dan-ika-unpad-perkuat-pemberdayaan-mahasiswa-berbasis-masjid</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_091056.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Semeru delapan kali erupsi dengan tinggi letusan capai 700 meter</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:27:34 +0700</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Gunung Semeru di perbatasan Kabupaten Lumajang dan Malang, Jawa Timur mengalami delapan kali erupsi dengan tinggi ...</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688685/semeru-delapan-kali-erupsi-dengan-tinggi-letusan-capai-700-meter</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-10.54.07.jpeg</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Kemensos benahi kedisiplinan pegawai termasuk praktik judol</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:23:40 +0700</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial membenahi kedisiplinan internal seluruh jajarannya, termasuk menskrining oknum pegawai kementerian ...</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688683/kemensos-benahi-kedisiplinan-pegawai-termasuk-praktik-judol</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG20260811094952_103356_1.jpg</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Sayap pemuda Golkar BMK 1957 ajak kader perkuat konsolidasi nasional</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:23:39 +0700</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Ketua Umum sayap pemuda Partai Golkar, Barisan Muda Kosgoro (BMK) 1957 Rizky Maulana mengajak seluruh jajaran pengurus ...</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688681/sayap-pemuda-golkar-bmk-1957-ajak-kader-perkuat-konsolidasi-nasional</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000480475_1.jpg</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>KKP dalami dugaan pelanggaran kapal tuna di Benoa</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:17:12 +0700</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Kementerian Kelautan dan Perikanan (KKP) mengatakan tengah mendalami dugaan pelanggaran yang melibatkan sejumlah kapal ...</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688677/kkp-dalami-dugaan-pelanggaran-kapal-tuna-di-benoa</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/05/25/IMG_20230510_112049.jpg</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Kemenpar-BI gelar pelatihan guna perkuat wisata ramah muslim</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:16:28 +0700</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Kementerian Pariwisata dan Departemen Ekonomi dan Keuangan Syariah (DEKS) Bank Indonesia (BI) menggelar pelatihan ...</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688676/kemenpar-bi-gelar-pelatihan-guna-perkuat-wisata-ramah-muslim</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/wisatawan-kapal-pesiar-kunjungi-masjid-raya-baiturrahman-aceh-111124-apls-4.jpg</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Uni Eropa siapkan jaringan listrik hadapi gerhana matahari</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:15:46 +0700</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Operator jaringan listrik Eropa telah mengambil sejumlah langkah tambahan untuk memastikan kelancaran operasi sistem ...</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688673/uni-eropa-siapkan-jaringan-listrik-hadapi-gerhana-matahari</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/antarafoto-gerhana-matahari-sebagian-di-bekasi-20042023-par-2.jpg</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Jelang Sidang Bersama, Karpet hingga Ornamen Merah Putih Mulai Terpasang</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:21:59 +0700</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Persiapan sidang tahunan MPR dan sidang bersama DPR-DPD pada 14 Agustus 2026 terus dilakukan. Rapat protokol dengan pihak kementerian berlangsung pagi ini.</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613416/jelang-sidang-bersama-karpet-hingga-ornamen-merah-putih-mulai-terpasang</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/persiapan-jelang-sidang-tahunan-mpr-dan-sidang-bersama-dpr-dpd-1786425599808_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Pembalap Drag Race Maut di Kotamobagu Berpotensi Jadi Tersangka</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:21:50 +0700</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Fistel Mukuan</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Pembalap bernama Tian Ngantung yang mengemudikan mobil maut itu berpotensi menjadi tersangka.</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613415/pembalap-drag-race-maut-di-kotamobagu-berpotensi-jadi-tersangka</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/mobil-peserta-drag-race-kotamobagu-tabrak-penonton-hingga-8-orang-meninggal-1786343760891_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Polisi Reka Ulang Kasus Mutilasi Pria di Depok, Saepul Dihadirkan</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:02:19 +0700</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Polisi menggelar reka ulang kasus pembunuhan dan mutilasi pria K di Depok. Tersangka Saepul dijerat pasal pembunuhan berencana dengan ancaman hukuman mati.</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613381/polisi-reka-ulang-kasus-mutilasi-pria-di-depok-saepul-dihadirkan</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/polisi-menggelar-reka-ulang-kasus-mutilasi-pria-di-depok-tersangka-saepul-ikut-dihadirkan-1786424451846_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Sopir Travel Pembunuh Wanita di Sulsel Gasak Duit Korban Rp 62 Juta</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:01:45 +0700</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Agung Pramono</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Sopir mobil travel bernama Alber alias Latu (37) pelaku pembunuhan Mita (26) di Morowali, Sulawesi Tengah (Sulteng) juga menggasak uang korban.</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613379/sopir-travel-pembunuh-wanita-di-sulsel-gasak-duit-korban-rp-62-juta</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/11/24/gadis-asal-wajo-paramitha-titania-anggelica-alias-mita-26-sudah-4-bulan-hilang_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Gerakan ASRI, Brimob Polda Metro Bersihkan Sampah di Pesisir Pantai Kaligaga</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:53:58 +0700</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Brimob Polda Metro Jaya laksanakan gerakan ASRI di Pantai Kaligaga, Jakut. Sebanyak 25 personel membereskan sampah untuk lingkungan yang lebih sehat dan nyaman.</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613369/gerakan-asri-brimob-polda-metro-bersihkan-sampah-di-pesisir-pantai-kaligaga</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/brimob-polda-metro-bersihkan-sampah-di-pesisir-pantai-kaligaga-jakarta-utara-1786423926521_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Mobil yang Ditumpangi Ditabrak Truk, Begini Kondisi Kiai Anwar Zahid</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:34:55 +0700</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Ainur Rofiq</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Kiai Anwar Zahid terlibat kecelakaan di Bojonegoro saat menunggu antrean. Kiai Anwar dan sopirnya selamat usai mobilnya ditabrak truk.</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613339/mobil-yang-ditumpangi-ditabrak-truk-begini-kondisi-kiai-anwar-zahid</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kiai-anwar-zahid-kecelakaan-di-bojonegoro-1786415552422_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Fahira Idris Dukung Rencana TransJ Kelola Transportasi ke Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:33:45 +0700</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Fahira Idris dukung pengalihan pengelolaan transportasi ke TransJakarta untuk Kepulauan Seribu. Dia soroti pentingnya integrasi dan keselamatan layanan.</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613323/fahira-idris-dukung-rencana-transj-kelola-transportasi-ke-kepulauan-seribu</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/fahira-idris-puji-rencana-transj-kelola-transportasi-ke-kepulauan-seribu-1786422621769_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Polisi Selidiki Challenge Hafalan Qur'an demi Miras Saat Konser di Jakut</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:33:17 +0700</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Viral aksi promosi miras dengan tantangan hafalan Al-Qur'an di konser The Sounds Project. Polisi menyelidiki kejadian tersebut.</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613322/polisi-selidiki-challenge-hafalan-quran-demi-miras-saat-konser-di-jakut</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/1144667396-1786419072166_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Dedi Congor Jadi Tersangka Gratifikasi yang Diusut Kortas Tipikor Polri</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:20:56 +0700</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Kortas Tipikor Polri telah menetapkan Ahmad Dedi alias Dedi Congor sebagai tersangka penerima gratifikasi berdasarkan penyidikan sejak 2023.</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613308/dedi-congor-jadi-tersangka-gratifikasi-yang-diusut-kortas-tipikor-polri</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/07/kabag-ops-kortas-tipikor-polri-kombes-ahmad-yusuf-afandi-1783415868317_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Jaksa KPK: Korupsi Kuota Haji Memperkaya Yaqut Rp 4,8 Miliar</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:19:22 +0700</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Jaksa menyakini perkara korupsi kuota haji memperkaya Yaqut sebesar USD 271.500 atau jika dikonversi dengan kurs saat ini yakni sekitar Rp 4,8 miliar.</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613306/jaksa-kpk-korupsi-kuota-haji-memperkaya-yaqut-rp-4-8-miliar</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/mantan-menag-yaqut-cholil-qoumas-1786417604158_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Bukan Bunker, Ruangan di Sekolah Jaksel TKP Temuan Senjata Basemen</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:04:56 +0700</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Polisi mengungkap isi basemen di sekolah swasta Jakarta, tempat ratusan senjata ditemukan. Penemuan ini terkait konflik internal yayasan.</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613292/bukan-bunker-ruangan-di-sekolah-jaksel-tkp-temuan-senjata-basemen</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363566_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>KPK Ungkap Selisih SGD 2.000 di Amplop Bupati Kuansing untuk Menhut</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:19:20 +0700</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>KPK menyelidiki selisih uang SGD 2 ribu dalam amplop dari Bupati Kuansing Suhardiman Amby untuk Menteri Kehutanan Raja Juli Antoni</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613216/kpk-ungkap-selisih-sgd-2-000-di-amplop-bupati-kuansing-untuk-menhut</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/22/jumpa-pers-kpk-1784716930554_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Siap-siap! Magang Nasional Batch 2 Dibuka Bulan Depan</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:32:37 +0700</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Pemerintah akan membuka program magang nasional batch 2 tahun 2026 pada September.</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613433/siap-siap-magang-nasional-batch-2-dibuka-bulan-depan</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/tampilan-siapkerja-untuk-program-magang-nasional-2026-1784528861950_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Mendagri Siapkan 3 Skema Bayar Gaji PPPK di Daerah</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:23:59 +0700</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Tiga skema disiapkan untuk mendukung pemerintah daerah (Pemda) dalam memenuhi pembayaran gaji Pegawai Pemerintah dengan Perjanjian Kerja (PPPK).</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613419/mendagri-siapkan-3-skema-bayar-gaji-pppk-di-daerah</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi-1785894664987_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Airlangga Kasih PR ke Maman: Kredit UMKM Harus Tembus Rp 2.000 T</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:11:51 +0700</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Perekonomian Airlangga Hartarto memberikan tugas ke Menteri UMKM untuk meningkatkan penyaluran kredit UMKM hingga Rp 2.000 triliun.</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613404/airlangga-kasih-pr-ke-maman-kredit-umkm-harus-tembus-rp-2-000-t</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/menteri-koordinator-bidang-perekonomian-airlangga-hartarto-1783665254890_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Destry Jadi Calon Tunggal Gubernur BI, 3 Pejabat Ekonomi Kompak Dukung</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:55:34 +0700</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Perekonomian dan pejabat lainnya dukung Destry Damayanti sebagai calon Gubernur BI. Destry dinilai berpengalaman dan respons pasar positif.</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613372/destry-jadi-calon-tunggal-gubernur-bi-3-pejabat-ekonomi-kompak-dukung</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/01/26/btn-economic-outlook-2024-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Kemnaker Sebut Peserta Magang Nasional Lebih Banyak di Luar Jawa</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:53:23 +0700</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengungkap sebaran peserta Program Pemagangan Nasional 2026 batch 1 angkatan kedua lebih merata.</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613368/kemnaker-sebut-peserta-magang-nasional-lebih-banyak-di-luar-jawa</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/14/program-magang-1776135871755_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>BPK Temukan Kelebihan Pembayaran di BSSN Meski Raih WTP</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:35:43 +0700</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>BPK memberikan opini WTP untuk laporan keuangan BSSN 2025, meski ditemukan kelebihan pembayaran dan rekomendasi untuk optimalisasi aset.</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613390/bpk-temukan-kelebihan-pembayaran-di-bssn-meski-raih-wtp</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/05/26/0dadd724-78e9-4380-9aed-8a12fc2c4c57_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Gemas! Ikut Mahalini Nyanyi, Selina Joget Gak Sabar Lari ke Atas Panggung</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:30:58 +0700</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Selina, putri Mahalini dan Rizky Febian bikin gemas. Ikut Mahalini nyanyi, Selina gak bisa diam ikut joget dan mau lari ke depan penonton.</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613331/gemas-ikut-mahalini-nyanyi-selina-joget-gak-sabar-lari-ke-atas-panggung</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/mahalini-1786422380970_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Lesti Kejora dan Asila Maisa Jalani Pemeriksaan di Polda Metro</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:09:24 +0700</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Rizky Billar, Lesti Kejora, dan Asila Maisa diperiksa di Polda Metro Jaya terkait laporan fitnah. Mereka memberikan keterangan tambahan untuk penyidik.</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613394/lesti-kejora-dan-asila-maisa-jalani-pemeriksaan-di-polda-metro</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rizky-billar-lesti-kejora-dan-asilla-1786424585636_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Poppy Sovia Idap Bipolar, Kehadiran Anak Bikin Merasa Lebih Berharga</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:25:33 +0700</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Poppy Sovia didiagnosis bipolar tipe 1 dan menemukan kekuatan hidup melalui anaknya. Dia berbagi pengalaman dan motivasi untuk yang mengalami masalah mental.</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613085/poppy-sovia-idap-bipolar-kehadiran-anak-bikin-merasa-lebih-berharga</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/poppy-sovia-1786088545842_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Reza Gladys Respons Berita Hoaks soal Dirinya Laporkan Suami dan Dhena Devanka atas Dugaan Perzinaan</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:32:02 +0700</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Reza Gladys memberikan respons terkait dengan berita hoaks soal dirinya melaporkan suami dan Dhena Devanka atas dugaan perzinaan.</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866790/reza-gladys-respons-berita-hoaks-soal-dirinya-laporkan-suami-dan-dhena-devanka-atas-dugaan-perzinaan</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/3EXsvrumltalnPf2ipCrcZrZzU4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Momen-Reza-Gladys-dan-suami-datangi-Polda-Metro-Jakarta-Selatan.jpg</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPS Kelas 10 SMA Kurikulum Merdeka Halaman 172 Edisi Revisi: Aktivitas 3.10</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:31:20 +0700</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Berikut ini kunci jawaban IPS kelas 10 SMA Kurikulum Merdeka Halaman  172 Edisi Revisi: Aktivitas 3.10.</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7866789/kunci-jawaban-ips-kelas-10-sma-kurikulum-merdeka-halaman-172-edisi-revisi-aktivitas-310</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/DSga7wM08_0kQh0WIsFqhAjs6F8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Simak-kunci-jawaban-Informatika-Kelas-5-Halaman-139.jpg</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Denny Sumargo Heran Agama hingga Etnisnya jadi Sasaran Hujat Gara-gara Undang Sarwendah di Podcast</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:30:02 +0700</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Denny Sumargo kecewa agama dan etnisnya ikut disentil lantaran mengundang Sarwendah di podcastnya.</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866788/denny-sumargo-heran-agama-hingga-etnisnya-jadi-sasaran-hujat-gara-gara-undang-sarwendah-di-podcast</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ik23waLzTdDpWPovuqWu3mZdce4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Denny-Sumargo-1-03082026.jpg</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu Bring Your Love - Madonna dan Sabrina Carpenter: Don’t Comment on My Ideas</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:28:43 +0700</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Simak lirik dan terjemahan lagu Bring Your Love yang dibawakan oleh Madonna bersama Sabrina Carpenter.</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7866787/terjemahan-lirik-lagu-bring-your-love-madonna-sabrina-carpenter-dont-comment-on-my-ideas</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zLN77GXG_MWcQ27NDqNvGgp-QJs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-musik-ilustrasi-lirik-ilustrasi-terjemahan-lirik-lagu.jpg</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Trump Media Tekor 238 Juta Dolar AS, Pendapatan Cuma 1,7 Juta Dolar AS, Saham Anjlok 8 Persen</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:28:42 +0700</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Trump Media milik Donald Trump rugi 238 juta dolar AS pada kuartal II 2026,  pendapatan hanya 1,7 juta dolar AS, saham anjlok 8 persen.</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866786/trump-media-tekor-238-juta-dolar-as-pendapatan-cuma-17-juta-dolar-as-saham-anjlok-8-persen</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/pd58Lh0QZkuUPrM04LfPl7UxG4o=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/residen-AS-Donald-Trump-Senin-27-Juli-2026-Foto-Res.jpg</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Ada Daya Pikat Legenda AC Milan, Federico Barba Ceritakan Alasannya Tinggalkan Persib</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:27:31 +0700</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Federico Barba menyebut legenda AC Milan Pippo Inzaghi di balik keputusannya gabung Palermo dan tinggalkan Persib Bandung</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866785/ada-daya-pikat-legenda-ac-milan-federico-barba-ceritakan-alasannya-tinggalkan-persib</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5s4Zz2yN9CDSsT-6PRNcPWWt6k8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Aksi-bek-Persib-Bandung-Federico-Barba-berduel-dengan-penyerang-Madura-United-Lulinha.jpg</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Jelang Sidang Tahunan 2026, Plt Sekjen DPR Ungkap Persiapan hingga Jadwal Acara</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:26:19 +0700</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>MPR, DPR, dan DPD, telah melakukan koordinasi untuk memastikan seluruh rangkaian kegiatan berjalan sesuai agenda.</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866784/jelang-sidang-tahunan-2026-plt-sekjen-dpr-ungkap-persiapan-hingga-jadwal-acara</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Qsn1R3WnhXiTZM5tZiOuW_dEYUI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Paripurna-DPR-RI-pada-14-Agustus.jpg</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Doa agar Hati dan Lisan Selalu Jujur dalam Perkataan dan Perbuatan</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:23:53 +0700</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Hati dan lisan seorang Muslim sebaiknya selalu jujur dalam perkataan dan perbuatan. Berikut doa yang dapat dibaca untuk menjaga kejujuran.</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7866783/doa-agar-hati-dan-lisan-selalu-jujur-dalam-perkataan-dan-perbuatan</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/U11q51q-CJ66-8lRNT5oRv2mai4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/DOA-AGAR-JUJUR-435634543TR.jpg</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Rizky Billar Santai jadi Saksi Penyebaran Hoaks Selingkuh dengan Asila Maisa, Sempat Goda Wartawan</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:23:47 +0700</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Rizky Billar terlihat santai saat hadir di Polda Metro Jaya untuk diperiksa sebagai saksi laporan penyebaran hoaks.</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866782/rizky-billar-santai-jadi-saksi-penyebaran-hoaks-selingkuh-dengan-asila-maisa-sempat-goda-wartawan</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/78EbReGI5C4Aj-1k0Orok3S4lnk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Rizky-Billar-1-31072026.jpg</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Gempa M 7,4 Porak-porandakan Kolombia, Darurat Nasional Diberlakukan, Korban Tewas Tembus 110 Jiwa</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:23:03 +0700</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Gempa M 7,4 guncang Kolombia, menewaskan lebih dari 110 orang. Presiden tetapkan darurat nasional, sementara bantuan internasional mulai berdatangan.</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866781/gempa-m-74-porak-porandakan-kolombia-darurat-nasional-diberlakukan-korban-tewas-tembus-110-jiwa</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/URaiCze4k2TRjD74O4lopRgG6kY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PRESIDEN-KOLOMBIA-Presiden-Kolombia-yang-baru-dilantik-Abelardo-de-la-Espriella.jpg</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Jadwal Acara TV Rabu, 12 Agustus 2026: FYP TRANS 7 dan Cipung Abubu Mentari TV</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:22:39 +0700</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Simak jadwal acara TV besok Rabu 12 Agustus 2026 terdapat tayangan FYP di TRANS 7 dan Cipung Abubu di Mentari TV.</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866780/jadwal-acara-tv-rabu-12-agustus-2026-fyp-trans-7-dan-cipung-abubu-mentari-tv</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/H5aLayjCy83MjA-P9TOjSo-_9Qw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ILUSTRASI-TELEVISI-3.jpg</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Seskab Teddy Klaim 30–40 Persen Peserta MagangHub Langsung Kerja, Bagaimana Nasib 60 Persen Lainnya?</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:22:04 +0700</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Perusahaan cenderung memilih merekrut peserta magang karena mereka telah dibekali keterampilan spesifik selama program berlangsung.</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866779/seskab-teddy-klaim-3040-persen-peserta-maganghub-langsung-kerja-bagaimana-nasib-60-persen-lainnya</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/monSidTVNgFKT-jHJHuzX_ZIV8c=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/maganghub-klaim-seskab.jpg</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Yaqut Berjabat Tangan dengan Dua Terdakwa Kasus Korupsi Kuota Haji di Persidangan</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:20:56 +0700</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Yaqut Cholil Qoumas menjalani sidang dakwaan kasus dugaan korupsi kuota haji, di Pengadilan Tipikor Jakarta Pusat, Selasa (11/8/2026).</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866778/yaqut-berjabat-tangan-dengan-dua-terdakwa-kasus-korupsi-kuota-haji-di-persidangan</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/U3akHItL4FpftqwfKv77oXWMCOk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kasus-tersebut-di-Pengadilan-Tipi.jpg</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Mengenal Definisi Hantavirus, Perhatikan Gejala dan Faktor Penularannya</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:20:49 +0700</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Hantavirus menjadi perhatian karena dapat menular melalui paparan hewan pengerat seperti tikus, berikut gejala, resiko hingga faktor penularannya.</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866777/mengenal-definisi-hantavirus-perhatikan-gejala-dan-faktor-penularannya</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/XGOK4B92fWuE_P0GM7lWTImkJRU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/CEK-KESEHATAN-Warga-lansia-di-Kelurahan-Purwantoro.jpg</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPS Kelas 10 SMA Kurikulum Merdeka Halaman 167 Edisi Revisi: Aktivitas 3.9</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:17:48 +0700</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Berikut ini kunci jawaban IPS kelas 10 SMA Kurikulum Merdeka Halaman 167 Edisi Revisi: Aktivitas 3.9.</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7866776/kunci-jawaban-ips-kelas-10-sma-kurikulum-merdeka-halaman-167-edisi-revisi-aktivitas-39</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/U9U0Ezm2sPloSaaCbS7kqX3m2cw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/suasana-hari-pertama-pembelajaran-tatap-muka-ptm-terbatas-di-kota-bogor-senin-18102021.jpg</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Edarkan Ribuan Butir Tramadol dan Eximer, Tiga Pria di Kelapa Dua Tangerang Ditangkap Polisi</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:17:27 +0700</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Polsek Kelapa Dua ringkus tiga pria edarkan obat keras daftar G tanpa resep, ribuan butir tramadol dan eximer disita.</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866775/edarkan-ribuan-butir-tramadol-dan-eximer-tiga-pria-di-kelapa-dua-tangerang-ditangkap-polisi</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/v9i6ibfO1bPc8YJ_o5Lf68tR8ys=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sejumlah-barang-bukti-berupa-ribuan-butir-obat-keras-daftar-G-jenis-Tramadol-dan-Eximer.jpg</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Sidang Korupsi Kuota Haji, Eks Menag Yaqut Didakwa Memperkaya Diri USD 271.500</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:15:48 +0700</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Yaqut Cholil Qoumas didakwa memperkaya diri sejumlah USD 271.500 atas pengisian kuota haji khusus tambahan periode tahun 2023 dan 2024.</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866774/sidang-korupsi-kuota-haji-eks-menag-yaqut-didakwa-memperkaya-diri-usd-271500</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0ngnyDDP7c9zEA8b30Lkx2Qud2o=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Yaqut-Cholil-Qoumas-DIDAKWA-RUGIKAN-NEGARA-622-miliar.jpg</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Awal Mula Kasus Penyekapan Berujung Tewasnya Handi, 4 Lokasi Kejadian hingga 8 Orang Jadi Tersangka</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:15:32 +0700</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Saat ditemukan, Handi berada dalam kondisi kaki terikat menggunakan kawat dan mengalami sejumlah luka.</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866773/awal-mula-kasus-penyekapan-berujung-tewasnya-handi-4-lokasi-kejadian-hingga-8-orang-jadi-tersangka</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/A1YYPLRilH3I4xpPq3AfPCEpo4M=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PENYEKAPAN-sumedang.jpg</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Beda Sikap dengan US Soccer, Trump Bela Infantino: Ganti Presiden FIFA Kesalahan Besar</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:10:59 +0700</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donal Trump memberi pembelaan terhadap Gianni Infantino yang mendapat desakan untuk mundur dari jabatan Presiden FIFA.</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866772/beda-sikap-dengan-us-soccer-trump-bela-infantino-ganti-presiden-fifa-kesalahan-besar</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/jJtKQdQXUic7dMeq4jn1wIzwv74=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Gianni-Infantino-bersama-dengan-Donald-Trump.jpg</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Andrey Santos Siap Gantikan Casemiro di Manchester United: Saya Bisa Lakukan Seperti Dia</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:10:36 +0700</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Andrey Santos siap menjadi penerus Casemiro di Manchester United. Tampil impresif di pramusim, bertekad bertahan lama di Old Trafford.</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866771/andrey-santos-siap-gantikan-casemiro-di-manchester-united-saya-bisa-lakukan-seperti-dia</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/AlltmgB8FC-kPtqdF1B1kPc6drs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Aksi-gelandang-anyar-Manchester-United-Andrey-Santos-saat-melawan-PSG.jpg</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Kemenko Polkam, BSSN, dan Telkom Perkuat Kolaborasi Hadapi Ancaman Era Komputasi Kuantum</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:44:15 +0700</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Ferry kisihandi</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Pemerintah mulai mempercepat langkah antisipasi menghadapi potensi ancaman keamanan siber seiring perkembangan teknologi komputasi kuantum. 
+Melalui Rapat Koordinasi Urgensi Penyusunan Kebijakan Menghadapi Post-Quantum Computing (PQC), Kamis...</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjl95r472/kemenko-polkam-bssn-dan-telkom-perkuat-kolaborasi-hadapi-ancaman-era-komputasi-kuantum</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/upaya-memperkuar-sinergi-untuk-menyiapkan-diri-menghadapi-era-pascakuantum_260811114246-855.jpeg</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Rupiah Dibuka Melemah 40 Poin Jadi Rp 17.795 per Dolar AS</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:26:38 +0700</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Analis mata uang Doo Financial Futures Lukman Leong mengatakan rupiah melemah seiring ketidakpastian geopolitik di Timur Tengah (Timteng). Nilai tukar rupiah terhadap dolar Amerika Serikat (AS) pada pembukaan...</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjl8ce423/rupiah-dibuka-melemah-40-poin-jadi-rp-17795-per-dolar-as</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/011418000-1780675525-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Infografis Guncang Gempa Kolombia Terkuat Abad Ini</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:44:59 +0700</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Gempa M7,4 mengguncang Kolombia dan terasa hingga Ekuador.</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266944/infografis-guncang-gempa-kolombia-terkuat-abad-ini</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/nHHr6ML2g-DBv-fwJmf1AcPgM6U=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321075/original/010300900_1786426972-45b224e2-a441-426f-bc27-2b77c0ef6b28.jpg</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Istri Eks Menag Yaqut Hadiri Sidang, Bawa Bantal untuk Suami</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:43:00 +0700</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Istri mantan Menteri Agama (Menag) Yaqut Cholil Qoumas, Eny Retno turut hadir dalam sidang perdana.</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266943/istri-eks-menag-yaqut-hadiri-sidang-bawa-bantal-untuk-suami</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/r2EHAFjxKLsUOBdFY3Xr4BeVjMs=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321074/original/094101400_1786426954-IMG_20260811_094900_510.jpg</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Terungkap Isi Ruangan yang Disebut Bunker Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:43:30 +0700</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Ruangan itu dipastikan bukan bunker, hanya basement yang terhubung dengan sejumlah ruangan.</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266939/terungkap-isi-ruangan-yang-disebut-bunker-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/DZ4ufKYVxSrVZgr_zDmvYxBWPZc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321073/original/094190400_1786426911-WhatsApp_Image_2026-08-11_at_12.40.02.jpeg</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Viral Challenge Hafalan Al-Qur'an Berhadiah Miras, Polisi Mulai Selidiki</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:20:59 +0700</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Video dugaan challenge hafalan Al-Qur'an berhadiah minuman keras di booth sponsor The Sounds Project viral dan menuai kecaman. Polisi kini menyelidikinya.</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266923/viral-challenge-hafalan-al-quran-berhadiah-miras-polisi-mulai-selidiki</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Fp5iC-vppn7dJSzwqGEBlrLz0gY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321055/original/059736500_1786425649-Jepretan_Layar_2025-08-11_pukul_12.15.34.jpg</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Di Depan Hakim, Yaqut Ungkap Kondisi Kesehatannya Pascaoperasi</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:13:30 +0700</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Yaqut sempat dibantarkan karena ada masalah kesehatan di pencernaan.</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266912/di-depan-hakim-yaqut-ungkap-kondisi-kesehatannya-pascaoperasi</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/nWrXsW3scvrby34Pqt9_kl75l98=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320896/original/035022100_1786418319-IMG-20260811-WA0012.jpg</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Polisi Cari Jejak di Balik 30 Item Senjata di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:08:18 +0700</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Puslabfor mengambil sampel DNA untuk menelusuri jejak orang di lokasi.</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266907/polisi-cari-jejak-di-balik-30-item-senjata-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Fl_NzWIZKKZEWAlAQ_ZHoXsZU5g=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317547/original/022307300_1786020542-WhatsApp_Image_2026-08-06_at_19.28.11.jpeg</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Warga Teriak Saat Mobil Bupati Lampung Selatan Terjebak Jalan Rusak, 'Jangan Janji Saja'</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:03:32 +0700</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Bupati Egi mengaku tak menyangka jalanan di Lampung Selatan rusak separah itu.</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266901/warga-teriak-saat-mobil-bupati-lampung-selatan-terjebak-jalan-rusak-jangan-janji-saja</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/mm_wGjwpk26oXordrwSB0W3gYec=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321037/original/009420000_1786424605-1001541253.jpg</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Yaqut Didakwa Rugikan Negara Rp 662 Miliar</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:48:46 +0700</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Yaqut disebut melakukan pelanggaran hukum secara bersama-sama dengan pihak lain.</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266885/yaqut-didakwa-rugikan-negara-rp-662-miliar</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/eYPEhafi5n-DU_gVv0slO1l2gbc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321012/original/036331400_1786423717-IMG-20260811-WA0043.jpg</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Eks Kepala Bea Cukai Marunda Jadi Tersangka Gratifikasi</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:25:31 +0700</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Ahmad Dedi diduga menerima hadiah atau janji dalam periode 2008 hingga 2016.</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266862/eks-kepala-bea-cukai-marunda-jadi-tersangka-gratifikasi</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/2qXbWmSS5nvoujQVDkZ55lzxOSI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320991/original/042546300_1786422321-WhatsApp_Image_2026-08-11_at_11.24.27.jpeg</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Puslabfor Kembali Periksa Sekolah di Jaksel, 30 Barang Dibawa</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:09:09 +0700</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Pemeriksaan ulang Puslabfor mengungkap puluhan item terkait senjata di sekolah.</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266793/puslabfor-kembali-periksa-sekolah-di-jaksel-30-barang-dibawa</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/CtM5XDTHJfKJmDzpcb6YMTVMeWI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317273/original/093250400_1786008225-1001014569.jpg</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Daftar 28 Nama yang Diperkaya dalam Kasus Kuota Haji: Yaqut hingga 313 PIHK</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:48:20 +0700</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Akibat perbuatan Yaqut dalam kasus korupsi kuota haji khusus, jaksa menyebut negara mengalami kerugian sebesar Rp 622.090.207.166,41.</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/12475941/daftar-28-nama-yang-diperkaya-dalam-kasus-kuota-haji-yaqut-hingga-313-pihk</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/bDSWiJQj25iIcI4EcSynE7cq6Eo=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7a8ccf063f1.jpg</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Tercatat Ada 1.070 Hotspot Selama 2026, Polda Lampung Siaga Karhutla dan Kekeringan</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:48:20 +0700</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Polda Lampung memperkuat kesiapsiagaan menghadapi karhutla serta dampak kekeringan di musim kemarau.</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/11/123113378/tercatat-ada-1070-hotspot-selama-2026-polda-lampung-siaga-karhutla-dan</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/mzFOfTGi1fZ7KOFZqTqHfk_pY1s=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7a99376603c.jpg</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Sepekan Jelang HUT RI, Semarak Pernak-pernik Kemerdekaan Penuhi Pasar Jatinegara Jaktim</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:48:20 +0700</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Di Pasar Jatinegara, sejumlah pembeli terlihat mencari perlengkapan untuk kegiatan kemerdekaan, mulai dari ibu-ibu, anggota PKK, hingga karyawan.</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/11/12110571/sepekan-jelang-hut-ri-semarak-pernak-pernik-kemerdekaan-penuhi-pasar</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/6ffdo7dCnX1i0lTqKS39TsPlH8M=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7a8f1d70649.jpeg</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I335"/>
+  <autoFilter ref="A1:I439"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$439</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$581</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I439"/>
+  <dimension ref="A1:I581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21069,8 +21069,6682 @@
         </is>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Absen dalam Asian Games 2026, loncat indah bidik SEA Games 2027</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:42:32 +0700</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Loncat indah Indonesia mulai memetakan nomor-nomor potensial medali emas pada SEA Games 2027 di Malaysia setelah ...</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688880/absen-dalam-asian-games-2026-loncat-indah-bidik-sea-games-2027</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/05/kejurnas-akuatik-indonesia-2026-2784829.jpg</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Kemendag bidik pasar Timur Tengah untuk produk F&amp;B halal RI</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:41:32 +0700</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Perdagangan (Wamendag) Dyah Roro Esti menyebutkan produk makanan dan minuman (food and beverage/F&amp;B) ...</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688877/kemendag-bidik-pasar-timur-tengah-untuk-produk-fb-halal-ri</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_3744.jpeg</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Bukan sekadar padamkan api, petugas Damkar unjuk ketangkasan di JFFC 2026</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:41:15 +0700</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Peserta mengikuti Hoselaying Challenge dalam Jakarta Fire Fighter Challenge (JFFC) 2026 di Pusat Pendidikan dan ...</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5688875/bukan-sekadar-padamkan-api-petugas-damkar-unjuk-ketangkasan-di-jffc-2026</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Jakarta-Fire-Fighter-Challenge-110826-Ada-3A.jpg</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Delapan penerima manfaat program pemerintah hadiri Sidang Tahunan</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:32:36 +0700</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>DPR RI akan menghadirkan delapan penerima manfaat program pemerintah dalam Sidang Tahunan MPR RI dan Sidang Bersama DPR ...</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688872/delapan-penerima-manfaat-program-pemerintah-hadiri-sidang-tahunan</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001303284.jpg</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Polisi selidiki dugaan penistaan agama dalam festival musik di Ancol</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:28:20 +0700</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Kepolisian tengah mendalami video viral yang memuat dugaan penistaan agama pada kegiatan festival musik "The ...</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688868/polisi-selidiki-dugaan-penistaan-agama-dalam-festival-musik-di-ancol</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000913154.jpg</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Bakamla RI ingin latihan penjaga pantai libatkan seluruh negara ASEAN</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:24:24 +0700</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Badan Keamanan Laut (Bakamla) RI mendorong latihan bersama penjaga pantai ke depan dapat melibatkan lebih banyak negara ...</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688867/bakamla-ri-ingin-latihan-penjaga-pantai-libatkan-seluruh-negara-asean</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_1763.jpeg</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>64 anggota Pramuka Jakpus ikut Jambore Nasional XII di Cibubur</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:22:54 +0700</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Sebanyak 64 kontingen Kwartir Cabang (Kwarcab) Gerakan Pramuka Jakarta Pusat akan mengikuti Jambore Nasional (Jamnas) ...</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688864/64-anggota-pramuka-jakpus-ikut-jambore-nasional-xii-di-cibubur</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000836243.jpg</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Cek fakta, kartu "ATM MBG" untuk penyaluran dana MBG ke siswa</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:22:08 +0700</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan foto di Facebook menampilkan kartu bertuliskan “ATM MBG ...</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688863/cek-fakta-kartu-atm-mbg-untuk-penyaluran-dana-mbg-ke-siswa</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/dapur-mbg-wajib-memiliki-sertifikat-laik-higiene-sanitasi-2835373.jpg</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Pemda Morowali-PT Vale siapkan Desa Wisata Unsongi berbasis komunitas</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:21:19 +0700</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Pemerintah Daerah Morowali, Sulawesi Tengah bersama PT Vale Indonesia Tbk menyiapkan Desa Wisata Unsongi berbasis ...</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688861/pemda-morowali-pt-vale-siapkan-desa-wisata-unsongi-berbasis-komunitas</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/DSC01810.jpg</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>KLH: Pemilah sampah dapat perlindungan sebagai "green collar worker"</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:20:38 +0700</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Menteri Lingkungan Hidup (LH) Jumhur Hidayat menyatakan gerakan mengubah paradigma mengganti istilah pemulung dengan ...</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688859/klh-pemilah-sampah-dapat-perlindungan-sebagai-green-collar-worker</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/DSC03734_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Hoaks! Video Prabowo ancam bongkar bunker rumah Jokowi berisi Rp198 triliun</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:20:36 +0700</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan video di Facebook menampilkan cuplikan Presiden Prabowo ...</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688856/hoaks-video-prabowo-ancam-bongkar-bunker-rumah-jokowi-berisi-rp198-triliun</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-18.34.36.jpeg</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Lebih dari dua pertiga wilayah di Inggris dilanda kekeringan</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:19:34 +0700</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Lebih dari dua pertiga wilayah Inggris kini secara resmi mengalami kekeringan setelah negara tersebut mencatat bulan ...</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688853/lebih-dari-dua-pertiga-wilayah-di-inggris-dilanda-kekeringan</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Sungai-mengering-di-Inggris-Agustus-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>3.000 bendera berkibar di perbatasan sebagai simbol kedaulatan</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:18:27 +0700</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Sebanyak 3.000 Bendera Merah Putih dikibarkan dan dibentangkan di sepanjang kawasan perbatasan Indonesia-Malaysia, ...</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688849/3000-bendera-berkibar-di-perbatasan-sebagai-simbol-kedaulatan</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0199.jpg</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Hoaks! Video Purbaya minta Prabowo agar koruptor dihukum mati</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:18:08 +0700</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan di Facebook menampilkan video yang memperlihatkan Menteri ...</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688845/hoaks-video-purbaya-minta-prabowo-agar-koruptor-dihukum-mati</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/konferensi-pers-kementerian-keuangan-2835033.jpg</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Hoaks! Berita Sandiaga Uno pukul presiden Komisaris BCA Jahja Setaatmadja</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:17:15 +0700</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan di Facebook menampilkan foto mantan Menteri Pariwisata dan ...</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688843/hoaks-berita-sandiaga-uno-pukul-presiden-komisaris-bca-jahja-setaatmadja</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/15/tempImagetS9jey.jpg</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Festival Golo Koe perayaan pertemukan iman dan tradisi di Labuan Bajo</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:10:18 +0700</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Menteri Pariwisata Widiyanti Putri Wardhana menyebut penyelenggaraan Festival Golo Koe yang diselenggarakan pada 10 ...</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688841/festival-golo-koe-perayaan-pertemukan-iman-dan-tradisi-di-labuan-bajo</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-12.08.36.jpeg</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Temuan senjata sekolah, KPAI nilai sekolah lakukan PJJ langkah tepat</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:08:27 +0700</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Komisi Perlindungan Anak Indonesia (KPAI) menilai pihak sekolah yang memutuskan untuk melaksanakan pembelajaran jarak ...</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688839/temuan-senjata-sekolah-kpai-nilai-sekolah-lakukan-pjj-langkah-tepat</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001016850.jpg</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Mentan siapkan langkah strategis atasi kendala peternak ayam</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:07:34 +0700</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Menteri Pertanian (Mentan) Andi Amran Sulaiman mengatakan pemerintah telah mengambil sejumlah langkah untuk mengatasi ...</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688835/mentan-siapkan-langkah-strategis-atasi-kendala-peternak-ayam</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_085244.jpg</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>KPK telusuri sumber dana aset dalam perkara TPPU SYL</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:06:56 +0700</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi (KPK) memastikan penyidikan dugaan tindak pidana pencucian uang (TPPU) dengan tersangka ...</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688832/kpk-telusuri-sumber-dana-aset-dalam-perkara-tppu-syl</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/14/antarafoto-sidang-lanjutan-syahrul-yasin-limpo-070724-adm-4.jpg</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Menpar: Festival Golo Koe 2026 perkuat pariwisata berkelanjutan</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:59:48 +0700</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Menteri Pariwisata Widiyanti Putri Wardhana mengatakan Festival Golo Koe 2026 menjadi ruang untuk mempertemukan iman, ...</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688831/menpar-festival-golo-koe-2026-perkuat-pariwisata-berkelanjutan</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-11.44.02.jpeg</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>KJRI Shanghai gelar "Pesta Rakyat" meriahkan HUT ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:57:12 +0700</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Konsulat Jenderal Republik Indonesia (KJRI) Shanghai menggelar perlombaan khas peringatan hari kemerdekaan bernama ...</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688828/kjri-shanghai-gelar-pesta-rakyat-meriahkan-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Weixin-Image_20260810173744_17_213.jpg</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>BKSDA antisipasi peningkatan konflik satwa akibat karhutla di Kotim</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:56:21 +0700</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Balai Konservasi Sumber Daya Alam (BKSDA) Kalimantan Tengah (Kalteng) mengantisipasi peningkatan konflik satwa liar ...</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688825/bksda-antisipasi-peningkatan-konflik-satwa-akibat-karhutla-di-kotim</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001739583.jpg</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Pemkot Banjarmasin bagikan ribuan bendera Merah Putih ke masyarakat</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:52:27 +0700</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Banjarmasin, Kalimantan Selatan membagikan ribuan Bendera Merah Putih ke masyarakat untuk menyambut HUT ...</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688820/pemkot-banjarmasin-bagikan-ribuan-bendera-merah-putih-ke-masyarakat</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000399300.jpg</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>PBB: Operasi militer Israel di Gaza terus membahayakan warga Palestina</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:52:11 +0700</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Perserikatan Bangsa-Bangsa (PBB) memperingatkan bahwa operasi militer Israel di seluruh Jalur Gaza masih membahayakan ...</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688819/pbb-operasi-militer-israel-di-gaza-terus-membahayakan-warga-palestina</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/thumbs_b_c_2e82e2a00a2bd465dbb33ea6a5681915.jpg</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>BMKG tetapkan Bangka Belitug siaga kekeringan</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:48:38 +0700</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) Provinsi Kepulauan Bangka Belitung menetapkan Kepulauan Babel ...</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688817/bmkg-tetapkan-bangka-belitug-siaga-kekeringan</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/kering2.jpg</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Pemprov Jabar Distribusikan 8,7 Juta Liter Air ke Warga Selama Kemarau</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:26:20 +0700</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Jawa Barat mendistribusikan 8,7 juta liter air bersih ke 23 kabupaten/kota untuk mengatasi kekeringan.</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613522/pemprov-jabar-distribusikan-8-7-juta-liter-air-ke-warga-selama-kemarau</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/26/banyak-seribu-orang-mengalami-krisis-air-bersih-di-jonggol-jogor-jawa-barat-jabar-1785045511783.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Legislator Gerindra Beri Bantuan untuk SD Plus Muhammadiyah Sungai Penuh</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:23:02 +0700</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Anggota DPR Rocky Candra menyerahkan bantuan Rp 300 juta untuk pembangunan SD Plus Muhammadiyah Kota Sungai Penuh, mendukung pendidikan dan motivasi siswa.</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613519/legislator-gerindra-beri-bantuan-untuk-sd-plus-muhammadiyah-sungai-penuh</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/legislator-gerindra-beri-bantuan-untuk-pembangunan-sd-di-sungai-penuh-1786428959007_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Perkelahian Saat Kondangan, Pria di Bekasi Tumbang Usai Dikepruk Batu</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:15:44 +0700</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Pria berinisial DAP (21) ditangkap usai memukul korban M (27) menggunakan batu hingga korban terluka di Kecamatan Cabangbungin, Kabupaten Bekasi.</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613514/perkelahian-saat-kondangan-pria-di-bekasi-tumbang-usai-dikepruk-batu</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/pria-berinisial-dap-21-ditangkap-usai-memukul-korban-m-27-menggunakan-batu-hingga-korban-terluka-di-kecamatan-cabangbungin-kab-1786428820728_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Ikuti Google Maps, Pemotor di Bogor Malah Masuk ke Tol Jagorawi</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Pengendara motor DK tersesat di Tol Jagorawi Km 39, Bogor, akibat tidak tahu jalan. Ia menggunakan Google Maps dan dihentikan petugas.</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613501/ikuti-google-maps-pemotor-di-bogor-malah-masuk-ke-tol-jagorawi</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/ikuti-goole-maps-pemotor-di-bogor-malah-masuk-ke-tol-jagorawi-1786428367396_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>STSB 2026 Jadi Momentum Hadirkan Suara Daerah dalam Arah Kebijakan Nasional</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:09:17 +0700</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Nasywa Azzahra</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>DPD RI siap selenggarakan Sidang Bersama DPR RI-DPD RI 2026 untuk mendengarkan Pidato Kenegaraan Presiden.</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613499/stsb-2026-jadi-momentum-hadirkan-suara-daerah-dalam-arah-kebijakan-nasional</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/wakil-ketua-dpd-ri-bidang-otonomi-daerah-politik-dan-hukum-gusti-kanjeng-ratu-hemas-1786428349206.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Pemprov Jabar Dukung MMS Jadi Ruang Silaturahmi &amp;amp; Gagasan Tokoh Sunda</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:05:39 +0700</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Jabar dukung Majelis Musyawarah Sunda (MMS) sebagai wadah silaturahmi dan pertukaran gagasan untuk pembangunan daerah.</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613487/pemprov-jabar-dukung-mms-jadi-ruang-silaturahmi-gagasan-tokoh-sunda</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/pemprov-jabar-dukung-mms-jadi-ruang-silaturahmi-gagasan-tokoh-sunda-1786428211415_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Geger Mayat Bayi Terbungkus Plastik Ditemukan dalam Tong Sampah di Depok</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:58:11 +0700</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Jasad bayi laki-laki ditemukan di tempat sampah di Depok. Mayat bayi tersebut terbungkus plastik merah.</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613474/geger-mayat-bayi-terbungkus-plastik-ditemukan-dalam-tong-sampah-di-depok</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/07/07/04d6bdb2-2cac-4687-93cd-130c776b3edd_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Heboh 36 Kambing Milik Warga Tergeletak Disembelih Maling di Sawah Serang</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:54:40 +0700</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Puluhan kambing di Kampung Setu, Desa Sukajaya, Kecamatan Pontang, Kabupaten Serang, tergeletak disembelih maling.</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613464/heboh-36-kambing-milik-warga-tergeletak-disembelih-maling-di-sawah-serang</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/lokasi-kandang-kambing-yang-dicuri-ariefdetikcom-1786427491486_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Wanita di Bekasi Dibegal hingga Tersungkur Berujung Motor Dibawa Kabur</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:52:58 +0700</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Seorang wanita menjadi korban pembegalan di Bekasi Utara. Pelaku berhasil merampas motor dan barang milik korban. Polisi masih memburu pelaku.</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613460/wanita-di-bekasi-dibegal-hingga-tersungkur-berujung-motor-dibawa-kabur</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/wanita-di-bekasi-dibegal-hingga-tersungkur-1786427513531_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>BNPP Raih Opini WTP ke-12 dari BPK atas Laporan Keuangan Tahun 2025</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:49:56 +0700</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Tenri Monic Libery Hana</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>BNPP RI meraih opini WTP ke-12 dari BPK RI. Makhruzi menekankan pentingnya evaluasi untuk pengelolaan keuangan yang lebih baik.</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613455/bnpp-raih-opini-wtp-ke-12-dari-bpk-atas-laporan-keuangan-tahun-2025</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/bnpp-raih-opini-wtp-ke-12-dari-bpk-atas-laporan-keuangan-tahun-2025-1786427331042_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Polisi Panggil EO Konser dan MC Buntut Challenge Hafalan Qur'an demi Miras</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:45:08 +0700</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Polisi selidiki dugaan penistaan agama terkait promosi miras dalam tantangan hafalan Al-Qur'an di konser The Sounds Project. Penyelenggara mengecam insiden ini.</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613448/polisi-panggil-eo-konser-dan-mc-buntut-challenge-hafalan-quran-demi-miras</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2018/03/30/61dc834f-d526-4893-93c5-e864929ef5ee_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>PDIP Kecam Challenge Hafalan Qur'an demi Miras: Agama Jangan Dijadikan Gimik</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:41:09 +0700</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Ia meminta pihak yang terlibat dapat membedakan kreativitas dalam promosi dengan tindakan yang merendahkan simbol dan kesakralan agama.</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613443/pdip-kecam-challenge-hafalan-quran-demi-miras-agama-jangan-dijadikan-gimik</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/04/09/waduh-di-china-ada-tren-baru-mukbang-minum-miras-yang-berbahaya-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Mensesneg dan Seskab Cek Gladi Parsial Upacara HUT RI di Istana</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:38:48 +0700</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Firda Cynthia Anggrainy</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Istana Merdeka menggelar gladi parsial HUT ke-81 RI. Mensesneg Prasetyo Hadi memeriksa persiapan, termasuk penambahan 3.400 undangan untuk masyarakat.</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613437/mensesneg-dan-seskab-cek-gladi-parsial-upacara-hut-ri-di-istana</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/mensesneg-dan-seskab-cek-gladi-parsial-upacara-hut-ri-di-istana-1786426651744_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Jaksa KPK: Yaqut Siapkan Rp 17,8 M untuk Pengaruhi Hasil Pansus Haji DPR</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:36:10 +0700</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Jaksa KPK menyebut mantan Menag Yaqut Cholil Qoumas siapkan USD 1 juta untuk pengaruhi hasil Pansus Angket Haji 2024.</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613434/jaksa-kpk-yaqut-siapkan-rp-17-8-m-untuk-pengaruhi-hasil-pansus-haji-dpr</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/kpk-perpanjang-penahanan-yaqut-di-kasus-kuota-haji-1778230419632_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Ali Masykur Musa Dorong NU Jadi Kekuatan Soft Diplomacy Dunia</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:32:31 +0700</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Ketua Umum NU, Ali Masykur, dorong NU perkuat peran global melalui soft diplomacy. NU diharapkan jadi kekuatan untuk menciptakan kehidupan damai dan seimbang.</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613432/ali-masykur-musa-dorong-nu-jadi-kekuatan-soft-diplomacy-dunia</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/ali-masykur-musa-dorong-nu-jadi-kekuatan-soft-diplomacy-dunia-1786426279178_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Istana Jamin Driver Ojol Tetap Dapat BHR Meski Jadi UMKM</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:36:44 +0700</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Prasetyo menyatakan driver ojol akan tetap mendapatkan BHR.</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613542/istana-jamin-driver-ojol-tetap-dapat-bhr-meski-jadi-umkm</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/mensesneg-prasetyo-hadi-1784627991720_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Airlangga Minta UMKM RI Belajar dari India: Jangan Cuma Produksi</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:30:07 +0700</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Menteri Airlangga Hartarto mendorong Indonesia belajar dari India untuk memajukan UMKM.</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613527/airlangga-minta-umkm-ri-belajar-dari-india-jangan-cuma-produksi</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/05/momen-airlangga-pamer-ekonomi-ri-tumbuh-lebih-tinggi-dari-as-china-1777977745900_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>OJK Ungkap Cuma 3,51% UMKM Punya Laporan Keuangan, Bikin Susah Dapat Kredit</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:09:01 +0700</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>OJK laporkan pembiayaan UMKM mencapai Rp 1.948,72 triliun per Juni 2026. Tantangan akses pembiayaan formal masih ada, terutama terkait laporan keuangan.</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613498/ojk-ungkap-cuma-3-51-umkm-punya-laporan-keuangan-bikin-susah-dapat-kredit</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pemerintah-kejar-rasio-wirausaha-8-persen-pada-2045-1785739243820_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Airlangga Minta UMKM Pakai Peserta Magang, 6 Bulan Gaji Ditanggung Pemerintah</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:47:45 +0700</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Menteri Airlangga dorong UMKM manfaatkan program magang nasional untuk tingkatkan kualitas SDM.</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613450/airlangga-minta-umkm-pakai-peserta-magang-6-bulan-gaji-ditanggung-pemerintah</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/13/menko-perekonomian-airlangga-hartarto-1783940653691_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Buruh Minta RUU Ketenagakerjaan Beri Rasa Keadilan</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:33:10 +0700</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Buruh bertemu Cak Imin untuk bahas RUU Ketenagakerjaan. Pimpinan konfederasi buruh minta dukungan PKB agar usulan mereka dibahas di DPR.</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613529/buruh-minta-ruu-ketenagakerjaan-beri-rasa-keadilan</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/27/may-day-2026-di-monas-diperkirakan-dihadiri-200-ribu-buruh-1777297065034_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Rizky Billar Dampingi Lesti Kejora dan Asila Jalani Pemeriksaan di PMJ</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:06:13 +0700</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Lesti Kejora dan Asila Maisa menjalani pemeriksaan sebagai saksi kasus dugaan penyebaran hoax di Polda Metro Jaya. Rizky Billar mendampingi sang istri.</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613489/rizky-billar-dampingi-lesti-kejora-dan-asila-jalani-pemeriksaan-di-pmj</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rizky-billar-lesti-kejora-dan-asilla-1786424585636_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Jaksa: Pengisian Kuota Haji Tambahan Satu Pintu Lewat Fuad Maktour</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:38:46 +0700</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Jaksa KPK ungkap dugaan korupsi pengisian kuota haji 2023-2024, melibatkan eks Menag Yaqut Cholil dan Fuad Hasan Masyhur Maktour.</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811125300-12-1390975/jaksa-pengisian-kuota-haji-tambahan-satu-pintu-lewat-fuad-maktour</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/18/kpk-periksa-fuad-hasan-masyhur-terkait-korupsi-haji-1781779639287_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Kondisi Pendakwah Anwar Zahid Usai Mobil Ditabrak Truk di Bojonegoro</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:26:41 +0700</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Pendakwah Anwar Zahid kecelakaan usai mobil ditabrak truk di Bojonegoro, Jawa Timur.</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811130054-20-1390977/kondisi-pendakwah-anwar-zahid-usai-mobil-ditabrak-truk-di-bojonegoro</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/pendakwah-anwar-zahid-kecelakaan-mobil-dihantam-truk-trailer-di-bojonegoro-1786422003014_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Polisi Periksa EO dan MC Usut Challenge Hafalan Al-Qu'ran Demi Miras</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:11:33 +0700</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Polisi periksa EO dan MC terkait promosi miras berkedok tantangan hafalan Al-Qur'an di festival musik.</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811125249-12-1390974/polisi-periksa-eo-dan-mc-usut-challenge-hafalan-al-quran-demi-miras</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/07/19/a834d1e4-4ec1-4741-af36-0730db51a562_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Karhutla Bromo Meluas Hingga 899 Hektare</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:00:24 +0700</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan dan lahan kawasan Gunung Bromo di Taman Nasional Bromo Tengger Semeru (TNBTS) terus meluas hingga mencapai 899 hektare, Selasa (12/8).</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811124420-20-1390971/karhutla-bromo-meluas-hingga-899-hektare</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/upaya-pemadaman-kebakaran-hutan-di-kawasan-tnbts-1786344599012_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Jaksa Ungkap SK Menag soal Kuota Haji Tambahan Dibuat Tanggal Mundur</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:54:58 +0700</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Jaksa dalam dakwaannya mengungkapkan Surat Keputusan Menteri Agama (KMA) Tahun 2023 tentang Kuota Haji Tambahan dibuat tanggal mundur atau backdate.</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811122807-12-1390962/jaksa-ungkap-sk-menag-soal-kuota-haji-tambahan-dibuat-tanggal-mundur</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/sidang-perdana-yaqut-cholil-qoumas-1786422428194_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Kecelakaan Maut Drag Race Kotamobagu, Pembalap Berpotensi Tersangka</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:46:00 +0700</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Polda Sulut ambil alih kasus kecelakaan drag race di Kotamobagu yang menewaskan 8 orang. Pembalap berpotensi menjadi tersangka.</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811122803-12-1390969/kecelakaan-maut-drag-race-kotamobagu-pembalap-berpotensi-tersangka</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/09/28/ba5e99b8-5d8e-49d5-bb76-aa2dd0f276f0_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>MBG untuk Semua: Sama Rasa, Tak Bersekat</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:45:26 +0700</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Program MBG di SDN Gentan memberikan akses makanan sehat bagi semua siswa, menciptakan kebersamaan dan kesetaraan tanpa memandang latar belakang.</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811123703-20-1390967/mbg-untuk-semua-sama-rasa-tak-bersekat</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/mbg-untuk-semua-1785909513152_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>FOTO: Sidang Perdana Kasus Kuota Haji Eks Menag Yaqut</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:26:03 +0700</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Mantan Menteri Agama Yaqut Cholil Qoumas menjalani sidang perdana perkara dugaan korupsi pengelolaan kuota haji tambahan 2023-2024.</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811115318-14-1390932/foto-sidang-perdana-kasus-kuota-haji-eks-menag-yaqut</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/sidang-perdana-yaqut-cholil-qoumas-1786422428262_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Keluarga Akui Sutrimo Kerja untuk Febrie: Berawal dari Tukang Bangunan</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:18:14 +0700</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Kepolisian menyelidiki kematian Sutrimo, mantan pekerja Febrie Adriansyah. Keluarga curiga ada kejanggalan dan laporkan kasus ini ke polisi.</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811111552-12-1390923/keluarga-akui-sutrimo-kerja-untuk-febrie-berawal-dari-tukang-bangunan</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/09/keluarga-sutrimo-didampingi-kuasa-hukum-membuat-laporan-ke-polresta-banyumas-1786243465746_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Cek Kesehatan ke Amerika, SBY Tak Hadir Sidang Tahunan MPR</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:05:50 +0700</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Presiden ke-6 RI SBY disebut tak dapat tidak hadir dalam Sidang Tahunan MPR pada 14 Agustus karena menjalani pemeriksaan kesehatan di Amerika.</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811115245-32-1390931/cek-kesehatan-ke-amerika-sby-tak-hadir-sidang-tahunan-mpr</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2014/09/27/f2d71c5c-15f7-4c91-a4c3-84da80af52ec_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Polisi Usut Challenge Surah Al-Qur'an Demi Miras</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:59:50 +0700</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Polisi selidiki promosi miras berkedok tantangan hafalan Al-Qur'an di festival musik. MUI telah keluarkan kecaman aksi yang viral itu.</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811114020-12-1390927/polisi-usut-challenge-surah-al-quran-demi-miras</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/02/19/2031beff-45a7-4456-8bd2-e8dac34fdf9f_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Jaksa KPK Beber Daftar 27 Nama yang Diperkaya dari Kasus Kuota Haji</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:52:07 +0700</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Jaksa KPK menyebut mantan Menteri Agama Yaqut Cholil Qoumas memperkaya diri US$271.500 atau sekitar Rp4,8 miliar terkait kasus dugaan korupsi kuota haji.</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811114412-12-1390929/jaksa-kpk-beber-daftar-27-nama-yang-diperkaya-dari-kasus-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/sidang-perdana-yaqut-cholil-qoumas-1786422428194_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Kecurigaan Keluarga dan Komunikasi Terakhir Sutrimo Sebelum Tewas</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:47:10 +0700</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Keluarga curiga atas kematian Sutrimo. Mereka mempertanyakan penyebab kematian dan barang-barang pribadi almarhum yang belum dikembalikan.</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811103454-12-1390904/kecurigaan-keluarga-dan-komunikasi-terakhir-sutrimo-sebelum-tewas</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/27/olah-tkp-kasus-kematian-sutrimo-1785144097593_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Siswi SMA Tertemper di Stasiun Jurangmangu Dimakamkan di TPU Marabunta</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:19:15 +0700</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Siswi SMA, AP (14), meninggal setelah tertemper KRL di Stasiun Jurangmangu. Proses penyelidikan masih berlangsung, belasungkawa disampaikan.</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811111521-20-1390921/siswi-sma-tertemper-di-stasiun-jurangmangu-dimakamkan-di-tpu-marabunta</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/02/13/melihat-stasiun-manggarai-saat-jam-pulang-kerja-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Sebelum Ditemukan Tewas, Sutrimo Kirim Foto Rumah Febrie ke Keluarga</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:18:04 +0700</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Polisi akan ekshumasi makam Sutrimo, yang disebut sebagai Kepala Rumah Tangga eks Jampidsus Febrie, untuk menyelidiki dugaan kematian janggalnya.</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811100839-12-1390901/sebelum-ditemukan-tewas-sutrimo-kirim-foto-rumah-febrie-ke-keluarga</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/09/keluarga-sutrimo-didampingi-kuasa-hukum-membuat-laporan-ke-polresta-banyumas-1786243465746_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Eks Menag Yaqut Didakwa Rugikan Negara Rp622 M di Kasus Kuota Haji</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:13:13 +0700</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Mantan Menag Yaqut Cholil Qoumas didakwa merugikan negara Rp622 miliar dalam kasus korupsi kuota haji 2023-2024. Tiga terdakwa lain terlibat.</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811110621-12-1390918/eks-menag-yaqut-didakwa-rugikan-negara-rp622-m-di-kasus-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/mantan-menteri-agama-ri-era-presiden-ke-7-joko-widodo-yaqut-cholil-qoumas-menyatakan-siap-menghadapi-persidangan-dakwaan-1786418523137_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Pendakwah Anwar Zahid Kecelakaan, Mobil Dihantam Truk di Bojonegoro</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:06:10 +0700</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Pendakwah KH Anwar Zahid dilaporkan mengalami kecelakaan dalam perjalanan menuju Kabupaten Banjarnegara, Jawa Tengah, untuk mengisi pengajian.</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811105656-20-1390913/pendakwah-anwar-zahid-kecelakaan-mobil-dihantam-truk-di-bojonegoro</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/09/28/803b1081-121c-4035-b949-47fd3f52f655_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Polisi Periksa Teman Siswi SMA yang Tertemper KRL di Jurangmangu</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:46:17 +0700</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Polisi selidiki kematian siswi SMA berinisial AP yang tertemper KRL di Stasiun Jurangmangu. Penyebab pasti masih dalam penyelidikan.</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811103724-20-1390905/polisi-periksa-teman-siswi-sma-yang-tertemper-krl-di-jurangmangu</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/pelajar-16-tahun-tewas-tertemper-krl-di-stasiun-jurangmangu-tangsel-1786367206988_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Rudy Tanoe Penuhi Panggilan KPK</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:43:13 +0700</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Bambang Rudijanto Tanoesoedibjo penuhi panggilan untuk diperiksa sebagai saksi dugaan korupsi bansos beras untuk Keluarga Penerima Manfaat (KPM).</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811103148-12-1390903/rudy-tanoe-penuhi-panggilan-kpk</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/12/14/bambang-rudijanto-tanoesoedibjo_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Eks Menag Yaqut Jelang Sidang Hari Ini: Semua yang Benar Akan Terlihat</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:27:21 +0700</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Mantan Menag era Presiden Jokowi, Yaqut Cholil Qoumas tiba di Pengadilan Tipikor Jakarta hari ini untuk menjalani sidang perdana kasus korupsi kuota haji.</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811101811-12-1390897/eks-menag-yaqut-jelang-sidang-hari-ini-semua-yang-benar-akan-terlihat</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/mantan-menteri-agama-ri-era-presiden-ke-7-joko-widodo-yaqut-cholil-qoumas-menyatakan-siap-menghadapi-persidangan-dakwaan-1786418397643_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Kasus Senjata di Sekolah Jaksel, Puslabfor Lakukan Uji Sampel DNA</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:14:31 +0700</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Puslabfor Polri diterjunkan untuk menguji sampel DNA dalam penyelidikan kasus temuan ratusan senjata di yayasan sekolah swasta di Pondok Pinang, Kebayoran Lama.</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811095734-12-1390890/kasus-senjata-di-sekolah-jaksel-puslabfor-lakukan-uji-sampel-dna</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308187_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Karhutla di Gunung Andong Magelang, 3,67 Hektare Hutan Hangus</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:10:40 +0700</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Karhutla terjadi di Gunung Andong, Magelang, awal pekan ini. Tim relawan dan aparat berhasil memadamkan api setelah 4 jam.</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811093540-20-1390885/karhutla-di-gunung-andong-magelang-367-hektare-hutan-hangus</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/07/16/90967674-7d0f-4992-ad54-242680fb814f_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>FOTO: KPK Tahan 4 Tersangka Kasus Korupsi Iklan bank bjb</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:09:51 +0700</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>KPK menahan empat tersangka kasus dugaan korupsi pengadaan iklan di Bank Pembangunan Daerah Jawa Barat dan Banten (bank bjb) tahun anggaran 2021-2023.</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811090549-14-1390872/foto-kpk-tahan-4-tersangka-kasus-korupsi-iklan-bank-bjb</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/kpk-tahan-tersangka-kasus-korupsi-pengadaan-iklan-bank-bjb-1786409946607_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>DPR Rapat dengan Polda dan Keluarga Istri Eks Polisi yang Tewas di Medan</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:05:04 +0700</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Komisi III DPR RI akan menggelar RDPU dengan Polda Sumut terkait kematian perempuan berinisial L. Keluarga korban diundang untuk memberikan keterangan.</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811095104-12-1390887/dpr-rapat-dengan-polda-keluarga-istri-eks-polisi-yang-tewas-di-medan</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/13/konferensi-pers-komisi-iii-dpr-terkait-ruu-perampasan-aset-1783941931109_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Kortas Tipidkor Sebut Dedi Congor Jadi Tersangka Kasus Gratifikasi</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:02:37 +0700</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Eks Kepala KPPBC Marunda, Dedi Congor, ditetapkan sebagai tersangka gratifikasi oleh Kortas Tipidkor Polri. Penyidikan berlangsung sejak 2017 hingga 2023.</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811092724-12-1390881/kortas-tipidkor-sebut-dedi-congor-jadi-tersangka-kasus-gratifikasi</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/07/24/0676200f-0af8-4c87-a754-bff6467e55d7_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Pria di Tangerang Rekayasa Pembunuhan Pacar Seolah Gantung Diri</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:41:06 +0700</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Kasus pembunuhan ini terungkap usai petugas curiga menemukan korban tewas dalam kondisi tergantung namun dengan posisi telapak kaki menyentuh lantai.</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811091234-12-1390879/pria-di-tangerang-rekayasa-pembunuhan-pacar-seolah-gantung-diri</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/05/30/ilustrasi-penangkapan-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Perwira TNI AL Didakwa Edarkan 9,83 Gram Sabu, Istri Cari Pembeli</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:33:08 +0700</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Mayor Laut (P) Faisal Mulia didakwa mengedarkan 14 paket sabu seberat 9,83 gram. Ia ditangkap saat berusaha mengirim narkoba ke Jakarta.</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811075715-12-1390845/perwira-tni-al-didakwa-edarkan-983-gram-sabu-istri-cari-pembeli</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/08/09/ilustrasi-sabu-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Siswa di Pontianak Sekolah Daring Imbas Asap Karhutla, Kasus ISPA Naik</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:53:11 +0700</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Pontianak meliburkan pembelajaran tatap muka untuk siswa TK hingga SMP akibat kabut asap. Kegiatan belajar dialihkan ke daring.</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811080741-20-1390848/siswa-di-pontianak-sekolah-daring-imbas-asap-karhutla-kasus-ispa-naik</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/08/20/fc3978e8-99a0-447c-9b22-37eb89383e6c_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Darurat Karhutla, Kabut Asap Selimuti Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:47:12 +0700</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Kabut asap akibat kebakaran hutan menyelimuti Kota Pontianak. Status darurat telah ditetapkan seiring jebloknya kualitas udara peningkatan kasus ISPA.</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811082546-12-1390860/darurat-karhutla-kabut-asap-selimuti-kota-pontianak</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/03/08/bmkg-kalbar-deteksi-206-titik-panas-1772970329606_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Tiga Peringatan MUI soal Agustusan: Pria Berbusana Wanita, Uang Lomba</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:23:01 +0700</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>MUI mengeluarkan fatwa larangan pria berbusana perempuan saat karnaval 17 Agustus. Juga diingatkan soal uang lomba yang berpotensi judi.</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811070625-20-1390838/tiga-peringatan-mui-soal-agustusan-pria-berbusana-wanita-uang-lomba</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/16/semarak-lomba-peringatan-hut-ke-80-kemerdekaan-ri-1755340255019_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Kebakaran Hebat di Permukiman Padat Makassar Hanguskan 37 Rumah</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:10:02 +0700</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Kebakaran hebat di permukiman padat penduduk di Makassar, Sulsel, menghanguskan 37 rumah yang dihuni 245 warga.</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811072559-20-1390843/kebakaran-hebat-di-permukiman-padat-makassar-hanguskan-37-rumah</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/02/situasi-terkini-pascakebakaran-kemayoran-1780381697458_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Risma dan Andreas Buka Peluang Ekspor bagi UMKM Eks Lokalisasi Dolly</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:06:39 +0700</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Mantan Wali Kota Surabaya Tri Rismaharini (Risma) mendorong UMKM di eks Lokalisasi Dolly dibukakan peluang ekspor agar produk mereka go internatioal.</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811080238-37-1390847/risma-dan-andreas-buka-peluang-ekspor-bagi-umkm-eks-lokalisasi-dolly</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/mantan-wali-kota-surabaya-tri-rismaharini-risma-dan-anggota-dpr-ri-andreas-eddy-susetyo-andreas-memberi-semangat-pada-ratusan--1786410197504_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Eks Menag Yaqut Jalani Sidang Perdana Kasus Kuota Haji Hari Ini</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:52:01 +0700</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Mantan Menag Yaqut Cholil Qoumas akan menjalani sidang perdana dugaan korupsi kuota haji 2023-2024. Kerugian negara diperkirakan mencapai Rp622 miliar.</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811061947-12-1390826/eks-menag-yaqut-jalani-sidang-perdana-kasus-kuota-haji-hari-ini</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/10/kpk-perpanjang-masa-penahanan-yaqut-cholil-qoumas-1778411257054_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>KPK Ungkap Aliran Dana di Kasus Bank Pembangunan Daerah</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:22:01 +0700</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>KPK ungkap penyalahgunaan dana iklan di bank bjb. Empat tersangka ditahan, termasuk pejabat bank dan pengusaha. Penyidikan terus berlanjut.</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811063825-12-1390832/kpk-ungkap-aliran-dana-di-kasus-bank-pembangunan-daerah</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/12/pengungkapan-suap-audit-laporan-keuangan-di-kabupaten-muara-enim-1781244746815_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>MUI Kecam Challenge Hafalan Surah Ad-Duha Demi Miras, MC Minta Maaf</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:08:44 +0700</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>MUI mengecam promosi miras berkedok tantangan hafalan Alquran yang terjadi di Festival Musik The Sound Project. Penyelenggara acara buka suara, MC minta maaf.</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811062448-12-1390828/mui-kecam-challenge-hafalan-surah-ad-duha-demi-miras-mc-minta-maaf</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/02/19/42d39253-de5d-4f1f-a565-ab661c227e40_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Wagub Jatim Beber Kendala Padamkan Kebakaran Bromo dengan Helikopter</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:51:03 +0700</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Wakil Gubernur Jatim Emil Dardak mengungkap kendala pemadaman kebakaran hutan di Bromo, termasuk cuaca kabut dan keterbatasan operasional helikopter.</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260811062057-20-1390829/wagub-jatim-beber-kendala-padamkan-kebakaran-bromo-dengan-helikopter</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/07/30/pemprov-jatim-butuh-56-hari-untuk-normalkan-pasokan-bbm-di-jember-1753857430597_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Daftar Kepala Daerah Pecah Kongsi di Tengah Isu Pilkada Tanpa Wakil</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:26:00 +0700</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Perselisihan antara kepala daerah dan wakilnya memicu wacana pilkada tanpa wakil. Kritik muncul karena wakil dianggap cuma vote getter.</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810195445-32-1390766/daftar-kepala-daerah-pecah-kongsi-di-tengah-isu-pilkada-tanpa-wakil</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/02/04/ilustrasi-pemilu_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Kebakaran Bromo Terus Meluas Capai 742 Hektare</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:15:33 +0700</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Karhutla di Gunung Bromo meluas hingga 742 hektare. Pemadaman melibatkan helikopter hingga akses wisata ditutup sementara.</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810193705-20-1390758/kebakaran-bromo-terus-meluas-capai-742-hektare</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/upaya-pemadaman-kebakaran-hutan-di-kawasan-tnbts-1786344599012_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Pakar Ungkap Pilkada Tanpa Wakil Berpotensi Langgar UUD</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:06:46 +0700</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Wacana pilkada tanpa wakil dinilai berisiko bagi demokrasi. Peneliti Perludem menekankan pentingnya perjanjian tugas untuk mencegah konflik kepala daerah.</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810195803-32-1390764/pakar-ungkap-pilkada-tanpa-wakil-berpotensi-langgar-uud</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/12/01/rekapitulasi-berjenjang-pilkada-jakarta-7_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Wagub Jatim Ungkap Dugaan Awal Kebakaran Bromo: Kelalaian Manusia</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Wakil Gubernur Jatim Emil Dardak mengungkap dugaan kelalaian manusia sebagai penyebab kebakaran di Gunung Bromo. Fokus saat ini adalah pemadaman api.</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810213650-20-1390794/wagub-jatim-ungkap-dugaan-awal-kebakaran-bromo-kelalaian-manusia</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/upaya-pemadaman-kebakaran-hutan-di-kawasan-tnbts-1786344598877_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Hasto: PDIP Tak Setuju Pilkada Tanpa Wakil Kepala Daerah</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:15:23 +0700</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>PDIP menolak wacana Pilkada tanpa calon wakil kepala daerah. Hasto menegaskan pentingnya peran wakil dalam pemerintahan dan menyiapkan calon secara sistemik.</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810214522-32-1390797/hasto-pdip-tak-setuju-pilkada-tanpa-wakil-kepala-daerah</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/20/hasto-tunggu-jawaban-bgn-soal-kader-pdip-terlibat-proyek-mbg-1784532554386_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Pemerintah Sebut Asap Karhutla Belum Ganggu Negara Tetangga</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 04:15:27 +0700</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Pemerintah Indonesia memastikan asap karhutla belum mengganggu negara tetangga. Upaya antisipasi terus dilakukan, termasuk operasi modifikasi cuaca.</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810170313-20-1390704/pemerintah-sebut-asap-karhutla-belum-ganggu-negara-tetangga</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kemenko-polkam-pastikan-situasi-nasional-aman-1785924470850_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Gugatan Gelar Pahlawan Bergulir</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 03:00:51 +0700</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Proses hukum gelar Pahlawan Nasional Soeharto berlanjut di PTUN Jakarta. Ahli warisnya, Tutut, kini menjadi Tergugat II Intervensi.</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810180404-12-1390725/gugatan-gelar-pahlawan-bergulir</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/11/10/aksi-tolak-gelar-pahlawan-soeharto-1762772653866_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Suami Polisi Gerebek Polwan Diduga Selingkuh, Polda Maluku Buka Suara</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 02:00:09 +0700</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Seorang polwan digerebek suaminya yang juga polisi karena diduga berselingkuh di sebuah kos di Kota Ambon. Polda Maluku buka suara.</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810093111-12-1390447/suami-polisi-gerebek-polwan-diduga-selingkuh-polda-maluku-buka-suara</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/05/31/ilustrasi-love-story-suami-selingkuh_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Diintai 3 Bulan, Kapal King Sun Penyelundup Narkoba di Kepri Ditangkap</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:30:55 +0700</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>TNI AL dan instansi terkait gagalkan penyelundupan 1,3 ton ketamine dari kapal MV King Sun. Delapan awak kapal, termasuk WN Myanmar dan Taiwan, diamankan.</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810145725-20-1390638/diintai-3-bulan-kapal-king-sun-penyelundup-narkoba-di-kepri-ditangkap</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/09/kasus-penyeludupan-13-ton-ketamin-1786267600728_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Polisi Minta Korban Pemaksaan Aborsi Duta Wisata Jatim Segera Melapor</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 00:01:24 +0700</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Polisi imbau korban dugaan pemaksaan aborsi oleh Tio Ferdian Rahmana untuk melapor. Tio, Duta Wisata Jatim, dipecat Pemkot Surabaya setelah kasus ini mencuat.</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810212324-12-1390790/polisi-minta-korban-pemaksaan-aborsi-duta-wisata-jatim-segera-melapor</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2014/11/27/7569bc98-96e0-4f82-9c43-509d15cd0796_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Trump: Selat Hormuz Kami Kuasai 100 Persen, Blokade Mustahil Gagal</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:21:11 +0700</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump kembali sesumbar bahwa pasukannya berhasil menguasai Selat Hormuz sepenuhnya.</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811120044-120-1390941/trump-selat-hormuz-kami-kuasai-100-persen-blokade-mustahil-gagal</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/06/presiden-amerika-donald-trump-1780743453641_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Usai di RI, WN Malaysia Ditangkap di Bandara India karena Bawa Narkoba</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:48:59 +0700</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Seorang warga Malaysia ditangkap di Bandara Internasional Chennai, India, karena diduga menyelundupkan narkoba.</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811121720-113-1390945/usai-di-ri-wn-malaysia-ditangkap-di-bandara-india-karena-bawa-narkoba</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/05/30/ilustrasi-penangkapan-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Trump Ngotot Minta Iran Bayar Kompensasi Perang Timteng</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:03:03 +0700</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat (AS) Donald Trump ngotot meminta kompensasi ke Iran untuk perangnya di Timur Tengah.</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811100833-134-1390894/trump-ngotot-minta-iran-bayar-kompensasi-perang-timteng</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/07/donald-trump-1778122334131_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Malaysia Dibekap Kabut Asap Imbas Kebakaran Hutan di RI</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:27:26 +0700</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Kabut asap menyelimuti Malaysia hingga dua negara bagian mencatat kualitas udara buruk, buntut kebakaran hutan dan lahan (karhutla) di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811104106-106-1390906/malaysia-dibekap-kabut-asap-imbas-kebakaran-hutan-di-ri</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/kawasan-bromo-kebakaran-hebat-1785799173478_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Influencer Rekam Horornya Gempa M 7,4 Guncang Bandara di Kolombia</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:55:31 +0700</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Seorang pria merekam detik-detik gempa M 7,4 saat mengguncang Bandara Matecana di Pereira, Kolombia, Senin (10/8).</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811100413-139-1390893/influencer-rekam-horornya-gempa-m-74-guncang-bandara-di-kolombia</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/thumbnail-video-1786417752247_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Viral Sex Toy Dikira Korban Pembunuhan di Australia</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:07:28 +0700</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Sebuah sex toy di Australia dikira korban pembunuhan, membuat heboh warga usai ditemukan di dalam koper di sebuah pedesaan.</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811054029-113-1390821/viral-sex-toy-dikira-korban-pembunuhan-di-australia</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2017/06/30/04072393-3343-4ed9-9d2e-a43bc0ea1c33_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Gempa Terkuat Dalam Sejarah Kolombia, 111 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:35:15 +0700</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Gempa dahsyat berkekuatan magnitudo 7,4 mengguncang sejumlah kota di Kolombia dan menyebabkan kerusakan parah pada Senin (10/8).</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811081126-139-1390850/gempa-terkuat-dalam-sejarah-kolombia-111-orang-tewas</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/gempa-terkuat-di-kolombia-111-orang-tewas-1786410872054_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Banjir Picu Tanah Longsor di Filipina, 12 Tewas 8 Hilang</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:05:05 +0700</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Banjir dan tanah longsor di Filipina telah menewaskan 12 orang dan melukai 13 orang. Sebanyak delapan orang sementara itu dilaporkan masih hilang.</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811080818-106-1390849/banjir-picu-tanah-longsor-di-filipina-12-tewas-8-hilang</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/asia-weatherphilippines-1786410714743_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>AS-Korsel Simulasi Perang Waspada Taktik Baru Tentara Korut di Ukraina</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:35:15 +0700</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Militer Korsel dan AS akan menggelar latihan militer "Ulchi Freedom Shield" pekan depan untuk menghadapi pertahanan melawan pasukan Korea Utara.</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810210431-113-1390787/as-korsel-simulasi-perang-waspada-taktik-baru-tentara-korut-di-ukraina</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/10/01/melihat-latihan-perang-angkatan-bersenjata-korsel-5_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Mojtaba Khamenei Tunjuk 2 Jenderal Pimpin IRGC dan Militer Iran</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Mojtaba tunjuk Ali Abdollahi pimpin angkatan bersenjata Iran dan Ahmad Vahidi sebagai panglima IRGC.</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811071707-120-1390840/mojtaba-khamenei-tunjuk-2-jenderal-pimpin-irgc-militer-iran</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/10/mojtaba-khamenei-1778379348614_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Calon Senator Pro Palestina El Sayed Dikontak Obama, Apa Pesannya?</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:35:35 +0700</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Setelah menang dalam pemilu pendahuluan, kandidat Senat AS dari Partai Demokrat di Michigan, Abdul El Sayed, ditelepon Barack Obama, Jumat (7/8).</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810130750-134-1390542/calon-senator-pro-palestina-el-sayed-dikontak-obama-apa-pesannya</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/02/10/4763815a-5c30-4d9f-8836-f9c47c6ebcb7_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>111 Orang Tewas Imbas Gempa Magnitudo 7,4 Kolombia</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:05:20 +0700</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Sebanyak 111 orang meninggal dunia imbas gempa bermagnitudo 7,4 mengguncang Kolombia, ribuan bangunan rusak.</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811064029-134-1390831/111-orang-tewas-imbas-gempa-magnitudo-74-kolombia</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/colombia-quake-1786405579689_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Trump Buka Suara usai Usulannya soal Perdamaian Gaza Ditolak Netanyahu</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:35:20 +0700</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Rencananya dan Board of Peace soal Gaza ditolak Netanyahu, Trump sebut hubungannya dengan PM Israel itu tetap baik.</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811061817-134-1390825/trump-buka-suara-usai-usulannya-soal-perdamaian-gaza-ditolak-netanyahu</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/21/benjamin-netanyahu-dan-donald-trump-1779324448748_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Sultan Brunei Cabut Gelar Kerajaan Menantu sampai PM Anwar Masuk RS</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Sultan Brunei cabut gelar kerajaan menantu karena perilaku yang mencoreng nama baik kerajaan hingga PM Malaysia Anwar Ibrahim masuk RS.</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811053033-106-1390820/sultan-brunei-cabut-gelar-kerajaan-menantu-sampai-pm-anwar-masuk-rs</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/prince-abdul-malik-isteri-pengiran-raabiatul-adawiyyah-1786342422541_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Apa Penyebab Sultan Brunei Mendadak Cabut Gelar Kerajaan Menantu?</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Menantu perempuan Sultan Brunei Hassanal Bolkiah, Raabidatul Adawiyyah Pengiran Haji Bolkiah, menjadi sorotan usai gelar kerajaanya dicabut pada pekan lalu.</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810204427-106-1390784/alasan-sultan-brunei-cabut-gelar-kerajaan-menantu</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/08/31/sultan-hassanal-bolkiah-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Ribuan Pedemo Protes Ujian PNS Bocor di India, Bentrok dengan Polisi</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Bentrokan antara polisi dan demonstran terjadi dalam unjuk rasa terkait dugaan kecurangan ujian masuk pegawai negeri di Jharkhand, India, pada Senin (10/8).</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810193837-117-1390759/ribuan-pedemo-protes-ujian-pns-bocor-di-india-bentrok-dengan-polisi</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/thumbnail-video-1786365643057_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Detik-detik Kamera Tangkap Penampakan Topan Dolphin Terjang Taiwan</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 04:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Angin Topan Dolphin melanda Distrik Tamsui, New Taipei, Taiwan, dan terekam kamera warga pada Sabtu (8/8).</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810101300-117-1390461/detik-detik-kamera-tangkap-penampakan-topan-dolphin-terjang-taiwan</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/detik-detik-topan-dolphin-terjang-taiwan-terekam-kamera-1786332063151_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>SOSOK Lucky Sugeha: Ketua Panitia Drag Race Maut di Kotamobagu, Irit Bicara Usai 8 Jam Diperiksa</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:29:43 +0700</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Nama Lucky Sugeha ikut jadi perbincangan usai kecelakaan maut di Drag Race di Kotamobagu, dia adalah ketua panitia dari ajang balap tersebut.</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866826/sosok-lucky-sugeha-ketua-panitia-drag-race-maut-di-kotamobagu-irit-bicara-usai-8-jam-diperiksa</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/B6ACRMhpZV93QRqBlucfyzSgRdY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Lucky-Sugeha-Ketua-panitia-penyelenggara-drag-race-maut.jpg</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Ukraina Cari Bantuan Korea Selatan Hadapi Rusia, Seoul Pilih Berhati-hati</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:29:10 +0700</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Ukraina mencari bantuan dari Korea Selatan untuk menghadapi Rusia yang disebut akan mendapat pasukan dan rudal balistik dari Korea Utara.</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866825/ukraina-cari-bantuan-korea-selatan-hadapi-rusia-seoul-pilih-berhati-hati</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/driSROkT3sAJEiRkdM0BUELgSNI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Z3L3NSKYY-345634563.jpg</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Inovasi Digital BUMN Asuransi TNI/Polri: Tingkat Autentikasi Peserta via Aplikasi Capai 98,26 Persen</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:28:49 +0700</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Langkah transformasi yang dilakukan ASABRI berfokus penuh pada kemudahan dan kecepatan akses bagi seluruh peserta di berbagai penjuru Indonesia.</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866824/inovasi-digital-bumn-asuransi-tnipolri-tingkat-autentikasi-peserta-via-aplikasi-capai-9826-persen</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0-kMaTfaJfSzRRDehSUnKFeCCRE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penyerahan-santunan-asuransi-TNIPolri-w.jpg</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Mengenal Baden Powell, Bapak Pramuka Dunia dan Pencetus Gerakan Kepanduan</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:28:15 +0700</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Simak informasi mengenai  Lord Baden-Powell, Bapak Pramuka Dunia dan sejarah kepanduan dunia.</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866823/mengenal-baden-powell-bapak-pramuka-dunia-dan-pencetus-gerakan-kepanduan</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/kP1cXwS79pmYQq2fwovZnZdkLXk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/baden-powell.jpg</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Gempa Kolombia: Bayi 6 Bulan dan Ibunya Selamat dari Bangunan Lima Lantai yang Runtuh</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:28:10 +0700</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Bayi perempuan berusia 6 bulan dan ibunya ditemukan selamat dari reruntuhan bangunan lima lantai setelah gempa 7,4 mengguncang Kolombia.</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866822/gempa-kolombia-bayi-6-bulan-dan-ibunya-selamat-dari-bangunan-lima-lantai-yang-runtuh</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Vy9oADuEKIrbX52T7tBkDaqmQ64=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/GEMPA-KOLOMBIA-Gempa-bumi-dahsyat-berkekuatan-magnitudo-74-mengguncang-wilayah-barat-Kolombia.jpg</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Perang Memperparah Krisis Ekonomi Iran, Keluarga Kelas Menengah Makin Terhimpit</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:27:07 +0700</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Perang telah memperparah krisis ekonomi Iran, semakin menekan anggaran rumah tangga, memukul dunia usaha, dan menimbulkan kekhawatiran…</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866821/perang-memperparah-krisis-ekonomi-iran-keluarga-kelas-menengah-makin-terhimpit</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/3WTtRInXVa32uXc-I5QT8aGX-14=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/BDeutsche-Welle75421511_403.jpg.jpg</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Wanita Tersungkur Dipepet 3 Begal di Bekasi, Sempat Diseret, Motornya Dibawa Kabur</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:26:45 +0700</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Dua orang pelaku begal menghampiri korban, salah satunya menyeret korban menjauh dari sepeda motornya.</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866820/wanita-tersungkur-dipepet-3-begal-di-bekasi-sempat-diseret-motornya-dibawa-kabur</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/05SAC9EiYB8tOFw8ES4tkGTWWx8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wanita-Terseret-Korban-Begal-di-Bekasi-Utara.jpg</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Dukungan Presiden Prabowo untuk Restorasi Ekosistem Dinilai Sangat Penting</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:26:22 +0700</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Dukungan Presiden Prabowo kuat terhadap restorasi ekosistem dan pemulihan lahan terdegradasi di Indonesia, termasuk komitmen.</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866819/dukungan-presiden-prabowo-untuk-restorasi-ekosistem-dinilai-sangat-penting</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/bNIpunZdShqkwqbqwLs6O65rOK0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Menhut-Raja-Juli-Antoni-di-Istana-Kepresidenan-Jakarta-kamis.jpg</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Sosok Brigpol IT, 2 Kali Digerebek Suami yang Juga Polisi, Akui Ada Masalah Rumah Tangga</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:26:11 +0700</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Polwan Polda Maluku, Brigpol IT dua kali digerebek suaminya yang juga polisi, Brigpol RL. Dalam kejadian kedua, Brigpol IT ditemukan seorang diri.</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866818/sosok-brigpol-it-2-kali-digerebek-suami-yang-juga-polisi-akui-ada-masalah-rumah-tangga</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/kupKldQkkea3ym6h-wAQ17ww838=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Brigpol-IT-digerebek-lagi.jpg</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Fit and Proper Test Destry Damayanti Digelar Setelah Reses DPR</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:25:35 +0700</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Uji kelayakan dan kepatutan Destry Damayanti sebagai calon Gubernur BI definitif akan dilakukan Komisi XI DPR setelah DPR menyelesaikan masa reses.</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866817/fit-and-proper-test-destry-damayanti-digelar-setelah-reses-dpr</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/wr-J6ZhrXUS5_VxafBPBDEf_igg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Hanif-Dhakiri-fit-proper-test-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Curhat Mahasiswa di MK: Data Bocor, Diteror Polisi Gadungan hingga Situs Kampus Jadi Iklan Judol</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:20:22 +0700</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Keresahan muncul ketika sejumlah mahasiswa menerima telepon dari orang yang mengaku anggota kepolisian.</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866816/curhat-mahasiswa-di-mk-data-bocor-diteror-polisi-gadungan-hingga-situs-kampus-jadi-iklan-judol</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/9KvRJnACwzTyMctjIrfcYT0WwRU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/K-Jakarta-Selasa-11082026-Tangka.jpg</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>SEA V Cup Rampung, Timnas Voli Putri Indonesia Tatap Ujian di AVC Continental Championship 2026</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:19:29 +0700</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Usai SEA V Cup, Timnas voli putri Indonesia bersiap menghadapi AVC Continental Championship 2026  pada 21-30 Agustus di Tianjin, China.</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866815/sea-v-cup-rampung-timnas-voli-putri-indonesia-tatap-ujian-di-avc-continental-championship-2026</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/SY_zBQnaWt-rYs-ehVIMWjWkzy0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pelepasan-Timnas-Voli-Putri-Indoensia.jpg</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Jelang Ekshumasi Jenazah Sutrimo: Makam Dijaga Ketat Polisi, Keluarga di Banyumas Minta Perlindungan</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:17:39 +0700</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Menjelang ekshumasi, pihak keluarga disebut meminta perlindungan hukum ke Polresta Banyumas usai melaporkan kasus kematian Sutrimo.</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866814/jelang-ekshumasi-jenazah-sutrimo-makam-dijaga-ketat-polisi-keluarga-di-banyumas-minta-perlindungan</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/kZFE6PfULAXOD752T0B7EGx5hp4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Rumah-Sutrimo-di-Banyumas-1.jpg</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Mensesneg: Belum Ada Rencana Reshuffle Kabinet, Kursi Wamentan Tetap Kosong</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:10:12 +0700</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Kursi jabatan Wakil Menteri Pertanian masih akan kosong untuk beberapa waktu ke depan.</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866813/mensesneg-belum-ada-rencana-reshuffle-kabinet-kursi-wamentan-tetap-kosong</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/cqTsHvyPWkdwTndCKjAcIRXjN_U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Prasetyo-Hadi12222.jpg</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Pegawai Bulog Tantang Balik Feri Amsari, Imbas Mensesneg Kabinet Bayangan Ajak Debat Mentan</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:07:45 +0700</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Feri Amsari menantang Mentan Andi Amran untuk melakukan debat terbuka tentang swasembada pangan. Namun tantangan itu justru dijawab Staf Bulog.</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866812/pegawai-bulog-tantang-balik-feri-amsari-imbas-mensesneg-kabinet-bayangan-ajak-debat-mentan</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/xabkz1ASKm2pOzy5qjewmXadnJw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/feri-amsari-debat-mentan-ss.jpg</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Penjelasan Pemdes di Cilacap setelah KDMP Dipakai Lomba Badminton, Tidak Ubah Fungsi Gedung</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:06:03 +0700</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Gedung Koperasi Desa Merah Putih di Cilacap viral usai dialihfungsikan menjadi lapangan badminton perlombaan HUT ke-81 RI.</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866811/penjelasan-pemdes-di-cilacap-setelah-kdmp-dipakai-lomba-badminton-tidak-ubah-fungsi-gedung</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/7QBY_5CNKt4_NA1KsD3sPNsIrWI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kopdesbadminton1111.jpg</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Kortas Tipidkor Polri Benarkan Sudah Tetapkan Dedi Congor Tersangka Kasus Gratifikasi Sejak 2023</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:05:46 +0700</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Yusuf mengatakan dalam kasus ini penyidik juga telah menyita sejumlah barang bukti terkait gratifikasi yang dilakukan Dedi Congor.</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866810/kortas-tipidkor-polri-benarkan-sudah-tetapkan-dedi-congor-tersangka-kasus-gratifikasi-sejak-2023</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ATHO5uu7I5rD9ApLyuR9Lecp7mo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PNS-Bea-Cukai-Ahmad-Dedi-alias-Dedi-Congor-lari-usai-diperiksa-KPK.jpg</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Menyoal Aliansi Militer Saudi, Pakistan, dan Turki</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Pakta Pertahanan Makkah Arab Saudi, Pakistan, dan Turki dibentuk di tengah kaotik geopolitik global, tiru mekanisme NATO.</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/tribunners/7866809/menyoal-aliansi-militer-saudi-pakistan-dan-turki</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ULgjTD2EVMaIlZ22lLFvNFN2PSw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/boy-anugerah-sip-msi-mpp-1786427492909.jpg</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Lesti Kejora dan Asila Maisa Dicecar 25 Pertanyaan Penyidik, Kompak Bantah Isu yang Beredar</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:04:47 +0700</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Lesti Kejora dan Asila Maisa diperiksa secara terpisah oleh penyidik Polda Metro Jaya terkait laporan Rizky Billar atas fitnah selingkuh.</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866808/lesti-kejora-dan-asila-maisa-dicecar-25-pertanyaan-penyidik-kompak-bantah-isu-yang-beredar</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/IyhX9bS8m0vMQjurrSkvxWycq_0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/lesti-kejora-aisa-maisa1.jpg</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Korban Tewas Gempa Kolombia Naik Jadi 132 dan 570 Terluka, Tim SAR Berpacu Cari Korban di Reruntuhan</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:00:27 +0700</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Gempa 7,4 mengguncang Kolombia, menewaskan 132 orang dan melukai 570 lainnya. Tim SAR masih berpacu mencari korban di reruntuhan.</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866807/korban-tewas-gempa-kolombia-naik-jadi-132-dan-570-terluka-tim-sar-berpacu-cari-korban-di-reruntuhan</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hzWx5otJiYfuvi7E1WBaYnCcYqs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KONDISI-KOTA-PEREIRA-SETELAH-GEMPA-GUNCANG-KOLOMBIA.jpg</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Pertamina Patra Niaga Rampungkan Docking 12 Kapal, Perkuat Keandalan Distribusi Energi Nasional</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:47:00 +0700</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Intan Pratiwi</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – PT Pertamina Patra Niaga merampungkan proses docking terhadap 12 kapal pada periode Februari hingga Juli 2026 sebagai bagian dari program pemeliharaan berkala (planned maintenance). Langkah ini merupakan...</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjl9eb522/pertamina-patra-niaga-rampungkan-docking-12-kapal-perkuat-keandalan-distribusi-energi-nasional</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/pt-pertamina-patra-niaga-merampungkan-proses-docking-terhadap-12_260811114904-116.jpeg</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Destry Damayanti Diajukan Sebagai Calon Tunggal Gubernur BI, Kapan Fit and Proper Test di DPR?</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:30:57 +0700</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Wakil Ketua Komisi XI DPR RI Muhammad Hanif Dhakiri angkat bicara mengenai  juga menilai Destry Damayanti merupakan sosok yang patut menjadi pemimpin bank sentral. Sebab, Destry dinilai...</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjle3l490/destry-damayanti-diajukan-sebagai-calon-tunggal-gubernur-bi-kapan-fit-and-proper-test-di-dpr</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260811130559-316.png</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>OJK dan LPS Kompak Dukung Destry Damayanti Jadi Gubenur BI, Ini Alasannya</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:07:05 +0700</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Pencalonan Destry Damayanti untuk menjadi Gubernur Bank Indonesia (BI) definitif menerima sambutan positif. Dukungan tersebut antara lain datang dari kepala lembaga anggota Komite Stabilitas Sistem Keuangan (KSSK),...</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlczt490/ojk-dan-lps-kompak-dukung-destry-damayanti-jadi-gubenur-bi-ini-alasannya</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260728070156-113.png</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Pengacara Gus Yaqut: Penegakan Hukum Korupsi Kuota Haji Setengah Hati</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:43:51 +0700</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Pengacara Gus Yaqut menilai, ada fakta yang tidak diungkap secara utuh dan sejumlah peristiwa yang dipaksakan</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267010/pengacara-gus-yaqut-penegakan-hukum-korupsi-kuota-haji-setengah-hati</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/tTpen3BDh_HpFS7yH4vb1yNIQ2o=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321149/original/084165400_1786430623-IMG_20260811_121041_552.jpg</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Persiapan HUT ke-81 RI, Paskibraka Mulai Latihan di Istana</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:37:59 +0700</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Gladi parsial dimulai, Istana Merdeka bersiap menyambut perayaan kemerdekaan.</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267002/persiapan-hut-ke-81-ri-paskibraka-mulai-latihan-di-istana</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/-V0wlCsyXf8-0fuWra7gYnJGBdQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321139/original/094425400_1786430208-9adace89-14a4-463f-beec-2276bb0e9775.JPG</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Wanita di Bekasi Dipepet Kawanan Begal hingga Jatuh, Motor Dirampas</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:47:25 +0700</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>wanita jadi korban begal di bekasi utara, tiga pelaku memepet hingga korban terjatuh.</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267015/wanita-di-bekasi-dipepet-kawanan-begal-hingga-jatuh-motor-dirampas</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/V-hMssUuM-SogBmJ3oXUnVnf2k0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321154/original/002246500_1786430844-Begal_Cewek.jpg</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Polisi Periksa EO dan MC Acara Tantangan Hafal Surah Alquran Berhadiah Miras</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:28:09 +0700</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Polisi kini membidik pihak yang terlibat dalam kegiatan tersebut.</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266994/polisi-periksa-eo-dan-mc-acara-tantangan-hafal-surah-alquran-berhadiah-miras</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Fp5iC-vppn7dJSzwqGEBlrLz0gY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321055/original/059736500_1786425649-Jepretan_Layar_2025-08-11_pukul_12.15.34.jpg</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Geger Mayat Bayi di Tong Sampah Sawangan Depok</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:26:01 +0700</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Penemuan mayat bayi tersebut berawal dari saksi saat akan memungut sampah botol plastik di dalam tong sampah drum plastik merah.</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266990/geger-mayat-bayi-di-tong-sampah-sawangan-depok</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/osQPDK8jd1aPhRLNvMYQvGVaiRE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321130/original/064177600_1786429555-IMG-20260811-WA0024.jpg</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Polisi Tangkap Sopir Taksi Online Cabul yang Viral di Medsos</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:15:29 +0700</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Video seorang sopir taksi online diduga melakukan perbuatan cabul terhadap penumpangnya viral di media sosial.</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266975/polisi-tangkap-sopir-taksi-online-cabul-yang-viral-di-medsos</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/lgPuyQlYytmtulVGn3I7KBx0Uyk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321101/original/095464500_1786428822-driver_online_cabul.jpg</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>SBY Dipastikan Tak Hadir Sidang Tahunan MPR</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:11:28 +0700</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Sidang Tahunan MPR dan sidang bersama MPR, DPR, dan DPD akan digelar pada Jumat, 14 Agustus 2026,</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266969/sby-dipastikan-tak-hadir-sidang-tahunan-mpr</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/i5n4_WawW2lq3qJR1T2bDriRKV4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5143809/original/017914000_1740554240-WAWANCARA_PRESIDEN_KE-6_SBY_ANG__14_.jpg</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Kado HUT Ke-81 RI, Pemerintah Siapkan Bantuan Beras Hampir 1 Juta Ton</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:48:58 +0700</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Bantuan Pangan Beras Tahap II menjadi bagian dari upaya menjaga akses pangan, melindungi daya beli masyarakat, dan memperkuat stabilitas harga beras.</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/13460921/kado-hut-ke-81-ri-pemerintah-siapkan-bantuan-beras-hampir-1-juta-ton</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/AE5kU07svjRGVc7g2pPFrF5GwAQ=/0x0:2560x1707/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/03/6a6fd9b415f79.jpg</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Terminal Penumpang Jadi Simpul Logistik Perkotaan</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:48:58 +0700</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Terminal yang hanya aktif pada jam pelayanan penumpang dapat memberikan manfaat lebih besar apabila kapasitas ruang dan waktunya dimanfaatkan tepat.</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/13275371/terminal-penumpang-jadi-simpul-logistik-perkotaan</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/aJJLkXVRGIkBez7pqR6eQOt2nmY=/162x0:1175x675/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/04/26/69ee3fdf14f03.jpg</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Pemkot Bogor Bakal Pindah ke Katulampa, Bagaimana Nasib Kantor OPD Lama?</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:48:58 +0700</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Pemkot Bogor membangun akses jalan terlebih dahulu sebagai penunjang fasilitas pemerintahan baru.</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/11/13070111/pemkot-bogor-bakal-pindah-ke-katulampa-bagaimana-nasib-kantor-opd-lama</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/nVtQkxVfNtx_yCpyzAstRRGaRfM=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/07/29/6a69d69034b5d.jpg</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I439"/>
+  <autoFilter ref="A1:I581"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$581</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$685</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I581"/>
+  <dimension ref="A1:I685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -27743,8 +27743,4898 @@
         </is>
       </c>
     </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Bulog Sumut pastikan penyaluran bantuan pangan 1,73 juta KPM pekan ini</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:01:20 +0700</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Perum Bulog Kantor Wilayah Sumatera Utara memastikan penyaluran bantuan pangan berupa beras kepada 1,73 juta keluarga ...</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689076/bulog-sumut-pastikan-penyaluran-bantuan-pangan-173-juta-kpm-pekan-ini</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0104.jpg</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Bagaimana olahraga bisa membantu mengurangi stres?</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:00:53 +0700</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Stres menjadi bagian yang cukup umum dalam kehidupan sehari-hari. Tuntutan pekerjaan, tugas sekolah, masalah keluarga, ...</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689075/bagaimana-olahraga-bisa-membantu-mengurangi-stres</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/27/pexels-marcus-aurelius-6787161.jpg</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>BI: Industri pengolahan jadi penopang ekonomi Jateng</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:59:29 +0700</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Kantor Perwakilan Bank Indonesia Provinsi Jawa Tengah menyebutkan bahwa industri pengolahan dan perdagangan menjadi ...</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689073/bi-industri-pengolahan-jadi-penopang-ekonomi-jateng</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001967856.jpg</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>OJK tanggapi wacana Masjid Istiqlal masuk Bursa lewat wakaf produktif</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:58:28 +0700</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Kepala Eksekutif Pengawas Pasar Modal, Keuangan Derivatif, dan Bursa Karbon Otoritas Jasa Keuangan (OJK) Hasan Fawzi ...</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689071/ojk-tanggapi-wacana-masjid-istiqlal-masuk-bursa-lewat-wakaf-produktif</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-13.30.14_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Pemkab Situbondo bikin terobosan KSP Wisata Bahari Pasir Putih</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:58:25 +0700</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten Situbondo, Jawa Timur, membuat terobosan baru yakni Kerja Sama Pemanfaatan (KSP) Wisata Bahari ...</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689068/pemkab-situbondo-bikin-terobosan-ksp-wisata-bahari-pasir-putih</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/MG_9998.jpg</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>DPR gelar rapat dengan pemerintah-KPA bahas konflik agraria mendesak</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:58:10 +0700</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Pimpinan DPR RI menggelar rapat koordinasi dengan lintas kementerian dari pemerintah bersama Konsorsium Pembaruan ...</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689065/dpr-gelar-rapat-dengan-pemerintah-kpa-bahas-konflik-agraria-mendesak</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001303394.jpg</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Conor Benn yakin bungkam Garcia untuk rebut sabuk kelas welter WBC</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:58:05 +0700</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Petinju Conor Benn optimistis membungkam Ryan Garcia untuk merebut sabuk juara dunia kelas welter (66,7 kg) World ...</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689064/conor-benn-yakin-bungkam-garcia-untuk-rebut-sabuk-kelas-welter-wbc</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/00f43e67-8d28-4e2a-a624-edb8baf90f74.jpeg</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Musim Mas dan Pemkab Deli Serdang Resmikan Alun-Alun Percut Sei Tuan, Hadirkan Ruang Publik untuk Masyarakat dan UMKM</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:57:08 +0700</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Masyarakat Kecamatan Percut Sei Tuan kini memiliki ruang publik baru yang dapat dimanfaatkan sebagai tempat ...</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689060/musim-mas-dan-pemkab-deli-serdang-resmikan-alun-alun-percut-sei-tuan-hadirkan-ruang-publik-untuk-masyarakat-dan-umkm</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Musim-Mas-dan-Pemerintah-Deli-Serdang.jpg</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Undangan HUT RI mulai dikirim ke mantan presiden dan wapres</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:57:01 +0700</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara Prasetyo Hadi mengatakan panitia HUT Ke-81 Kemerdekaan Republik Indonesia mulai mengantarkan ...</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689056/undangan-hut-ri-mulai-dikirim-ke-mantan-presiden-dan-wapres</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_3748.jpeg</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Kolombia tetapkan status bencana nasional usai gempa magnitudo 7,4</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:55:53 +0700</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Otoritas Kolombia menetapkan status bencana nasional menyusul gempa dahsyat yang mengguncang negara tersebut pada Senin ...</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689052/kolombia-tetapkan-status-bencana-nasional-usai-gempa-magnitudo-74</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/thumbs_b_c_e726e95b76c6f0cd719dcf122fc06d02.jpg</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>DeTect Dapatkan Kontrak Untuk Memasok MERLIN™ True3D® Bird Detection Radar ke Bandara Soekarno-Hatta Jakarta</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:54:35 +0700</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>DeTect, Inc. mendapatkan kontrak untuk memasok MERLIN 7360 True3D Bird Detection Radar ke Bandara Soekarno-Hatta ...</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689051/detect-dapatkan-kontrak-untuk-memasok-merlin-true3d-bird-detection-radar-ke-bandara-soekarno-hatta-jakarta</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/MERLIN-True3D-Bird-Detection.jpg</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Tips memulai "running routine" untuk Anda yang pekerja kantoran</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:54:16 +0700</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Kesibukan bekerja dari pagi hingga sore sering membuat aktivitas fisik menjadi hal yang mudah ditunda. Duduk berjam-jam ...</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689047/tips-memulai-running-routine-untuk-anda-yang-pekerja-kantoran</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/04/07/running-gefdf2d723_1280.jpg</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Danantara targetkan groundbreaking PSEL di Yogyakarta pada akhir 2026</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:53:14 +0700</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Badan Pengelola Investasi Daya Anagata Nusantara (Danantara) menargetkan peletakan batu pertama atau groundbreaking ...</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689045/danantara-targetkan-groundbreaking-psel-di-yogyakarta-pada-akhir-2026</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_135515.jpg</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Tim gabungan Bea Cukai Langsa gagalkan penyelundupan sepeda motor</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:52:58 +0700</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Tim gabungan Bea Cukai Langsa bersama Bea Cukai Medan menggagalkan penyelundupan sepeda motor besar atau moge beserta ...</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689044/tim-gabungan-bea-cukai-langsa-gagalkan-penyelundupan-sepeda-motor</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/sepeda-motor-selundupan.jpg</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>DPR minta pemerintah siapkan pelatihan bagi pengemudi ojol</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:52:39 +0700</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi VII DPR RI Chusnunia meminta pemerintah menindaklanjuti penetapan pengemudi ojek daring (ojek ...</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689040/dpr-minta-pemerintah-siapkan-pelatihan-bagi-pengemudi-ojol</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/25/1003229188.jpg</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Yaqut didakwa rugikan negara Rp622 miliar di kasus korupsi kuota haji</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:51:21 +0700</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Menteri Agama periode 2020-2024 Yaqut Cholil Qoumas didakwa merugikan keuangan negara senilai Rp622,09 miliar terkait ...</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689037/yaqut-didakwa-rugikan-negara-rp622-miliar-di-kasus-korupsi-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/sidang-dakwaan-yaqut-110826-bay-4A.jpg</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Wamenekraf: Masuknya gim global buka peluang kembangkan talenta lokal</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:50:17 +0700</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kehadiran perusahaan gim global resmi di pasar gim Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689033/wamenekraf-masuknya-gim-global-buka-peluang-kembangkan-talenta-lokal</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000457405.jpg</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>PKK Cilegon beri pendampingan door to door ke UMKM agar naik kelas</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:49:42 +0700</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua Tim Penggerak Pemberdayaan Kesejahteraan Keluarga (PKK) Kota Cilegon, Alfi Rizki Aghnia Robinsar bersama ...</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688977/pkk-cilegon-beri-pendampingan-door-to-door-ke-umkm-agar-naik-kelas</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-11-142520.jpg</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Seskab Teddy tegaskan dukungan Presiden Prabowo pada Magang Nasional</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:49:34 +0700</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Sekretaris Kabinet Teddy Indra Wijaya menegaskan dukungan Presiden Prabowo Subianto kepada Program Magang ...</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689032/seskab-teddy-tegaskan-dukungan-presiden-prabowo-pada-magang-nasional</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_7901.jpg</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Tiket Eras Tour Swift sempat jadi sandera uang tebusan oleh peretas</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:49:08 +0700</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Tiket "Eras Tour" bintang pop dunia Taylor Swift sempat menjadi sandera untuk uang tebusan operasi kejahatan ...</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689031/tiket-eras-tour-swift-sempat-jadi-sandera-uang-tebusan-oleh-peretas</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/01/taylor-swift-1a.jpg</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Kapan waktu yang tepat untuk mengganti pakaian?</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:48:55 +0700</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Mengganti pakaian secara rutin penting untuk menjaga kebersihan tubuh dan kesehatan kulit. Namun, frekuensinya tidak ...</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689028/kapan-waktu-yang-tepat-untuk-mengganti-pakaian</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/01/24/cuci.jpg</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Jorge Martin tak peduli gelar juara dunia</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:48:43 +0700</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Pembalap Aprilia Racing Jorge Martin tidak peduli dengan gelar juara dunia MotoGP.
+"Saya sudah menjadi ...</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689025/jorge-martin-tak-peduli-gelar-juara-dunia</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/Report-MGP-GP-FR.jpeg</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Komisi II sambut baik kebijakan pemerintah cegah PPPK dirumahkan</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:45:50 +0700</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Ketua Komisi II DPR RI Rifqinizamy Karsayuda menyambut baik kebijakan pemerintah untuk mencegah Pegawai Pemerintah ...</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689024/komisi-ii-sambut-baik-kebijakan-pemerintah-cegah-pppk-dirumahkan</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/15/raker-komisi-ii-dpr-dengan-pemerintah-2821844.jpg</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Temuan senjata di sekolah, polisi cocokkan data dan barang bukti</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:45:48 +0700</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Pihak kepolisian telah melakukan pengecekan tambahan, yakni pencocokan data dan barang bukti senjata di sebuah sekolah ...</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689021/temuan-senjata-di-sekolah-polisi-cocokkan-data-dan-barang-bukti</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260630_094425.jpg</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Pemerintah finalisasi Pepres tentang ojol, lengkapi sejumlah formula</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:45:44 +0700</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Pemerintah tengah melakukan finalisasi Peraturan Presiden (perpres) yang mengatur ekosistem transportasi daring terkait ...</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689020/pemerintah-finalisasi-pepres-tentang-ojol-lengkapi-sejumlah-formula</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/6b504038-1fa7-4906-a931-30e468891c23.jpg</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Polisi tangkap dua begal yang serang anggota Polda Sumsel</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:45:35 +0700</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Polrestabes Palembang, Sumatera Selatan, menangkap dua tersangka pencurian dengan kekerasan (curas) terhadap seorang ...</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689016/polisi-tangkap-dua-begal-yang-serang-anggota-polda-sumsel</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001554933.jpg</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>BNPB: Karhutla di Magetan dan Jombang padam kurang dari 24 jam</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:43:44 +0700</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) menyatakan peristiwa kebakaran hutan dan lahan (karhutla) di Kabupaten ...</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689013/bnpb-karhutla-di-magetan-dan-jombang-padam-kurang-dari-24-jam</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0000.jpg</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Bapenda Batam dekatkan layanan pajak ke mal setiap pekan</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:42:08 +0700</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Badan Pendapatan Daerah (Bapenda) Kota Batam, Kepulauan Riau (Kepri) memperluas dan mendekatkan layanan perpajakan ...</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689009/bapenda-batam-dekatkan-layanan-pajak-ke-mal-setiap-pekan</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/236f1b15-68e2-49dc-a26f-e7b0fde92ad1.jpeg</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Hasil Studi Global yang Dipublikasikan di Aesthetic Surgery Journal Open Forum Ungkap Kaitan antara Kepercayaan Diri dan Estetika</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:41:46 +0700</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Aesthetic Surgery Journal Open Forum (ASJ Open Forum) pada bulan ini menerbitkan hasil studi global Merz ...</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689007/hasil-studi-global-yang-dipublikasikan-di-aesthetic-surgery-journal-open-forum-ungkap-kaitan-antara-kepercayaan-diri-dan-estetika</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Aesthetics-and-Self-Affirmation.jpg</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Conscious living: Cara jalani hidup lebih sadar tanpa ikut-ikutan</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:40:41 +0700</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Di tengah kehidupan yang serba cepat, mengikuti apa yang sedang populer rasanya sudah menjadi hal yang sulit dihindari. ...</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689004/conscious-living-cara-jalani-hidup-lebih-sadar-tanpa-ikut-ikutan</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/09/27/IMG-20230927-WA0031_2.jpg</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Sudin SDA Jakpus normalisai saluran di Cempaka Putih Tengah XXII</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:40:01 +0700</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Suku Dinas Sumber Daya Air (SDA) Jakarta Pusat menormalisasi saluran air sepanjang 273 meter di Jalan Cempaka Putih ...</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689000/sudin-sda-jakpus-normalisai-saluran-di-cempaka-putih-tengah-xxii</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/01/10/InShot_20250110_075904218.jpg</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Kemenag susun pedoman pesantren ramah anak, panduan cegah kekerasan</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:39:06 +0700</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Kementerian Agama tengah menyusun pedoman Pesantren Ramah Anak Tahun 2026 yang akan menjadi panduan bersama dalam ...</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688996/kemenag-susun-pedoman-pesantren-ramah-anak-panduan-cegah-kekerasan</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000177468.jpg</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Pramono: Kenaikan jumlah penumpang transportasi umum bisa tekan polusi</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:38:24 +0700</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung Wibowo meyakini peningkatan jumlah pengguna transportasi umum dapat menekan ...</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688993/pramono-kenaikan-jumlah-penumpang-transportasi-umum-bisa-tekan-polusi</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_6800.jpeg</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Pelindo Multi Terminal Catat Kinerja Positif pada Semester I 2026</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:38:13 +0700</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA) – PT Pelindo Multi Terminal, anak usaha PT Pelabuhan Indonesia (Persero) yang bergerak dalam ...</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688989/pelindo-multi-terminal-catat-kinerja-positif-pada-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-13.25.21.jpeg</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Imigrasi Tanjungpinang hadirkan layanan antar paspor IDEPAS</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:38:04 +0700</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Kantor Imigrasi Kelas I TPI Tanjungpinang bekerja sama dengan PT Pos Indonesia (Persero) Cabang Tanjungpinang, ...</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688987/imigrasi-tanjungpinang-hadirkan-layanan-antar-paspor-idepas</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/20260811_142335.jpg</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>POJK Demutualisasi tidak batasi kepemilikan atas BEI dengan syarat</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:37:53 +0700</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) tengah mengkaji suatu konsep terkait pembatasan kepemilikan maksimum atas PT Bursa Efek ...</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688984/pojk-demutualisasi-tidak-batasi-kepemilikan-atas-bei-dengan-syarat</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-13.30.14.jpeg</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Jaksa Agung lantik kajati dan pejabat eselon II Kejagung</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:36:19 +0700</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Jaksa Agung ST Burhanuddin melantik para kepala Kejaksaan Tinggi (kajati) dan pejabat eselon II di lingkungan Kejaksaan ...</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688981/jaksa-agung-lantik-kajati-dan-pejabat-eselon-ii-kejagung</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000087642.jpg</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>WBA perpanjang negosiasi perebutan juara dunia Schofield lawan Bahdi</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:36:12 +0700</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>World Boxing Association (WBA) memperpanjang masa negosiasi pertarungan perebutan gelar juara dunia kelas ringan (61,2 ...</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688980/wba-perpanjang-negosiasi-perebutan-juara-dunia-schofield-lawan-bahdi</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/d3a64113-0099-4ae6-8c0a-8f62335d756c_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>10 aktivitas selain nongkrong yang bisa dilakukan di akhir pekan</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:35:35 +0700</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Akhir pekan biasanya menjadi waktu yang paling ditunggu setelah disibukkan oleh rutinitas harian. Tidak sedikit orang ...</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688979/10-aktivitas-selain-nongkrong-yang-bisa-dilakukan-di-akhir-pekan</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/08/08/pexels-august-de-richelieu-4259140.jpg</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Mensesneg cek latihan gabungan Paskibraka bersama TNI-Polri di Istana</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:32:47 +0700</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Sekretaris Negara (Mensesneg) Prasetyo Hadi, Selasa (11/8), meninjau langsung latihan gabungan ...</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688931/mensesneg-cek-latihan-gabungan-paskibraka-bersama-tni-polri-di-istana</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/MENSESNEG-CEK-LATIHAN-GABUNGAN-PASKIBRAKA-BERSAMA-TNI-POLRI-DI-ISTANA.jpg</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Utang rental Rp600 ribu berujung maut delapan orang jadi tersangka</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:32:00 +0700</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Polres Sumedang, Jawa Barat, menetapkan delapan tersangka dalam kasus dugaan penyekapan dan penganiayaan seorang pria ...</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688975/utang-rental-rp600-ribu-berujung-maut-delapan-orang-jadi-tersangka</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/491570.jpg</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Menhan RI perkuat kerja sama dengan Amerika Serikat</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:31:26 +0700</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Menteri Pertahanan RI Sjafrie Sjamsoeddin berupaya mempererat hubungan bilateral dengan pemerintah Amerika Serikat agar ...</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688971/menhan-ri-perkuat-kerja-sama-dengan-amerika-serikat</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001569672.jpg</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Dari dapur SPPG ke sekolah, MBG jangkau 375 ribu penerima di Sulbar</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:26:04 +0700</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Sejumlah pekerja membawa ompreng Program Makan Bergizi Gratis (MBG) menggunakan gerobak untuk disalurkan ke sekolah di ...</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5688969/dari-dapur-sppg-ke-sekolah-mbg-jangkau-375-ribu-penerima-di-sulbar</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Capaian-realisasi-program-MBG-di-Sulawesi-Barat-110826-At-1A.jpg</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Demokrat ungkap SBY sedang cek kesehatan di AS, tak akan hadiri HUT RI</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:25:45 +0700</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Umum Partai Demokrat Benny K. Harman mengungkapkan Presiden Ke-6 RI Susilo Bambang Yudhoyono ...</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688965/demokrat-ungkap-sby-sedang-cek-kesehatan-di-as-tak-akan-hadiri-hut-ri</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/Pidato-politik-SBY-070224-fah-2.jpg</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Pemerintah Yaman ancam balas serangan Houthi yang kian intensif</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:25:32 +0700</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Pemerintah Yaman, yang diakui secara internasional, pada Senin menyatakan akan merespons serangan berkelanjutan dari ...</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688964/pemerintah-yaman-ancam-balas-serangan-houthi-yang-kian-intensif</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/Tentara-Yaman.jpg</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Gubernur: Pembebasan lahan Tol Jambi-Rengat tuntas Desember 2026</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:21:03 +0700</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Gubernur Jambi Al Haris memastikan seluruh proses penetapan lokasi (penlok) hingga pendataan ganti rugi lahan ...</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688961/gubernur-pembebasan-lahan-tol-jambi-rengat-tuntasdesember-2026</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/575577.jpg</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Mensesneg: Pemerintah fokus tangani karhutla di sejumlah wilayah</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:20:47 +0700</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara (Mensesneg) Prasetyo Hadi memastikan pemerintah saat ini tengah fokus menangani kebakaran ...</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688957/mensesneg-pemerintah-fokus-tangani-karhutla-di-sejumlah-wilayah</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/cceb30b0-6d5e-4bd4-a740-126ce8224881.jpg</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>TNI AU kaji Tol Probolinggo-Banyuwangi jadi landasan pesawat</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:19:47 +0700</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>TNI Angkatan Udara mengkaji penggunaan ruas jalan tol di Jawa Timur sebagai landasan alternatif pesawat untuk mendukung ...</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688956/tni-au-kaji-tol-probolinggo-banyuwangi-jadi-landasan-pesawat</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/09/uji-coba-pendaratan-pesawat-tempur-di-jalan-tol-terpeka-1mgau-dom.jpg</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Pertamina Patra Niaga rampungkan proses docking 12 unit kapal</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:16:40 +0700</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>PT Pertamina Patra Niaga merampungkan proses docking terhadap 12 unit kapal pada periode Februari 2026 hingga Juli 2026 ...</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688944/pertamina-patra-niaga-rampungkan-proses-docking-12-unit-kapal</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000407478.jpg</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Istana minta maaf persiapan HUT Ke-81 RI ganggu lalu lintas</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:16:27 +0700</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara (Mensesneg) Prasetyo Hadi menyampaikan permohonan maaf kepada masyarakat atas penyesuaian dan ...</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688940/istana-minta-maaf-persiapan-hut-ke-81-ri-ganggu-lalu-lintas</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_3746.jpeg</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>AHY Soroti Birokrasi yang Bikin Investor Susah Investasi: Jangan Dipingpong</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:42:52 +0700</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Menteri AHY soroti birokrasi yang menyulitkan investor di Indonesia. Ia minta pemerintah ciptakan kepastian dan kemudahan dalam perizinan investasi.</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613682/ahy-soroti-birokrasi-yang-bikin-investor-susah-investasi-jangan-dipingpong</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/menko-ahy-brigitta-beliadetikcom-1786434144294_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Digitalisasi Akta Kelahiran Diluncurkan, Layanan Publik Kian Terintegrasi</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:42:34 +0700</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Pemerintah luncurkan digitalisasi akta kelahiran terintegrasi dengan layanan kesehatan. Proses penerbitan akta kini lebih cepat dan efisien bagi masyarakat.</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613681/digitalisasi-akta-kelahiran-diluncurkan-layanan-publik-kian-terintegrasi</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/digitalisasi-akta-kelahiran-diluncurkan-layanan-publik-kian-terintegrasi-1786434114981.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Jaksa Agung Lantik 15 Kajati, Minta Beri Perhatian Khusus Setiap Kasus Besar</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:41:11 +0700</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Jaksa Agung ST Burhanuddin melantik pejabat baru di Kejaksaan Agung. Pelantikan ini bertujuan memperkuat manajemen karier dan meningkatkan kinerja institusi.</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613679/jaksa-agung-lantik-15-kajati-minta-beri-perhatian-khusus-setiap-kasus-besar</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/jaksa-agung-republik-indonesia-st-burhanuddin-1786434039773_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Terungkap di Dakwaan, Ini Hitungan Kerugian Negara Korupsi Kuota Haji Rp 622 M</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:35:38 +0700</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Hitung-hitungan kerugian negara Rp 622 miliar akibat kasus korupsi kuota haji terungkap di persidangan.</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613657/terungkap-di-dakwaan-ini-hitungan-kerugian-negara-korupsi-kuota-haji-rp-622-m</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/eks-menag-yaqut-didakwa-perkara-kuota-haji-negara-disebut-rugi-rp622-miliar-1786428544309_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Dikira Bunuh Diri, Wanita di Tangerang Ternyata Tewas Dibunuh Pacar</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:24:27 +0700</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Seorang wanita ditemukan tewas tergantung di Tangerang. Penyelidikan mengungkap bahwa pacarnya, pria berinisial A, adalah pelaku pembunuhan.</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613647/dikira-bunuh-diri-wanita-di-tangerang-ternyata-tewas-dibunuh-pacar</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/04/01/ilustrasi-garis-polisi_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Viral Sejumlah Pemuda Sweeping Waria di Alun-alun Kota Rangkasbitung</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:24:24 +0700</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Aris Rivaldo</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Sejumlah pemuda melakukan sweeping keberadaan wanita-pria (waria) di Alun-alun Kota Rangkasbitung, Lebak, Banten. Video sweeping waria itu viral di medsos.</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613649/viral-sejumlah-pemuda-sweeping-waria-di-alun-alun-kota-rangkasbitung</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/01/10/ilustrasi-media-sosial_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Bawa Kabur Motor Teman, Pria Bogor Ditangkap di Kaki Gunung Merbabu</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:21:07 +0700</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Polisi menangkap pria berinisial T (34) di kaki Gunung Merbabu. T ditangkap usai diduga membawa kabur motor temannya dari wilayah Gunung Putri, Bogor.</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613641/bawa-kabur-motor-teman-pria-bogor-ditangkap-di-kaki-gunung-merbabu</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/pria-di-bogor-ditangkap-di-kaki-gunung-merbabu-usai-membawa-kabur-motor-temannya-1786432519401_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Mensos Ajak Jajaran Jadikan Momentum HUT RI untuk Berbenah-Berprestasi</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:13:09 +0700</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Menteri Sosial Gus Ipul mengajak jajaran Kemensos refleksi dan berbenah saat HUT RI ke-81. Ia menekankan integritas dan keterbukaan untuk meningkatkan layanan.</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613622/mensos-ajak-jajaran-jadikan-momentum-hut-ri-untuk-berbenah-berprestasi</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/mensos-ajak-jajaran-jadikan-momentum-hut-ri-untuk-berbenah-berprestasi-1786432327429_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Siswa Sekolah Rakyat Bacakan Puisi 'Kamipun Ingin Merdeka' di Kemensos</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:05:39 +0700</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Peringatan HUT RI ke-81 di Kemensos diwarnai penampilan puisi oleh siswa Sekolah Rakyat. Gus Ipul menekankan pentingnya integritas dalam pelayanan.</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613605/siswa-sekolah-rakyat-bacakan-puisi-kamipun-ingin-merdeka-di-kemensos</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kamipun-ingin-merdeka-puisi-anak-sekolah-rakyat-saat-tampil-di-kemensos-1786431674236.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Rapat di DPR, Pakar Usul RUU Perampasan Aset Diubah Jadi RUU Melindungi Aset</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:02:58 +0700</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Bambang Harymurti mengusulkan nama RUU Perampasan Aset jadi RUU Melindungi Aset. Ia tak ingin UU ini nantinya melegalisir upaya pencurian aset secara legal.</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613597/rapat-di-dpr-pakar-usul-ruu-perampasan-aset-diubah-jadi-ruu-melindungi-aset</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rapat-dengar-pendapat-umum-komisi-iii-dpr-bersama-sejumlah-pakar-di-gedung-dpr-senayan-jakarta-selasa-1182026-1786431721843_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Aiptu Asep Gugur Jadi Korban Tabrak Lari di Bandung, Keluarga Berduka</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:55:48 +0700</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Tim detikJabar</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Aiptu Asep Suhara, anggota Polrestabes Bandung, gugur akibat tabrak lari saat bertugas. Keluarga berduka, dan kasus ini sedang ditangani polisi.</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613578/aiptu-asep-gugur-jadi-korban-tabrak-lari-di-bandung-keluarga-berduka</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/istri-dan-anak-aiptu-asep-suhara-polisi-korban-tabrak-lari-di-bandung-1786332714961_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Mensesneg Minta Maaf Jl Veteran-Merdeka Utara Ditutup Imbas Latihan HUT RI</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:52:33 +0700</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Firda Cynthia Anggrainy</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Mensesneg Prasetyo Hadi minta maaf atas penutupan Jalan Veteran III dan Medan Merdeka Utara untuk latihan HUT RI</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613571/mensesneg-minta-maaf-jl-veteran-merdeka-utara-ditutup-imbas-latihan-hut-ri</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/mensesneg-dan-seskab-cek-gladi-parsial-upacara-hut-ri-di-istana-1786426651660_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Polisi Tetapkan 8 Tersangka Kasus Tewasnya Handi di Sumedang</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:38:13 +0700</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Dwiky Maulana Vellayati</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Polisi pun menetapkan delapan tersangka dalam kasus ini.</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613545/polisi-tetapkan-8-tersangka-kasus-tewasnya-handi-di-sumedang</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/polisi-tetapkan-8-orang-menjadi-tersangka-penyekapan-di-sumedang-1786423710480_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Jaksa: Surat Keputusan Yaqut Terkait Kuota Haji Tambahan Dibuat Backdated</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:35:15 +0700</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Jaksa KPK ungkap dugaan korupsi kuota haji oleh mantan Menteri Agama Yaqut, termasuk penandatanganan SK yang backdated</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613540/jaksa-surat-keputusan-yaqut-terkait-kuota-haji-tambahan-dibuat-backdated</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/eks-menag-yaqut-didakwa-perkara-kuota-haji-negara-disebut-rugi-rp622-miliar-1786428544180_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Soal Senjata di Sekolah Jaksel, Polisi Sebut Ada Kerja Sama Olahraga Menembak</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:32:11 +0700</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Polisi mengungkap ratusan senjata di sekolah swasta Jakarta, terkait kerja sama olahraga menembak. Legalitas senjata masih didalami. Temukan juga narkotika.</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613528/soal-senjata-di-sekolah-jaksel-polisi-sebut-ada-kerja-sama-olahraga-menembak</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kabid-humas-polda-metro-jaya-kombes-budi-hermanto-1786089469648_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Dana Wakaf Masjid Istiqlal Bakal Masuk Pasar Modal, Begini Skemanya</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:57:39 +0700</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Bursa Efek Indonesia rencanakan Masjid Istiqlal masuk ekosistem pasar modal melalui dana wakaf produktif, dikelola profesional oleh manajer investasi.</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8613719/dana-wakaf-masjid-istiqlal-bakal-masuk-pasar-modal-begini-skemanya</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/04/penjabat-sementara-pjs-direktur-utama-bei-jeffrey-hendrik-1780560925234_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Naik Kereta Ekonomi Diskon 17%, LRT Jabodebek Cuma Bayar Rp 8</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:48:03 +0700</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Promo spesial disediakan PT Kereta Api Indonesia (Persero) untuk memperingati Hari Kemerdekaan ke-81 Republik Indonesia.</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613698/naik-kereta-ekonomi-diskon-17-lrt-jabodebek-cuma-bayar-rp-8</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/19/lrt-jabodebek-makin-jadi-andalan-transum-warga-1779203242481_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Suara Istana untuk Destry Damayanti</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:44:25 +0700</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>20detik Signature</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Sejauh mana Destry dapat memberikan perubahan di sisi moneter Indonesia?</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613637/suara-istana-untuk-destry-damayanti</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/detiksore-11-agustus-2026-1786432519241_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>12 Kapal Pertamina Selesai Docking, Distribusi Dipastikan Aman</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:41:38 +0700</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>PT Pertamina Patra Niaga rampungkan docking 12 kapal untuk pemeliharaan armada. Ini memastikan distribusi energi nasional tetap aman dan andal.</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8613549/12-kapal-pertamina-selesai-docking-distribusi-dipastikan-aman</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/patra-niaga-1786430381337_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Peringatan Dini Hujan di Indonesia Rabu, 12 Agustus 2026: Aceh dan Sumatra Utara Waspada</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:52:51 +0700</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>BMKG keluarkan peringatan dini cuaca Rabu, 12 Agustus 2026. Aceh dan Sumatra Utara masuk kategori Waspada.</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866893/peringatan-dini-hujan-di-indonesia-rabu-12-agustus-2026-aceh-dan-sumatra-utara-waspada</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/otmRvhuUu5tHTOcJr1Dtcz93LKI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Hujan-deras-di-Bogor565.jpg</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>30 Puisi Maulid Nabi Muhammad SAW yang Menyentuh Hati, Penuh Cinta dan Kerinduan</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:51:38 +0700</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Peringatan Maulid Nabi Muhammad SAW pada tahun 2026 jatuh pada Selasa, 25 Agustus. Inilah 30 puisi Maulid Nabi Muhammad SAW dapat menjadi inspirasi.</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866892/30-puisi-maulid-nabi-muhammad-saw-yang-menyentuh-hati-penuh-cinta-dan-kerinduan</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/OgXugpB4daFlVGoTnMGvRC4ZyOM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/perayaan-maulid-nabi-di-kapung-kali-pasir-kota-tangerang_20211020_235657.jpg</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Terseret Kasus Hukum Buntut Aduan Icel, Karier Akting Anrez Adelio Hancur Berantakan?</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:51:18 +0700</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Jadwal kerja Anrez yang sudah tersusun rapi, berantakan akibat keputusan pihak televisi dan rumah produksi yang memilih menunda keterlibatannya.</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866891/terseret-kasus-hukum-buntut-aduan-icel-karier-akting-anrez-adelio-hancur-berantakan</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Dc65IpfbpvxFFlsbdabCUd0thdA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ANREZ-HAMILI-ICEL.jpg</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Madura Jawa Timur Rabu, 12 Agustus 2026: Cerah Berawan di Arjasa dan Kangayan</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:51:05 +0700</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Pantauan prakiraan cuaca lengkap BMKG untuk wilayah Pulau Madura, Jawa Timur, pada Rabu (12/8/2026) langit cerah berawan</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866890/prakiraan-cuaca-madura-jawa-timur-rabu-12-agustus-2026-cerah-berawan-di-arjasa-dan-kangayan</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5fNbv8oJSiEcLybciut8NHRHy6Y=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/tim-basarnas-saat-lakukan-pencarian-korban-di-perairan-sumenep-rabu-1962019.jpg</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Nasib Pilu Paramitha Titania, Ditemukan Tinggal Tengkorak usai 2 Tahun Hilang, Dibunuh Sopir Travel</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Paramitha Titania ditemukan tinggal tengkorak setelah dibunuh sopir travel Alber yang sakit hati dan membuang jasadnya ke jurang.</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866889/nasib-pilu-paramitha-titania-ditemukan-tinggal-tengkorak-usai-2-tahun-hilang-dibunuh-sopir-travel</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/BbzHBa9Bq4R9l1GSGNqJ_X8jvC4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Nasib-Pilu-Paramitha-Titania-Ditemukan-Tinggal-Tengkorak-usai-2-Tahun-Hilang-Dibunuh-Sopir-Travel.jpg</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Jadwal Kick-off Super League, Championship dan Liga Putri 2026/2027, Catat Tanggalnya</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:49:52 +0700</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Jadwal kompetisi Liga Indonesia 2026/2027 telah ditetapkan. Super League, Championship, hingga Liga Putri siap kembali bergulir.</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866888/jadwal-kick-off-super-league-championship-dan-liga-putri-20262027-catat-tanggalnya</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/VBz6VCmSehzqT9rfwL9t4QXveDU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Persib-Bandung-berhasil-meraih-gelar-juara-Super-League-20252026.jpg</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Kubu Yaqut Bantah KPK Sita Rp100 Miliar saat Geledah Rumah Eks Menag: Tak Ada Uang Selembar Pun</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:48:54 +0700</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Mellisa menyatakan narasi yang menyebut KPK menyita uang Rp 100 miliar dari rumah Yaqut, tidak benar.</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866887/kubu-yaqut-bantah-kpk-sita-rp100-miliar-saat-geledah-rumah-eks-menag-tak-ada-uang-selembar-pun</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1c6TMgqEDReVN4O5qe9cNoMcmmc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/melissa-bantaaaahhhh.jpg</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Spesifikasi Kapal Mewah Grand Maloekoe yang Bawa Rombongan Jessica Mila ke Pulau Padar saat Ditutup</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:48:27 +0700</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Rombongan Jessica Mila yang mendatangi Pulau Padar menggunakan kapal mewah Grand Maloekoe jadi sorotan.</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866886/spesifikasi-kapal-mewah-grand-maloekoe-yang-bawa-rombongan-jessica-mila-ke-pulau-padar-saat-ditutup</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/S1aHyqxvCXmNSxS9G5nu-RgKrz4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/keindahan-pulau-padar-labuan-bajo_20210329_114748.jpg</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Bansos PKH dan BPNT Triwulan III 2026 Resmi Disalurkan, Ini Cara Cek Penerimanya</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:48:07 +0700</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Bansos PKH dan BPNT Triwulan III 2026 untuk periode Juli-September terus disalurkan kepada jutaan KPM secara bertahap.</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866885/bansos-pkh-dan-bpnt-triwulan-iii-2026-resmi-disalurkan-ini-cara-cek-penerimanya</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Hp59702bRqdb4QGtrmgujM6Ebls=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-uang-bansos-1.jpg</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Uji UU Pelindungan Data Pribadi di MK, Saksi Ungkap Kekhawatiran Bocornya 204 Juta Data Pemilih KPU</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:45:27 +0700</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Sidang uji materi Undang-Undang Pelindungan Data Pribadi (UU PDP) di Mahkamah Konstitusi (MK) turut menyinggung isu keamanan data pemilih.</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866884/uji-uu-pelindungan-data-pribadi-di-mk-saksi-ungkap-kekhawatiran-bocornya-204-juta-data-pemilih-kpu</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/PAbAgyV5hyPTSxXruCP4txKklzA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/gugat-uu-pdp-di-MK.jpg</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>“Kata Siapa?” Istana Buka Suara soal Kabar Pratikno Sakit dan Mundur</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:44:56 +0700</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Kabar Pratikno sakit dan mundur dari kabinet mencuat. Prasetyo Hadi merespons dengan pertanyaan singkat yang bikin penasaran.</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866883/kata-siapa-istana-buka-suara-soal-kabar-pratikno-sakit-dan-mundur</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/40n_NtqmQqryvyMyNWCtt6PdB-c=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Menteri-Sekretaris-Negara-Mensesneg-Prasetyo-Hadi-di-Istana-Kepresidenan-b.jpg</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Jelang PKKMB UNS 2026: Cerita Maba Garap Tugas 'Dance Challenge' hingga Mental Rantau</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:43:45 +0700</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Maba UNS siap sambut PKKMB 2026. Ada cerita unik tugas 'dance challenge' hingga orang tua asal Medan rela sewa kos di Solo</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7866882/jelang-pkkmb-uns-2026-cerita-maba-garap-tugas-dance-challenge-hingga-mental-rantau</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/4G0NWMjUzqUXIUVsEEURnGIRP3A=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Mahasiswa-baru-berfoto-mengenakan-almamater-Universitas-Sebelas-Maret.jpg</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Mendikti Saintek Dorong Pekerja dan Buruh Tempuh Pendidikan Tinggi, Bawa Dampak Positif Masyarakat</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:42:45 +0700</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>KSPSI dan Universitas Terbuka (UT) buka akses kuliah bagi pekerja, termasuk pengakuan pengalaman belajar yang bisa mempercepat kelulusan.</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866881/mendikti-saintek-dorong-pekerja-dan-buruh-tempuh-pendidikan-tinggi-bawa-dampak-positif-masyarakat</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/tzBDOVxrLDBVSDlbXh27qvBe29A=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/mou-kspsi-dengan.jpg</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca BMKG Kepulauan Bangka Belitung Rabu, 12 Agustus 2026: Seluruh Wilayah Berawan</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:42:31 +0700</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Simak prakiraan cuaca BMKG untuk 7 kabupaten/kota di wilayah Provinsi Kepulauan Bangka Belitung pada Rabu, 12 Agustus 2026 besok.</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866880/prakiraan-cuaca-bmkg-kepulauan-bangka-belitung-rabu-12-agustus-2026-seluruh-wilayah-berawan</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/d6Z05zmYE-ZlbOieHWf6t6Q66ws=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-cerah-berawan-247.jpg</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Meski Tampil Memukau di Pramusim, Karier Bek Muda Liverpool Terhalang Izin Kerja di Inggris</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:41:42 +0700</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Ifeanyi Ndukwe tampil memukau di laga pramusim, tapi bek 18 tahun itu tak bisa bela Liverpool di laga resmi karena terkendala izin kerja Inggris.</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866879/meski-tampil-memukau-di-pramusim-karier-bek-muda-liverpool-terhalang-izin-kerja-di-inggris</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/2Ptks1b2u5Or_qpErExe_Sl1zFE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wonderkid-Liverpool-Ifeanyi-Ndukwe.jpg</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Sebelum Tewas Tertabrak KRL di Jurangmangu, Siswi Sempat Tulis Surat Terima Kasih untuk Guru</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:38:42 +0700</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Siswi tewas tertabrak KRL di Jurangmangu dikenang hangat, beretika, dan penuh perhatian; sekolah siapkan pendampingan emosional.</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866878/sebelum-tewas-tertabrak-krl-di-jurangmangu-siswi-sempat-tulis-surat-terima-kasih-untuk-guru</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/uU3KeK61xobdJ3IbGB3Mfc2n0Ww=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Suasana-di-Stasiun-Jurangmangu-32019.jpg</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Trump Sesumbar AS Kuasai Selat Hormuz, Klaim Ranjau Iran Sudah Disapu Bersih Angkatan Laut</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:36:59 +0700</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Trump klaim AS kini menguasai Selat Hormuz dan telah membersihkan ranjau Iran. Namun, lalu lintas kapal masih lesu dan ketegangan kawasan belum mereda</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866877/trump-sesumbar-as-kuasai-selat-hormuz-klaim-ranjau-iran-sudah-disapu-bersih-angkatan-laut</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oDBKmF-o4X7LaPeSgKFA268fB_4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/irak-iran-hormuz-minyak.jpg</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Perpres Ojol Hampir Rampung, Tinggal Finalisasi Rumusan Layanan Bisnisnya</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:36:56 +0700</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Pemerintah sedang memfinalisasi Peraturan Presiden tentang Transportasi Online dan dan memasukkan driver ojol sebagai pelaku UMKM.</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866876/perpres-ojol-hampir-rampung-tinggal-finalisasi-rumusan-layanan-bisnisnya</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ToY5RNXIMgCawdSlzIrqK_cvB4s=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Prasetyo-Hadi-usai-acara-pembukaan-Konvensi-Sains.jpg</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>UEFA Rombak Penggunaan VAR, Panduan Penggunaan Disiapkan Khusus</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:35:13 +0700</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>UEFA mengeluarkan panduan resmi dari mereka untuk penggunaan VAR di kompetisi yang berada di bawah naungan mereka.</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866875/uefa-rombak-penggunaan-var-panduan-penggunaan-disiapkan-khusus</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/TMVb2tGYVxi4Uz1fYumSRXNSLos=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/VIDEO-ASSISTANT-REFEREE-Wasit-Indonesia-Thoriq-Alkatiri.jpg</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Bangkit Pascabencana, MIN 4 Aceh Tamiang Kembali Miliki Ruang Belajar Layak</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:33:34 +0700</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Pemulihan MIN 4 Aceh Tamiang menjadi bagian dari upaya mengembalikan layanan pendidikan di wilayah terdampak bencana.</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866874/bangkit-pascabencana-min-4-aceh-tamiang-kembali-miliki-ruang-belajar-layak</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Xy_VAKrCeb-sGCPMuGLokFR9_OQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/renovasi-min-4-aceh-tam.jpg</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>iCAR Resmikan Dealer ke-2 di SCBD, Perluas Akses Kendaraan Listrik di Pusat Bisnis Jakarta</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:02:03 +0700</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Ferry kisihandi</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- iCAR Indonesia terus memperluas jaringan dealer di Indonesia melalui peresmian iCAR Andalan SCBD, dealer terbaru hasil kolaborasi dengan Andalan Group. 
+Berlokasi di kawasan pusat bisnis Jakarta,...</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlibf472/icar-resmikan-dealer-ke2-di-scbd-perluas-akses-kendaraan-listrik-di-pusat-bisnis-jakarta</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/icar-indonesia-meresmikan-icar-andalan-scbd-dealer-terbaru-hasil_260811145931-618.jpeg</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>OJK Siapkan Aturan Batas Kepemilikan Saham BEI Pasca-Demutualisasi</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:54:39 +0700</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Otoritas Jasa Keuangan (OJK) tengah mengkaji suatu konsep terkait pembatasan kepemilikan maksimum atas PT Bursa Efek Indonesia (BEI), yang akan dimasukkan sebagai ketentuan dalam Peraturan OJK (POJK)...</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlhz3370/ojk-siapkan-aturan-batas-kepemilikan-saham-bei-pascademutualisasi</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/033504600-1785491442-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Pertamina Patra Niaga Jalin Kerja Sama dengan Dukcapil, Perkuat Ketepatan Penyaluran Subsidi Energi</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:12:12 +0700</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Intan Pratiwi</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – PT Pertamina Patra Niaga dan Direktorat Jenderal Kependudukan dan Pencatatan Sipil (Ditjen Dukcapil) Kementerian Dalam Negeri menandatangani Perjanjian Kerja Sama (PKS) tentang Pemberian Hak Akses dan Pemanfaatan...</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlg0c522/pertamina-patra-niaga-jalin-kerja-sama-dengan-dukcapil-perkuat-ketepatan-penyaluran-subsidi-energi</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/pt-pertamina-patra-niaga-dan-direktorat-jenderal-kependudukan-dan_260811141200-810.jpeg</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Pelindo Multi Terminal Catat Kinerja Positif pada Semester I 2026</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:59:37 +0700</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Anak usaha PT Pelabuhan Indonesia (Persero), PT Pelindo Multi Terminal mencatatkan kinerja positif sepanjang Semester I 2026. SVP Sekretariat Perusahaan Pelindo Multi Terminal, Finan Syaifullah menyampaikan performa...</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlffd370/pelindo-multi-terminal-catat-kinerja-positif-pada-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260625140731-748.png</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Gejolak Harga Ayam di Tingkat Peternak, Ini Langkah yang Disiapkan Menteri Amran</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:55:56 +0700</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, MAKASSAR -- Menteri Pertanian (Mentan) Andi Amran Sulaiman mengatakan pemerintah telah mengambil sejumlah langkah untuk mengatasi kendala yang dialami pengusaha, khususnya peternak ayam skala kecil. Amran Sulaiman di Makassar,...</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlf98490/gejolak-harga-ayam-di-tingkat-peternak-ini-langkah-yang-disiapkan-menteri-amran</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/menteri-pertanian-mentan-andi-amran_260730145848-982.jpg</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Jaksa Beberkan 27 Nama Penerima Uang dari Kasus Korupsi Kuota Haji Khusus</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:54:05 +0700</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Angka yang mengalir ribuan hingga hingga jutaan dolar Amerika Serikat.</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267091/jaksa-beberkan-27-nama-penerima-uang-dari-kasus-korupsi-kuota-haji-khusus</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/Kcc9tinbWO-BlcvrzhwjP66t9xo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321231/original/009653200_1786434165-IMG_20260811_135837_642.jpg</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Jaksa Agung Lantik 15 Kajati Baru, Berikut Daftarnya</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:52:44 +0700</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Jaksa Agung melantik 15 Kajati baru, Sutikno ditunjuk memimpin Kejati Daerah Khusus Jakarta.</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267066/jaksa-agung-lantik-15-kajati-baru-berikut-daftarnya</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/Yo5lT28An9SWE-jU_7jwadGWHig=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321214/original/065490500_1786433230-72289.jpg</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Istana Tanggapi Isu Pratikno Sakit dan Mundur dari Menko PMK</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:06:22 +0700</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Pratikno dipastikan dalam keadaan sehat.</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267027/istana-tanggapi-isu-pratikno-sakit-dan-mundur-dari-menko-pmk</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/cZ7D2E3mgROFKh5jB2cRxitzHZs=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5429260/original/030041500_1764578706-Menteri_Koordinator_Bidang_Pembangunan_Manusia_dan_Kebudayaan__Menko_PMK___Pratikno__Membahas_Perihal_Screen_Time_dan_Kesehatan_Mental_Anak.jpg</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Terungkap Awal Mula Ratusan Senjata Tersembunyi di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:09:29 +0700</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Pemeriksaan dilakukan di tiga ruangan, yakni ruang kerja eks ketua pengurus, ruang kerja eks sekretaris, serta ruang sarana dan prasarana.</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267049/terungkap-awal-mula-ratusan-senjata-tersembunyi-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/ETTDU2qEXOzAfRQOJ_Mo1H87TaE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317518/original/012310700_1786017988-Bungker.webp</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>DKI Tawarkan 41 Aset Milik SKPD, Bidik Investasi Rp 13,1 T</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:00:39 +0700</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Jakarta membuka peluang investasi dari 41 aset dengan nilai fantastis.</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267033/dki-tawarkan-41-aset-milik-skpd-bidik-investasi-rp-131-t</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/DMN55_i-MOmhSUpVkYalQRTbCqk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321182/original/059652700_1786431601-fa13744b-1936-4aaa-9bac-1142fe76d418.jpg</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Momen Kiai Anwar Zahid Terduduk di Pinggir Jalan Usai Kecelakaan</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:07:29 +0700</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Anwar Zahid terlihat duduk di pinggir jalan setelah kecelakaan. Dia mengenakan kemeja biru dan sarung tanpa alas kaki.</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267024/momen-kiai-anwar-zahid-terduduk-di-pinggir-jalan-usai-kecelakaan</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/nxBkJ0PQhGFf1fSMuinrfWXvbhw=/0x0:498x281/673x379/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321169/original/028536600_1786431222-WhatsApp_Image_2026-08-11_at_13.23.08.jpeg</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Sidang Perdana Yaqut Didakwa Rugikan Negara Rp 622 Miliar</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:54:06 +0700</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Mantan Menteri Agama Yaqut Cholil Qoumas didakwa menerima USD271.500 dalam perkara dugaan korupsi pembagian kuota haji dan penyelenggaraan ibadah haji periode 2023-2024. Dakwaan dibacakan di Pengadilan Tipikor Jakarta, Selasa (11/8/2026). Jaksa juga mendakwa Yaqut terlibat dalam pengisian kuota haji khusus tambahan dengan jemaah tanpa masa tunggu. Perkara tersebut disebut menimbulkan kerugian negara lebih dari Rp 622 miliar berdasarkan laporan pemeriksaan investigatif BPK.</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/photo/read/8267016/sidang-perdana-yaqut-didakwa-rugikan-negara-rp-622-miliar</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/26W93yGTfQ9cKfAXNkCELGOQoJQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321155/original/021946300_1786430943-ya1.jpg</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>SDN Kebayoran Lama Selatan 09 dan 11 Akan Digabung, Gedung Baru Ditargetkan Rampung Setahun</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:06:14 +0700</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>SDN Kebayoran Lama Selatan 09 akan digabung dengan SDN Kebayoran Lama Selatan 11. Kedua gedung akan dibongkar dan dibangun ulang dalam setahun.</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/11/15060751/sdn-kebayoran-lama-selatan-09-dan-11-akan-digabung-gedung-baru</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/pWlBYooKUUhEeV1FbfnCux5Ac0s=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/07/21/6a5ef7461e48a.jpeg</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Ketika Bendera Merah Putih Tak Lagi Ramai Diburu, Pedagang Rasakan Lesunya Daya Beli</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:06:14 +0700</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Meski omzet anjlok lebih dari 50%, Budiman pedagang bendera musiman di Tangerang tak gentar. Baginya, merah putih adalah tradisi dan hormat pada para pahlawan.</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/11/14572991/ketika-bendera-merah-putih-tak-lagi-ramai-diburu-pedagang-rasakan-lesunya</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/hcwlM_-Nl37vQth-mRauUBsutvI=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7abaf0ba928.jpg</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Diduga Gejala Keracunan MBG Kambuh, 7 Siswa SMPN 3 Candimulyo Magelang Kembali Dirawat</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:06:14 +0700</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Sebelumnya, sebanyak 26 siswa SMP 3 Candimulyo dilaporkan keracunan MBG pada 7 Agustus lalu.</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/11/143820678/diduga-gejala-keracunan-mbg-kambuh-7-siswa-smpn-3-candimulyo-magelang</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/DdCunleASRWX8Wicn6QGvk-WFww=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7ac5abc4f14.jpg</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I581"/>
+  <autoFilter ref="A1:I685"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$685</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$833</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I685"/>
+  <dimension ref="A1:I833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -32633,8 +32633,6964 @@
         </is>
       </c>
     </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>KI: Keterbukaan informasi buka ruang warga berpartisipasi bangun kota</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:47:10 +0700</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Komisi Informasi DKI Jakarta menyampaikan keterbukaan informasi bukan sekadar kewajiban administratif badan publik, ...</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689379/ki-keterbukaan-informasi-buka-ruang-warga-berpartisipasi-bangun-kota</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000319464.jpg</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Panduan Menggunakan eSIM untuk Perjalanan Luar Negeri, Ini Langkah yang Perlu Diperhatikan</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:46:54 +0700</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Penggunaan eSIM untuk perjalanan luar negeri semakin diminati karena menawarkan akses internet tanpa perlu mengganti ...</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689375/panduan-menggunakan-esim-untuk-perjalanan-luar-negeri-ini-langkah-yang-perlu-diperhatikan</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/10/23/IMG_7248.jpg</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Pemerintah akan bentuk tim lintas kementerian atasi konflik agraria</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:46:43 +0700</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara (Mensesneg) Prasetyo Hadi mengatakan pemerintah akan membentuk tim lintas kementerian untuk ...</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689373/pemerintah-akan-bentuk-tim-lintas-kementerian-atasi-konflik-agraria</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001303588.jpg</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>‎DPR ingatkan pemda tangani sampah terintegrasi dari hulu ke hilir</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:46:19 +0700</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Anggota DPR RI dari Daerah Pemilihan (Dapil)  Kepulauan Bangka Belitung (Babel) Bambang Pati Jaya menilai ...</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689371/dpr-ingatkan-pemda-tangani-sampah-terintegrasi-dari-hulu-ke-hilir</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-15.09.56.jpeg</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Satgas PRR sisir Padang Pariaman himpun data kerusakan bencana</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:45:22 +0700</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Tim Satuan Tugas (Satgas) Percepatan Rehabilitasi dan Rekonstruksi Pascabencana Sumatera yang dibentuk oleh pemerintah ...</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689367/satgas-prr-sisir-padang-pariaman-himpun-data-kerusakan-bencana</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000979876.jpg</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>China Dental Show 2026 Hadirkan Inovasi Kedokteran Gigi yang Lebih Cerdas</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:45:05 +0700</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>China Dental Show 2026 (CDS 2026) akan digelar pada 13–16 Oktober di National Exhibition and Convention Center ...</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689364/china-dental-show-2026-hadirkan-inovasi-kedokteran-gigi-yang-lebih-cerdas</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/NECC-Shanghai-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Misi dagang Jatim-Kalbar bukukan transaksi Rp2,3 triliun</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:44:51 +0700</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Misi dagang dan investasi Jawa Timur-Kalimantan Barat membukukan komitmen transaksi Rp2,3 triliun, mencakup perdagangan ...</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689361/misi-dagang-jatim-kalbar-bukukan-transaksi-rp23-triliun</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-16.02.02.jpeg</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Pemkot Bogor mulai bangun jalan 1,4 km menuju pusat pemerintahan baru</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:42:18 +0700</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Bogor, Jawa Barat, mulai membangun jalan sepanjang 1,4 kilometer sebagai akses menuju kawasan pusat ...</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689360/pemkot-bogor-mulai-bangun-jalan-14-km-menuju-pusat-pemerintahan-baru</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1003330304.jpg</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>DKI promosikan 40 aset di JAFEX 2026 dengan potensi investasi Rp22,3 T</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:41:01 +0700</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi DKI Jakarta mempromosikan 40 Barang Milik Daerah (BMD) dengan estimasi potensi investasi awal ...</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689357/dki-promosikan-40-aset-di-jafex-2026-dengan-potensi-investasi-rp223-t</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_6812.jpeg</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Anomali suhu laut, BMKG: Waspada hujan sedang hingga lebat di Sumut</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:38:31 +0700</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi Klimatologi dan Geofisika (BMKG) menyebutkan masih terdapat anomali suhu muka laut yang hangat di ...</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689352/anomali-suhu-laut-bmkg-waspada-hujan-sedang-hingga-lebat-di-sumut</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/02/22/Banjir-Akibat-Drainase-Buruk-051018-SP-1.jpg</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Pemkot Cimahi salurkan Rastrada untuk jaga daya beli warga miskin</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:38:07 +0700</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Cimahi, Jawa Barat, bersama Bulog menyalurkan beras sejahtera daerah (Rastrada) kepada 2.227 ...</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689348/pemkot-cimahi-salurkan-rastrada-untuk-jaga-daya-beli-warga-miskin</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/491876.jpg</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Imigrasi Bali jaring 66 WNA bermasalah dalam sepekan</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:36:30 +0700</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Kantor Wilayah Direktorat Jenderal Imigrasi Bali memeriksa 66 warga negara asing (WNA) dari 27 negara yang terjaring ...</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689344/imigrasi-bali-jaring-66-wna-bermasalah-dalam-sepekan</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0013_1.jpg</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Gempa Kolombia, 188 orang di Valle del Cauca dilaporkan hilang</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:36:19 +0700</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Presiden Kolombia Abelardo de la Espriella telah mengonfirmasi sedikitnya 188 orang di Departemen Valle del ...</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689341/gempa-kolombia-188-orang-di-valle-del-cauca-dilaporkan-hilang</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/columbia1.jpg</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>BI: Festival Kopi Papua 2026 catat transaksi UMKM Rp1,12 miliar</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:36:05 +0700</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Kantor Perwakilan Bank Indonesia (BI) Papua mencatat transaksi usaha mikro, kecil, dan menengah (UMKM) mencapai Rp1,12 ...</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689337/bi-festival-kopi-papua-2026-catat-transaksi-umkm-rp112-miliar</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1002088908.jpg</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Tak cuma Soto Banjar, Chef Yulita soroti kuliner khas Kalsel</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:35:24 +0700</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Alumni MasterChef Indonesia Musim 5 Koki Yulita Intan Sari mengatakan Kalimantan Selatan memiliki beragam kuliner yang ...</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689336/tak-cuma-soto-banjar-chef-yulita-soroti-kuliner-khas-kalsel</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/tempImageMdRwTC.jpg</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Demak dibantu irigasi di 115 lokasi untuk optimalisasi pertanian</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:33:13 +0700</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Kabupaten Demak, Jawa Tengah, mendapatkan bantuan program irigasi dari pemerintah pusat yang tersebar di 115 lokasi ...</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689333/demak-dibantu-irigasi-di-115-lokasi-untuk-optimalisasi-pertanian</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IRPOM-DEMAK.jpg</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Ketum PSSI: Kami tidak pernah menomorduakan sepak bola putri</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:32:49 +0700</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Ketua Umum PSSI Erick Thohir menyebut tidak pernah menomorduakan sepak bola putri Indonesia, pada jumpa pers peluncuran ...</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689329/ketum-pssi-kami-tidak-pernah-menomorduakan-sepak-bola-putri</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0008.jpg</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Tim medis Bogor layani kesehatan warga terdampak banjir Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:32:27 +0700</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Tim Bogor Peduli Bencana memberikan pelayanan kesehatan gratis kepada warga terdampak banjir bandang di Desa Lintang ...</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689325/tim-medis-bogor-layani-kesehatan-warga-terdampak-banjir-aceh-tamiang</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1003330183.jpg</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Asap karhutla tak sehat, Pemprov Jambi kaji liburkan anak sekolah</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:31:51 +0700</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemrpov) Jambi tengah mengkaji untuk mengeluarkan surat edaran libur sekolah dampak asap akibat ...</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689324/asap-karhutla-tak-sehat-pemprov-jambi-kaji-liburkan-anak-sekolah</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/575711.jpg</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Menkeu tekankan pengawasan anggaran untuk stabilitas fiskal NTT</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:31:45 +0700</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa menekankan pentingnya pengawasan anggaran untuk memastikan penyaluran ...</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689321/menkeu-tekankan-pengawasan-anggaran-untuk-stabilitas-fiskal-ntt</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001673717.jpg</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Koki Firhan promosikan Rabeg, sajian khas Banten</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:30:57 +0700</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Koki Firhan Ashari menyampaikan perlunya upaya untuk terus mempromosikan kuliner khas daerah, termasuk di ...</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689320/koki-firhan-promosikan-rabeg-sajian-khas-banten</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/tempImagem6aSfk.jpg</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Satu WNI dilaporkan tewas dalam serangan di Selat Bab Al-Mandeb</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:30:08 +0700</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Seorang warga negara Indonesia (WNI) dilaporkan menjadi satu dari tiga anak buah kapal (ABK) yang tewas akibat sebuah ...</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689317/satu-wni-dilaporkan-tewas-dalam-serangan-di-selat-bab-al-mandeb</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/05/thumbs_b_c_6044ab5460e833073b11835da72b9b30.jpg</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>UI-Universitas Agung Podomoro kolaborasi riset cetak talenta unggul</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:29:44 +0700</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Universitas Indonesia (UI) dan Universitas Agung Podomoro (UAP) menjalin kerja sama di bidang pendidikan, riset, dan ...</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689315/ui-universitas-agung-podomoro-kolaborasi-riset-cetak-talenta-unggul</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0009-1.jpg</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Pakar usul 10 "pagar pelindung" harta rakyat di RUU Perampasan Aset</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:29:31 +0700</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Pakar kebijakan publik Bambang Harymurti mengusulkan 10 "pagar pelindung" harta rakyat untuk diatur di dalam ...</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689311/pakar-usul-10-pagar-pelindung-harta-rakyat-di-ruu-perampasan-aset</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Bambang-Harymurti.jpeg</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Pemkot Jaksel relokasi siswa SDN Kebayoran Lama dalam waktu dekat</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:27:12 +0700</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Jakarta Selatan menargetkan relokasi siswa SDN Kebayoran Lama Selatan 09 ke sekolah lain ...</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689307/pemkot-jaksel-relokasi-siswa-sdn-kebayoran-lama-dalam-waktu-dekat</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001022862.jpg</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Singapura naikkan proyeksi pertumbuhan 2026 jadi 4,5-5,5 persen</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:26:39 +0700</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Pemerintah Singapura pada Selasa (11/8) menaikkan proyeksi pertumbuhan ekonomi negara tersebut untuk 2026 menjadi ...</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689304/singapura-naikkan-proyeksi-pertumbuhan-2026-jadi-45-55-persen</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/03/26/singapura.jpg</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Menbud tantang cendekiawan menulis sejarah secara komprehensif</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:26:12 +0700</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Menteri Kebudayaan Fadli Zon menantang para cendekiawan dan ahli-ahli sejarah untuk menulis sejarah secara komprehensif ...</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689300/menbud-tantang-cendekiawan-menulis-sejarah-secara-komprehensif</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/20260811_094025.jpg</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Temuan senjata di sekolah, KPAI serukan pendampingan psikososial siswa</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:24:41 +0700</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Komisi Perlindungan Anak Indonesia (KPAI) meminta Pemprov DKI Jakarta untuk melakukan pendampingan psikososial bagi ...</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689297/temuan-senjata-di-sekolah-kpai-serukan-pendampingan-psikososial-siswa</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/1001017729.jpg</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Kejagung periksa tiga saksi terkait kasus TPPU Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:22:50 +0700</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Penyidik tim Kejaksaan Agung (Kejagung) atau Tim 9 memeriksa tiga saksi terkait kasus dugaan tindak pidana pencucian ...</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689295/kejagung-periksa-tiga-saksi-terkait-kasus-tppu-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000087690.jpg</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>CORE nilai hilirisasi perlu selaras dengan keterampilan tenaga kerja</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:22:22 +0700</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Direktur Eksekutif Center of Reform on Economics (CORE) Indonesia Mohammad Faisal menilai proyek hilirisasi perlu ...</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689293/core-nilai-hilirisasi-perlu-selaras-dengan-keterampilan-tenaga-kerja</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1002458130_1.png</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Tim gabungan tangani karhutla Bromo di area seluas 899,35 hektare</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:21:20 +0700</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Komandan Sektor Penanganan Kebakaran Hutan dan Lahan (Karhutla) Taman Nasional Bromo Tengger Semeru (TNBTS), Kolonel ...</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689289/tim-gabungan-tangani-karhutla-bromo-di-area-seluas-89935-hektare</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001413615.jpg</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Estella Loupatty dan Isabelle Nottet gabung klub Liga Putri Indonesia</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:20:23 +0700</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Anggota Komite Eksekutif PSSI Vivin Cahyani Sungkono memastikan dua pemain diaspora timnas putri Indonesia yaitu ...</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689287/estella-loupatty-dan-isabelle-nottet-gabung-klub-liga-putri-indonesia</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_7524-1.jpg</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Komisi III DPR minta polisi usut tuntas kematian mantan istri polisi di Medan</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:19:16 +0700</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Komisi III DPR RI meminta kepada kepolisian, khususnya Polrestabes Medan untuk mengusut tuntas kasus kematian Winda ...</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689283/komisi-iii-dpr-minta-polisi-usut-tuntas-kematian-mantan-istri-polisi-di-medan</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-4.07.56-PM.jpeg</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>8 serial Netflix terbaru 2026 yang wajib ditonton</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:19:05 +0700</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Netflix kembali menghadirkan beragam serial terbaru pada 2026, mulai dari drama romantis, komedi, hingga serial yang ...</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689281/8-serial-netflix-terbaru-2026-yang-wajib-ditonton</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/08/netflix.jpg</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Iran sebut Pemimpin Tertinggi Mojtaba Khamenei dalam kondisi sehat</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:18:14 +0700</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Presiden Iran Masoud Pezeshkian pada Senin (10/8) mengatakan bahwa Pemimpin Tertinggi Iran Mojtaba Khamenei dalam ...</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689279/iran-sebut-pemimpin-tertinggi-mojtaba-khamenei-dalam-kondisi-sehat</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/thumbs_b_c_0fa090334c2bffb41a324c288ecfa60e.jpg</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Bahlil temui Purbaya bahas pola penyaluran subsidi BBM</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:18:06 +0700</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menemui Menteri Keuangan (Menkeu) Purbaya Yudhi ...</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689277/bahlil-temui-purbaya-bahas-pola-penyaluran-subsidi-bbm</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_161319.jpg</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Menteri Transmigrasi ajak Unhas perkuat SDM unggul ke pelosok</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:17:41 +0700</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Menteri Transmigrasi (Mentrans) Iftitah Sulaiman Suryanagara mendorong perguruan tinggi, khususnya Universitas ...</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689275/menteri-transmigrasi-ajak-unhas-perkuat-sdm-unggul-ke-pelosok</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0034.jpg</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Wamen: Investasi budaya berdampak pada pariwisata dan ekonomi kreatif</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:17:39 +0700</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Wakil Menteri (Wamen) Kebudayaan Republik Indonesia Giring Ganesha Djumaryo mengatakan investasi di bidang kebudayaan ...</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689271/wamen-investasi-budaya-berdampak-pada-pariwisata-dan-ekonomi-kreatif</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001107069.jpg</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Parti Libur 2026 hadirkan konsep festival musik di wahana bermain</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:16:37 +0700</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Festival musik Parti Libur 2026 menawarkan konsep yang memadukan pertunjukan musik dan wahana bermain di Batu Night ...</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689269/parti-libur-2026-hadirkan-konsep-festival-musik-di-wahana-bermain</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/501c07ab-c6c7-4202-a845-9460246daca3.jpeg</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>RSUD Koja gelar Kultura Market dengan UMKM tingkatkan produk lokal</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:16:11 +0700</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Rumah Sakit Umum Daerah (RSUD) Koja, Jakarta Utara menggelar Kultura Market yang melibatkan pelaku Usaha Mikro ...</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689265/rsud-koja-gelar-kultura-market-dengan-umkm-tingkatkan-produk-lokal</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Screen-Shot-2026-08-11-at-15.42.49.jpg</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Apakah lari saat cuaca panas aman untuk tubuh?</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:15:48 +0700</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Lari menjadi salah satu olahraga yang banyak dipilih karena sederhana dan bisa dilakukan hampir kapan saja. Namun, ...</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689261/apakah-lari-saat-cuaca-panas-aman-untuk-tubuh</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/01/19/pexels-tirachard-kumtanom-112571-347134.jpg</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Bos BEI sebut kewenangan sepenuhnya di MSCI jelang review 12 Agustus</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:14:46 +0700</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Direktur Utama PT Bursa Efek Indonesia (BEI) Jeffrey Hendrik menyatakan bahwa kewenangan sepenuhnya berada di kendali ...</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689259/bos-bei-sebut-kewenangan-sepenuhnya-di-msci-jelang-review-12-agustus</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-13.28.03.jpeg</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Shenzhen tandai hitung mundur 100 hari jelang pertemuan APEC 2026</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:13:43 +0700</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Dengan papan pengumuman, spanduk, dekorasi, serta berbagai instalasi luar ruangan bertema, Kota ...</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689255/shenzhen-tandai-hitung-mundur-100-hari-jelang-pertemuan-apec-2026</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000014_20260811_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>BPS: Sekitar enam persen anak Indonesia belum punya akta kelahiran</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:12:45 +0700</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mengatakan sekitar enam persen anak Indonesia berusia 0-17 tahun belum memiliki ...</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689249/bps-sekitar-enam-persen-anak-indonesia-belum-punya-akta-kelahiran</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-14.17.06.jpg</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Bea Cukai gagalkan pengiriman 8,96 juta batang rokok ilegal</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:12:39 +0700</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Direktorat Jenderal Bea dan Cukai (DJBC) menggagalkan pengiriman 8,96 juta batang rokok ilegal yang tidak dilekati pita ...</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689247/bea-cukai-gagalkan-pengiriman-896-juta-batang-rokok-ilegal</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/3ae0aa15-e4eb-4216-b0b2-fe107c1efc93.jpeg</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Venezuela tetap waspada usai gempa di Kolombia</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:12:19 +0700</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Gempa bumi bermagnitudo 7,4 yang mengguncang Kolombia pada Senin (10/8) juga terasa di sejumlah negara bagian di ...</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689244/venezuela-tetap-waspada-usai-gempa-di-kolombia</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000015_20260811_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Semarak HUT ke-81 RI, KAI Hadirkan Diskon Tiket 17% dan Tarif Rp8 untuk LRT Jabodebek serta Commuter Line</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:12:17 +0700</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) menghadirkan Promo Spesial 17-8-2026 dalam rangka menyemarakkan Hari Ulang Tahun ...</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689240/semarak-hut-ke-81-ri-kai-hadirkan-diskon-tiket-17-dan-tarif-rp8-untuk-lrt-jabodebek-serta-commuter-line</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/KAI-Hadirkan-Diskon-Tiket-17.jpg</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Ekspor gim Indonesia diproyeksi jadi pendorong pertumbuhan ekonomi</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:11:37 +0700</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Direktur Gim Kementerian Ekonomi Kreatif Luat Sihombing mengatakan pasar global yang mengonsumsi produk gim Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689237/ekspor-gim-indonesia-diproyeksi-jadi-pendorong-pertumbuhan-ekonomi</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000457420.jpg</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Bahan tradisional tak boleh dihilangkan saat kreasikan kuliner daerah</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:09:51 +0700</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Pakar kuliner sekaligus lulusan MasterChef Indonesia koki Yulita Intan Sari dan koki Firhan Ashari menilai penggunaan ...</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689233/bahan-tradisional-tak-boleh-dihilangkan-saat-kreasikan-kuliner-daerah</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/tempImagewoHyoB.jpg</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Persib Bandung pinjamkan Hamra Hehanussa ke Garudayaksa</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:08:46 +0700</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Persib Bandung meminjamkan bek Al Hamra Hehanussa kepada klub promosi Garudayaksa untuk mendapatkan pengalaman dan ...</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689229/persib-bandung-pinjamkan-hamra-hehanussa-ke-garudayaksa</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_9443.jpeg</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Politik</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Siapa saja tokoh perumus teks Proklamasi? Ini daftarnya</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Teks Proklamasi Kemerdekaan Indonesia menjadi salah satu catatan bersejarah yang memiliki arti penting bagi perjalanan ...</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689120/siapa-saja-tokoh-perumus-teks-proklamasi-ini-daftarnya</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/07/26/Proklamasi060809-1.jpg</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Politik</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Mengenal Sayuti Melik, sosok di balik pengetik teks Proklamasi</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:14:07 +0700</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Sayuti Melik merupakan salah satu tokoh penting dalam sejarah Proklamasi Kemerdekaan Indonesia. Ia dikenal sebagai ...</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689097/mengenal-sayuti-melik-sosok-di-balik-pengetik-teks-proklamasi</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/sayutimalik.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Bea Cukai Priok Cegah Pengiriman 8,9 Juta Rokok Ilegal Disamarkan Baja Ringan</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:44:26 +0700</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Bea Cukai Tanjung Priok dan Direktorat P2 Bea Cukai menggagalkan pengiriman 8,96 juta batang rokok ilegal yang hendak dikirimkan ke wilayah Sumatera.</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613930/bea-cukai-priok-cegah-pengiriman-8-9-juta-rokok-ilegal-disamarkan-baja-ringan</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/bea-cukai-tanjung-priok-dan-direktorat-p2-bea-cukai-menggagalkan-pengiriman-896-juta-batang-rokok-ilegal-yang-hendak-dikirimka-1786441342921_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Klarifikasi &amp;amp; Permohonan Maaf Newport soal Kejadian di The Sounds Project</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:39:10 +0700</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Newport menyampaikan permohonan maaf atas kejadian di The Sound Project. Aktivitas tersebut bukan merupakan program maupun konsep promosi.</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613924/klarifikasi-permohonan-maaf-newport-soal-kejadian-di-the-sounds-project</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/1144667396-1786419072166.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Ada Saksi Mahkota di Kasus Saepul Mutilasi Pria, Sempat Cium Bau Darah</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:38:46 +0700</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Polisi ungkap fakta baru tentang Saepul, tersangka pembunuhan dan mutilasi di Depok. Teman kontrakan sempat curiga setelah mencium bau darah.</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613923/ada-saksi-mahkota-di-kasus-saepul-mutilasi-pria-sempat-cium-bau-darah</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rekonstruksi-kasus-saepul-mutilasi-pria-di-depok-1786441089086_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>WN Nigeria Jadi Tersangka Usai Overstay 3.073 Hari, Ditahan di Lapas Bekasi</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:29:33 +0700</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Audrey Santoso</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Kantor Imigrasi Bekasi menetapkan WN Nigeria OCO sebagai tersangka overstay 3.073 hari. OCO ditahan setelah pelanggaran keimigrasian terungkap.</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613908/wn-nigeria-jadi-tersangka-usai-overstay-3-073-hari-ditahan-di-lapas-bekasi</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/wn-nigeria-berinisial-oco-sebagai-tersangka-karena-overstay-selama-3073-hari-dok-istimewa-1786440547197_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Andre Rosiade Kecam Promosi 'Hafal Quran Berhadiah Miras': Penistaan!</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:26:54 +0700</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Gibran Maulana Ibrahim</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Wakil Ketua DPR Andre Rosiade mengecam tantangan hafalan Al-Qur'an untuk miras di festival musik. Ia desak penegakan hukum dan revisi izin acara.</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613904/andre-rosiade-kecam-promosi-hafal-quran-berhadiah-miras-penistaan</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/03/andre-rosiade-1780476535979_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sambangi Kejagung, Minta Pendampingan Usai Kasus Tata Kelola MBG</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:26:49 +0700</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono menyambangi Kejagung. Dia bersilaturahmi sekaligus meminta pendampingan dan pengawasan pelaksanaan program Makan Bergizi Gratis (MBG).</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613903/kepala-bgn-sambangi-kejagung-minta-pendampingan-usai-kasus-tata-kelola-mbg</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/13/ilustrasi-kejagung-1755064730615_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Komplotan Rampok Pegawai Koperasi di Bekasi 3 Kali Beraksi, Sasar Korban Acak</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:24:25 +0700</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Para pelaku tidak mengenal korban. Dalam kasus terakhir, pelaku membuntuti nasabah koperasi sedari bank hingga akhirnya melakukan perampokan.</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613897/komplotan-rampok-pegawai-koperasi-di-bekasi-3-kali-beraksi-sasar-korban-acak</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/perampokan-nasabah-bank-di-siang-bolong-di-cibitung-bekasi-1786238003822_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Kejanggalan Kematian Wanita di Tangerang yang Ternyata Dibunuh Pacar</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:21:10 +0700</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Polisi ungkap kejanggalan kematian wanita di Tangerang, yang awalnya dianggap bunuh diri. Ternyata korban dibunuh pacarnya karena permintaan menikah.</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613891/kejanggalan-kematian-wanita-di-tangerang-yang-ternyata-dibunuh-pacar</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/07/25/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Pakar Dorong Perampasan Aset Permanen Diputus Pengadilan Independen</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:18:15 +0700</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Bambang Harymurti menekankan pentingnya pengadilan independen dalam RUU Perampasan Aset, membedakan antara pembekuan sementara dan perampasan permanen.</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613887/pakar-dorong-perampasan-aset-permanen-diputus-pengadilan-independen</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rapat-dengar-pendapat-umum-komisi-iii-dpr-bersama-sejumlah-pakar-di-gedung-dpr-senayan-jakarta-selasa-1182026-1786431721843_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Polusi Jakarta Disorot Saat AC Milan Vs Chelsea, Pramono Siapkan Hujan Buatan</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:15:30 +0700</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Polusi udara Jakarta jadi sorotan saat laga AC Milan vs Chelsea. Gubernur Pramono Anung sebut hujan buatan dan dorong penggunaan transportasi umum.</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613886/polusi-jakarta-disorot-saat-ac-milan-vs-chelsea-pramono-siapkan-hujan-buatan</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/ahy-dan-pramono-anung-beliadetikcom-1786435906041_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Yaqut Bantah Terima Rp 1 Pun di Kasus Kuota Haji dan Ajukan Jadi Tahanan Rumah</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:13:23 +0700</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Mantan Menag Yaqut Cholil Qoumas membantah dakwaan korupsi kuota haji, menyatakan tidak menerima uang. Kuasa hukumnya minta pengalihan status tahanan.</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613881/yaqut-bantah-terima-rp-1-pun-di-kasus-kuota-haji-dan-ajukan-jadi-tahanan-rumah</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/eks-menag-yaqut-didakwa-perkara-kuota-haji-negara-disebut-rugi-rp622-miliar-1786428543901_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Sempat Kabur, Kakek Pemerkosa ABG di Bogor hingga Hamil Ditangkap</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:05:49 +0700</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Seorang remaja 15 tahun di Bogor diduga diperkosa oleh tetangga hingga hamil. Pelaku berusia 70 tahun telah ditangkap polisi untuk penanganan lebih lanjut.</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613864/sempat-kabur-kakek-pemerkosa-abg-di-bogor-hingga-hamil-ditangkap</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/05/03/ilustrasi-pelaku-pencabulan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Bayi Lahir di Luar Faskes Akan Dapat Akta Kelahiran Digital</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:04:27 +0700</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Chayyara Zulghifary</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian pastikan akta kelahiran digital untuk bayi lahir di luar faskes. Surat edaran akan memudahkan pelaporan kelahiran dan kematian.</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613861/bayi-lahir-di-luar-faskes-akan-dapat-akta-kelahiran-digital</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kemendagri-1786439043619_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Kejagung Periksa Sekretaris Kepala BGN Terkait Korupsi Tata Kelola MBG</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:59:59 +0700</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Kejagung memeriksa 12 saksi dalam kasus dugaan korupsi Makan Bergizi Gratis. Salah satunya Sekretaris Kepala BGN berinisial RRNWP</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613849/kejagung-periksa-sekretaris-kepala-bgn-terkait-korupsi-tata-kelola-mbg</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/13/ilustrasi-kejagung-1755064730562_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Bambang Harymurti Minta RUU Perampasan Aset Atur Aset Bersama Suami-Istri</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:58:14 +0700</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Bambang Harymurti mengatakan RUU Perampasan Aset perlu memerhatikan aset yang dimiliki oleh suami istri. Pengadilan perlu menentukan kepemilikan yang sah.</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613846/bambang-harymurti-minta-ruu-perampasan-aset-atur-aset-bersama-suami-istri</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rapat-komisi-iii-dpr-1786438674309_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Pakar Minta RUU Perampasan Aset Jangan Jadi Pembungkaman Lawan Politik</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:52:57 +0700</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Bambang Harymurti mengatakan RUU Perampasan Aset jangan sampai jadi alat pembungkaman lawan politik. Menurut dia, RUU itu jangan jadi alat kekuasaan penguasa.</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613836/pakar-minta-ruu-perampasan-aset-jangan-jadi-pembungkaman-lawan-politik</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rapat-dengar-pendapat-umum-komisi-iii-dpr-bersama-sejumlah-pakar-di-gedung-dpr-senayan-jakarta-selasa-1182026-1786431721843_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Saepul Pemutilasi Bawa Obat Saat Reka Ulang, Polisi: Dia Menderita HIV</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:50:40 +0700</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Tersangka Saepul membawa obat saat reka ulang kasus mutilasi. Polisi menyebutkan Saepul menderita HIV.</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613823/saepul-pemutilasi-bawa-obat-saat-reka-ulang-polisi-dia-menderita-hiv</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/polisi-menggelar-reka-ulang-kasus-mutilasi-pria-di-depok-tersangka-saepul-ikut-dihadirkan-1786424451846_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Pernyataan 'Otak Kamu Ada Nggak' Dikecam KWP, Benny Harman Minta Maaf</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:45:10 +0700</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Wartawan DPR mengecam pernyataan merendahkan Benny K Harman yang berkata 'otak kamu ada nggak' kepada wartawan. KWP menilai pernyataan itu merendahkan wartawan.</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613812/pernyataan-otak-kamu-ada-nggak-dikecam-kwp-benny-harman-minta-maaf</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/25/ketua-fraksi-partai-demokrat-mpr-ri-benny-k-harman-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Chat WA di HP Korban Bongkar Rekayasa Pembunuhan Wanita di Tangerang</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:43:24 +0700</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Polresta Tangerang mengungkap kasus wanita yang meninggal ternyata dibunuh. Pelaku adalah pacar yang enggan menikahi korban lantaran sudah berkeluarga.</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613808/chat-wa-di-hp-korban-bongkar-rekayasa-pembunuhan-wanita-di-tangerang</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/29/kapolresta-tangerang-kombes-andi-muhammad-indra-waspada-amirullah-1782747349426_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Reses di Kolaka, Bahtra Bagikan Sembako dan Sertifikat Tanah ke 3 Desa</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:43:15 +0700</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Waka Komisi II DPR RI, Bahtra Banong, melakukan reses di Kolaka, mendengarkan aspirasi masyarakat, dan menyerahkan ratusan paket sembako serta sertifikat tanah.</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613807/reses-di-kolaka-bahtra-bagikan-sembako-dan-sertifikat-tanah-ke-3-desa</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/bahtra-banong-1786437760447_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Sutrimo Kirim Foto Duduk Seberang Rumah Febrie ke Adik Sebelum Ditemukan Tewas</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:41:45 +0700</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Tim detikJateng</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Keluarga menyebut Sutrimo masih berkirim pesan termasuk saat duduk di seberang rumah eks Jampidsus Febrie Adriansyah beberapa jam sebelum ditemukan tewas.</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613804/sutrimo-kirim-foto-duduk-seberang-rumah-febrie-ke-adik-sebelum-ditemukan-tewas</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/sutrimo-1786212205527_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Kejagung Periksa Saksi Pihak Perbankan soal Kasus TPPU Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:39:48 +0700</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Kejagung memeriksa 3 saksi terkait tindak pidana pencucian uang (TPPU) yang menjerat eks Jampidsus Febrie Adriansyah. Dua di antara saksi dari pihak perbankan.</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613802/kejagung-periksa-saksi-pihak-perbankan-soal-kasus-tppu-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/13/ilustrasi-kejagung-1755064730562_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Kapolri Hadiri Silaturahmi Pimpinan Lembaga Negara di Cilangkap, Perkuat Kebersamaan</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:37:00 +0700</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Kapolri Jenderal Listyo Sigit Prabowo menghadiri makan siang bersama Menko Polkam dan pimpinan TNI, memperkuat koordinasi antarinstansi untuk keamanan nasional.</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613793/kapolri-hadiri-silaturahmi-pimpinan-lembaga-negara-di-cilangkap-perkuat-kebersamaan</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kapolri-jenderal-listyo-sigit-prabowo-menghadiri-agenda-makan-siang-bersama-menko-bidang-politik-dan-keamanan-polkam-ri-djamar-1786437112585_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Pihak Keluarga Ungkap Awal Mula Sutrimo Kerja di Rumah Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:35:40 +0700</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Anang Firmansyah</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Sutrimo, pria yang tewas di depan klinik kecantikan, bekerja lama dengan mantan Jaksa Agung Muda Febrie Adriansyah. Keluarga mengungkapkan detail pekerjaannya.</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613791/pihak-keluarga-ungkap-awal-mula-sutrimo-kerja-di-rumah-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/polisi-masih-mendalami-penyebab-tewasnya-pria-bernama-sutrimo-di-depan-klinik-kecantikan-mordent-di-jaksel-penyebab-kematian-s-1785156176528_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>4 Jam Diperiksa KPK Terkait Korupsi Bansos 2020, Rudy Tanoe: Tak Ada Tanggapan</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:32:11 +0700</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Adrial akbar</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Setelah diperiksa, Rudy enggan bicara banyak. Dia meminta materi pemeriksaannya ditanyakan ke tim pengacaranya.</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613788/4-jam-diperiksa-kpk-terkait-korupsi-bansos-2020-rudy-tanoe-tak-ada-tanggapan</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rudy-tanoe-usai-diperiksa-kpk-di-kasus-korupsi-bansos-tahun-anggaran-2020-adrialdetikcom-1786436818083_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Cegah Penurunan Tanah, AHY Minta DKI Perkuat Infrastruktur</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:31:16 +0700</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Menteri Agus Harimurti Yudhoyono mendorong penguatan infrastruktur Jakarta untuk menghadapi penurunan muka tanah dan kenaikan air laut.</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613784/cegah-penurunan-tanah-ahy-minta-dki-perkuat-infrastruktur</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/menteri-koordinator-bidang-infrastruktur-dan-pembangunan-kewilayahan-agus-harimurti-yudhoyono-ahy-1786437021760_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>KDM Usulkan Ubah Batas Maksimum Gaji Orang Tua Mahasiswa Penerima KIP</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:30:44 +0700</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Tenri Monic Libery Hana</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Gubernur Jabar usulkan perubahan syarat gaji orang tua penerima KIP Kuliah. Ia berikan motivasi dan bantuan untuk mahasiswa dengan keterbatasan ekonomi.</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613746/kdm-usulkan-ubah-batas-maksimum-gaji-orang-tua-mahasiswa-penerima-kip</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kdm-usulkan-ubah-batas-maksimum-gaji-orang-tua-mahasiswa-penerima-kip-1786435744070_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Penjelasan Versi EO dan MC soal Challenge Hafalan Al-Qur'an Berhadiah Miras</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:27:27 +0700</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Video challenge menghafal surah Al-Qur'an dengan hadiah miras ramai dikecam. Pihak event organizer (EO) festival musik buka suara soal dugaan penistaan agama.</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613779/penjelasan-versi-eo-dan-mc-soal-challenge-hafalan-al-quran-berhadiah-miras</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/1144667396-1786419072166_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Ada Lagi Penebangan Pohon Ilegal di Bandung, Kini di Dago</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:20:27 +0700</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Rifat Alhamidi</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Bandung kembali menemukan sejumlah pohon di Jalan Ir H Juanda atau kawasan Dago yang ditebang sembarangan.</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613768/ada-lagi-penebangan-pohon-ilegal-di-bandung-kini-di-dago</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/penebangan-pohon-ilegal-di-jalan-dago-1786417401892_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Jaksa KPK Ungkap Dampak Korupsi Kuota Haji: Ribuan Jemaah Gagal Berangkat</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:19:07 +0700</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Jaksa ungkap kasus korupsi kuota haji 2023-2024 oleh eks Menag Yaqut, menyebabkan ribuan jemaah gagal berangkat dan kerugian negara Rp 622 miliar.</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613763/jaksa-kpk-ungkap-dampak-korupsi-kuota-haji-ribuan-jemaah-gagal-berangkat</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/eks-menag-yaqut-didakwa-perkara-kuota-haji-negara-disebut-rugi-rp622-miliar-1786428544309_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Alasan Pramono Tunjuk TransJ Kelola Transportasi ke Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:15:30 +0700</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Keputusan itu diambil berdasarkan pengalaman Transjakarta dalam mengelola transportasi publik di Jakarta dan Jabodetabek.</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613755/alasan-pramono-tunjuk-transj-kelola-transportasi-ke-kepulauan-seribu</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/ahy-dan-pramono-anung-beliadetikcom-1786435906041_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Dasco Pimpin Rapat DPR dengan Pemerintah, Bahas Konflik Agraria</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:07:40 +0700</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>DPR menggelar rapat koordinasi dengan pemerintah membahas permasalahan agraria. Wakil Ketua DPR Sufmi Dasco minta penyelesaian cepat atas temuan di lapangan.</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613739/dasco-pimpin-rapat-dpr-dengan-pemerintah-bahas-konflik-agraria</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rapat-koordinasi-dpr-dan-pemerintah-di-gedung-dpr-senayan-jakarta-selasa-1182026-1786435617828_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Relokasi PKL Kiaracondong Bandung, 800 Kios Disiapkan &amp;amp; Gratis 3 Bulan</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:04:24 +0700</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Nasywa Azzahra</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Pemerintah Jabar dan Kota Bandung menertibkan bangunan liar dan PKL di Kiaracondong. Relokasi pedagang disiapkan di Pasar BTM dengan 800 kios tersedia.</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613728/relokasi-pkl-kiaracondong-bandung-800-kios-disiapkan-gratis-3-bulan</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/sekda-jabar-herman-suryatman-1786435253954.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Saepul Pemutilasi Incar Korban Lewat Aplikasi Hornet</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:01:11 +0700</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Polisi ungkap fakta baru kasus pembunuhan dan mutilasi oleh Saepul, yang mengenal korban melalui aplikasi kencan. Pelaku dijerat dengan pasal pembunuhan.</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613723/saepul-pemutilasi-incar-korban-lewat-aplikasi-hornet</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/polisi-menggelar-reka-ulang-kasus-mutilasi-pria-di-depok-tersangka-saepul-ikut-dihadirkan-1786424451846_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>PBNU Sesalkan Challenge Hafalan Qur'an demi Miras: Usut Tuntas</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:53:30 +0700</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Kanavino Ahmad Rizqo</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>PBNU menyesalkan aksi promosi minuman keras (miras) berkedok tantangan (challenge) hafalan Al-Qur'an saat konser musik di Ancol, Jakarta Utara (Jakut).</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613710/pbnu-sesalkan-challenge-hafalan-quran-demi-miras-usut-tuntas</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/19/ketua-pbnu-gus-fahrur-ditemui-di-masjid-al-akbar-surabaya_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Di Depan AHY, Pramono Singgung APBD Jakarta Dipotong: Jangan Nambah Lagi</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:52:11 +0700</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Pramono Anung menyinggung pemotongan anggaran Jakarta saat menghadiri JAFEX 2026. Pramono berharap pemotongan anggaran Jakarta tak ditambah lagi.</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613707/di-depan-ahy-pramono-singgung-apbd-jakarta-dipotong-jangan-nambah-lagi</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/gubernur-dki-jakarta-pramono-anung-1786434591327_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Viral Pria ODGJ Lempari Kepala Balita Pakai Batu di Lampung</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:50:56 +0700</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Tommy Saputra</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Viral pria melempar batu ke kepala balita di rumah makan bakso di Kabupaten Lampung Timur, Lampung.</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613706/viral-pria-odgj-lempari-kepala-balita-pakai-batu-di-lampung</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/05/03/ilustrasi-pelaku-pencabulan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Dedi Congor Tersangka di Polri, KPK Pastikan Penyidikan Bea Cukai Tetap Jalan</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:49:55 +0700</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Adrial akbar</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>KPK memastikan penyidikan kasus korupsi Dedi Congor tetap berjalan meski ia ditetapkan sebagai tersangka gratifikasi oleh Polri. Perkara berbeda objek.</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613705/dedi-congor-tersangka-di-polri-kpk-pastikan-penyidikan-bea-cukai-tetap-jalan</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/13/plt-direktur-penyidikan-kpk-achmad-taufik-husein-1776092670324_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Saepul Peragakan 51 Adegan Mutilasi Pria hingga Buang Jasad di Reka Ulang</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:49:38 +0700</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Polisi menggelar reka ulang kasus pembunuhan dan mutilasi pria di Depok. Tersangka Saepul memeragakan 51 adegan, termasuk penusukan dan pembuangan jasad.</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613703/saepul-peragakan-51-adegan-mutilasi-pria-hingga-buang-jasad-di-reka-ulang</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rekonstruksi-kasus-saepul-mutilasi-pria-kenalan-medsos-di-depok-1786434539840_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Pramono Ungkap Sejumlah Proyek yang Bakal Jadi Wajah Baru Jakarta, Apa Saja?</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:49:04 +0700</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Pramono berbicara mengenai target wajah baru Jakarta. Dia menjelaskan sejumlah proyek di Jakarta tengah digenjot agar selesai dan beroperasi di tahun depan.</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613702/pramono-ungkap-sejumlah-proyek-yang-bakal-jadi-wajah-baru-jakarta-apa-saja</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/pramono-anung-beliadetikcom-1786434368622_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Mobil Minum Pertalite Bakal Makin Diperketat</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:23:48 +0700</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Pemerintah akan memperketat pembelian BBM subsidi, khususnya Pertalite, untuk kelompok ekonomi atas. Pembatasan ini bertujuan agar subsidi tepat sasaran.</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8613895/mobil-minum-pertalite-bakal-makin-diperketat</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/pertamax-pertamax-turbo-dan-green-95-kompak-turun-harga-1785651003482_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Penindakan Rokok Ilegal Bea Cukai Melonjak 100%, Tembus 1,2 Miliar Batang!</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:19:10 +0700</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>Penindakan terhadap peredaran rokok ilegal meningkat drastis dibanding 2025.</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613889/penindakan-rokok-ilegal-bea-cukai-melonjak-100-tembus-1-2-miliar-batang</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/direktur-jenderal-bea-dan-cukai-djaka-budi-utama-1786439830568_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Transaksi Digital Melonjak, Sistem Pembayaran Pemerintah Diperkuat</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:00:06 +0700</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Ardan Adhi Chandra</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Sistem pembayaran nasional diperkuat dengan pengembangan berbasis riset dan didukung rekomendasi kebijakan yang implementatif.</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613893/transaksi-digital-melonjak-sistem-pembayaran-pemerintah-diperkuat</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2018/06/08/cbe5e480-7ccd-4daf-8fd6-635d9d509d47_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Penyaluran LPG 3 Kg Bakal Makin Ketat, Data NIK Dipakai untuk Verifikasi</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:54:36 +0700</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Fadhly Fauzi Rachman</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Pertamina Patra Niaga dan Ditjen Dukcapil sepakat memanfaatkan data kependudukan untuk verifikasi penyaluran LPG 3 kg, memastikan subsidi tepat sasaran.</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8613899/penyaluran-lpg-3-kg-bakal-makin-ketat-data-nik-dipakai-untuk-verifikasi</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/21/gas-lpg-melon-1776782266499_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Pemerintah Dorong Satgas buat Urai Hambatan Investasi</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:50:55 +0700</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Pemerintah akan mempercepat penyelesaian berbagai hambatan investasi melalui Satuan Tugas (Satgas) Debottlenecking.</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613833/pemerintah-dorong-satgas-buat-urai-hambatan-investasi</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/17/investasi-ekonomi-1752736286324_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Bea Cukai Gagalkan Penyelundupan Rokok Ilegal Rp13,3 M</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:50:53 +0700</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Pradita Utama</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Rokok ilegal senilai Rp13,3 miliar digagalkan di Pelabuhan Tanjung Priok. Penindakan ini mencegah potensi kerugian negara Rp8,6 miliar.</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8613824/bea-cukai-gagalkan-penyelundupan-rokok-ilegal-rp13-3-m</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/bea-cukai-gagalkan-penyelundupan-rokok-ilegal-rp133-m-1786438108211.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Bea Cukai Tindak 8,9 Juta Batang Rokok Ilegal, Selamatkan Duit Negara Rp 8,66 M</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:37:17 +0700</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Direktorat Jenderal Bea dan Cukai Kementerian Keuangan menggagalkan pengiriman 8,96 juta batang rokok ilegal.</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613794/bea-cukai-tindak-8-9-juta-batang-rokok-ilegal-selamatkan-duit-negara-rp-8-66-m</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/direktur-jenderal-bea-dan-cukai-djaka-budi-utama-1786437390909_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Calon Gubernur PFII Sudah Ada, Airlangga: Dari dalam Pemerintah</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:27:28 +0700</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Menteri Airlangga Hartarto mengungkapkan calon Gubernur Pusat Finansial Internasional Indonesia sudah ada dari internal pemerintah.</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613778/calon-gubernur-pfii-sudah-ada-airlangga-dari-dalam-pemerintah</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/02/menko-perekonomian-airlangga-hartarto-evadetikcom-1770026987861_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>OJK Siapkan Bos Baru Bursa Mineral, Bakal Awasi Komoditas Strategis</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:03:53 +0700</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>OJK mengonfirmasi surat presiden tentang pembentukan Dewan Komisioner baru untuk mengawasi Bursa Mineral dan Komoditas Strategis demi kemakmuran rakyat.</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613727/ojk-siapkan-bos-baru-bursa-mineral-bakal-awasi-komoditas-strategis</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/12/30/92b40aae-7615-45cc-8e4c-0d4951ac21b9_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Angela Lorenza Hamil Anak Cowok: Gak Sabar Ketemu</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:12:25 +0700</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Angela Lorenza membagikan kabar terbaru terkait kehamilan. Ia mengungkapkan jenis kelamin anaknya.</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613867/angela-lorenza-hamil-anak-cowok-gak-sabar-ketemu</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/angela-lorenza-1786439134272_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Tya Ariestya Ajarkan Anak Menghargai Uang Lewat Cara Hidup Sederhana</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:09:53 +0700</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>Aktris Tya Ariestya menerapkan gaya asuh sederhana untuk anak-anaknya, mengajarkan nilai uang dan pentingnya beradaptasi dengan berbagai kalangan masyarakat.</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613348/tya-ariestya-ajarkan-anak-menghargai-uang-lewat-cara-hidup-sederhana</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/tya-ariestya-1786421110381_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Potret Pernikahan YouTuber Aulion dengan Pila</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:09:53 +0700</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>YouTuber Aulion resmi menikah. Ia mempersunting pujaan hatinya, Pila.</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613731/potret-pernikahan-youtuber-aulion-dengan-pila</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/aulion-1786435403661_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Innalillahi... Audy Item Keguguran</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:00:10 +0700</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Kabar duka datang dari pasangan penyanyi Audy Item dengan Iko Uwais. Audy Item mengumumkan kehilangan calon buah hati ketiganya.</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613671/innalillahi-audy-item-keguguran</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/03/audy-item-umumkan-hamil-1783062155696_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Gaya Estetis Lisa BLACKPINK Liburan ke Antelope Canyon</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:19:40 +0700</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Lisa BLACKPINK menyapa penggemar lewat unggahan foto liburan. Kali ini ia memamerkan momen mengeksplorasi keindahan ngarai Antelope Canyon, AS.</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613624/gaya-estetis-lisa-blackpink-liburan-ke-antelope-canyon</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/lisa-blackpink-1786432354000_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Lesti Kejora Tolak Damai kepada Penyebar Hoax Billar Selingkuh dengan Asila</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:58:12 +0700</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>Lesti Kejora dan Asila Maisa diperiksa Polda Metro Jaya sebagai saksi dalam kasus pencemaran nama baik yang dilaporkan Rizky Billar. Proses hukum berlanjut.</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613593/lesti-kejora-tolak-damai-kepada-penyebar-hoax-billar-selingkuh-dengan-asila</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rizky-billar-lesti-kejora-dan-asilla-1786424585636_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>AI Permudah Perusahaan Seleksi Kandidat Secara Akurat Saat Proses Rekrutmen</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:32:44 +0700</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>‎Peserta mencoba simulasi interview secara mandiri saat menerima pertanyaan lalu merekam jawabannya dalam bentuk video.</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866962/ai-permudah-perusahaan-seleksi-kandidat-secara-akurat-saat-proses-rekrutmen</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/KA-W3V-ut6iNC2ZQ7eonXnmciLc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sheeren-Yolanda-Innovation-Talent-Science-Director-KTM.jpg</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Derby County Sejengkal Lagi Sandang Gelar Tim Sultan, Pihak Saudi Malah Batalkan Pembelian</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:30:53 +0700</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>Pejabat Arab Saudi, Turki Alalshikh, membatalkan agenda pembelian tim Inggris, Derby County, meski sudah mendapatkan persetujuan berbagai pihak.</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866961/derby-county-sejengkal-lagi-sandang-gelar-tim-sultan-pihak-saudi-malah-batalkan-pembelian</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MWVzO6SIqhnjHWs7h5pQiMjNfiU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/para-pemain-derby-county-sebelum-pertandingan.jpg</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Curhat Pasien BPJS Yurizal Tunggu 8 Jam untuk Dapat Kamar Dicibir Nakes, PB IDI Soroti HCU RSCM</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:17:18 +0700</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>Ketua Umum PB IDI Slamet Budiarto heran, mengapa ada pasien yang sampai harus menunggu selama delapan jam untuk mendapatkan kamar HCU.</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866960/curhat-pasien-bpjs-yurizal-tunggu-8-jam-untuk-dapat-kamar-dicibir-nakes-pb-idi-soroti-hcu-rscm</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/p0kXUyCR8fnZZnvbSAImBeiibE4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KOMENTAR-PASIEN-BPJS-1.jpg</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Produk UMKM Sulit Terjual Karena Barang Impor Banjiri Pasar Domestik</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:14:52 +0700</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Pasar domestik Indonesia saat ini terlalu banyak dipenuhi produk impor, membuat produk UMKM lokal sulit bersaing.</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866959/produk-umkm-sulit-terjual-karena-barang-impor-banjiri-pasar-domestik</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5W2Gs7JNQcNGcGTlShWwv44lx1I=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Maman-Abdurrahman-Pasar-RI-dibanjiri-produk-impor.jpg</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Richa Novisha Kini Akui Pengin Main Film Lagi usai Lama Vakum Berakting sejak Dinikahi Gary Iskak</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:11:54 +0700</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Richa Novisha mengungkap kerinduannya bermain layar lebar. Ungkap alasan lebih pilih main film daripada sinetron.</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866958/richa-novisha-kini-akui-pengin-main-film-lagi-usai-lama-vakum-berakting-sejak-dinikahi-gary-iskak</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/RyUPKflJRbXPqi5E1QglsLI4r0k=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Richa-Novisha-ketika-ditemui-di-kawasan-Tanah-Abang-Jakarta-Pusat.jpg</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>4 Alasan Wajib Nonton Sterling Point, Drama Keluarga dan Persahabatan Tayang di Prime Video</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:11:03 +0700</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>4 alasan wajib nonton serial Sterling Point di Prime Video, drama coming-of-age kisah keluarga, persahabatan, persaudaraan, hingga romansa remaja.</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866957/4-alasan-wajib-nonton-sterling-point-drama-keluarga-persahabatan-tayang-di-prime-video</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/H-cp1Eliz1KpiQDL-alZeFC5s8w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/serial-Sterling-Point-ewfe.jpg</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Paragon Scholarship Program 2026 Dibuka, Ada Beasiswa hingga Rp7 Juta per Semester, Cek Syaratnya</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:05:39 +0700</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Paragon Scholarship Program 2026 membuka 2 jalur beasiswa, yakni PSP Excellence dan PSP Elevate. Pendaftaran dibuka mulai 10 Agustus - 10 September.</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7866956/paragon-scholarship-program-2026-dibuka-ada-beasiswa-hingga-rp7-juta-per-semester-cek-syaratnya</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/APl54Pt-jqYk1pdFcoIv3drkSHs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Paragon-Scholarship-Program-2026-Dibuka.jpg</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Pakar Soroti RUU Perampasan Aset: Jangan Beri Aparat Kuasa Merampas Harta Tanpa Putusan Hakim</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:05:22 +0700</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>RUU Perampasan Aset juga harus membedakan secara tegas antara penyitaan atau pembekuan sementara dengan perampasan aset secara permanen.</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866955/pakar-soroti-ruu-perampasan-aset-jangan-beri-aparat-kuasa-merampas-harta-tanpa-putusan-hakim</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/-rLW5IRULNC6gmEcHCgOWx2XQwM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/RUU-PERAMPASAN-ASET-Rapat-Dengar-Pe.jpg</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Pengamat: Kalau Amerika atau Trump Ingin Diplomasi dengan Iran, Itu Artinya Mereka Mulai Melemah</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:04:24 +0700</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Perseteruan Amerika Serikat dan Iran masih berlanjut dengan Selat Hormuz sebagai pusat konflik.</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866954/pengamat-kalau-amerika-atau-trump-ingin-diplomasi-dengan-iran-itu-artinya-mereka-mulai-melemah</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yH16Tb-BlYif7mthXqogvBozRkE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pengamat-Timur-Tengah-Zulfan-Lindan-dalam-dialo.jpg</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Heboh Tantangan Hafal Surat Alquran Hadiah Alkohol di Festival Musik, Brand Miras Klarifikasi</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:58:34 +0700</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Tantangan yang viral di media sosial memicu reaksi keras dan kemarahan publik lantaran dinilai telah melecehkan nilai-nilai sakral agama Islam.</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866953/heboh-tantangan-hafal-surat-alquran-hadiah-alkohol-di-festival-musik-brand-miras-klarifikasi</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8B7-tOOAfYmiFuYoe0DfUHM1lNQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/the-sounds-project-vol-6_photo4.jpg</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Pihak Richard Lee Pastikan Siap Buka Fakta Lagi di Persidangan Kasus Skincare: Bakal Luar Biasa</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:53:42 +0700</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Kasus skincare yang dilaporkan Doktif berlanjut, pihak Richard Lee pastikan siap buka fakta lagi di persidangan.</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866952/pihak-richard-lee-pastikan-siap-buka-fakta-lagi-di-persidangan-kasus-skincare-bakal-luar-biasa</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/raMS_Fi5E6sdVoc15LmEgpnQh_M=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Richard-Lee-bap-doktif.jpg</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>WHO Beri Peringatan Soal Kemunculan Covid Varian Baru di Singapura: Laju Penularannya Cepat</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:52:45 +0700</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Varian ini menarik perhatian sebab punya konsentrasi penularan signifikan di Singapura. Tingkat risiko kesehatan masyarakat dari varian ini didalami..</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866951/who-beri-peringatan-soal-kemunculan-covid-varian-baru-di-singapura-laju-penularannya-cepat</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/-zkZge3_MpolrWYlxRV84TExz_E=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pfi-pusat-gelar-swab-antigen-covid-19_20210214_201437.jpg</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Cegah Peredaran Narkoba, Pimpinan Komisi III DPR Sahroni Minta Polisi Perketat Pengawasan Klub Malam</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:51:56 +0700</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Ahmad Sahroni minta polisi perketat pengawasan klub malam di seluruh Indonesia untuk mencegah peredaran narkoba.</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866950/cegah-peredaran-narkoba-pimpinan-komisi-iii-dpr-sahroni-minta-polisi-perketat-pengawasan-klub-malam</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0ClJlHbL8DvjcRaN6GHTfO1f1OY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/wakil-ketua-komisi-iii-dpr-ri-ahmad-sahroni-mar-2021.jpg</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Sarwendah Diduga Langgar Kesepakatan dengan Ruben Onsu, Praktisi Hukum Soroti 3 Poin Ini</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:51:46 +0700</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Sarwendah diduga melanggar kesepakatan dengan Ruben Onsu, praktisi hukum menyoroti tiga poin ini.</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866949/sarwendah-diduga-langgar-kesepakatan-dengan-ruben-onsu-praktisi-hukum-soroti-3-poin-ini</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hejjyutIHrD-Ze4ySSbS4hhh3cc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/sarwendah-komnas-perempuan.jpg</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Mata Hari, Sang Penari Eksotis yang Jadi Mata-Mata</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:50:37 +0700</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>Mata Hari memukau kaum elite dengan kecantikan dan performanya. Dituduh menjadi mata-mata Perang Dunia I, ia pun dieksekusi regu tembak…</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866948/mata-hari-sang-penari-eksotis-yang-jadi-mata-mata</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/NT64-FDkRheg4WSvtPIh6Ip8Y6k=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/BDeutsche-Welle78186235_403.jpg.jpg</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Pontianak Besok, Rabu 12 Agustus 2026: Didominasi Udara Kabur</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:50:38 +0700</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>Simak prakiraan cuaca Kota Pontianak Besok, Rabu 12 Agustus 2026, didominasi udara kabur.</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866947/prakiraan-cuaca-pontianak-besok-rabu-12-agustus-2026-didominasi-udara-kabur</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Eh-VM9JugL-I8mSjMBMU42UQpy0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/TRIBUN-PONTIANAK-Ni-Made-Gunarsih.jpg</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Kasus Dugaan Penistaan Agama: Challenge Surah Ad-Dhuha Berhadiah Miras Diadukan ke Polisi</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:48:13 +0700</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>Challenge hafalan Surah Ad-Dhuha berhadiah miras dilaporkan ke polisi. Penyelenggara menyatakan kegiatan itu di luar persetujuannya.</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866946/kasus-dugaan-penistaan-agama-challenge-surah-ad-dhuha-berhadiah-miras-diadukan-ke-polisi</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/y9ePoBYQGKY1-iNVcW-LrJkFdcQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Advokat-Tim-Hukum-Muslim-Mohammad-Rizki-pengaduan-ke-Polda-Metro-berhadiah-miras.jpg</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Seriuskah Kemdiktisaintek Menjaga Mutu Pendidikan Tinggi</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:47:08 +0700</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Pendidikan tinggi menghadapi krisis penjaminan mutu dan integritas akademik, termasuk dugaan plagiasi, fabrikasi, serta persoalan tata kelola.</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/tribunners/7866945/seriuskah-kemdiktisaintek-menjaga-mutu-pendidikan-tinggi</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/jPaYgQQ8Eotf3ovd5e9yxU8nfnE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ir-yanto-st-mse-phd-ipm-1786437957485.jpg</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Mojtaba Tata Ulang Kekuatan IRGC, Ini Daftar Enam Jenderal Senior yang Perkuat Pertahanan Iran</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:44:49 +0700</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Khamenei rombak pimpinan IRGC! Enam jenderal senior ditunjuk memperkuat pertahanan Iran dengan strategi komando berlapis di tengah eskalasi konflik.</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866944/mojtaba-tata-ulang-kekuatan-irgc-ini-daftar-enam-jenderal-senior-yang-perkuat-pertahanan-iran</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/f984dYfGez4JJcOKoAxn4M_OUjk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Prajurit-IRGC-Iran-dgd.jpg</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Dalih Takut, Eks Pejabat Bea Cukai Tak Langsung Kembalikan Uang Suap yang Diterimanya dari Blueray</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:40:09 +0700</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Gatot mengklaim telah berniat mengembalikan uang itu kepada Lembaga Anti rasuah sejak awal penerimaan, namun dirinya mengaku sempat ketakutan.</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866943/dalih-takut-eks-pejabat-bea-cukai-tak-langsung-kembalikan-uang-suap-yang-diterimanya-dari-blueray</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/AV902um6RaFaDQf-s1dc0gUUsVc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sidang-Korupsi-Bea-Cukai_28-Juli-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Inklusi Keuangan Syariah Turun, Ekonom: Industri Gagal Tawarkan Keunggulan</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:31:19 +0700</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Indeks inklusi keuangan syariah justru turun ketika akses masyarakat terhadap layanan keuangan secara umum semakin luas. Berdasarkan hasil Survei Nasional Literasi dan Inklusi Keuangan (SNLIK) 2026 yang...</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlmg7423/inklusi-keuangan-syariah-turun-ekonom-industri-gagal-tawarkan-keunggulan</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/044573400-1760018319-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Seluruh Rekomendasi BPK Dituntaskan, BSSN Diminta Jaga Perbaikan Tata Kelola</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Badan Siber dan Sandi Negara (BSSN) kembali memperoleh opini Wajar Tanpa Pengecualian (WTP) atas Laporan Keuangan Tahun 2025. Dalam pemeriksaan tersebut, Badan Pemeriksa Keuangan (BPK) juga mencatat...</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlh1y416/seluruh-rekomendasi-bpk-dituntaskan-bssn-diminta-jaga-perbaikan-tata-kelola</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260811143704-987.png</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Rencana Masjid Istiqlal Masuk ke Pasar Modal Indonesia, Ini Penjelasan OJK</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:15:10 +0700</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Kepala Eksekutif Pengawas Pasar Modal, Keuangan Derivatif, dan Bursa Karbon Otoritas Jasa Keuangan (OJK) Hasan Fawzi mengatakan inisiasi Masjid Istiqlal masuk ke pasar modal Indonesia melalui pengelolaan...</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlixa490/rencana-masjid-istiqlal-masuk-ke-pasar-modal-indonesia-ini-penjelasan-ojk</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260402164340-949.png</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Airlangga Naikkan Target Pembiayaan UMKM Jadi Rp 2.000 Triliun</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:11:12 +0700</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Menteri Koordinator Bidang Perekonomian RI Airlangga Hartarto menaikkan target pembiayaan bagi Usaha Mikro, Kecil, dan Menengah (UMKM) menjadi sebesar Rp 2.000 triliun, sebagai upaya untuk mendongkrak realisasi...</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjliqo370/airlangga-naikkan-target-pembiayaan-umkm-jadi-rp-2000-triliun</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/umkm-batik-melalui-partisipasi-dalam-pameran-puspa-nuswantara_260710100914-597.jpeg</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Didakwa Rugikan Negara Rp 622 Miliar, Yaqut Siapkan Perlawanan</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:39:49 +0700</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>Kuasa hukum Yaqut meminta waktu sepekan untuk menyiapkan perlawanan atas dakwaan Jaksa KPK.</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267204/didakwa-rugikan-negara-rp-622-miliar-yaqut-siapkan-perlawanan</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/zva03GdB2RWgoVZNb-ZCUrSTzLg=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321379/original/055838800_1786441180-IMG_20260811_141726_9.jpg</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Sampah Bisa Jadi Sumber Cuan, Pemuda Diminta Ambil Peran</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:28:24 +0700</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Sampah tak lagi sekadar limbah, ada peluang ekonomi di baliknya.</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267044/sampah-bisa-jadi-sumber-cuan-pemuda-diminta-ambil-peran</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/kMEB8Cqm3Kl2UCjz32ZrURXPS6k=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5404534/original/034004500_1762409350-gal4.jpg</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>AHY Ungkap Keluhan Investor: Jangan Dikerjain dan Dipingpong</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:42:19 +0700</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>AHY menyoroti pelayanan birokrasi yang tidak boleh berbelit-belit.</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267236/ahy-ungkap-keluhan-investor-jangan-dikerjain-dan-dipingpong</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/bFIoYYfc1pM9lu3IoXP_coCwtOU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321374/original/094594800_1786440655-06b56d13-a0ae-4dcb-a075-49407806fa1a.jpg</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Newport Minta Maaf, Sebut Tantangan Hafal Surah Alquran Berhadiah Miras Spontan</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:23:16 +0700</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Newport mengaku menyesal atas insiden yang dinilai telah menyinggung perasaan banyak pihak.</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267196/newport-minta-maaf-sebut-tantangan-hafal-surah-alquran-berhadiah-miras-spontan</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Fp5iC-vppn7dJSzwqGEBlrLz0gY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321055/original/059736500_1786425649-Jepretan_Layar_2025-08-11_pukul_12.15.34.jpg</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Pratikno: Saya Sehat dan Sedang di Bromo Rakor Pemadaman Api</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:21:07 +0700</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Penegasan itu disampaikan Pratikno menjawab kabar menyebutkannya sakit dan akan mundur dari jabatan Menko PMK.</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267193/pratikno-saya-sehat-dan-sedang-di-bromo-rakor-pemadaman-api</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/v7T1HIXrr1naqq66YB477MHNM78=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321359/original/040865600_1786440061-Menko_PMK_Pratikno_rakor_kebakaran_bromo.jpg</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Mensesneg Ungkap Perkembangan Terbaru Perpres Ojol</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:06:29 +0700</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Semua substansi sudah dirumuskan oleh para pemangku kepentingan.</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267175/mensesneg-ungkap-perkembangan-terbaru-perpres-ojol</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/iXAcFGBzaeqes_gFAnf97VAP8ls=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5550839/original/029409500_1775710216-foto2.jpg</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>PP Muhammadiyah Soroti Hafalan Al-Qur'an Berhadiah Miras</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:51:48 +0700</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>Anggota Majelis Tarjih dan Tajdid PP Muhammadiyah Qaem Aulassyahied menyebut, kemungkinan ada unsur mencemooh dan mengolok-olok Al-Qur'an dari peristiwa itu.</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267165/pp-muhammadiyah-soroti-hafalan-al-quran-berhadiah-miras</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Fp5iC-vppn7dJSzwqGEBlrLz0gY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321055/original/059736500_1786425649-Jepretan_Layar_2025-08-11_pukul_12.15.34.jpg</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Pramono Sebut DKI Punya Aset Senilai Rp 126,9 T</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:26:37 +0700</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>DKI Jakarta punya ribuan sertifikat aset baru dengan nilai fantastis.</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267159/pramono-sebut-dki-punya-aset-senilai-rp-1269-t</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/cwW7GmeEQJQmVViM58Zz8Y4jHXg=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321324/original/079976200_1786437978-cc1c0894-efc9-4668-9b52-5f7b647e0b78.jpg</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Pesan Jaksa Agung ke Direktur Penyidikan Jampidsus Baru Saiful Bahri Siregar</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:41:11 +0700</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Direktur Penyidikan Jampidsus sebelumnya Syarief Sulaeman Nahdi kini menjabat Direktur III pada Jaksa Agung Muda Bidang Intelijen.</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267145/pesan-jaksa-agung-ke-direktur-penyidikan-jampidsus-baru-saiful-bahri-siregar</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/07UExinGr2t37pgmnaNjhOxLnPY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321317/original/020256700_1786437562-WhatsApp_Image_2026-08-11_at_15.37.53.jpeg</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Mendagri Siapkan Aturan, Bayi Lahir di Luar Faskes Bisa Dapat Akta Digital</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:21:02 +0700</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Mendagri tengah menyiapkan surat edaran yang ditujukan kepada pemerintah desa atau kepala desa.</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267123/mendagri-siapkan-aturan-bayi-lahir-di-luar-faskes-bisa-dapat-akta-digital</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/YlRYvFLxl1FjUrafWkAMgROOEbs=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321290/original/074976300_1786436459-WhatsApp_Image_2026-08-11_at_15.14.18.jpeg</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Rekonstruksi Kasus Mutilasi di Depok, Polisi Temukan Fakta Baru</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:13:57 +0700</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Rekonstruksi kasus mutilasi pria di Depok digelar hari ini. Polisi temukan fakta baru soal aksi tersangka.</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267111/rekonstruksi-kasus-mutilasi-di-depok-polisi-temukan-fakta-baru</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/L54vKChMwpgp3InZLojNRbcDte8=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321279/original/076645100_1786436028-20260811_131750.jpg</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>DPR dan Pejabat Polda Sumut Bahas Kematian Mantan Istri Polisi</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:08:27 +0700</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Korban ditemukan meninggal dunia di rumah mantan suaminya pada Minggu (2/8/2026).</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267105/dpr-dan-pejabat-polda-sumut-bahas-kematian-mantan-istri-polisi</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/oz9O7w0Cfg1-qt84SY_B4ikc7_U=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5473565/original/045606700_1768449409-e8f30a03-0f34-4cca-868f-659668113d39.jpeg</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>HUT ke-81 RI, Istana Mulai Kirim Undangan ke Mantan Presiden-Wapres</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:07:12 +0700</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Sejumlah pejabat pemerintah telah ditugaskan untuk mengantarkan undangan kepada presiden dan wakil presiden terdahulu.</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267102/hut-ke-81-ri-istana-mulai-kirim-undangan-ke-mantan-presiden-wapres</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/gHbesCjp-SNAzXm496ZCYwbc5s0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320299/original/065432400_1786344095-mensesneg.jpg</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Tol di Jatim Ini Disiapkan Jadi Landasan Darurat Pesawat</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:10:37 +0700</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>TNI AU sedang melakukan kajian meliputi kesiapan teknis, keselamatan, dan keamanan.</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267104/tol-di-jatim-ini-disiapkan-jadi-landasan-darurat-pesawat</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/9FCaNToM6vm6wWp6_JRcqnngck8=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5318339/original/071212000_1755479879-1000013946__3_.jpg</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>RUU Perampasan Aset Diminta Lindungi Pihak Ketiga yang Beriktikad Baik</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:53:17 +0700</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Jurnalis senior mengusulkan agar RUU Perampasan Aset mengatur perlindungan tegas bagi pihak ketiga yang beriktikad baik.</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/16531151/ruu-perampasan-aset-diminta-lindungi-pihak-ketiga-yang-beriktikad-baik</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/TfIQKhGtKHpFPlSbGsOU2Uq64tE=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7ae8d3ca1f4.jpg</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Bukan Cuma Bawaan Lahir, Mata Juling Juga Bisa Menyerang Dewasa</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:53:17 +0700</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Mata juling ternyata tidak hanya dialami bayi sejak lahir. Diabetes, hipertensi, hingga gangguan tiroid bisa memicunya di usia dewasa. Ini faktanya.</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>https://health.kompas.com/read/26H11163700768/bukan-cuma-bawaan-lahir-mata-juling-juga-bisa-menyerang-dewasa</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/VkG5JPDP62DuNDTl8x41nNWTc88=/0x107:1280x960/1200x675/filters:watermark(data/photo/2026/01/30/697c819f9c086.png,0,-0,1)/data/photo/2026/08/10/6a79c6a21fb91.jpeg</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Wanita Dibunuh Pacar di Tangerang, Direkayasa Seolah Bunuh Diri</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:53:17 +0700</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Seorang pria merekayasa pembunuhan pacar yang dilakukannya dengan membuat korban seolah bunuh diri.</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/11/16190471/wanita-dibunuh-pacar-di-tangerang-direkayasa-seolah-bunuh-diri</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/UAxTXWuyR3--bc0iEqYylTIIDcQ=/0x0:750x500/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2023/06/14/648975f352789.jpg</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I685"/>
+  <autoFilter ref="A1:I833"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$833</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$992</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I833"/>
+  <dimension ref="A1:I992"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -39589,8 +39589,7481 @@
         </is>
       </c>
     </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>BPJPH perkuat kompetensi SDM di daerah jelang Wajib Halal</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:39:18 +0700</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>Badan Penyelenggara Jaminan Produk Halal (BPJPH) memastikan penguatan kompetensi sumber daya manusia (SDM) bidang ...</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689503/bpjph-perkuat-kompetensi-sdm-di-daerah-jelang-wajib-halal</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/aaaf98cd-b4cb-48b4-88d9-5214a7fa3a3b.jpeg</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Prabowo instruksikan percepatan pemadaman kebakaran Bromo</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:39:16 +0700</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara Prasetyo Hadi mengatakan pemerintah pusat mendukung penuh percepatan pemadaman ...</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689499/prabowo-instruksikan-percepatan-pemadaman-kebakaran-bromo</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-14.08.16.jpeg</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Pakar usulkan nama RUU Perampasan Aset diganti jadi "Melindungi Aset"</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:38:49 +0700</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Pakar kebijakan publik Bambang Harymurti mengusulkan nomenklatur Rancangan Undang-Undang (RUU) tentang Perampasan Aset ...</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689496/pakar-usulkan-nama-ruu-perampasan-aset-diganti-jadi-melindungi-aset</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Bambang.jpeg</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Datangi Kejagung, BGN bahas pendampingan hukum hingga kerja sama</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:37:22 +0700</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>Pimpinan Badan Gizi Nasional (BGN) mendatangi Gedung Kejaksaan Agung, Jakarta, Selasa, dalam rangka silaturahmi ...</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689493/datangi-kejagung-bgn-bahas-pendampingan-hukum-hingga-kerja-sama</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000087739.jpg</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Bank Jakarta bangun fasilitas pengolah limbah organik di Rorotan Jakut</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:36:06 +0700</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Bank Jakarta membangun fasilitas pengolah limbah komunal berbasis sampah organik (biodigester) di Rusunawa Rorotan dan ...</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689487/bank-jakarta-bangun-fasilitas-pengolah-limbah-organik-di-rorotan-jakut</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000307498.jpg</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Salim Group bidik pasar gim konsol Indonesia lewat Nintendo</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:35:29 +0700</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>Salim Group melalui PT Nusantara Interactive Niaga, membidik pertumbuhan pasar industri gim Indonesia dengan memperluas ...</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689484/salim-group-bidik-pasar-gim-konsol-indonesia-lewat-nintendo</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000595385.jpg</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>YouTube ubah syarat monetisasi, jam tayang minimal naik dua kali lipat</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:35:14 +0700</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>YouTube menetapkan persyaratan baru bagi kreator konten yang ingin memperoleh pendapatan dari tayangan iklan dan jumlah ...</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689483/youtube-ubah-syarat-monetisasi-jam-tayang-minimal-naik-dua-kali-lipat</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/11/Yutub.jpg</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>RI jajaki kolaborasi dengan China perkuat pengawasan obat-pangan</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:34:06 +0700</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Badan Pengawas Obat dan Makanan (BPOM) mendorong penguatan kerja sama regulatori dengan China, mulai dari pengawasan ...</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689479/ri-jajaki-kolaborasi-dengan-china-perkuat-pengawasan-obat-pangan</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1786436806431.jpg</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Jakarta pastikan dua lapangan latihan dukung FIFA ASEAN Cup 2026</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:32:07 +0700</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi DKI Jakarta memastikan kesiapan dua lapangan yaitu Lapangan Banteng dan GOR Soemantri ...</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689477/jakarta-pastikan-dua-lapangan-latihan-dukung-fifa-asean-cup-2026</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/06/Malorca.jpg</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Ketum PBNU: Pesantren terapkan model pendidikan yang komprehensif</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:31:01 +0700</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Ketua Umum Pengurus Besar Nahdlatul Ulama (PBNU) KH Yahya Cholil Staquf “Gus Yahya” mengatakan pesantren ...</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689473/ketum-pbnu-pesantren-terapkan-model-pendidikan-yang-komprehensif</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_1866.jpeg</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Purbaya akui biasa bekerja sama dengan Destry Damayanti</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:28:36 +0700</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengakui sudah sering berkoordinasi dan bekerja sama dengan calon ...</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689471/purbaya-akui-biasa-bekerja-sama-dengan-destry-damayanti</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_172529.jpg</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Mendiktisaintek tantang psikolog tulis buku ringan ala "Atomic Habits"</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:28:17 +0700</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Menteri Pendidikan Tinggi, Sains, dan Teknologi (Mendiktisaintek) Brian Yuliarto menantang pakar psikologi Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689469/mendiktisaintek-tantang-psikolog-tulis-buku-ringan-ala-atomic-habits</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/WhatsApp-Image-2026-07-27-at-20.44.49-1.jpeg</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Menteri UMKM sebut pasar domestik dipenuhi produk-produk impor</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:26:25 +0700</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>Menteri Usaha Mikro Kecil dan Menengah (UMKM) Maman Abdurrahman menyatakan pasar domestik dipenuhi produk-produk impor, ...</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689467/menteri-umkm-sebut-pasar-domestik-dipenuhi-produk-produk-impor</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-13.20.26_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Pertamina tanam 760 bibit pulihkan terumbu karang Pulau Tikus Bengkulu</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:25:24 +0700</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Pertamina Patra Niaga Regional Sumatera Bagian Selatan (Sumbagsel) menanam 760 bibit terumbu karang di tiga titik ...</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689465/pertamina-tanam-760-bibit-pulihkan-terumbu-karang-pulau-tikus-bengkulu</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000844371.jpg</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>80 Siswa Banyumas ikuti MPLS Sekolah Nasional Terintegrasi</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:25:12 +0700</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebanyak 80 siswa Sekolah Nasional Terintergrasi (SNT) asal Kabupaten Banyumas, Jawa Tengah, berangkat ...</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689415/80-siswa-banyumas-ikuti-mpls-sekolah-nasional-terintegrasi</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/80-SISWA-BANYUMAS-IKUTI-MPLS-SEKOLAH-NASIONAL-TERINTEGRASI.jpg</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Pemkot Jakpus gelar lomba dayung di Pasar Baru pada 29-30 Agustus</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:22:51 +0700</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Jakarta Pusat melalui Suku Dinas Pemuda dan Olahraga menggelar lomba dayung di kawasan Pasar Baru ...</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689461/pemkot-jakpus-gelar-lomba-dayung-di-pasar-baru-pada-29-30-agustus</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/21/Festival-Passer-Baroe-sambut-HUT-Jakarta-ke-498-210625-fah-2-1.jpg</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Pemprov Sulteng: Rute Guangzhou–Palu buka pertumbuhan ekonomi daerah</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:22:18 +0700</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) Sulawesi Tengah (Sulteng) menyatakan rute penerbangan Guangzhou (Cina)–Palu, telah ...</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689460/pemprov-sulteng-rute-guangzhou-palu-buka-pertumbuhan-ekonomi-daerah</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-17.23.21.jpeg</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Menhut Raja Juli enggan bicara soal pengembalian uang ke KPK</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:22:13 +0700</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Menteri Kehutanan Raja Juli Antoni enggan berbicara dugaan Komisi Pemberantasan Korupsi (KPK) yang ...</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689457/menhut-raja-juli-enggan-bicara-soal-pengembalian-uang-ke-kpk</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001303633.jpg</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Polda Sulsel gagalkan peredaran narkotika, 16 orang ditangkap</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:21:00 +0700</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>Tim Direktorat Direktur Reserse Narkoba (Ditresnarkoba) Polda Sulsel menggagalkan peredaran narkotika berbagai jenis ...</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689453/polda-sulsel-gagalkan-peredaran-narkotika-16-orang-ditangkap</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/rilis-narkoba-sabu-cairan-sintetis.jpg</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Gelar dialog kebangsaan, polresta Ambon pastikan kamtibmas terjaga</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:20:31 +0700</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>ANTARA - Polresta Ambon mengajak generasi muda berperan aktif mencegah potensi konflik dan menjaga keamanan lingkungan ...</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689440/gelar-dialog-kebangsaan-polresta-ambon-pastikan-kamtibmas-terjaga</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/GELAR-DIALOG-KEBANGSAAN-POLRESTA-AMBON-PASTIKAN-KAMTIBMAS-TERJAGA.jpg</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>WhatsApp hadirkan agen AI untuk bantu bisnis layani pelanggan 24 jam</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:18:30 +0700</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>WhatsApp menghadirkan Meta Business Agent, agen berbasis kecerdasan artifisial (Artificial Intelligence/AI) yang ...</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689451/whatsapp-hadirkan-agen-ai-untuk-bantu-bisnis-layani-pelanggan-24-jam</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000142807.jpg</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Pemkot Jakpus perbaiki 16 fasilitas lapangan olahraga untuk masyarakat</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:17:11 +0700</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Jakarta Pusat melalui Suku Dinas Pemuda dan Olahraga (Sudin Pora) memperbaiki 16 kegiatan sarana ...</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689447/pemkot-jakpus-perbaiki-16-fasilitas-lapangan-olahraga-untuk-masyarakat</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000836357.jpg</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>PBNU kembangkan model pendidikan “Pesantren Ramah Anak”</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:15:46 +0700</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>Ketua Umum Pengurus Besar Nahdlatul Ulama (PBNU) KH Yahya Cholil Staquf “Gus Yahya” meminta pesantren ...</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689443/pbnu-kembangkan-model-pendidikan-pesantren-ramah-anak</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_1865.jpeg</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>BNNP gelar bimtek penguatan ekonomi di kawasan zona merah narkoba</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:12:55 +0700</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Narkotika Nasional (BNN) Provinsi Banten berkolaborasi dengan Disporapar Kota Cilegon, Selasa (11/8), ...</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689353/bnnp-gelar-bimtek-penguatan-ekonomi-di-kawasan-zona-merah-narkoba</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BNNP-GELAR-BIMTEK-PENGUATAN-EKONOMI-DI-KAWASAN-ZONA-MERAH-NARKOBA.jpg</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Dirjen Bea Cukai masih kaji soal penambahan layer baru cukai rokok</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:12:19 +0700</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Direktur Jenderal Bea dan Cukai Djaka Budi Utama menyampaikan, pihaknya masih melakukan kajian soal rencana penambahan ...</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689437/dirjen-bea-cukai-masih-kaji-soal-penambahan-layer-baru-cukai-rokok</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/09e566f6-d792-4981-92c4-cdcf88dac419.jpeg</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Purbaya sebut pengendalian subsidi BBM dilakukan secara bertahap</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:12:01 +0700</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengatakan pengendalian subsidi bahan bakar minyak (BBM) khususnya ...</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689435/purbaya-sebut-pengendalian-subsidi-bbm-dilakukan-secara-bertahap</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_170408.jpg</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Pemprov Jatim ajak Kalbar kembangkan sektor peternakan</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:08:44 +0700</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Gubernur Jawa Timur Khofifah Indar Parawansa menawarkan penguatan kerja sama di sektor peternakan melalui peningkatan ...</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689433/pemprov-jatim-ajak-kalbar-kembangkan-sektor-peternakan</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-16.53.13.jpeg</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>UNU Lampung hilirisasi pengering surya untuk pakan mandiri Gapoktan</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:07:52 +0700</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Universitas Nahdlatul Ulama Lampung (UNU Lampung) melakukan hilirisasi teknologi Solar Tunnel Dryer (STD) untuk ...</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689431/unu-lampung-hilirisasi-pengering-surya-untuk-pakan-mandiri-gapoktan</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/foto_antarA_1280x720.jpg</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Yaqut didakwa perkaya diri Rp4,83 miliar pada kasus korupsi kuota haji</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:07:51 +0700</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Menteri Agama periode 2020–2024 Yaqut Cholil Qoumas didakwa memperkaya diri senilai 271.500 dolar Amerika Serikat ...</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689429/yaqut-didakwa-perkaya-diri-rp483-miliar-pada-kasus-korupsi-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/sidang-dakwaan-yaqut-110826-bay-3.jpg</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Pesepak bola putri antusias menyambut bergulirnya Liga Putri Indonesia</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:07:06 +0700</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>Pesepak bola putri Indonesia Hanipa Halimatusyadiah yang kini membela FC Bekasi City mengaku antusias menyambut ...</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689427/pesepak-bola-putri-antusias-menyambut-bergulirnya-liga-putri-indonesia</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0010.jpg</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Kanwil Ditjenpas DKI perluas layanan kesehatan lewat operasi katarak</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:06:56 +0700</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Kantor Wilayah Direktorat Jenderal Pemasyarakatan (Kanwil Ditjenpas) DKI Jakarta terus memperluas akses pelayanan ...</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689425/kanwil-ditjenpas-dki-perluas-layanan-kesehatan-lewat-operasi-katarak</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/InShot_20260811_161934981.jpg</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>BGN minta guru edukasi siswa agar konsumsi MBG sesuai ketentuan</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:06:08 +0700</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) meminta guru dan tenaga pendidik mengedukasi siswa agar mengonsumsi Makan Bergizi Gratis ...</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689423/bgn-minta-guru-edukasi-siswa-agar-konsumsi-mbg-sesuai-ketentuan</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Capaian-realisasi-program-MBG-di-Sulawesi-Barat-110826-At-1A.jpg</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>129 kasus narkotika terungkap dalam dua pekan di NTB</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:05:24 +0700</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Sebanyak 129 kasus penyalahgunaan dan peredaran narkotika terungkap dalam dua pekan giat penindakan Operasi Antik ...</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689421/129-kasus-narkotika-terungkap-dalam-dua-pekan-di-ntb</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/kabid-humas-kombes-kholid.jpg</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Mendag: Kenaikan harga minyak dunia salah satu pemicu defisit dagang</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:04:47 +0700</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Menteri Perdagangan (Mendag) Budi Santoso mengungkapkan kenaikan harga minyak dunia akibat eskalasi konflik di Selat ...</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689417/mendag-kenaikan-harga-minyak-dunia-salah-satu-pemicu-defisit-dagang</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_3752.jpeg</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>TNI dan warga Papua perkuat nasionalisme dengan kibarkan merah putih</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:02:43 +0700</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Personel Marinir TNI AL yang tergabung dalam Satgas Pamtas Mobile RI-PNG Yonif 2 Marinir bersama warga Papua perkuat ...</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689416/tni-dan-warga-papua-perkuat-nasionalisme-dengan-kibarkan-merah-putih</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001570127.jpg</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>IHSG ditutup melemah ke 6.267, pasar tunggu tinjauan MSCI di Agustus</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:01:08 +0700</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa sore, ditutup melemah seiring pelaku pasar ...</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689413/ihsg-ditutup-melemah-ke-6267-pasar-tunggu-tinjauan-msci-di-agustus</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IHSG-ditutup-menguat-65-94-poin-070826-Fah-4.jpg</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Venezuela akan kirim tim penyelamat ke Kolombia pascagempa besar</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:59:06 +0700</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Presiden Sementara Venezuela, Delcy Rodriguez, akan mengirimkan bantuan kemanusiaan dan tim penyelamat ke Kolombia ...</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689411/venezuela-akan-kirim-tim-penyelamat-ke-kolombia-pascagempa-besar</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/thumbs_b_f9b52ee0700d8eaa192c1b747adcdda6.jpg</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Kapolri silaturahmi bersama pimpinan lembaga negara, perkuat soliditas</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:56:49 +0700</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Kapolri Jenderal Pol. Listyo Sigit Prabowo menghadiri silaturahmi strategis bersama Menko Bidang Politik dan Keamanan ...</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689409/kapolri-silaturahmi-bersama-pimpinan-lembaga-negara-perkuat-soliditas</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000087734.jpg</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Wali Kota soroti aspek kolektif soal RW di Jakbar swadaya pasang CCTV</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:56:48 +0700</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Wali Kota Jakarta Barat Iin Mutmainnah menyoroti aspek kolektif dari warga RW 07 Kelurahan Tamansari yang memasang ...</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689408/wali-kota-soroti-aspek-kolektif-soal-rw-di-jakbar-swadaya-pasang-cctv</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_161815.v1.jpg</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Pertamina Patra Niaga-Dukcapil perkuat ketepatan penyaluran subsidi</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:55:57 +0700</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>PT Pertamina Patra Niaga bekerja sama dengan Direktorat Jenderal Kependudukan dan Pencatatan Sipil (Ditjen Dukcapil) ...</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689405/pertamina-patra-niaga-dukcapil-perkuat-ketepatan-penyaluran-subsidi</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000407605.jpg</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>2000 peserta bersaing di Mandar Domino Tournament 2026</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:54:09 +0700</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Sebanyak 2000 peserta bersaing di Mandar Domino Tournament 2026 yang berlangsung Stadion H.S. Mengga, Polewali Mandar, ...</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689404/2000-peserta-bersaing-di-mandar-domino-tournament-2026</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260810-WA0046.jpg</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Mentan copot Korwil KPPG Surabaya saat rapat pengunggasan</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:53:27 +0700</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Menteri Pertanian (Mentan) RI Amran Sulaiman mencopot Koordinator Wilayah Kantor Pelayanan Pemenuhan Gizi (KPPG) ...</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689403/mentan-copot-korwil-kppg-surabaya-saat-rapat-pengunggasan</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1346957.jpg</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Wagub Lampung: Empat Program PPDS baru Unila perkuat SDM kesehatan</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:53:13 +0700</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Wakil Gubernur (Wagub) Lampung Jihan Nurlela mengatakan dibukanya empat Program Pendidikan Dokter Spesialis (PPDS) baru ...</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689400/wagub-lampung-empat-program-ppds-baru-unila-perkuat-sdm-kesehatan</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/pU8rkSv6tcatIXhCRQR1biHoZlF2yZQbvv6sbOCp-1.jpg</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Pakar usul perampasan aset tak boleh tanpa putusan pengadilan</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:53:04 +0700</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>Pakar kebijakan publik Bambang Harymurti mengusulkan perampasan aset tidak boleh dilakukan tanpa putusan pengadilan ...</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689396/pakar-usul-perampasan-aset-tak-boleh-tanpa-putusan-pengadilan</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/tempImager2y0Vc.jpg</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Rupiah melemah seiring konflik AS-Iran atas Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:51:33 +0700</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Selasa, bergerak melemah 106 poin atau 0,60 persen ...</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689392/rupiah-melemah-seiring-konflik-as-iran-atas-selat-hormuz</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/23/1000680361.jpg</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>PBNU perkuat 20 pesantren di Kalsel bangun “Pesantren Aman”</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:50:35 +0700</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>Pengurus Besar Nahdlatul Ulama (PBNU) memperkuat 20 pondok pesantren di Kalimantan Selatan untuk membangun ...</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689388/pbnu-perkuat-20-pesantren-di-kalsel-bangun-pesantren-aman</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_1863.jpeg</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Bea Cukai Tanjung Priok gagalkan peredaran 8,96 juta batang rokok ilegal</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:50:06 +0700</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>Petugas Bea Cukai berdiri di depan barang bukti berupa rokok ilegal saat gelar kasus penindakan rokok ilegal di ...</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5689385/bea-cukai-tanjung-priok-gagalkan-peredaran-896-juta-batang-rokok-ilegal</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Penggagalan-Peredaran-8-96-Juta-Rokok-Ilegal-110826-MRH-1.jpg</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Bea Cukai gagalkan 1,2 miliar batang rokok ilegal hingga Juli 2026</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:49:16 +0700</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Direktur Jenderal Bea dan Cukai Djaka Budi Utama menyampaikan telah menggagalkan peredaran 1,2 miliar batang rokok ...</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689383/bea-cukai-gagalkan-12-miliar-batang-rokok-ilegal-hingga-juli-2026</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/0f73a5e8-f86b-4538-bf88-69c48df7239c.jpeg</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Jaksa Agung Minta BGN Evaluasi Usai Kasus Tata Kelola MBG: Jangan Terjadi Lagi</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:25:35 +0700</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Jaksa Agung menyampaikan agar korupsi tata kelola Makan Bergizi Gratis (MBG) yang telah terjadi menjadi bahan evaluasi kepemimpinan BGN yang sekarang.</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614036/jaksa-agung-minta-bgn-evaluasi-usai-kasus-tata-kelola-mbg-jangan-terjadi-lagi</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/kapuspenkum-kejagung-anang-supriatna-1767165080913_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Satgas PRR Pacu Realisasi TKD Nagan Raya untuk Pulihkan Akses Warga</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:24:25 +0700</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Satgas PRR mendorong Pemkab Nagan Raya percepat realisasi TKD untuk pemulihan infrastruktur pascabencana. Anggaran masih rendah, perlu tindakan cepat.</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614035/satgas-prr-pacu-realisasi-tkd-nagan-raya-untuk-pulihkan-akses-warga</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/satgas-prr-pacu-realisasi-tkd-nagan-raya-untuk-pulihkan-akses-warga-1786443760873.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Gerindra Respons Usulan PKS Rekrut Orang Baru Non-partai di Kabinet</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:21:12 +0700</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>Juru bicara Gerindra, Bahtra Banong, menghargai usulan reshuffle kabinet dari PKS. Ia menegaskan hak prerogatif presiden dalam pengisian jabatan.</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614027/gerindra-respons-usulan-pks-rekrut-orang-baru-non-partai-di-kabinet</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/bahtra-banong-anggidetikcom-1785827703841_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Kronologi Pacar Rekayasa Pembunuhan Wanita Ditemukan Tergantung di Tangerang</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:01:29 +0700</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Polisi ungkap kronologi pembunuhan wanita berinisial R di Tangerang. Pelaku A ditangkap setelah rekayasa kematian terungkap melalui komunikasi WhatsApp.</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613980/kronologi-pacar-rekayasa-pembunuhan-wanita-ditemukan-tergantung-di-tangerang</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/29/d22171e8-7238-4c47-bcd6-802c24f7da62_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Jelang HUT Ke-22, DPD RI Gelar Penghargaan untuk Penggerak Perubahan Daerah</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:00:39 +0700</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>DPD RI Awards 2026 memberikan penghargaan bagi individu berkontribusi nyata di bidang Pendidikan, Kesehatan, Seni, dan Ketahanan Pangan.</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613978/jelang-hut-ke-22-dpd-ri-gelar-penghargaan-untuk-penggerak-perubahan-daerah</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/16/jelang-sidang-tahunan-mpr-helikopter-kepresidenan-siaga-di-gedung-dpr.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Polda Riau Geledah Toko Diduga Jual Hasil PETI, Ratusan Gram Emas Disita</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:52:37 +0700</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>Polda Riau menggeledah Toko Emas Syafira, menyita ratusan gram emas dan peralatan terkait penambangan ilegal. Penggeledahan ini bagian dari kasus PETI.</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613956/polda-riau-geledah-toko-diduga-jual-hasil-peti-ratusan-gram-emas-disita</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/polda-riau-menggeledah-toko-emas-di-kampar-yang-diduga-menjual-hasil-peti-ratusan-gram-emas-disita-1786441938135_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Kejagung Tepis Kabar Temuan Brankas Saat Geledah Rumah Febrie: Lemari Biasa</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:50:11 +0700</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Anang menjelaskan di dalam lemari itu penyidik menemukan sejumlah dokumen. Dia memastikan tidak ada uang yang ditemukan dalam lemari tersebut.</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613950/kejagung-tepis-kabar-temuan-brankas-saat-geledah-rumah-febrie-lemari-biasa</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/12/kapuspenkum-kejagung-anang-supriatna-rumondangdetikcom-1778574173490_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Masih Dengar Ada Pungli, Kepala BNN Perketat Pengawasan Rehabilitasi</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:49:14 +0700</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>Kepala BNN RI, Komjen Suyudi, menggandeng kementerian untuk perbaiki rehabilitasi narkoba, atasi pungli, dan tingkatkan mutu layanan secara komprehensif.</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613948/masih-dengar-ada-pungli-kepala-bnn-perketat-pengawasan-rehabilitasi</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/23/kepala-bnn-ri-komjen-suyudi-ario-seto-dalam-acara-peringatan-hari-anti-narkotika-internasional-di-lido-bogor-pada-kamis-237202-1784778300227_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Di Tengah Kemarau, Sawah Pesisir Jakarta Tetap Panen</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:00:43 +0700</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Pradita Utama</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>Sejumlah petani memanen padi di Sungai Tiram, Marunda, Jakarta Utara. Di tengah kemarau, sawah pesisir Jakarta tetap produktif.</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8613163/di-tengah-kemarau-sawah-pesisir-jakarta-tetap-panen</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/di-tengah-kemarau-sawah-pesisir-jakarta-tetap-panen-1786415670325_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Destry Calon Tunggal Gubernur BI, Purbaya: Nggak Ada Masalah</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:53:55 +0700</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya mendukung Destry Damayanti sebagai calon tunggal Gubernur BI. Destry dinilai berpengalaman untuk memimpin bank sentral.</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8613960/destry-calon-tunggal-gubernur-bi-purbaya-nggak-ada-masalah</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/toko-online-lega-pemerintah-tunda-pajak-final-05-persen-1785929270093_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>IHSG Ditutup Melemah, Balik ke Level 6.200an</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:37:28 +0700</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>IHSG ditutup melemah di level 6.200-an, turun 1,53%. Meskipun menguat bulanan, IHSG masih tercatat minus secara tahunan dan tiga bulanan.</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8613920/ihsg-ditutup-melemah-balik-ke-level-6-200an</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/04/ihsg-terpuruk-kekhawatiran-pasar-meningkat-1780558039793_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Purbaya Beri Waktu Berbenah hingga September, Bos Bea Cukai Bilang Begini</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:35:59 +0700</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>Yang pasti kan Bea Cukai sudah berusaha untuk memperbaiki dirinya. Tentunya bisa dilihat,bisa dilihat sekarang ini seperti apa Bea Cukai, kata Djaka.</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613916/purbaya-beri-waktu-berbenah-hingga-september-bos-bea-cukai-bilang-begini</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/direktur-jenderal-bea-dan-cukai-djaka-budi-utama-1786439830568_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Perkuat Layanan Haji, BSI Gandeng Ratusan Penyelenggara Ibadah Haji Khusus</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:33:48 +0700</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>PT Bank Syariah Indonesia (BSI) hadirkan layanan haji terintegrasi untuk mempermudah masyarakat merencanakan ibadah haji, mengatasi masa tunggu yang panjang.</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8613912/perkuat-layanan-haji-bsi-gandeng-ratusan-penyelenggara-ibadah-haji-khusus</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/bsi-1786440793868_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Habis Juara Piala Dunia, Pedro Porro Lamar Maria Hurtado</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:35:21 +0700</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>Pemain bola Pedro Porro lamar kekasihnya, Maria Hurtado. Momen itu terjadi setelah menjadi juara Piala Dunia 2026.</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613940/habis-juara-piala-dunia-pedro-porro-lamar-maria-hurtado</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/pedro-porro-1786441532314_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Asila Maisa Tegaskan Dirinya Korban Hoax Isu Selingkuhan Rizky Billar</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:07:30 +0700</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Asila Maisa menegaskan dirinya sebagai korban dari haox Rizky Billar selingkuh. Asila diisukan sebagai orang ketiga dalam rumah tangga Billar dan Lesti.</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613633/asila-maisa-tegaskan-dirinya-korban-hoax-isu-selingkuhan-rizky-billar</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/lesti-kejora-1786427746731_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Bea Cukai Bakal Telusuri Produsen di Balik Peredaran Rokok Ilegal dari Jawa Timur</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:31:11 +0700</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Djaka berharap dengan adanya penyelidikan di kawasan Jawa Timur, maka dalang dari beredarnya rokok-rokok ilegal di Indonesia bisa ditangkap.</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7867008/bea-cukai-bakal-telusuri-produsen-di-balik-peredaran-rokok-ilegal-dari-jawa-timur</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/aoeKuYGtX8gxZsCgECPN9e1Mgic=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pengungkapan-rokok-ilegal-di-tanjung-priok.jpg</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Cara Hitung Berat Badan Ideal Pakai Tinggi Badan dan Gunakan Rumus Ini</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:30:37 +0700</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Cara menghitung berat badan ideal dapat dilakukan dengan menggunakan tinggi badan sebagai dasar perhitungan, menurut ahli Gizi.</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7867007/cara-hitung-berat-badan-ideal-pakai-tinggi-badan-dan-gunakan-rumus-ini</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/4pIoHetaG0oXokEiNQj24DEDxF0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/MENURUNKAN-BERAT-BADAN-Program-penurunan-berat-badan.jpg</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Jadwal Acara TV Rabu, 12 Agustus 2026: Rumahnya Seleb di MNC TV,  Kara dan Mayi di JAK TV</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:27:09 +0700</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>Simak jadwal acara TV Rabu, 12 Agustus 2026, terdapat tayangan Rumahnya Seleb di MNC TV,  Kara dan Mayi di JAK TV.</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867006/jadwal-acara-tv-rabu-12-agustus-2026-rumahnya-seleb-di-mnc-tv-kara-dan-mayi-di-jak-tv</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Fl8aETmbMmkOkLsjx-fRlfD8IZo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ilustrasi-Televisi-digital.jpg</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Tak Perlu Lagi ke Dukcapil, Akta Kelahiran Digital Bayi Baru Lahir Kini Dikirim ke Email Orang Tua</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:24:58 +0700</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>Pemerintah mulai menerapkan digitalisasi layanan akta kelahiran yang memungkinkan dokumen digital dikirim langsung kepada orang tua.</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867005/tak-perlu-lagi-ke-dukcapil-akta-kelahiran-digital-bayi-baru-lahir-kini-dikirim-ke-email-orang-tua</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/iE3iK3mWa4Ip3J8N4qUq5aL8Obc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Peluncuran-Digitalisasi-Akta-Kelahiran-melalui-Integrasi-SatuSehat-SIAK.jpg</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Dusan Vlahovic Tak Lagi Sekadar Pemain Gratisan, Komisi Agen Bikin Transfer Berbelit</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:21:41 +0700</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>Dusan Vlavohic bukan lagi sekedar pemain gratisan karena tuntutan komisi sang agen membuat transfernya kian berbelit.</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867004/dusan-vlahovic-tak-lagi-sekadar-pemain-gratisan-komisi-agen-bikin-transfer-berbelit</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/lzwZ6yovui4Tu_-YxoAFgijC2YA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/vlahovic-cetak-gol.jpg</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Duduk di Kursi Terdakwa, Suara Mantan Kabaranahan Leonardi Bergetar: Saya Hanya Jalankan Perintah</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:20:07 +0700</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>Leonardi, terdakwa kasus dugaan korupsi pengadaan satelit tampak lemas dan emosional saat skors persidangan di Pengadilan Militer Tinggi II.</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867003/duduk-di-kursi-terdakwa-suara-mantan-kabaranahan-leonardi-bergetar-saya-hanya-jalankan-perintah</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/2MSt2X0Lc7ThInj_GJ92lSgk6tc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kasus-satelit-kemhan-8.jpg</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>DPR Sebut Label Batas Konsumsi MBG Jangan Sekadar Formalitas: Dapur Harus Diawasi</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:20:02 +0700</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>DPR meminta BGN mencantumkan label batas waktu konsumsi dalam program Makan Bergizi Gratis (MBG).</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867002/dpr-sebut-label-batas-konsumsi-mbg-jangan-sekadar-formalitas-dapur-harus-diawasi</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/eOjfMLum0CAACYoP1RV_Hb37e9A=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/dpr-ri-77-anggota-komisi-x-dpr-ri-ledia-hanifa-amaliah.jpg</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Mobilnya Ditabrak saat Berhenti di Bojonegoro, KH Anwar Zahid: MashaAlloh, Rasane Koyo Dikopyok</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:19:06 +0700</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>KH Anwar Zahid ungkap detik-detik mobilnya ditabrak truk di Bojonegoro. Meski terguncang, ia tetap melanjutkan perjalanan tausiah ke Jateng.</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867001/mobilnya-ditabrak-saat-berhenti-di-bojonegoro-kh-anwar-zahid-mashaalloh-rasane-koyo-dikopyok</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/T_Rz4deJ5u4IXHubQFXxo-XsYus=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KH-Anwar-Zahid-Kecelakaan-di-Bojonegoro.jpg</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Kubu Eks Kabaranahan Baca 90 Halaman Pledoi, Sebut Dakwaan dan Tuntutan Kasus Satelit Kemhan Cacat</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:16:07 +0700</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Tim penasihat hukum secara bergantian menyampaikan 90 halaman pledoi atas tuntutan oditur militer 8 tahun penjara dterhadap Leonardi</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867000/kubu-eks-kabaranahan-baca-90-halaman-pledoi-sebut-dakwaan-dan-tuntutan-kasus-satelit-kemhan-cacat</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/FVP9DJ7rjB_yXRfDdFyb-fkmLrA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Laksamana-Muda-Laksda-TNI-Purn-Leonardi-311029.jpg</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Program Magang Mahasiswa Batch III Kemendagri 2026 Dibuka, Cek Syarat dan Cara Daftarnya</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:11:36 +0700</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>Program Magang Mahasiswa Kemendagri Batch III 2026 menyediakan 65 posisi yang tersebar di 12 unit kerja. Pendaftaran telah dibuka 10 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7866999/program-magang-mahasiswa-batch-iii-kemendagri-2026-dibuka-cek-syarat-dan-cara-daftarnya</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/RixqCVoi2eRj_v8lGLbauj4BapY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Program-Magang-Mahasiswa-Batch-III-Kemendagri-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Kenapa Duel Persija vs Persib Digelar di Pekan Kedua? Ini Penjelasan I.League</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:09:44 +0700</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Persib Bandung dan Borneo FC menjadi dua klub yang mendapatkan perhatian khusus terkait jadwal pertandingan mereka di AFC.</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866998/kenapa-duel-persija-vs-persib-digelar-di-pekan-kedua-ini-penjelasan-ileague</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oyf129Zn72lCvqxli1Q3cHini20=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/DIRUT-PT-LIB-FERRY-PAULUS-Direktur-Utama-PT-LIB-Ferry-Paulus.jpg</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Program Magang Nasional 2026 Buka Kesempatan bagi Lulusan Profesi dan Penyandang Disabilitas</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:08:45 +0700</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>keterlibatan lulusan profesi menjadi salah satu pembeda Program Magang Nasional kali ini dibandingkan angkatan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866997/program-magang-nasional-2026-buka-kesempatan-bagi-lulusan-profesi-dan-penyandang-disabilitas</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/o8KN9AJQ2Q0n6Y96gLJIHFrkKnA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Teddy-di-Kick-off-Program-Magang-Nasional.jpg</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Jelang Peringatan HUT ke-81 RI, Gerakan Nurani Bangsa Sampaikan 8 Poin Pesan Kemerdekaan</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:08:28 +0700</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Gerakan Nurani Bangsa (GNB) menyampaikan delapan poin pesan kemerdekaan jelang peringatan HUT RI ke-81 yang jatuh pada 17 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866996/jelang-peringatan-hut-ke-81-ri-gerakan-nurani-bangsa-sampaikan-8-poin-pesan-kemerdekaan</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/LI2WpngaYQVgwY5fTXTrBmo6VOE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/gnb-konpers-11-agt-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Prabowo Ajukan Destry sebagai Calon Tunggal Gubernur BI ke DPR</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:07:38 +0700</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Prabowo mengajukan Destry Damayanti sebagai calon tunggal Gubernur BI. DPR kini menyiapkan uji kelayakan sebelum keputusan.</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866995/prabowo-ajukan-destry-sebagai-calon-tunggal-gubernur-bi-ke-dpr</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/65Lo5yaCMnnV5UuorcZ5wxSBZwE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penjabat-Gubernur-Bank-Indonesia-BI-Destry-Damayanti-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Audy Item Keguguran Anak Ketiga di Usia Kandungan 7 Minggu, Istri Iko Uwais Sudah Siapkan Nama</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:06:53 +0700</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Audy Item mengalami keguguran anak ketiga dalam usia kandungan tujuh minggu. Audy sudah siapkan nama untuk anaknya yang ia yakini laki-laki.</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866994/audy-item-keguguran-anak-ketiga-di-usia-kandungan-7-minggu-istri-iko-uwais-sudah-siapkan-nama</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/dOXxpDhUf4S95ktDSFO0wfZ0I1s=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Audy-Item-dan-Iko-Uwais-pasutri.jpg</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Anak Mulai Terjun di Dunia Akting, Richa Novisha Siap Beri Dukungan Penuh</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:05:55 +0700</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>Istri mendiang aktor Gary Iskak, Richa Novisha, siap beri dukungan penuh untuk anaknya yang mulai terjun di dunia akting.</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866993/anak-mulai-terjun-di-dunia-akting-richa-novisha-siap-beri-dukungan-penuh</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/RyUPKflJRbXPqi5E1QglsLI4r0k=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Richa-Novisha-ketika-ditemui-di-kawasan-Tanah-Abang-Jakarta-Pusat.jpg</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Hampir 7 Tahun Jalan Alpen Selatan Jepang Ditutup, Pemulihan Belum Juga Dimulai</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:03:45 +0700</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>Hampir tujuh tahun pasca-Topan Hagibis, ruas Jalan Alpen Selatan Jepang masih ditutup. Longsor terus terjadi dan pemulihan belum dimulai</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866992/hampir-7-tahun-jalan-alpen-selatan-jepang-ditutup-pemulihan-belum-juga-dimulai</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/j0x1lHbAa1UFYbQifu5sUSbabho=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/jalanalpen111111.jpg</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Mantan Pemimpin Suriah Bashar al-Assad Dijatuhi Hukuman Mati oleh Pengadilan Damaskus</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:03:04 +0700</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>Pengadilan Damaskus menjatuhkan hukuman mati secara in absentia kepada mantan Presiden Suriah Bashar al-Assad dan adiknya, Maher.</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866991/mantan-pemimpin-suriah-bashar-al-assad-dijatuhi-hukuman-mati-oleh-pengadilan-damaskus</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ZBhLRX3Ne0ft7tFW3Ij28Q9tVeg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/foto-2-presiden-suriah-bashar-al-assad.jpg</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Investor Indonesia Mulai Diperhitungkan di Pasar Properti Australia, Sydney Jadi Incaran</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:02:54 +0700</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Masuknya investor Indonesia terjadi ketika peta investor asing di pasar properti Australia mulai mengalami perubahan.</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866990/investor-indonesia-mulai-diperhitungkan-di-pasar-properti-australia-sydney-jadi-incaran</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/9pyczKliahYkvoAdY6ZSIcAAPC0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/CEO-Capital-Value-International-Group-CVIG-Chandra-Leonardi.jpg</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>FIFA Restui Super League 2027 Dihadiri Suporter Away Kecuali Persija vs Persib, Arema vs Persebaya</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:01:13 +0700</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>Meski mendapat lampu hijau, I.League tetap memberlakukan pengecualian untuk pertandingan dengan tingkat rivalitas tinggi.</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866989/fifa-restui-super-league-2027-dihadiri-suporter-away-kecuali-persija-vs-persib-arema-vs-persebaya</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/9HsAQqSqPH8QrPKwIahxD0GtFdo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wawancara-direktur-utama-ILeague-Ferry-Paulus.jpg</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Dibanding Malaysia dan Thailand, Pasar Pembiayaan RI Masih Sangat Besar</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:40:42 +0700</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>Plt. Dirut MUF, Dapot Parasian, menyatakan potensi bisnis multifinance di Indonesia sangat besar meski dalam kondisi geopolitik menantang.</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811173155-17-758385/dibanding-malaysia-thailand-pasar-pembiayaan-ri-masih-sangat-besar</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/30/sejumlah-pengunjung-berjalan-melewati-beberapa-kendaraan-yang-dipajang-dalam-giias-2026-di-ice-bsd-tangerang-kamis-3072026-1785406876473_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Video: Asing Mulai Masuk Tapi IHSG Anjlok 1,5%-Rupiah Melemah, Kenapa?</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:31:08 +0700</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>Asing Mulai Masuk Tapi IHSG Melemah 1,5% hingga Rupiah Terkoreksi, Ada Apa?</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811172159-19-758383/video-asing-mulai-masuk-tapi-ihsg-anjlok-15-rupiah-melemah-kenapa</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/asing-mulai-masuk-tapi-ihsg-melemah-15-hingga-rupiah-terkoreksi-ada-apa-1786444182862_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Supres Prabowo ke DPR Soal Pengawas Bursa Mineral, OJK Buka Suara</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:20:02 +0700</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>OJK akan menambah posisi Kepala Eksekutif Pengawas Bursa Mineral dan Komoditas Strategis. Ketua OJK berharap calon dapat menjalankan mandat dengan baik.</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811162302-17-758349/supres-prabowo-ke-dpr-soal-pengawas-bursa-mineral-ojk-buka-suara</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/06/13/area-tambang-smelter-feronikel-dan-hpal-harita-nikel-di-obi-halmahera-selatan-jumat-1362025-cnbc-indonesiapratama-guitarra-1749794600855_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Prabowo Pilih Destry Jadi Calon Tunggal Bos BI, Purbaya Ungkap Hal Ini</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:17:08 +0700</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya buka suara ihwal pencalonan tunggal Destry Damayanti sebagai Gubernur BI oleh Presiden Prabowo Subianto.</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811171254-17-758378/prabowo-pilih-destry-jadi-calon-tunggal-bos-bi-purbaya-ungkap-hal-ini</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/menteri-keuangan-purbaya-yudhi-sadewa-dan-pjs-gubernur-bank-indonesia-destry-damayanti-berbincang-saat-konferensi-pers-hasil-r-1785751311273_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>IHSG Anjlok 1,53% Balik ke Level 6.267 Terseret Kinerja Saham Ini</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:35:25 +0700</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>IHSG kembali tertekan, turun 1,53% ke 6.267,88. Mayoritas saham melemah, dengan total transaksi mencapai Rp 14,49 triliun.</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811153520-17-758347/ihsg-anjlok-153-balik-ke-level-6267-terseret-kinerja-saham-ini</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019138_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>BNBR Kena Notasi Khusus G, OJK Buka Suara</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:55:05 +0700</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>OJK mengungkapkan notasi G pada emiten Bakrie Group, BNBR, sebagai peringatan bagi investor. Notasi ini menunjukkan pelanggaran peraturan pasar modal.</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811101720-17-758179/bnbr-kena-notasi-khusus-g-ojk-buka-suara</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/04/30/1bbe588b-383f-4c6e-86d3-bbadc51db2bb_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Bos Oona Insurance Buka-bukaan Soal Risiko Asuransi Mobil Listrik</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:51:15 +0700</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>Oona Insurance menjadi pionir dalam asuransi kendaraan listrik di Indonesia. CEO Vincent Soegianto menyoroti tantangan risiko dan loss ratio yang tinggi.</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811154345-17-758334/bos-oona-insurance-buka-bukaan-soal-risiko-asuransi-mobil-listrik</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/president-director-chief-executive-officer-ceo-oona-insurance-indonesia-vincent-c-soegianto-saat-menyampaikan-pemaparan-dalam--1786417368095_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Video: Calon Gubernur BI Direspons Positif, Rupiah Lanjut Menguat?</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:25:48 +0700</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>Calon Gubernur BI Direspons Positif, Rupiah Diramal Bisa Naik ke Rp 17.400 per USD</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811150108-19-758310/video-calon-gubernur-bi-direspons-positif-rupiah-lanjut-menguat</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/calon-gubernur-bi-direspons-positif-rupiah-diramal-bisa-naik-ke-rp-17400-per-usd-1786436184833_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Emas Cetak Kenaikan Terbaik 7 Bulan, Investor Mulai Borong Lagi</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>Harga emas mencatatkan kenaikan 7% dalam seminggu. Investor mulai membidik potensi kenaikan lebih lanjut.</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811140822-17-758283/emas-cetak-kenaikan-terbaik-7-bulan-investor-mulai-borong-lagi</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/07/05/brankas-emas-milik-federal-reserve-bank-of-new-york-1751700499604_169.gif?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Video: Hormuz Bergejolak Lagi - Rebalancing MCSI, IHSG Anjlok Kembali</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>Selat Hormuz Kembali Bergejolak - Sentimen Rebalancing MCSI, IHSG Kembali Tertekan</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811150110-19-758311/video-hormuz-bergejolak-lagi--rebalancing-mcsi-ihsg-anjlok-kembali</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/selat-hormuz-kembali-bergejolak-sentimen-rebalancing-mcsi-ihsg-kembali-tertekan-1786435924736_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Rupiah Kehabisan Tenaga, Dolar AS Kembali Naik ke Rp17.830</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah ditutup melemah terhadap dolar Amerika Serikat (AS) pada perdagangan Selasa (11/8/2026).</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811145417-17-758313/rupiah-kehabisan-tenaga-dolar-as-kembali-naik-ke-rp17830</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/08/petugas-menjunjukkan-uang-pecahan-dolar-amerika-serikat-as-dan-rupiah-di-dolar-asia-money-changer-jakarta-rabu-872026-1783496342158_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Video: Anjlok Lagi, IHSG Melemah Lebih Dari 1% dan Merosot ke 6.200-an</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:55:39 +0700</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>Koreksi Berlanjut, IHSG Melemah Lebih Dari 1% dan Merosot ke 6.200-an</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811144234-19-758302/video-anjlok-lagi-ihsg-melemah-lebih-dari-1-merosot-ke-6200-an</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/koreksi-berlanjut-ihsg-melemah-lebih-dari-1-merosot-ke-6200-an-1786434707996_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Fit and Proper Test Calon Gubernur BI Destry Segera Digelar, Kapan?</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:50:26 +0700</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>Komisi XI DPR RI akan jadwalkan uji kelayakan Destry Damayanti sebagai calon Gubernur Bank Indonesia setelah masa reses.</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811143837-17-758303/fit-and-proper-test-calon-gubernur-bi-destry-segera-digelar-kapan</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/pjs-gubernur-bank-indonesia-destry-damayanti-saat-konferensi-pers-hasil-rapat-berskla-kssk-iii-tahun-2016-di-jakarta-senin-382-1785749975842_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>OJK Ungkap Pembiayaan UMKM Sentuh Rp 1.948 Triliun</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:50:23 +0700</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>OJK melaporkan pembiayaan UMKM mencapai Rp 1.948,7 triliun pada Juni 2026, tumbuh 2,16% yoy. Sektor perbankan masih dominan dalam pembiayaan.</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811132912-17-758271/ojk-ungkap-pembiayaan-umkm-sentuh-rp-1948-triliun</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/03/26/ilustrasi-ojk-cnbc-indonesiafaisal-rahman-1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Asing Net Sell Rp774 Miliar di Sesi I, Ini Daftar Sahamnya</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:38:04 +0700</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>IHSG turun 0,87% di sesi I, tertekan oleh aksi jual asing Rp774,89 miliar. Sektor utilitas dan finansial paling terpukul. Simak analisis lengkapnya.</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811143432-17-758299/asing-net-sell-rp774-miliar-di-sesi-i-ini-daftar-sahamnya</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019138_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>OJK Ungkap Sederet Tantangan Industri Multifinance</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:54:52 +0700</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>OJK mengungkap tantangan industri multifinance, termasuk suku bunga tinggi dan kualitas pembiayaan. Inovasi dan adaptasi bisnis jadi kunci keberlanjutan.</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811125038-17-758247/ojk-ungkap-sederet-tantangan-industri-multifinance</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/deputi-komisioner-pengawas-lembaga-pembiayaan-perusahaan-modal-ventura-lembaga-keuangan-mikro-dan-lembaga-jasa-keuangan-lainny-1786415946597_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Penyebab IHSG Kembali di Zona Merah, Sesi 1 Turun 0,97%</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:22:02 +0700</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>IHSG turun 0,87% di sesi I perdagangan hari ini, Selasa (11/8/2026).</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811121150-17-758225/penyebab-ihsg-kembali-di-zona-merah-sesi-1-turun-097</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/06/29/ilustrasi-bursa-efek-indonesia-cnbc-indonesiaandrean-kristianto-1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Video: Nantikan Pidato Prabowo, Investor Cermati Defisit APBN 2027</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:16:19 +0700</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Nantikan Pidato Kenegaraan Prabowo, Investor Cermati Postur Fiskal - Defisit APBN 2027</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811104255-19-758184/video-nantikan-pidato-prabowo-investor-cermati-defisit-apbn-2027</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/nantikan-pidato-kenegaraan-prabowo-investor-cermati-postur-fiskal-defisit-apbn-2027-1786420802248_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Destry Jadi Calon Tunggal Gubernur BI, Ini Komentar Bos OJK</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:05:44 +0700</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>OJK mendukung pencalonan Destry Damayanti sebagai Gubernur BI. Sosoknya dinilai memiliki rekam jejak baik, terutama dalam pengembangan UMKM.</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811114609-17-758209/destry-jadi-calon-tunggal-gubernur-bi-ini-komentar-bos-ojk</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/ketua-dewan-komisioner-otoritas-jasa-keuangan-ojk-friderica-widyasari-dewi-saat-doorstop-usai-acara-umkm-finance-summit-2026-d-1786423105689_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Video: Harapan Damai Hormuz Memudar, Harga Minyak Batu Bara Melambung</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:05:06 +0700</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>Harapan Damai Selat Hormuz Memudar, Harga Minyak Batu Bara Melambung</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811114034-19-758207/video-harapan-damai-hormuz-memudar-harga-minyak-batu-bara-melambung</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/harapan-damai-selat-hormuz-memudar-harga-minyak-batu-bara-melambung-1786423629418_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Video:Calon Gubernur BI Dipantau hingga IHSG dan Rupiah Anjlok Berjamaah</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:51:31 +0700</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Calon Gubernur BI Dipantau hingga IHSG dan Rupiah Anjlok Berjamaah</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811113956-19-758206/videocalon-gubernur-bi-dipantau-hingga-ihsg-rupiah-anjlok-berjamaah</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/calon-gubernur-bi-dipantau-hingga-ihsg-rupiah-anjlok-berjamaah-1786423561954_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Makin Banyak KUR Cair Modal Agunan HAKI, Kini Tembus Rp 5,85 T</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:30:03 +0700</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>Pemerintah telah menyalurkan kredit program untuk mendukung sektor ekonomi kreatif senilai Rp 5,85 triliun per semester I-2026.</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811111450-17-758196/makin-banyak-kur-cair-modal-agunan-haki-kini-tembus-rp-585-t</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/01/30/deputi-bidang-koordinasi-pengelolaan-dan-pengembangan-usaha-badan-usaha-milik-negara-kementerian-koordinator-bidang-perekonomi-1769764148498_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Tiba-Tiba Ada Transaksi Jumbo di Emiten Hapsoro</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:15:27 +0700</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>Saham Singaraja Putra (SINI) mencatat transaksi jumbo 150 juta saham di harga Rp5.070, jauh di bawah harga pasar Rp7.000.</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811105534-17-758187/tiba-tiba-ada-transaksi-jumbo-di-emiten-hapsoro</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797018492_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Kenaikan Suku Bunga Jadi "Momok" buat Industri Multifinance</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:12:18 +0700</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>Deputi OJK Jasmi membahas tantangan industri multifinance, terutama terkait kenaikan suku bunga yang mempengaruhi biaya perusahaan.</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811110850-17-758195/kenaikan-suku-bunga-jadi-momok-buat-industri-multifinance</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/deputi-komisioner-pengawas-lembaga-pembiayaan-perusahaan-modal-ventura-lembaga-keuangan-mikro-dan-lembaga-jasa-keuangan-lainny-1786415946251_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Video: Prabowo Usul Destry Jadi Gubernur BI, Ini Efeknya ke Rupiah-SBN</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:10:26 +0700</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>Destry Diusulkan Prabowo Jadi Gubernur BI, Apa Efeknya ke SBN dan Rupiah?</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811104259-19-758185/video-prabowo-usul-destry-jadi-gubernur-bi-ini-efeknya-ke-rupiah-sbn</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/destry-diusulkan-prabowo-jadi-gubernur-bi-apa-efeknya-ke-sbn-rupiah-1786420725903_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>BI: Penjualan Eceran Balik Positif, Tumbuh 0,7% di Juni 2026</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:03:17 +0700</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>BI melaporkan penjualan eceran Juni 2026 tumbuh 0,7% (mtm). Pertumbuhan didorong oleh barang lainnya dan suku cadang, dengan proyeksi Juli positif.</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811105950-17-758188/bi-penjualan-eceran-balik-positif-tumbuh-07-di-juni-2026</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/03/27/bc331953-cd88-4102-990c-27a283556a27_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Debitur Sulit Bayar, NPF Multifinance Sudah 3%</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:26:02 +0700</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>OJK menyoroti tantangan kemampuan bayar debitur di industri multifinance.</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811101048-17-758174/debitur-sulit-bayar-npf-multifinance-sudah-3</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/deputi-komisioner-pengawas-lembaga-pembiayaan-perusahaan-modal-ventura-lembaga-keuangan-mikro-dan-lembaga-jasa-keuangan-lainny-1786415946676_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Harga Minyak Dunia Kembali Bergeliat, Brent Dekati US$88 per Barel</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:15:20 +0700</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>Harga minyak dunia menguat pada 11 Agustus 2026, dipicu risiko gangguan pasokan akibat meredupnya harapan kesepakatan AS-Iran. Brent dan WTI naik signifikan.</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811093304-17-758164/harga-minyak-dunia-kembali-bergeliat-brent-dekati-us-88-per-barel</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/27/phe-1785130282348_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Bukan Gen Alpha, Ini Generasi yang Jadi Raja Keuangan RI</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:10:10 +0700</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Hasil Survei Nasional Literasi dan Inklusi Keuangan 2026 menunjukkan indeks literasi keuangan nasional mencapai 69,57%, meningkat dari tahun sebelumnya.</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811092707-17-758159/bukan-gen-alpha-ini-generasi-yang-jadi-raja-keuangan-ri</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/konferensi-pers-hasil-survei-nasional-literasi-dan-inklusi-keuangan-snlik-tahun-2026-senin-1182026-1786405552129_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Harga Naik Ugal-ugalan, BEI Gembok Perdagangan Saham TRUK</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:50:25 +0700</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>Bursa Efek Indonesia menghentikan sementara perdagangan saham PT Guna Timur Raya Tbk (TRUK) pada 11 Agustus 2026 untuk melindungi investor.</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811093725-17-758165/harga-naik-ugal-ugalan-bei-gembok-perdagangan-saham-truk</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019719_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Video: Rupiah Kembali Melemah ke Rp 17.780 per USD - IHSG Masih Lesu</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:46:09 +0700</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>Rupiah Kembali Melemah ke Rp 17.780 per USD hingga IHSG Masih Lesu</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811092012-19-758156/video-rupiah-kembali-melemah-ke-rp-17780-per-usd--ihsg-masih-lesu</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/rupiah-kembali-melemah-ke-rp-17780-per-usd-hingga-ihsg-masih-lesu-1786416183338_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Ada Transaksi Nego Rp1,3 Triliun di Saham DSSA</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:40:13 +0700</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Saham DSSA Grup Sinar Mas mencatat transaksi jumbo Rp 1,3 triliun di pasar negosiasi. Transaksi ini terjadi bersamaan dengan aksi korporasi buyback saham.</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811093013-17-758160/ada-transaksi-nego-rp13-triliun-di-saham-dssa</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2020/12/14/dok-dssa_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Terungkap! 87% Pemilik Asuransi Tak Tahu Polisnya Bakal Dijamin LPS</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:30:25 +0700</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>Hasil SNLIK 2026 menunjukkan 87,53% pemilik asuransi non-BPJS belum tahu tentang penjaminan polis yang mulai berlaku 2028.</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811085446-17-758151/terungkap-87-pemilik-asuransi-tak-tahu-polisnya-bakal-dijamin-lps</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/29/ilustrasi-lps-dok-lps-1780059811834_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Breaking, IHSG Merosot 1% Lebih Terseret Kinerja Saham Ini</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:29:38 +0700</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>IHSG anjlok 1,15% ke 6.292,28 pada 10 Agustus 2026, dipicu pelemahan saham BBCA dan DSSA. Investor asing mulai masuk meski terbatas.</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811092043-17-758158/breaking-ihsg-merosot-1-lebih-terseret-kinerja-saham-ini</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797018901_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Saham Naik Ratusan Persen, BEI Pantau Ketat 2 Saham Ini</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:25:16 +0700</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>Bursa Efek Indonesia memantau ketat saham MCAS dan FUTR karena Unusual Market Activity. Investor diimbau untuk cermati perkembangan dan kinerja emiten.</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811091716-17-758155/saham-naik-ratusan-persen-bei-pantau-ketat-2-saham-ini</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019966_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Rupiah Dibuka Melemah 0,17%, Nilai Tukar Dolar AS Naik ke Rp17.780</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:06:08 +0700</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>Rupiah kehilangan sedikit tenaganya setelah mencatatkan penguatan selama empat hari perdagangan beruntun.</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811083143-17-758152/rupiah-dibuka-melemah-017-nilai-tukar-dolar-as-naik-ke-rp17780</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/04/08/petugas-menjunjukkan-uang-pecahan-dolar-as-dan-rupiah-di-dolarindo-money-changer-jakarta-selasa-842025-1744086560941_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>IHSG Sesi I Dibuka Menguat 0,29% ke Level 6.383</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:04:08 +0700</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>IHSG dibuka menguat di level 6.383,81 pada 10 Agustus 2026, dengan transaksi Rp 139,52 miliar. Sentimen global dan domestik mempengaruhi pergerakan pasar.</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811084941-17-758153/ihsg-sesi-i-dibuka-menguat-029-ke-level-6383</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893013334_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Data BPS: 62,5% Nasabah RI Sudah Tahu Simpanannya Dijamin LPS</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:00:45 +0700</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>Hasil Survei Nasional Literasi dan Inklusi Keuangan 2026 menunjukkan rendahnya pengetahuan masyarakat Indonesia tentang Lembaga Penjamin Simpanan (LPS).</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811083745-17-758148/data-bps-625-nasabah-ri-sudah-tahu-simpanannya-dijamin-lps</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/konferensi-pers-hasil-survei-nasional-literasi-dan-inklusi-keuangan-snlik-tahun-2026-dok-bps-1786409504090_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Intip 5 Rekomendasi Saham yang Potensi Kasih Cuan Hari Ini</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:49:27 +0700</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>IHSG melemah 0,69% di level 6.365,37. Investor asing net sell Rp875,51 miliar. CMRY dan IFSH catat laba bersih meningkat. Rekomendasi saham hari ini tersedia.</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811081706-17-758140/intip-5-rekomendasi-saham-yang-potensi-kasih-cuan-hari-ini</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/market-1786411026-1786411026718_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Asing Terciduk Serok 10 Saham Ini Kala IHSG Merah</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:37:41 +0700</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>IHSG turun 0,69% ke 6.365,3. Investor asing mencatatkan pembelian bersih Rp829,70 miliar. Simak 10 saham teratas yang dibeli asing!</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811082041-17-758143/asing-terciduk-serok-10-saham-ini-kala-ihsg-merah</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019138_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Mengenal ETF Emas, Keunggulan dan Cara Belinya</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:32:41 +0700</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>Romys Binekasri</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>Emas kini bisa diinvestasikan tanpa harus membeli fisiknya. ETF emas menawarkan cara fleksibel dan likuid untuk mendapatkan eksposur terhadap harga emas.</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811082636-17-758144/mengenal-etf-emas-keunggulan-dan-cara-belinya</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797018492_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Literasi Keuangan RI Naik, Papua Pegunungan Masih Tertinggal Jauh</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:30:16 +0700</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Indeks Literasi Keuangan Indonesia meningkat menjadi 69,57% pada 2026, dengan DKI Jakarta tertinggi. Namun, provinsi timur masih di bawah rata-rata.</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811080916-17-758139/literasi-keuangan-ri-naik-papua-pegunungan-masih-tertinggal-jauh</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/konferensi-pers-hasil-survei-nasional-literasi-dan-inklusi-keuangan-snlik-tahun-2026-dok-bps-1786409504090_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>IHSG Lesu, Asing Kompak Buang 10 Saham Ini</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:20:16 +0700</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>IHSG ditutup turun 0,69% di level 6.365,3 pada 10 Agustus 2026. Investor asing mencatatkan pembelian bersih Rp829,70 miliar. Simak saham yang dilepas asing!</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811081741-17-758142/ihsg-lesu-asing-kompak-buang-10-saham-ini</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893013334_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Tito Buka Opsi Guru PPPK Jadi ASN Pusat, Beban APBD Bisa Berkurang</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:25:29 +0700</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian mengkaji opsi penarikan guru PPPK menjadi ASN pusat untuk mengatasi pengelolaan dan pembiayaan tenaga pendidik di daerah.</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811071029-17-758120/tito-buka-opsi-guru-pppk-jadi-asn-pusat-beban-apbd-bisa-berkurang</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/dok-kementerian-dalam-negeri-1786365111260_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Survei BPS Terbaru: 7 dari 10 Orang Indonesia Kini Melek Keuangan</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 06:55:18 +0700</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>Survei Nasional Literasi dan Inklusi Keuangan 2026 menunjukkan peningkatan signifikan, dengan indeks literasi mencapai 69,57% dan inklusi 93,61%.</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810170637-17-758040/survei-bps-terbaru-7-dari-10-orang-indonesia-kini-melek-keuangan</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/konferensi-pers-hasil-survei-nasional-literasi-dan-inklusi-keuangan-snlik-tahun-2026-senin-1182026-1786405552129_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Cari Kerja Kantoran Susah, Sekarang Marak Fenomena Wawancara Palsu</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Fenomena 'Joki' AI dalam wawancara kerja mengubah proses rekrutmen. Perusahaan harus beradaptasi untuk menghindari risiko. Simak!</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811141759-37-758286/cari-kerja-kantoran-susah-sekarang-marak-fenomena-wawancara-palsu</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/01/21/ilustrasi-fresh-graduate-mencari-pekerjaan-cnbc-indonesiamuhammad-sabki-4_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>DPR Kirim Surat ke Pemerintah, Kasih Peringatan Bahaya Besar</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Novina Putri Bestari</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>DPR AS memperingatkan pemerintah untuk mencegah pengiriman chip canggih ke China. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811140659-37-758282/dpr-kirim-surat-ke-pemerintah-kasih-peringatan-bahaya-besar</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/09/23/bendera-tiongkok-dan-as-ditampilkan-pada-papan-sirkuit-cetak-dengan-chip-semikonduktor-reutersflorence-lofile-photo_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Akun WhatsApp Diblokir Mendadak Jadi Korban Judol, Begini Modusnya</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>Pengguna WhatsApp melaporkan akun diblokir mendadak. Pakar keamanan siber mengungkap modus peretasan. Simak!</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811134512-37-758276/akun-whatsapp-diblokir-mendadak-jadi-korban-judol-begini-modusnya</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2019/07/26/2bdfd888-1b1c-404d-a284-71aa1c14308d_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Peringatan Keras Buat Trump, Amerika Bisa Kalah Telak Melawan China</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>Mark Zuckerberg mendesak pemerintah AS untuk memangkas regulasi AI open-source untuk bisa bersaing dengan China. Simak!</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811121951-37-758233/peringatan-keras-buat-trump-amerika-bisa-kalah-telak-melawan-china</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/15/presiden-china-xi-jinping-memperlihatkan-suasana-kompleks-bersejarah-zhongnanhai-kepada-presiden-amerika-serikat-donald-trump--1778835074284_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Biaya Produksi iPhone Baru Sudah Tak Masuk Akal, Begini Dampaknya</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Novina Putri Bestari</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>Apple menghadapi kenaikan biaya komponen iPhone 18 hingga 38% YoY. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811121152-37-758226/biaya-produksi-iphone-baru-sudah-tak-masuk-akal-begini-dampaknya</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/10/17/calon-pembeli-melihat-iphone-17-series-di-gerai-ibox-kota-kasablanka-jakarta-jumat-17102025-cnbc-indonesiafaisal-rahman-1760684677150_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Mengungkap Masa Depan dan Tantangan Ekosistem Perbankan Digital</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:09:41 +0700</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>Transformasi digital mengubah akses layanan keuangan. Forum Digital Banking 2026 akan bahas masa depan perbankan digital dan inovasi layanan.</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811150556-37-758317/mengungkap-masa-depan-dan-tantangan-ekosistem-perbankan-digital</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/digital-banking-forum-2026-1786435759229_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>UMKM Kini Bisa Balas Chat Pelanggan 24 Jam Full Pakai AI di WhatsApp</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Intan Rakhmayanti</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>WhatsApp Business kini hadirkan Meta Business Agent, agen AI 24 jam untuk respons otomatis. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811143247-37-758296/umkm-kini-bisa-balas-chat-pelanggan-24-jam-full-pakai-ai-di-whatsapp</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2019/07/26/831f49f1-63bc-4059-82d2-8e52851123f6_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Kolaborasi Kemenko Polkam, BSSN, Telkom Hadapi Era Komputasi Kuantum</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:08:17 +0700</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>Pemerintah Indonesia mempercepat antisipasi ancaman keamanan siber akibat teknologi komputasi kuantum.</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811140230-37-758280/kolaborasi-kemenko-polkam-bssn-telkom-hadapi-era-komputasi-kuantum</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/dok-telkom-1786432077911_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Cara Ngecas HP yang Benar Agar Baterai Awet, Banyak Orang Tak Tahu</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Intan Rakhmayanti</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>Pelajari cara mengisi daya HP yang benar untuk menjaga kesehatan baterai. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811111914-37-758197/cara-ngecas-hp-yang-benar-agar-baterai-awet-banyak-orang-tak-tahu</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2020/03/12/875b1aa9-f40b-49a9-9e22-fb1f02cbb6d3_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Ketahuan Bawa Kabur Uang Rp 16 Miliar, Agen FBI Langsung Ditangkap</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>Seorang agen FBI, Patrick Steven Yaroch, ditangkap karena mencuri hampir Rp 16 miliar dalam aset kripto. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811114615-37-758210/ketahuan-bawa-kabur-uang-rp-16-miliar-agen-fbi-langsung-ditangkap</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/26/logo-fbi-dok-istimewa-1772091871757_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Wabah Kecanduan Sudah Parah, 3.000 Kasus Masuk Pengadilan</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>Lebih dari 3.000 gugatan diajukan di AS terhadap raksasa media sosial, menuduh mereka merancang platform yang membuat anak kecanduan.</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811112622-37-758200/wabah-kecanduan-sudah-parah-3000-kasus-masuk-pengadilan</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/30/sejumlah-anak-memainkan-ponsel-mereka-sesuai-pulang-sekolah-di-jakarta-senin-3032026-pemerintah-resmi-melarang-anak-di-bawah-u-1774857452595_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Pangeran Arab Mau Tarik Gunung Es dari Kutub ke Timur Tengah</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>Pangeran Arab Saudi berniat menarik gunung es dari kawasan kutub ke Timur Tengah supaya banyak air.</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811100335-37-758167/pangeran-arab-mau-tarik-gunung-es-dari-kutub-ke-timur-tengah</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/02/16/kapal-pemecah-es-italia-laura-bassi-membawa-para-ilmuwan-yang-meneliti-di-antartika-berlayar-di-dekat-teluk-wales-antartika-da_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Modus Penipuan Baru Incar Pegawai Kantoran, Rekening Langsung Ludes</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 11:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>Pelaku meminta uang melalui platform digital, termasuk WhatsApp dan email.</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811091406-37-758180/modus-penipuan-baru-incar-pegawai-kantoran-rekening-langsung-ludes</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/12/14/ilustrasi-1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Pencurian Terbesar Dalam Sejarah, Rp 500 Miliar Lenyap Seketika</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 10:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>Tahun 2026 mencatat pencurian kripto terburuk, dengan US$30 juta hilang dalam enam bulan. Total upaya pencurian mencapai US$107 juta.</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810185138-40-758078/pencurian-terbesar-dalam-sejarah-rp-500-miliar-lenyap-seketika</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/infografis-pencurian-terbesar-dalam-sejarah-1786362681628_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>5G Bakal Dibangun Habis-habisan di Penjuru RI Demi AI</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:19:00 +0700</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>Kementerian Komunikasi dan Digital percepat roadmap 5G untuk mendukung ekonomi digital berbasis AI.</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811091424-37-758154/5g-bakal-dibangun-habis-habisan-di-penjuru-ri-demi-ai</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/29/komdigi-1785319040479_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Ahli Jerman Ungkap Kesalahan Soal Danau Toba yang Sudah Lama Dipercaya</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>Penelitian terbaru menunjukkan letusan Gunung Toba 74.000 tahun lalu hanya menyebabkan pendinginan 0,5°C selama 18 bulan.</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811072943-37-758127/ahli-jerman-ungkap-kesalahan-soal-danau-toba-yang-sudah-lama-dipercaya</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2019/07/29/add2a486-d6e6-40c6-840b-7f20b7921565_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Karyawan Setia Ramai-Ramai Resign, Bos Google Malah Senang</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>Jeff Dean, kepala ilmuwan AI Google, meninggalkan perusahaan setelah 27 tahun untuk mendirikan Discovery Loop.</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811072517-37-758125/karyawan-setia-ramai-ramai-resign-bos-google-malah-senang</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/01/21/trump-inauguration-2_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>BMKG Beberkan Waktu Gerhana Matahari Total 12 Agustus Melintas di RI</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 07:05:36 +0700</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>Gerhana Matahari Total akan terjadi pada 12 Agustus 2026, namun tidak dapat dilihat dari Indonesia.</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811070249-37-758118/bmkg-beberkan-waktu-gerhana-matahari-total-12-agustus-melintas-di-ri</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/04/09/proses-gerhana-matahari-di-as-reutersandrew-kelly_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>ESR dan INA Garap Proyek Logistik Baru di Cikarang</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – ESR bersama Indonesia Investment Authority (INA) dan mitra pemodal lainnya memperluas investasi di sektor logistik Indonesia melalui pembangunan dua fasilitas logistik modern di Cikarang, Jawa Barat....</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlkx2416/esr-dan-ina-garap-proyek-logistik-baru-di-cikarang</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260811165200-323.png</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>1.300 Tukik Hasil Penukaran Botol Plastik Dilepas ke Laut Banyuwangi</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:30:11 +0700</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>Ribuan tukik kembali ke laut, kampanye sampah plastik ikut berperan.</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267326/1300-tukik-hasil-penukaran-botol-plastik-dilepas-ke-laut-banyuwangi</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/p2wadFqzNVqPOFAQyZNQSTQQPEg=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321490/original/043420700_1786443574-FOTO_2_-_Dorong_Pelestarian_Penyu__BCA_Bersama_100_Pelajar_Gelar_Edukasi_dan_Pelepasan_Tukik_di_Banyuwangi.jpeg</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Kejagung Periksa 12 Saksi Terkait Kasus Korupsi MBG</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:25:42 +0700</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>Salah satu saksi yang diperiksa merupakan Sekretaris Kepala Badan Gizi Nasional (BGN).</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267325/kejagung-periksa-12-saksi-terkait-kasus-korupsi-mbg</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Y9TE7xG2JA6_i8rqt0nVTPtgvjE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318584/original/056702000_1786106661-IMG_3040.jpg</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Alasan Kejagung Batal Pilih Rinaldi Umar jadi Direktur Penyidikan Jampidsus</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:04:29 +0700</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>Jaksa Agung melantik Saiful Bahri Siregar sebagai Dirdik Jampidsus.</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267296/alasan-kejagung-batal-pilih-rinaldi-umar-jadi-direktur-penyidikan-jampidsus</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/AdibnpaOlQuNR5w3Be37I-wjLuE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320653/original/012439900_1786362162-71890.jpg</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Kabut Asap dari Kalimantan Selimuti Kota Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:08:57 +0700</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>Kabut asap menyelimuti Kuala Lumpur pada Selasa 11 Agustus 2026 hingga mengurangi jarak pandang di sekitar Menara Merdeka dan kawasan gedung komersial. Kondisi ini terjadi saat otoritas Malaysia memperingatkan masyarakat mengenai peningkatan polusi udara yang berkaitan dengan kebakaran hutan dan lahan. Departemen Meteorologi Malaysia mengimbau warga terdampak untuk membatasi aktivitas di luar ruangan dan tetap berada di dalam ruangan. Kabut asap lintas batas dari Kalimantan Indonesia disebut turut memengaruhi kualitas udara di Kuala Lumpur.</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/photo/read/8267293/kabut-asap-dari-kalimantan-selimuti-kota-kuala-lumpur</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/gv17MWRqsJH9Ar3TrOT8nxqUv04=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321455/original/082537400_1786442447-mal1.jpg</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Pramono Respons Usulan Hapus Jalur Sepeda Jakarta</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:03:51 +0700</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>Pemprov DKI Jakarta akan membahas secara khusus keberadaan fasilitas sepeda di Jakarta.</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267295/pramono-respons-usulan-hapus-jalur-sepeda-jakarta</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/y8sjuWRcdBl2J5yNBe5R3uRmk6I=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321463/original/098770600_1786442544-aae5a694-28b2-47cc-9dff-974e32a8efc3.jpg</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Pramono Kecam Challenge Hafalan Alquran Berhadiah Miras di Ancol</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:57:50 +0700</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>Pramono meminta agar jajarannya mengambil tindakan tegas terkait kegiatan yang kini tengah menjadi sorotan publik tersebut.</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267286/pramono-kecam-challenge-hafalan-alquran-berhadiah-miras-di-ancol</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/BciATTOic643MhSI8OphV_W4u4o=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321452/original/026657000_1786442263-aae5a694-28b2-47cc-9dff-974e32a8efc3.jpg</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Pimpinan BGN Temui Jaksa Agung</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:54:53 +0700</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>Kejagung dan BGN sepakat bekerja sama.</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267279/pimpinan-bgn-temui-jaksa-agung</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/uDqIO0mL9gT_GHK6dNSTdp5wiAc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321444/original/024492100_1786441742-72452.jpg</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Reaksi Raja Juli Ditanya SGD 2.000 Hilang dari Amplop Bupati Kuansing</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:54:42 +0700</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>Raja Juli memilih menghindari pertanyaan dan hanya membahas reforma agraria.</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267277/reaksi-raja-juli-ditanya-sgd-2000-hilang-dari-amplop-bupati-kuansing</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/QjqXMyr542XnoOWmkkwylLS7D10=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5616746/original/005533300_1778202507-57316f55-f4f7-455d-9c12-7372ebfd6541.jpeg</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Dalih Gus Yaqut Didakwa Terima Rp 4,8 M dari Korupsi Kuota Haji</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 16:52:22 +0700</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>Gus Yaqut menyebut tudingan tersebut hanya didasarkan pada asumsi.</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267273/dalih-gus-yaqut-didakwa-terima-rp-48-m-dari-korupsi-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/dEJh5bHXLbWY-xjNqlv0hmU5sv0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321445/original/031700800_1786441788-IMG_20260811_141130_5.jpg</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>Tekno</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Meta: Orang Indonesia Tak Lagi Keberatan Dilayani AI di WhatsApp</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:46:09 +0700</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>Mayoritas pengguna internet di Indonesia kini tak lagi mempermasalahkan dilayani agen AI di WhatsApp, asalkan kebutuhan mereka bisa diselesaikan.</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>https://tekno.kompas.com/read/2026/08/11/17460077/meta--orang-indonesia-tak-lagi-keberatan-dilayani-ai-di-whatsapp</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Wp2Q9tgGDFWyQUQ-3XzDgPsEwtg=/448x439:3648x2573/1200x675/filters:watermark(data/photo/2026/01/30/697c816a7af9e.png,0,-0,1)/data/photo/2026/08/11/6a7ae3b9d3465.jpeg</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Gelar Wakil 1 Raka Jatim 2026 Dicabut Usai Viral Dugaan Paksa Aborsi</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:46:09 +0700</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>Gelar TFR sebagai Runner-up Raka Jatim 2026 dicopot oleh Disbudpar Jatim menyusul viralnya kasus paksaan aborsi.</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>https://surabaya.kompas.com/read/2026/08/11/172728878/gelar-wakil-1-raka-jatim-2026-dicabut-usai-viral-dugaan-paksa-aborsi</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/2x1O1bS-5jMPudic-BaGBVb4CfQ=/0x0:1012x675/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a79a6fd1da34.jpeg</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Evaluasi Subsidi Migas, Bahlil Pastikan Pertalite untuk Motor Tak Dibatasi</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:46:09 +0700</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>Bahlil mengatakan pemerintah belum menghitung besaran penghematan yang dapat diperoleh dari evaluasi dan pembatasan subsidi tersebut.</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/11/170954126/evaluasi-subsidi-migas-bahlil-pastikan-pertalite-untuk-motor-tak-dibatasi</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/-TSVvYp-k7CL4yE2at_4ezfLI7w=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/11/6a7af08d73cef.jpg</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I833"/>
+  <autoFilter ref="A1:I992"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$992</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1088</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I992"/>
+  <dimension ref="A1:I1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -47062,8 +47062,4521 @@
         </is>
       </c>
     </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Askrindo pertahankan peringkat kredit proyeksi stabil idAA+</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:35:05 +0700</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>PT Asuransi Kredit Indonesia (Persero) atau Askrindo mempertahankan peringkat kredit proyeksi stabil idAA+ (Stable ...</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689615/askrindo-pertahankan-peringkat-kredit-proyeksi-stabil-idaa-</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-15.11.54.jpeg</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Kortastipidkor Polri: Dedi Congor tersangka kasus gratifikasi</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:33:26 +0700</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>Korps Pemberantasan Tindak Pidana Korupsi (Kortastipidkor) Polri menyatakan bahwa Pejabat Fungsional Bea Cukai Madya, ...</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689612/kortastipidkor-polri-dedi-congor-tersangka-kasus-gratifikasi</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/08/kpk-periksa-ahmad-dedi-sebagai-saksi-2786367.jpg</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Dieng Culture Festival 28-30 Agustus 2026 usung "Spirit of Harmony"</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:31:34 +0700</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>Pergelaran Dieng Culture Festival (DCF) 2026 di kawasan Candi Dieng, Dieng Kulon, Kabupaten Banjarnegara, Jawa ...</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689611/dieng-culture-festival-28-30-agustus-2026-usung-spirit-of-harmony</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1002097496.jpg</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Program MBG pulau terluar di Simeuleu mulai Oktober 2026</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:31:29 +0700</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>Penanggung Jawab Badan Gizi Nasional (BGN) Kabupaten Simeulue Zainuddin menyatakan program Makanan Bergizi Gratis (MBG) ...</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689608/program-mbg-pulau-terluar-di-simeuleu-mulai-oktober-2026</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/sekolah-pulau-terluar.jpeg</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>BI catat kinerja penjualan eceran Juni 2026 stabil</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:30:54 +0700</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>Bank Indonesia (BI) mencatat kinerja penjualan eceran pada Juni 2026 masih relatif stabil.
+Dalam Survei Penjualan ...</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689607/bi-catat-kinerja-penjualan-eceran-juni-2026-stabil</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-05-13-at-11.55.22.jpeg</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Ketum PBNU tegaskan Muktamar ke-35 fokus program dan arah kepemimpinan</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:30:44 +0700</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>Ketua Umum Pengurus Besar Nahdlatul Ulama (PBNU) KH Yahya Cholil Staquf yang akrab disapa “Gus Yahya” ...</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689604/ketum-pbnu-tegaskan-muktamar-ke-35-fokus-program-dan-arah-kepemimpinan</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_1870.jpeg</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Balai TNGR: Kebakaran lahan di kawasan Rinjani telah padam</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:29:50 +0700</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>Balai Taman Nasional Gunung Rinjani (TNGR) Nusa Tenggara Barat (NTB) menyatakan kebakaran permukaan lahan di sekitar ...</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689600/balai-tngr-kebakaran-lahan-di-kawasan-rinjani-telah-padam</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1005763318.jpg</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Mendagri: Bayi lahir di luar faskes bisa dapat akta kelahiran digital</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:27:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>Menteri Dalam Negeri Muhammad Tito Karnavian memastikan layanan penerbitan akta kelahiran digital tetap bisa dinikmati ...</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689596/mendagri-bayi-lahir-di-luar-faskes-bisa-dapat-akta-kelahiran-digital</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000583719.jpg</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Bapas Jakpus minta masyarakat hapus stigma terhadap mantan napi</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:25:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>Balai Pemasyarakatan (Bapas) Jakarta Pusat meminta masyarakat menghapus stigma terhadap mantan narapidana yang sedang ...</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689595/bapas-jakpus-minta-masyarakat-hapus-stigma-terhadap-mantan-napi</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000836307.jpg</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>CATL dan BYD berlomba kembangkan baterai "solid-state" pada 2027</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:25:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>Dua produsen baterai kendaraan listrik (EV) terbesar China, CATL dan BYD, tengah berlomba mengembangkan teknologi ...</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5689588/catl-dan-byd-berlomba-kembangkan-baterai-solid-state-pada-2027</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/02/catl-factory.jpeg.jpg</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Hujan lebat mengancam, Beijing aktifkan respons kendali banjir</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:25:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>Pemerintah Beijing, China, pada Selasa mengaktifkan respons darurat pengendalian banjir Level II, level kedua ...</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689592/hujan-lebat-mengancam-beijing-aktifkan-respons-kendali-banjir</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000020_20260811_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Eks presiden Suriah Bashar Al-Assad divonis mati secara "in absentia"</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:25:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>Mantan presiden Suriah Bashar Al-Assad beserta adiknya, Maher Al-Assad, dijatuhi hukuman mati dalam ketidakhadiran atau ...</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689585/eks-presiden-suriah-bashar-al-assad-divonis-mati-secara-in-absentia</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/23/thumbs_b_c_81edbce52422bafd7fba35e612901db4.jpg</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR soroti penebangan pohon ilegal di lapang padel Bandung</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR RI Eddy Soeparno menyoroti kasus penebangan 10 pohon secara ilegal di Jalan LLRE Martadinata (Riau), ...</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689584/wakil-ketua-mpr-soroti-penebangan-pohon-ilegal-di-lapang-padel-bandung</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_9446.jpeg</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>KuCoin Raih Sertifikasi ISO 22301:2019, Perkuat Ketahanan Operasional</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:23:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>Di tengah pesatnya perkembangan aset digital dalam sistem keuangan global, kemampuan menjaga kesinambungan layanan ...</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689580/kucoin-raih-sertifikasi-iso-223012019-perkuat-ketahanan-operasional</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/KuCoin-Raih-ISO-223012019.jpg</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Kementerian Pariwisata dukung pengembangan Parapuar dan Golo Mori</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:22:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>Kementerian Pariwisata mendukung percepatan pengembangan daerah wisata Parapuar dan Golo Mori sebagai bagian dari ...</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689576/kementerian-pariwisata-dukung-pengembangan-parapuar-dan-golo-mori</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Menteri-Pariwisata-di-Parapuar.jpeg</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Menteri UMKM: Perpres transportasi digital beri manfaat ekonomi ojol</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:21:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>Menteri Usaha Mikro, Kecil, dan Menengah (UMKM) Maman Abdurrahman mengungkapkan Peraturan Presiden (Perpres) tentang ...</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689573/menteri-umkm-perpres-transportasi-digital-beri-manfaat-ekonomi-ojol</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1040.jpg</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>"Pertemuan teh susu" gantikan rapat formal warga lintas etnis Xinjiang</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:19:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>Di sebuah komunitas di Daerah Otonom Uighur Xinjiang, China barat laut, teh susu bukanlah sekadar minuman.    Saat ...</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689569/pertemuan-teh-susu-gantikan-rapat-formal-warga-lintas-etnis-xinjiang</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000022_20260811_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Beasiswa YPMAK siapkan SDM Mimika untuk bangun daerah</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:18:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>Program beasiswa Yayasan Pengembangan Masyarakat Amungme dan Kamoro (YPMAK) menyiapkan sumber daya manusia asal Mimika, ...</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689565/beasiswa-ypmak-siapkan-sdm-mimika-untuk-bangun-daerah</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-15.55.57_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Legislator: Soekarno Cup panggung talenta muda pesepak bola Indonesia</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:16:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>Anggota DPRD DKI Jakarta Hardiyanto Kenneth menilai turnamen sepakbola Soekarno Cup 2026 yang digelar di Jawa Timur ...</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689563/legislator-soekarno-cup-panggung-talenta-muda-pesepak-bola-indonesia</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-17.24.00.jpeg</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Indonesia bidik investasi AI via ASOCIO Digital Summit 2026 di Jakarta</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>Indonesia membidik investasi, transfer teknologi dan akses pasar industri digital melalui ASOCIO Digital &amp; AI ...</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689557/indonesia-bidik-investasi-ai-via-asocio-digital-summit-2026-di-jakarta</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/F5DE283F-B921-4A52-A45C-5CC6650B327D.jpeg</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Target inklusi keuangan tercapai lebih cepat</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>Akses masyarakat terhadap layanan keuangan terus meningkat, bahkan melampaui target yang ditetapkan dalam Rencana ...</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5689549/target-inklusi-keuangan-tercapai-lebih-cepat</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/20260811-Target-inklusi-keuangan-tercapai-lebih-cepat.jpg</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Papua kirim 30 ton kopra senilai Rp516 juta ke Surabaya</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:12:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Provinsi Papua melepas pengiriman 30 ton kopra hasil produksi petani Kabupaten Sarmi dengan nilai ...</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689513/papua-kirim-30-ton-kopra-senilai-rp516-juta-ke-surabaya</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PAPUA-KIRIM-30-TON-KOPRA-SENILAI-RP516-JUTA-KE-SURABAYA.jpg</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>KRP rawat tradisi dan perjuangan Reyog jadi warisan budaya dunia</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:07:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>Komunitas Reyog Ponorogo (KRP) terus menunjukkan komitmennya dalam menjaga, merawat, dan memperkenalkan kesenian Reyog ...</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689553/krp-rawat-tradisi-dan-perjuangan-reyog-jadi-warisan-budaya-dunia</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-16.56.57.jpeg</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Indocement wujudkan rumah layak untuk tukang yang mengabdi 51 tahun</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:07:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>PT Indocement Tunggal Prakarsa Tbk mewujudkan rumah layak bagi Sonijan (68), tukang bangunan di Lampung yang telah ...</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689552/indocement-wujudkan-rumah-layak-untuk-tukang-yang-mengabdi-51-tahun</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1003330149.jpg</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Menko PMK Pratikno bantah rumor dirinya minta mundur karena sakit</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:01:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Pembangunan Manusia dan Kebudayaan Pratikno membantah rumor yang menyebut dirinya ...</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689547/menko-pmk-pratikno-bantah-rumor-dirinya-minta-mundur-karena-sakit</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_5576.jpg</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Mentan ajak maba Unhas berinovasi untuk kedaulatan pangan</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:58:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>Menteri Pertanian sekaligus Ketua Umum Ikatan Alumni Universitas Hasanuddin Andi Amran Sulaiman, mengajak 10.401 ...</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689545/mentan-ajak-maba-unhas-berinovasi-untuk-kedaulatan-pangan</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0088.jpg</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Pemkot Palangka Raya perpanjang status tanggap darurat karhutla dan kekeringan hingga 8 September 2026</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:58:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>Petugas berupaya memadamkan kebakaran lahan di Petuk Katimpun, Palangka Raya, Kalimantan Tengah.</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5689543/pemkot-palangka-raya-perpanjang-status-tanggap-darurat-karhutla-dan-kekeringan-hingga-8-september-2026</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Status-Tanggap-Darurat-Karhutla-Dan-Kekeringan-Di-Palangka-Raya-110826-Aul-3.jpg</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Nusron sebut transformasi pelayanan pertanahan untuk tutup gerak mafia</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:58:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>Menteri Agraria dan Tata Ruang/Kepala Badan Pertanahan Nasional (ATR/BPN) Nusron Wahid mengatakan bahwa transformasi ...</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689539/nusron-sebut-transformasi-pelayanan-pertanahan-untuk-tutup-gerak-mafia</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260803_175241.jpg</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Bapas Jakpus catat kasus narkoba dominasi klien pembebasan bersyarat</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:55:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>Balai Pemasyarakatan (Bapas) Jakarta Pusat mencatat kasus narkotika menjadi jenis perkara yang paling banyak ...</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689535/bapas-jakpus-catat-kasus-narkoba-dominasi-klien-pembebasan-bersyarat</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000836313.jpg</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Unhas wakili Indonesia dalam Konferensi Perdamaian di Hiroshima</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:54:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin menjadi satu-satunya perguruan tinggi dari Indonesia yang terlibat dalam 6th University ...</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689532/unhas-wakili-indonesia-dalam-konferensi-perdamaian-di-hiroshima</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0055.jpg</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>BCA Syariah sebut emas masih jadi pilihan investasi jangka panjang</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:53:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>PT Bank BCA Syariah mengatakan emas masih menjadi instrumen investasi pilihan masyarakat untuk jangka ...</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689531/bca-syariah-sebut-emas-masih-jadi-pilihan-investasi-jangka-panjang</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_0507.jpeg</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Gubernur Jateng: Penanganan sampah butuh aksi bersama</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:53:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>Gubernur Jawa Tengah (Jateng) Ahmad Luthfi menyatakan penanganan sampah di wilayah tersebut membutuhkan aksi ...</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689528/gubernur-jateng-penanganan-sampah-butuh-aksi-bersama</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1002097440.jpg</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Maluku hadirkan replika rumah Laksamana Maeda sambut HUT ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:51:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Maluku menghadirkan replika rumah Laksamana Tadashi Maeda di Kota Ambon sebagai bagian dari ...</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689527/maluku-hadirkan-replika-rumah-laksamana-maeda-sambut-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Tanpa-Judul_2.jpg</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Pemkot Jaksel bagikan bendera Merah Putih jelang peringatan HUT RI</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:47:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Jakarta Selatan melakukan Gerakan Pembagian Bendera Merah Putih menjelang peringatan Hari Ulang Tahun ...</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689523/pemkot-jaksel-bagikan-bendera-merah-putih-jelang-peringatan-hut-ri</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001022944.jpg</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Airlangga: Satgas Debottlenecking selesaikan 124 aduan perusahaan</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:46:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Perekonomian Airlangga Hartarto menyebut Satgas Debottlenecking telah menyelesaikan 124 dari ...</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689519/airlangga-satgas-debottlenecking-selesaikan-124-aduan-perusahaan</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/779C2F71-F737-4EB6-AB41-D3E05C413485.jpeg</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Dirjen Bea Cukai sebut pembenahan kinerja instansinya mulai terlihat</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:45:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>Direktur Jenderal Bea dan Cukai Djaka Budi Utama menanggapi soal tenggat waktu yang diberikan Menteri Keuangan Purbaya ...</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689516/dirjen-bea-cukai-sebut-pembenahan-kinerja-instansinya-mulai-terlihat</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/e8bb8266-c29a-48d2-be88-451361dbd840.jpeg</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Mentan ancam cabut izin pelaku manipulasi harga pakan dan telur</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:43:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>Menteri Pertanian (Mentan) Andi Amran Sulaiman mengancam mencabut izin usaha pelaku manipulasi harga pakan dan telur ...</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689511/mentan-ancam-cabut-izin-pelaku-manipulasi-harga-pakan-dan-telur</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1347084.jpg</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Warga Pulau Seribu sambut transportasi laut dikelola Transjakarta</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:42:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>Warga Pulau Sabira, Kabupaten Kepulauan Seribu, Agung, menyambut positif rencana pengalihan pengelolaan transportasi ...</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689509/warga-pulauseribu-sambut-transportasi-laut-dikelola-transjakarta</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/20260811105212.jpeg</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>KJRI Kuching gelar rangkaian HUT ke-81 di Sarawak</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:41:42 +0700</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>Konsulat Jenderal Republik Indonesia (KJRI) Kuching bersama masyarakat Indonesia menggelar rangkaian kegiatan ...</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689508/kjri-kuching-gelar-rangkaian-hut-ke-81-di-sarawak</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/DSC08638_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>HIMKI bidik pengembangan kekuatan ekspor industri kerajinan di Jabar</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:41:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>Himpunan Industri Mebel dan Kerajinan Indonesia (HIMKI) membidik Kawasan Priangan, Jawa Barat (Jabar), sebagai sentra ...</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689504/himki-bidik-pengembangan-kekuatan-ekspor-industri-kerajinan-di-jabar</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Roadshow-Himki.jpg</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Rakor Konflik Agraria, Mendes Rekomendasikan Solusi Desa dalam Kawasan Hutan</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:31:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Chayyara Zulghifary</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>Menteri Yandri Susanto merekomendasikan solusi untuk konflik agraria di desa, melibatkan kementerian terkait dan memastikan pemulihan masyarakat.</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614179/rakor-konflik-agraria-mendes-rekomendasikan-solusi-desa-dalam-kawasan-hutan</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kemendes-1786447831798.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Bejat! Guru Ngaji di Serang Diduga Cabuli Bocah 9 Tahun</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:30:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>Seorang guru ngaji berinisial MS ditangkap karena mencabuli muridnya yang berusia 9 tahun. Pencabulan terjadi dua kali di rumah korban saat orang tua tidak ada.</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614178/bejat-guru-ngaji-di-serang-diduga-cabuli-bocah-9-tahun</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/21/ilustrasi-kekerasan-pada-anak_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Pramono Terima Banyak Masukan Jalur Sepeda Dihapus: Akan Dibahas Khusus</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:21:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>Warga Jakarta usulkan penghapusan jalur sepeda di jalan protokol. Gubernur Pramono Anung akan evaluasi penggunaan fasilitas sepeda untuk mengurangi kemacetan.</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614156/pramono-terima-banyak-masukan-jalur-sepeda-dihapus-akan-dibahas-khusus</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pramono-anung-beliadetikcom-1785834009810_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Wamensos Minta Bupati Mandailing Natal Kebut Pengajuan Sekolah Rakyat</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:20:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>Moch. Prima Fauzi</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>Wamensos Agus Jabo mendorong Pemkab Mandailing Natal percepat pembangunan Sekolah Rakyat dan pemutakhiran Data Tunggal Sosial untuk program pemerintah.</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614081/wamensos-minta-bupati-mandailing-natal-kebut-pengajuan-sekolah-rakyat</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/wamensos-agus-jabo-1786445183993_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Perusak Palang Kereta di Sleman Ternyata Juga Rusak Bendera di Bantul</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:18:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>Pradito Rida</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>Polisi selidiki perusakan tiang dan bendera merah putih di Bantul. Pelaku, mahasiswa luar Jogja, diduga dalam kondisi mabuk saat beraksi.</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614153/perusak-palang-kereta-di-sleman-ternyata-juga-rusak-bendera-di-bantul</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/03/21/teks-undang-undang-dasar-1945-pembukaan-hingga-maknanya_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Kejagung Gandeng PPATK Telusuri Uang TTPU di Kasus Febrie</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:17:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>Kejagung RI menggandeng PPATK untuk mengusut kasus TPPU mantan Jampidsus Febrie Adriansyah. Penelusuran aliran uang dilakukan dengan hati-hati dan profesional.</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614152/kejagung-gandeng-ppatk-telusuri-uang-ttpu-di-kasus-febrie</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/febrie-adriansyah-dibawa-ke-kejagung-untuk-diperiksa-tim-9-1786087110132_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>USU Buka Suara Terkait Dugaan Pengosongan Paksa Gereja Chapel</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:13:42 +0700</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Rechtin Hani Ritonga</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>Puluhan jemaat Gereja POUK Chapel USU histeris setelah pengosongan paksa. USU menjelaskan relokasi untuk renovasi demi peningkatan fasilitas ibadah.</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614145/usu-buka-suara-terkait-dugaan-pengosongan-paksa-gereja-chapel</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/gereja-di-usu-1786348148267_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Kepala BGN Minta Kejati dan Kejari Ikut Awasi Pelaksanaan Program MBG</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:11:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>Sudaryono meminta langsung kepada Jaksa Agung ST Burhanuddin agar kejati dan kejari ikut mendampingi dan mengawasi pelaksanaan program Makan Bergizi Gratis.</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614139/kepala-bgn-minta-kejati-dan-kejari-ikut-awasi-pelaksanaan-program-mbg</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/jajaran-bgn-menyambangi-kejagung-untuk-bersilaturahmi-sekaligus-meminta-pendampingan-dan-pengawasan-pelaksanaan-program-makan--1786440210989_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Pratikno Bantah Isu Mundur dari Menko PMK: Saya Lagi Bertugas di Bromo</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:05:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Firda Cynthia Anggrainy</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>Menko PMK Pratikno membantah rumor sakit dan mundur. Ia aktif mengikuti rapat penanganan kebakaran hutan di Bromo, memastikan tetap bertugas.</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614134/pratikno-bantah-isu-mundur-dari-menko-pmk-saya-lagi-bertugas-di-bromo</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/menko-pmk-pratikno-cek-karhutla-di-bromo-1786446259408_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Akta Kelahiran Kini Semakin Mudah, Langsung Terbit Setelah Bayi Lahir</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:59:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>Pemerintah Digitalisasi Penerbitan Akta Kelahiran, integrasi SIAK di Puskesmas Pasar Minggu. Proses penerbitan dokumen kependudukan lebih cepat &amp; efisien.</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614117/akta-kelahiran-kini-semakin-mudah-langsung-terbit-setelah-bayi-lahir</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kemenpan-rb-1786445973378_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Jaksa Agung Minta Kajati Beri Perhatian Kasus Terkait Hajat Hidup Masyarakat</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:56:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>Jaksa Agung ST Burhanuddin meminta para kajati memberikan perhatian khusus terhadap kasus-kasus yang menyangkut hajat hidup masyarakat.</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614111/jaksa-agung-minta-kajati-beri-perhatian-kasus-terkait-hajat-hidup-masyarakat</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/jaksa-agung-st-burhanuddin-meminta-para-kajati-memberikan-perhatian-khusus-terhadap-kasus-kasus-yang-menyangkut-hajat-hidup-ma-1786445750598_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Soekarno Cup 2026, Kenneth PDIP Dorong Talenta Muda Berani Bermimpi Besar</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:55:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>Politisi PDI Perjuangan Hardiyanto Kenneth apresiasi Soekarno Cup 2026, menekankan pentingnya pembinaan sepakbola untuk talenta muda Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614108/soekarno-cup-2026-kenneth-pdip-dorong-talenta-muda-berani-bermimpi-besar</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/politisi-pdi-perjuangan-hardiyanto-kenneth-mengapresiasi-diadakannya-soekarno-cup-2026-1786445694184_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Nusron soal Isu Reshuffle Usai 17 Agustus: Tak Elok Menteri Ngomong Itu</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:54:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>Menteri ATR/BPN Nusron Wahid menanggapi isu reshuffle kabinet. Dia menegaskan semua prerogatif presiden dan tak elok menteri membahas hal itu.</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614107/nusron-soal-isu-reshuffle-usai-17-agustus-tak-elok-menteri-ngomong-itu</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/menteri-atr-bpn-nusron-wahid-di-dpr-dwi-rahmawatidetik-1786445662574.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Rangkul Generasi Muda, PDIP Lantik Dewan Taruna Merah Putih</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:52:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>PDI Perjuangan melantik DPP Taruna Merah Putih untuk merangkul generasi muda. Fokus pada pendidikan politik dan mengubah persepsi politik menjadi lebih positif.</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614099/rangkul-generasi-muda-pdip-lantik-dewan-taruna-merah-putih</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/pdip-1786445540734_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Pigai Perintahkan Jajaran KemenHAM Bantu Kendalikan Dampak El Nino</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:47:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Chayyara Zulghifary</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>Menteri HAM Natalius Pigai perintahkan KemenHAM RI untuk berkoordinasi dengan pemerintah daerah dalam mengatasi dampak fenomena El Nino.</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614082/pigai-perintahkan-jajaran-kemenham-bantu-kendalikan-dampak-el-nino</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/menteri-hak-asasi-manusia-ham-natalius-pigai-1786445195449.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Mahasiswa Mabuk Jadi Tersangka Tabrak Lari Aiptu Asep, 2 Anggota TNI Jadi Saksi</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:46:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>Wisma Putra</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>Polisi menetapkan mahasiswa berinisial A sebagai tersangka tabrak lari yang menewaskan Aiptu Asep Suhara. Pelaku mengemudi dalam kondisi mabuk.</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614084/mahasiswa-mabuk-jadi-tersangka-tabrak-lari-aiptu-asep-2-anggota-tni-jadi-saksi</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/konferensi-pers-kasus-tabrak-lari-di-bandung-1786438422534_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Viral TPS Liar Cilincing, Pram Minta Pengelola Diberhentikan dan Disanksi</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:44:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>Hamparan sampah di Cilincing, Jakut ramai disorot publik. Gubernur DKI Pramono Anung meminta pihak swasta pengelola TPS itu diberhentikan dan diberi sanksi.</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614073/viral-tps-liar-cilincing-pram-minta-pengelola-diberhentikan-dan-disanksi</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/gunungan-sampah-liar-cemari-kawasan-cilincing-1778231251896_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Andre Rosiade Terima Aspirasi Serikat Pekerja PT Pos, Dorong Solusi Bersama Danantara</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:43:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>Andre Rosiade mengatakan Komisi VI DPR akan fasilitasi pertemuan antara serikat pekerja dan PT Pos Indonesia untuk membahas isu kesejahteraan dan hak pekerja.</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614071/andre-rosiade-terima-aspirasi-serikat-pekerja-pt-pos-dorong-solusi-bersama-danantara</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/komisi-iv-dpr-menerima-audiensi-serikat-pekerja-pt-pos-indonesia-1786443565666_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Pramono Kecam Challenge Hafalan Qur'an demi Miras: Nodai Kehidupan Keagamaan</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:42:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung mengecam promosi miras yang mengaitkan dengan hafalan Al-Qur'an. Ia minta tindakan tegas agar hal ini tidak terjadi lagi.</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614068/pramono-kecam-challenge-hafalan-quran-demi-miras-nodai-kehidupan-keagamaan</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/gubernur-dki-jakarta-pramono-anung-1786444893623_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Menkes Ungkap Ada 300 Ribu Pecandu Narkoba di Indonesia</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:41:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>Menkes Budi Gunadi Sadikin mengungkapkan 300 ribu pecandu narkoba di Indonesia, banyak di penjara. Ia mendorong rehabilitasi untuk pemulihan dan produktivitas.</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614064/menkes-ungkap-ada-300-ribu-pecandu-narkoba-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/07/rsppn-gandeng-china-kembangkan-pengobatan-tradisional-1759829199185_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Sinergi Kemensos dan INABA Entaskan Kemiskinan Melalui Sekolah Rakyat</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:40:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>Moch. Prima Fauzi</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial dan Universitas Indonesia Membangun (INABA) menandatangani MoU untuk memperkuat kolaborasi dalam pengentasan kemiskinan.</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614063/sinergi-kemensos-dan-inaba-entaskan-kemiskinan-melalui-sekolah-rakyat</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kemensos-kerja-sama-dengan-inaba-entaskan-kemiskinan-1786444816995_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Kejagung Hati-hati Usut Kasus Febrie: Yang Kita Hadapi Mantan Pendekar Hukum</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:39:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>Kapuspenkum Kejagung Anang Supriatna mengatakan pihaknya siap buka-bukaan di persidangan dalam membeberkan peran dari Febrie Adriansyah.</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614061/kejagung-hati-hati-usut-kasus-febrie-yang-kita-hadapi-mantan-pendekar-hukum</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/03/kapuspenkum-kejagung-anang-supriatna-1770098880799_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Polisi Pastikan Saepul Pemutilasi Pria di Depok Pelaku Tunggal</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:01:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>Polisi mengatakan Saepul pemutilasi pria adalah pelaku tunggal. Dipastikan tidak ada keterlibatan pihak lain dalam perkara ini</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8613723/polisi-pastikan-saepul-pemutilasi-pria-di-depok-pelaku-tunggal</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/polisi-menggelar-reka-ulang-kasus-mutilasi-pria-di-depok-tersangka-saepul-ikut-dihadirkan-1786424451846_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Prabowo Mau Alihkan Sebagian Keuntungan Danantara untuk Cadangan APBN</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:57:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya mengungkapkan rencana Prabowo untuk mengalihkan sebagian keuntungan Danantara sebagai cadangan APBN. Besaran kontribusi masih dibahas.</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8614116/prabowo-mau-alihkan-sebagian-keuntungan-danantara-untuk-cadangan-apbn</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/presiden-prabowo-subianto-saat-acara-peresmian-bendungan-di-lombok-1783667921544_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Eks Suami Aura Kasih Ungkap Alasan Balik ke Indonesia</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:07:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>Eryck Amaral kembali ke Indonesia untuk menghabiskan waktu bersama putrinya, Arabella.</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612488/eks-suami-aura-kasih-ungkap-alasan-balik-ke-indonesia</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/08/eryck-amaral-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Istana Siapkan Tambahan 3.400 Kursi untuk HUT ke-81 RI, Pendaftar Membeludak</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:32:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>Prasetyo Hadi mengumumkan penambahan 3.400 kursi undangan menyusul membeludaknya jumlah pendaftar yang mencapai lebih dari 336 ribu orang.</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867038/istana-siapkan-tambahan-3400-kursi-untuk-hut-ke-81-ri-pendaftar-membeludak</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oHgOnMumZx2eDe3eQfY_LcDLSRA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Prasetyo-Hadi-di-Kompleks-Parlemen-23072026.jpg</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>HFX International Berjangka Dukung E-Sports Kapolri Cup 2026, Siapkan Talenta Digital Indonesia</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:31:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>Dukungan HFX ini  menjadi bagian dari upaya perusahaan untuk ikut mendorong terciptanya ruang pengembangan bagi generasi muda</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/adv/7867037/hfx-international-berjangka-dukung-e-sports-kapolri-cup-2026-siapkan-talenta-digital-indonesia</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/r8IUS0wdW8s1PsNNxOkWUWcl_sA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/HFX-International-Berjangka-mendukung-E-Sports-Kapolri-Cup-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Mensesneg Ungkap Ada 25 Calon Dubes yang Diajukan Prabowo ke DPR</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:30:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>Presiden mengajukan 25 calon duta besar (dubes) Republik Indonesia, dalam surat presiden (surpres) yang telah dikirim ke DPR, pada Senin (10/8/2026).</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867036/mensesneg-ungkap-ada-25-calon-dubes-yang-diajukan-prabowo-ke-dpr</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/40n_NtqmQqryvyMyNWCtt6PdB-c=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Menteri-Sekretaris-Negara-Mensesneg-Prasetyo-Hadi-di-Istana-Kepresidenan-b.jpg</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Megawati Minta Taruna Merah Putih Jadi Ruang Terbuka Pendidikan Politik Generasi Muda</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:30:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>Megawati saat memimpin langsung pelantikan pengurus DPP TMP di Kantor DPP PDIP, Jalan Diponegoro, Menteng, Jakarta Pusat, Selasa (11/8/2026).</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867035/megawati-minta-taruna-merah-putih-jadi-ruang-terbuka-pendidikan-politik-generasi-muda</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/iPK6MfxQSoCui5NXOx8keM179iQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/tmp-megawati-4.jpg</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Fraksi PAN Kecam Promosi Minuman Keras Menggunakan Ayat Suci Alquran</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:29:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>PAN mengecam keras aksi promosi minuman keras yang diduga menggunakan ayat suci Al-Quran sebagai bagian dari tantangan berhadiah.</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867034/fraksi-pan-kecam-promosi-minuman-keras-menggunakan-ayat-suci-alquran</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/obyAq-9wBAJdeS3JzwLeLMisNxs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Anggota-DPR-RI-Verrell-Bramasta-saat-mengikuti-rapat-di-Komisi-X-Gedung-DPR-RI.jpg</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>AS Roma Menggeliat Lagi di Bursa Transfer, Giallorossi Datangkan Bek Baru</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:28:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>AS Roma mendatangkan bek asal Argentina, Nahuel Molina, dari Atletico Madrid senilai 18 juta Euro untuk memperkuat lini belakang mereka.</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867033/as-roma-menggeliat-lagi-di-bursa-transfer-giallorossi-datangkan-bek-baru</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/SRQdWanRop5LtrNKgXA80jLLrFg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/AS-Roma-Eldor-Shomurodov-74.jpg</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Kunci Gitar Lagu Kau Yang Utama - Syahrini: Kau Selalu Akan Menjadi yang Utama yang Bertakhta</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:28:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>Kunci gitar lagu Kau Yang Utama - Syahrini chord dasar mudah dimainkan: kau selalu akan menjadi yang utama  yang bertakhta di hatiku untuk selama.</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7867032/kunci-gitar-lagu-kau-yang-utama-syahrini-kau-selalu-akan-menjadi-yang-utama-yang-bertakhta</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MJbiAjzVSUq6jvpH4Ihys6ac5WI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Syahrini-tanggapi-isu-kontroversi-Cannes.jpg</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Kunci Gitar Lagu Karma - Cokelat: Selamat Tinggal Sayang</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:28:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>Berikut ini merupakan chord kunci gitar lagu Karma yang dipopulerkan oleh grup band Cokelat, dimainkan dari kunci C.</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7867031/kunci-gitar-lagu-karma-cokelat-selamat-tinggal-sayang</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/GphyHvOUni2z8m3vRko7OvuuWYQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Potret-seseorang-sedang-bermain-gitar-dengan-kunci-chord-dasar-mudah-dimainkan.jpg</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Kunci Gitar Lagu Back To Me - Kodaline: You've Got a Whole Lot of Life Left So Don't Give Up</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:27:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>Kunci gitar lagu Back To Me - Kodaline chord dasar mudah dimainkan: You've got a whole lot of life left So don't give up quite yet, come back to me.</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7867030/kunci-gitar-lagu-back-to-me-kodaline-youve-got-a-whole-lot-of-life-left-so-dont-give-up</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/eR3zla2C-eLuRKdct7nJlHf_pG0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Potret-gitar-akustik-untuk-kunci-chord-dasar-mudah-dimainkan-ifan-main-gitar.jpg</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Dalami Karakter Sophia di Film Seni Merayu Tuhan, Lutesha Sampai Tanya Teman soal Cinta Beda Agama</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:26:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>Aktris Lutesha Sadhewa sampai belajar ke teman-temannya yang pernah pacaran beda agama demi dalami karakter Sophia di Film Seni Merayu Tuhan.</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867029/dalami-karakter-sophia-di-film-seni-merayu-tuhan-lutesha-sampai-tanya-teman-soal-cinta-beda-agama</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/6QDU-A5OOgZKMGf3STeqKDQEYbs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Lutesha-1-12062026.jpg</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>“Enggak, Saya di Bromo”, Jawaban Pratikno Saat Isu Mundur Beredar</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:25:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>Isu Pratikno sakit dan mundur kembali beredar. Ia berada di Bromo, sementara Istana memastikan kabar tersebut tidak benar.</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867028/enggak-saya-di-bromo-jawaban-pratikno-saat-isu-mundur-beredar</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/u0NInv8a37nGL6w162QjOkUPogw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Menko-PMK-Pratiknotengah-di-Kawasan-Bromo.jpg</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Tiket Malaysia vs Vietnam Naik 66 Persen, FAM Jadi Sasaran Kritik Suporter</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:13:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>Kenaikan harga tiket semifinal Piala AFF 2026 Malaysia vs Vietnam menuai kritik suporter, di tengah misi memutus rekor buruk.</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867027/tiket-malaysia-vs-vietnam-naik-66-persen-fam-jadi-sasaran-kritik-suporter</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1WNe2Qaqla-dt4wi-y3ufRMaWz8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Duel-pemain-Malaysia-melawan-Laos-pada-pertandingan-lanjutan-Grup-F.jpg</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>50 Ide Nama Regu Pramuka Putra-Putri yang Unik dan Berkesan, Cocok untuk Kegiatan di Sekolah</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:09:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>Pemilihan nama regu dapat memperkuat identitas dan kekompakan anggota, sehingga nama yang unik dan bermakna cocok digunakan.</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867026/50-ide-nama-regu-pramuka-putra-putri-yang-unik-dan-berkesan-cocok-untuk-kegiatan-di-sekolah</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/jo-cczR-g1VXqTpl5fVdiPXq8q0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pemkot-malang-gelar-peringatan-hari-pramuka_20230819_130208.jpg</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Kota Sorong Rabu, 12 Agustus 2026: Mayoritas Wilayah Berawan</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:08:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>BMKG memprakirakan, cuaca berawan akan mendominasi langit Kota Sorong, Provinsi Papua Barat Daya, pada Rabu (12/8/2026).</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867025/prakiraan-cuaca-kota-sorong-rabu-12-agustus-2026-mayoritas-wilayah-berawan</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/T3-SSNlj5aoy3q2FcSs_HLhT1Ok=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-berawan-343r.jpg</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Sawah di Gresik Terancam Kekeringan, Ratusan Hektare Terdampak, Mentan: Tak Boleh Dianggap Remeh</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:07:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>Ratusan hektare sawah di Gresik terancam kekeringan. Mentan Amran turun langsung ke lokasi dan siapkan dua solusi jitu untuk para petani.</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867024/sawah-di-gresik-terancam-kekeringan-ratusan-hektare-terdampak-mentan-tak-boleh-dianggap-remeh</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/eLF2WvXGH06viVoEEOjZss2qkdU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/menteri-pertanian-Andi-Amran-Sulaiman-saat-kunjungan-ke-gresik-kemarau-kekeringan.jpg</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Aset BCA Syariah Tumbuh 17,2 Persen Jadi Rp20,7 Triliun hingga Juni 2026</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:04:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>Pertumbuhan juga terlihat dari laba setelah pajak atau profit after tax (PAT) yang naik 9,2 persen YoY menjadi Rp109 miliar.</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7867023/aset-bca-syariah-tumbuh-172-persen-jadi-rp207-triliun-hingga-juni-2026</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/M9XheOB5uguig5j8A2qbspXrE8E=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bca-syariah-002.jpg</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Tingkatkan Kesejahteraan Petani, Produktivitas Pertanian di Dua Wilayah Digenjot</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:00:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>PPI menyalurkan sarana pendukung kegiatan pertanian berupa 13 unit sprayer pestisida kepada tiga Gapoktan di kedua wilayah pertanian</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7867022/tingkatkan-kesejahteraan-petani-produktivitas-pertanian-di-dua-wilayah-digenjot</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/SXUeN1MHSU5FIX52c-5ssOmmTQA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/gapoktan-PPI-di-indramayu.jpg</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Sepanjang 2026, Bea Cukai Klaim Gagalkan Peredaran 1,2 Miliar Batang Rokok Ilegal</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:56:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>hingga 31 Juli 2026, Bea Cukai telah menggagalkan lebih dari 1 miliar batang rokok ilegal beredar untuk konsumen dalam negeri.</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7867021/sepanjang-2026-bea-cukai-klaim-gagalkan-peredaran-12-miliar-batang-rokok-ilegal</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ZtjSZdLN0na1W9fF4cZ3CaaG_X8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Dirjen-Bea-Cukai-Kemenkeu-Djaka-Budhi-Utama-saat-konpers-rokok-ilegal-di-priok.jpg</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Menpora Erick Thohir Apresiasi Dukungan Pramono Anung untuk FIFA ASEAN Cup 2026</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:55:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>Pengalaman Pramono dalam membantu penyelenggaraan FIFA U-17 World Cup 2023 di Indonesia menjadi salah satu modal penting</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867020/menpora-erick-thohir-apresiasi-dukungan-pramono-anung-untuk-fifa-asean-cup-2026</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/BLNOUsr0p6SbsFdC7cZ-6zvK9HU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Menteri-Pemuda-dan-Olahraga-Menpora-Erick-Thohir-1221.jpg</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Putrinya Dituding Selingkuhan Rizky Billar, Avi Basalamah: Ini Proses Hidup</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:52:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>Bersama sang suami, Ramzi, Avi berkomitmen untuk menjaga keharmonisan keluarga agar tetap berjalan normal di tengah proses hukum yang berjalan.</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867019/putrinya-dituding-selingkuhan-rizky-billar-avi-basalamah-ini-proses-hidup</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/sj4sFJY9tnZ0ZxQBKNLggAS_vJ8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Avi-Basalamah-1-11082026.jpg</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Jaringan Purnajual Xpeng Merambah Jawa Tengah Lewat Semarang</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:25:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>Israr Itah</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Jaringan layanan menjadi salah satu kebutuhan penting bagi merek otomotif yang tengah memperluas pasar. Semakin banyak dealer akan membuat konsumen lebih mudah memperoleh akses penjualan, perawatan, dan...</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlrra348/jaringan-purnajual-xpeng-merambah-jawa-tengah-lewat-semarang</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/xpeng-experience-service-center_260811182314-782.jpg</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Desa Tambakmekar Kembangkan Wisata Alam dan Budaya Lewat Pinus Kujang</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, SUBANG -- Desa Tambakmekar, Kecamatan Jalancagak, Kabupaten Subang, Jawa Barat, mengembangkan potensi wisata berbasis alam dan kearifan lokal melalui Festival Pinus Kujang 2026. Kegiatan yang digelar di kawasan Timman...</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlmzf416/desa-tambakmekar-kembangkan-wisata-alam-dan-budaya-lewat-pinus-kujang</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/kegiatan-festival-pinus-kujang-di-desa-tambakmekar-kecamatan-jalancagak_260811164118-858.jpeg</t>
+        </is>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Kejagung Ungkap Alasan Periksa Pegawai BI di Kasus TPPU Febrie</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:06:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>Kejagung terus mendalami kasus TPPU yang menjerat mantan Jampidsus Febrie Adriansyah.</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267373/kejagung-ungkap-alasan-periksa-pegawai-bi-di-kasus-tppu-febrie</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/2WEvQ2hmLFTijz9iyBipOx1Njqg=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318624/original/089072000_1786113401-IMG_3067.jpg</t>
+        </is>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Viral TPS Liar di Cilincing, Pramono Buka Suara</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:02:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>Gunungan sampah hampir setinggi rumah warga di Cilincing, Jakarta Utara, viral di media sossial.</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267371/viral-tps-liar-di-cilincing-pramono-buka-suara</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/7a5oAtHzUp_PhFOGhcN9vSJrY40=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321518/original/073330700_1786446145-eff6749f-e90e-491d-85af-deb70b9fe17a.jpg</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Seskab Teddy: 40 Persen Peserta Magang Nasional Langsung Direkrut Kerja</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:03:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>Salah satu peserta magang di Jakarta memperoleh penghasilan sekitar Rp 5,5 juta hingga Rp 5,7 juta per bulan.</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267372/seskab-teddy-40-persen-peserta-magang-nasional-langsung-direkrut-kerja</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/JkD3uD5S4C7mq_CyLE-cj09TyT0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321110/original/098803900_1786429030-email-attachment_2026_08_11_ariefhakim-at-klyid_ada-kuota-150-ribu-orang-magang-nasional-angkatan-2-dibuka-bertahap-hingga-oktober-2026_1000404420.jpg</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Pramono Yakin Transjakarta Bisa Kelola Transportasi Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:50:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>Tahun 2027, transportasi Kepulauan Seribu ditargetkan sepenuhnya dikelola Transjakarta.</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267355/pramono-yakin-transjakarta-bisa-kelola-transportasi-kepulauan-seribu</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/XfeHQTc02O4ALPSqS-HfpuOkmNo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5341440/original/005282500_1757313161-IMG_9023.jpeg</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>AHY Sebut Jakarta di Bawah Pramono Bisa Jadi Contoh, Ini Alasannya</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:58:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>Tantangannya bukan menghentikan urbanisasi, melainkan memastikan kota-kota memiliki standar, sumber daya, dan sistem logistik yang mampu menopang pertumbuhan.</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267363/ahy-sebut-jakarta-di-bawah-pramono-bisa-jadi-contoh-ini-alasannya</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/3BVkMgQGOEqyQmwPCKocWE51fuM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321513/original/078925900_1786445913-8dbdc105-046a-48f0-88eb-4a1babc96d88.jpg</t>
+        </is>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>DPR Minta Polisi Tindak Challenge Alquran Hadiah Miras: Umat Bisa Marah</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:43:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>Pasha menilai aparat perlu segera bertindak agar persoalan tersebut tidak memicu kemarahan masyarakat.</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267341/dpr-minta-polisi-tindak-challenge-alquran-hadiah-miras-umat-bisa-marah</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Fp5iC-vppn7dJSzwqGEBlrLz0gY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321055/original/059736500_1786425649-Jepretan_Layar_2025-08-11_pukul_12.15.34.jpg</t>
+        </is>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Vietnam dan Australia Makin Mesra, Sepakat Perkuat Kerja Sama Pertahanan</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:41:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>Pemerintah Australia dan Vietnam semakin mesra dan sepakat untuk memperdalam kemitraan strategis komprehensif.</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/global/read/2026/08/11/184100970/vietnam-dan-australia-makin-mesra-sepakat-perkuat-kerja-sama-pertahanan</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/sbCV6TSUbqSqLPp6cu7bf52vi3U=/0x0:1023x682/1200x675/filters:watermark(data/photo/2026/01/30/697c81ac46b81.png,0,-0,1)/data/photo/2025/08/20/68a53ceb248e6.jpg</t>
+        </is>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Pemerintah Luncurkan Digitalisasi Penerbitan Akta Lahir, Bayi Lahir Bisa Langsung Dapatkan Akta</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:41:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>Melalui layanan ini, akta kelahiran dapat diterbitkan secara otomatis dan dikirim secara daring sesaat setelah bayi lahir di fasilitas</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/18234501/pemerintah-luncurkan-digitalisasi-penerbitan-akta-lahir-bayi-lahir-bisa</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/OQinD-MsYkhl0oMkgVRNveSgMSM=/160x107:1440x959/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7b02396ad05.jpg</t>
+        </is>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Pernah Tuntaskan Full Marathon di Usia 60 Tahun, Ini Kisah Restu Didik Menekuni Lari</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:41:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>Mulai lari di usia 54 tahun, Restu Didik berhasil menuntaskan full marathon di usia 60 tahun dan kini tetap konsisten berlari.</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>https://lifestyle.kompas.com/read/2026/08/11/180500820/pernah-tuntaskan-full-marathon-di-usia-60-tahun-ini-kisah-restu-didik</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/FFQHUNEHPHTglA2_BAP8CGJfeVQ=/0x0:1280x853/1200x675/filters:watermark(data/photo/2026/01/30/697c817ed68bb.png,0,-0,1)/data/photo/2026/08/10/6a79c8cc14073.jpg</t>
+        </is>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I992"/>
+  <autoFilter ref="A1:I1088"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1088</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1177</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1088"/>
+  <dimension ref="A1:I1177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -51575,8 +51575,4191 @@
         </is>
       </c>
     </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Wagub Jatim dorong inovasi Umsura menjadi produk siap pakai</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:35:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>Wakil Gubernur Jawa Timur Emil Elestianto Dardak mendorong 38 inovasi teknologi tepat guna hasil Kuliah Kerja Nyata ...</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689724/wagub-jatim-dorong-inovasi-umsura-menjadi-produk-siap-pakai</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1347464.jpg</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Kementerian UMKM sebut ojol harus naik kelas dalam segala aspek</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:31:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>Kementerian Usaha Mikro Kecil dan Menengah (UMKM) menyebutkan driver atau pengemudi ojek online (ojol) harus ...</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689723/kementerian-umkm-sebut-ojol-harus-naik-kelas-dalam-segala-aspek</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1041.jpg</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Sumedang anggarkan minimal Rp100 miliar untuk perbaiki jalan pada 2027</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:27:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten (Pemkab) Sumedang, Jawa Barat, menyiapkan anggaran minimal Rp100 miliar untuk perbaikan ...</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689721/sumedang-anggarkan-minimal-rp100-miliar-untuk-perbaiki-jalan-pada-2027</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/492210.jpg</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Pramono segera bahas soal jalur sepeda di DKI</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:27:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung Wibowo bersama jajaran segera membahas jalur sepeda di sejumlah ruas jalan ...</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689720/pramono-segera-bahas-soal-jalur-sepeda-di-dki</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_6814.jpeg</t>
+        </is>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro jadi tuan rumah peluncuran MotoGP 2027</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:25:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Brasil, terpilih menjadi tuan rumah peluncuran musim MotoGP 2027 yang akan digelar di Pantai Botafogo ...</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689717/rio-de-janeiro-jadi-tuan-rumah-peluncuran-motogp-2027</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/01/14/antarafoto-francesco-bagnaia-juara-motogp-mandalika-2023-151023-as-7-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Pelatihan upacara HUT Ke-81 RI bagi pasien ODGJ</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:23:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>Pasien dengan gangguan jiwa (ODGJ) memberikan hormat kepada bendera Merah Putih saat pelatihan upacara di Yayasan ...</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5689716/pelatihan-upacara-hut-ke-81-ri-bagi-pasien-odgj</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Pelatihan-upacara-HUT-ke-81-RI-bagi-pasien-ODGJ-110826-ryl-5.jpg</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Kementerian UMKM dan OJK sepakat akselerasi akses pembiayaan UMKM</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:23:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>Kementerian Usaha Mikro Kecil Menengah (UMKM) dan Otoritas Jasa Keuangan (OJK) bersepakat melakukan akselerasi akses ...</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689715/kementerian-umkm-dan-ojk-sepakat-akselerasi-akses-pembiayaan-umkm</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-18.20.09.jpeg</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Aceh Besar percepat penanganan sawah terdampak kekeringan</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:23:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten Aceh Besar terus berupaya mengatasi kekeringan sawah milik petani akibat kemarau panjang yang ...</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689711/aceh-besar-percepat-penanganan-sawah-terdampak-kekeringan</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-18.55.54.jpeg</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Pramono minta Presiden Prabowo resmikan LRT Kelapa Gading-Manggarai</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:23:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung Wibowo mengaku dirinya sudah meminta kepada Presiden Prabowo Subianto untuk ...</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689709/pramono-minta-presiden-prabowo-resmikan-lrt-kelapa-gading-manggarai</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_6814.jpeg</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Kemenhub pacu modernisasi transportasi darat lewat kolaborasi global</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:22:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan (Kemenhub) memperkuat modernisasi transportasi darat melalui penguatan kolaborasi internasional ...</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689708/kemenhub-pacu-modernisasi-transportasi-darat-lewat-kolaborasi-global</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/E6442E4B-CB1E-4A96-99D8-94A8FF3089E5.jpeg</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Kemarau, 8,7 juta liter air telah disalurkan ke 23 daerah di Jabar</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:20:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) Jawa Barat (Jabar) menyebut mereka bersama tim gabungan telah menyalurkan sebanyak 8,7 ...</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689704/kemarau-87-juta-liter-air-telah-disalurkan-ke-23-daerah-di-jabar</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1002091225.jpg</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Pemprov NTB targetkan legalitas lahan segera tuntas di Gili Trawangan</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:18:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Nusa Tenggara Barat (NTB) menargetkan seluruh persoalan legalitas terkait status kepemilikan lahan ...</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689703/pemprov-ntb-targetkan-legalitas-lahan-segera-tuntas-di-gili-trawangan</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001449206.jpg</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Kejagung ungkap alasan Rinaldi Umar batal jadi Dirdik Jampidsus baru</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:18:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>Kepala Pusat Penerangan Hukum Kejaksaan Agung Anang Supriatna mengungkapkan alasan Rinaldi Umar batal diangkat ...</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689701/kejagung-ungkap-alasan-rinaldi-umar-batal-jadi-dirdik-jampidsus-baru</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000087747.jpg</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Rayakan Kemerdekaan, Pelajar di Manokwari ikuti lomba gerak jalan HUT RI</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:17:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>Pelajar mengikuti lomba gerak jalan dalam rangka HUT Ke-81 Republik Indonesia di Manokwari, Papua Barat.</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5689700/rayakan-kemerdekaan-pelajar-di-manokwari-ikuti-lomba-gerak-jalan-hut-ri</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Lomba-Gerak-Jalan-HUT-RI-Di-Manokwari-110826-ci-2.jpg</t>
+        </is>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Kemenekraf jadikan Tomohon kota florikultura berdaya saing global</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:15:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>Kementerian Ekonomi Kreatif menilai Kota Tomohon, Sulawesi Utara, sebagai destinasi wisata yang membawa identitas lokal ...</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689697/kemenekraf-jadikan-tomohon-kota-florikultura-berdaya-saing-global</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000595716.jpg</t>
+        </is>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Pemprov Sumbar siapkan penyitaan aset penunggak pajak air permukaan</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:14:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Provinsi Sumatera Barat menyiapkan langkah penyitaan aset terhadap perusahaan sawit yang menunggak ...</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689631/pemprov-sumbar-siapkan-penyitaan-aset-penunggak-pajak-air-permukaan</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMPROV-SUMBAR-SIAPKAN-PENYITAAN-ASET-PENUNGGAK-PAJAK-AIR-PERMUKAAN.jpg</t>
+        </is>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Gandeng Nintendo, RI dorong pengembang gim lokal mendunia</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:11:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Indonesia resmi menjajaki kerja sama dengan raksasa industri gim dunia, Nintendo, agar dapat ...</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689561/gandeng-nintendo-ri-dorong-pengembang-gim-lokal-mendunia</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_41_35_18.Still486.jpg</t>
+        </is>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Tanah Laut jadikan pengelolaan sampah penopang pariwisata</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:10:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten Tanah Laut (Pemkab Tala), Kalimantan Selatan, menjadikan pengelolaan sampah sebagai bagian dari ...</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689692/tanah-laut-jadikan-pengelolaan-sampah-penopang-pariwisata</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260810_171835.jpg</t>
+        </is>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>BKPRMI minta promosi miras dikaitkan hafalan Al Quran diusut</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:10:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>DPP Badan Komunikasi Pemuda Remaja Masjid Indonesia (BKPRMI) meminta pihak terkait untuk mengevaluasi konten promosi ...</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689689/bkprmi-minta-promosi-miras-dikaitkan-hafalan-al-quran-diusut</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/dok-ketum-bkprmi.jpg</t>
+        </is>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Tokyo menaikkan subsidi pembelian kendaraan listrik dan hibrida</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:07:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>Pemerintah Metropolitan Tokyo di Jepang menaikkan subsidi dalam pembelian kendaraan listrik dan hibrida guna ...</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5689688/tokyo-menaikkan-subsidi-pembelian-kendaraan-listrik-dan-hibrida</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/03/20/shutterstock_735265675.jpg</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Konsultan usulkan debitur skor SLIK 2 dipermudah peroleh kredit</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:06:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>Konsultan dan Perencana Keuangan Elvi Diana mengusulkan agar Otoritas Jasa Keuangan (OJK) maupun penyelenggara industri ...</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689684/konsultan-usulkan-debitur-skor-slik-2-dipermudah-peroleh-kredit</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/02/Sosialisasi-SLIK-OJK-230218-pf-3.jpg</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>BMW siapkan pembaruan untuk BMW seri 5 touring, akan diproduksi 2027</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:05:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>BMW saat ini tengah mempersiapkan pembaruan untuk BMW seri 5 touring yang diperkirakan bahwa produksi akan dimulai di ...</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5689680/bmw-siapkan-pembaruan-untuk-bmw-seri-5-touring-akan-diproduksi-2027</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/08/20/IMG_20240820_143100.jpg</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>BPK: Mahkamah Agung tindak lanjuti 96,65 persen rekomendasi BPK</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:03:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>Anggota I Badan Pemeriksa Keuangan (BPK) Nyoman Adhi Suryadnyana menyampaikan bahwa Mahkamah Agung telah ...</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689676/bpk-mahkamah-agung-tindak-lanjuti-9665-persen-rekomendasi-bpk</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-06-at-15.26.03.jpeg</t>
+        </is>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Diskop catat 174 KDKMP beroperasi di Bali didominasi gerai sembako</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:03:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>Dinas Koperasi dan UKM (Diskop UKM) Bali mencatat dari 716 Koperasi Desa Kelurahan Merah Putih (KDKMP) di Bali telah ...</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689675/diskop-catat-174-kdkmp-beroperasi-di-bali-didominasi-gerai-sembako</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/nilai-transaksi-kopdes-merah-putih-bali-310726-nhw-6.jpg</t>
+        </is>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>I.League pastikan larangan suporter tandang resmi dicabut musim depan</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:01:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>Operator kompetisi sepak bola Indonesia I.League memastikan kebijakan larangan suporter tandang sudah dicabut untuk ...</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689671/ileague-pastikan-larangan-suporter-tandang-resmi-dicabut-musim-depan</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/12/Persib-Bandung-Menang-Melawan-Persija-Jakarta-110126-DAN-01.jpg</t>
+        </is>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Dharma Jaya dorong kemandirian pangan di Jakarta, kurangi sapi impor</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:01:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>Perumda Dharma Jaya mendorong kemandirian pangan di Jakarta melalui penguatan produksi protein hewani dan pengembangan ...</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689669/dharma-jaya-dorong-kemandirian-pangan-di-jakarta-kurangi-sapi-impor</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000306724.jpg</t>
+        </is>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Trump dikawal sistem rudal Avenger saat main golf di New Jersey</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:01:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump mendapat pengawalan ketat dari sistem rudal darat-ke-udara (SAM) bertipe Avenger ...</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689667/trump-dikawal-sistem-rudal-avenger-saat-main-golf-di-new-jersey</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/07/19/2024-07-19T023529Z_224256324_HP1EK7J07712I_RTRMADP_3_USA-ELECTION-REPUBLICANS-CONVENTION.jpg</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Airlangga: Pertalite dan biodiesel RI masih aman meski gejolak global</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:01:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Perekonomian Airlangga Hartarto memastikan pasokan Pertalite dan biodiesel Indonesia tetap ...</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689663/airlangga-pertalite-dan-biodiesel-ri-masih-aman-meski-gejolak-global</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/779C2F71-F737-4EB6-AB41-D3E05C413485.jpg</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Perkuat diplomasi di Samudera Hindia, Kemlu luncurkan Satgas IORA 2026</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:01:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>Kementerian Luar Negeri meluncurkan “Satuan Tugas Indian Ocean Rim Association (IORA) Indonesia 2026”, ...</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689659/perkuat-diplomasi-di-samudera-hindia-kemlu-luncurkan-satgas-iora-2026</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/17864220736a7aa339335ea_IMG_9150_JPG.jpeg</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>USK siap perkuat kolaborasi pendidikan di Aceh</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:00:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>Universitas Syiah Kuala (USK) Banda Aceh menyatakan siap memperkuat kolaborasi dan sinergi dengan UIN Ar-Raniry dalam ...</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689655/usk-siap-perkuat-kolaborasi-pendidikan-di-aceh</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/DSC03268.JPG.jpeg</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>KSP kawal percepatan realisasi investasi dan hilirisasi nasional</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:59:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Staf Kepresidenan Jenderal TNI (Purn.) Prof. Dr. Dudung Abdurachman, menggelar pertemuan dengan Wakil ...</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689581/ksp-kawal-percepatan-realisasi-investasi-dan-hilirisasi-nasional</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_44_48_04.Still487.jpg</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Pramono kecam tantangan hafal Al Quran berhadiah miras di acara musik</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:58:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung Wibowo mengecam aksi tantangan hafalan Al Quran berhadiah minuman keras (miras) di ...</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689651/pramono-kecam-tantangan-hafal-al-quran-berhadiah-miras-di-acara-musik</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_6813.jpeg</t>
+        </is>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Menag: UIN Ar-Raniry Aceh harus jadi pusat peradaban Islam modern</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:57:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>Menteri Agama (Menag) Nasaruddin Umar menyatakan Universitas Islam Negeri (UIN) Ar-Raniry Banda Aceh harus ...</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689648/menag-uin-ar-raniry-aceh-harus-jadi-pusat-peradaban-islam-modern</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/menag.jpg</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Bupati Pati: Telur peternak lokal diprioritaskan penuhi kebutuhan SPPG</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:56:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>Pelaksana tugas (Plt) Bupati Pati Risma Ardhi Chandra menegaskan kebutuhan telur bagi Satuan Pelayanan Pemenuhan ...</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689645/bupati-pati-telur-peternak-lokal-diprioritaskan-penuhi-kebutuhan-sppg</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/TELUR-PATI-LOKAL-SPPG.jpg</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Laga Persija vs Persib digelar di Jakarta dengan kehadiran penonton</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:56:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>Direktur Utama I.League Ferry Paulus memastikan duel klasik antara Persija Jakarta versus Persib Bandung pada kompetisi ...</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689644/laga-persija-vs-persib-digelar-di-jakarta-dengan-kehadiran-penonton</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/11/persija-jakarta-kalahkan-persebaya-surabaya-2770671.jpg</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>KAI Sampaikan Permohonan Maaf atas Gangguan Access by KAI, Pemulihan Sistem Terus Dilakukan</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:55:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) menyampaikan permohonan maaf kepada seluruh pelanggan atas gangguan pada layanan ...</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689640/kai-sampaikan-permohonan-maaf-atas-gangguan-access-by-kai-pemulihan-sistem-terus-dilakukan</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Gangguan-Access-by-KAI.jpg</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Megawati lantik Taruna Merah Putih yang dipimpin Diah Pikatan Haprani</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:54:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>Ketua Umum DPP PDI Perjuangan Megawati Soekarnoputri melantik kepengurusan organisasi pemuda Dewan Pimpinan Pusat ...</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689639/megawati-lantik-taruna-merah-putih-yang-dipimpin-diah-pikatan-haprani</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001303745.jpg</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Dugaan penistaan agama di festival musik, sejumlah pihak dilaporkan</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:51:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>Tim Hukum Muslim melaporkan lima orang ke Polda Metro Jaya atas dugaan tindak pidana penistaan agama yang terjadi dalam ...</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689637/dugaan-penistaan-agama-di-festival-musik-sejumlah-pihak-dilaporkan</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000913553.jpg</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>JPU: 27 pihak dan 313 PIHK terima aliran dana dari kasus korupsi haji</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:50:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>Jaksa Penuntut Umum dari Komisi Pemberantasan Korupsi (KPK) Fahmi Idris menduga terdapat sebanyak 27 pihak dan 313 ...</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689636/jpu-27-pihak-dan-313-pihk-terima-aliran-dana-dari-kasus-korupsi-haji</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Yaqut-Cholil-Didakwa-Rugikan-Negara-Ratusan-Miliar-110826-Bay-3.jpg</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Dosen PTS gugat aturan pendanaan pendidikan tinggi ke MK</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:49:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>Seorang dosen perguruan tinggi swasta (PTS) mengajukan uji materi Undang-Undang Nomor 12 Tahun 2012 tentang Pendidikan ...</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689635/dosen-pts-gugat-aturan-pendanaan-pendidikan-tinggi-ke-mk</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000001970.jpg</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Kemendikdasmen perkuat kompetensi guru vokasi jawab dunia kerja</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:48:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Dasar dan Menengah (Kemendikdasmen) kembali membuka program Peningkatan Kompetensi bagi Pendidik ...</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689632/kemendikdasmen-perkuat-kompetensi-guru-vokasi-jawab-dunia-kerja</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000232710.jpg</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Kemenbud: Budaya pemersatu bangsa dan antar umat beragama</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:46:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>Staf Khusus Kementerian Kebudayaan (Kemenbud) Sri Eko Sriyanto Galgendu menegaskan bahwa kebudayaan memiliki peran ...</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689629/kemenbud-budaya-pemersatu-bangsa-dan-antar-umat-beragama</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/budaya.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Pemerintah pastikan tidak ada PPPK dirumahkan</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:43:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>Menteri Dalam Negeri Muhammad Tito Karnavian menyatakan pemerintah menyiapkan tiga skema untuk mendukung ...</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689628/pemerintah-pastikan-tidak-ada-pppk-dirumahkan</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Rapat-persiapan-pembangunan-rumah-layak-huni-di-Papua-150426-fzn-7.jpg</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>PBNU minta Kemenag lebih perketat izin pesantren guna cegah kekerasan</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:42:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>Pengurus Besar Nahdlatul Ulama (PBNU) meminta Kementerian Agama (Kemenag) agar lebih memperketat lagi perizinan ...</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689625/pbnu-minta-kemenag-lebih-perketat-izin-pesantren-guna-cegah-kekerasan</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_1871.jpeg</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Bareskrim Terbitkan 2 DPO Kasus Narkoba Five Stars Bali, Salah Satunya Owner</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:23:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>Dittipid Narkoba Bareskrim Polri menerbitkan dua DPO terkait peredaran narkoba di THM Five Stars, Denpasar. Ciri-ciri dan domisili pelaku diungkap.</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614268/bareskrim-terbitkan-2-dpo-kasus-narkoba-five-stars-bali-salah-satunya-owner</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/bareskrim-polri-mengungkap-peredaran-di-five-stars-denpasar-bali-dan-mengamankan-53-orang-1786079431797_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Gus Alex Didakwa Perkaya Diri Sendiri Rp 93,6 Miliar di Kasus Kuota Haji</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:17:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>Gus Alex didakwa korupsi kuota haji, merugikan negara Rp 622 miliar. Tiga terdakwa terlibat, termasuk mantan Menag Yaqut Cholil Qoumas.</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614250/gus-alex-didakwa-perkaya-diri-sendiri-rp-93-6-miliar-di-kasus-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/17/gus-alex-langsung-diborgol-eks-stafsus-yaqut-cholil-qoumas-resmi-ditahan-kpk-1773736846668_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Polisi Selidiki Kasus 36 Kambing Disembelih, Pelaku Diduga Lebih dari 1 Orang</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:13:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>Polres Serang selidiki pencurian 46 kambing yang disembelih di sawah. Korban alami kerugian Rp50 juta. Pelaku diduga lebih dari satu orang.</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614247/polisi-selidiki-kasus-36-kambing-disembelih-pelaku-diduga-lebih-dari-1-orang</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/tkp-pencurian-dan-penyembelihan-kambing-1786450353007_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Perusahaan Angkut Sampah Ke TPS Ilegal di Cilincing Didenda Rp 10 Juta</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:11:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>Pemprov DKI Jakarta denda PT SBCI Rp10 juta karena buang sampah ilegal di Cilincing. DLH tegaskan pengawasan akan diperkuat untuk mencegah pelanggaran serupa.</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614235/perusahaan-angkut-sampah-ke-tps-ilegal-di-cilincing-didenda-rp-10-juta</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/gunungan-sampah-liar-cemari-kawasan-cilincing-1778231251974_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Kakorlantas Ajak Driver Ojol Jadi Pelopor Keselamatan Lalu Lintas, Perkuat Sinergi</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:01:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Herianto Batubara</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>Kakorlantas Polri Irjen Wibowo bertemu komunitas ojol untuk memperkuat sinergi dalam keselamatan lalu lintas. Ojol diharapkan jadi mitra keselamatan di jalan.</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614227/kakorlantas-ajak-driver-ojol-jadi-pelopor-keselamatan-lalu-lintas-perkuat-sinergi</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kakorlantas-ajak-driver-ojol-jadi-pelopor-keselamatan-lalu-lintas-1786449624135_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>KP2MI Buka Pendaftaran Pelatihan Asta Mandala SMK Go Global Tahap Pertama</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>Kementerian P2MI buka pendaftaran Pelatihan SMK Go Global untuk 500.000 calon pekerja migran. Program ini siapkan generasi muda hadapi pasar kerja internasional</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614210/kp2mi-buka-pendaftaran-pelatihan-asta-mandala-smk-go-global-tahap-pertama</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kp2mi-1786449281276.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Jaksa Agung Minta Jajaran Jaga Integritas dan Hidup Sederhana</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:43:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>Jaksa Agung ST Burhanuddin melantik 15 Kajati, menekankan pentingnya integritas dan pola hidup sederhana. Dia juga mendorong transparansi dan pengawasan ketat.</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614198/jaksa-agung-minta-jajaran-jaga-integritas-dan-hidup-sederhana</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/13/jaksa-agung-st-burhanuddin-1773341038180_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Challenge Hafalan Qur'an Demi Miras Saat Konser Dilaporkan ke Polda Metro</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:38:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>Kasus promosi miras berkedok tantangan hafalan Al-Qur'an di konser The Sounds Project dilaporkan ke polisi. Penyelidikan sedang berlangsung.</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614190/challenge-hafalan-quran-demi-miras-saat-konser-dilaporkan-ke-polda-metro</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/tim-hukum-muslim-melaporkan-kasus-challenge-hafalan-quran-demi-miras-ke-polda-metro-jaya-1786448216677_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Purbaya &amp;amp; Bahlil Sepakat Harga BBM Subsidi Tak Bakal Naik</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:00:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil dan Menteri Keuangan Purbaya sepakat harga BBM subsidi tidak akan naik, meski harga minyak dunia fluktuatif.</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8614186/purbaya-bahlil-sepakat-harga-bbm-subsidi-tak-bakal-naik</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/04/purbaya-dan-bahlil-1759581063819_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Hoax Selingkuh dengan Asila Berujung Laporan, Rizky Billar Ingin Pelaku Jera</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:07:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>Rizky Billar mendampingi Lesti Kejora dan Asila Maisa dalam pemeriksaan di Polda Metro Jaya terkait laporan penyebaran berita bohong. Billar mau pelaku jera.</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613786/hoax-selingkuh-dengan-asila-berujung-laporan-rizky-billar-ingin-pelaku-jera</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rizky-billar-lesti-kejora-dan-asilla-1786424585636_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Potret Nikah Pebulutangkis Leo Rolly Carnando dengan Indah</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:33:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>Kabar soal pebulutangkis Leo Rolly Carnando dengan Indah Cahya Sari benar adanya. Indah membagikan foto nikah.</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8614126/potret-nikah-pebulutangkis-leo-rolly-carnando-dengan-indah</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/leo-rolly-carnando-1786446060203_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Dokter Ungkap Kanker Payudara dan Serviks Sering Berkembang Tanpa Gejala, Penting Skrining Rutin</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:31:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>Banyak pasien kanker payudara memeriksakan diri setelah menemukan benjolan dan merasa nyeri. Padahal belum tentu itu muncul saat kanker di tahap awal.</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7867061/dokter-ungkap-kanker-payudara-dan-serviks-sering-berkembang-tanpa-gejala-penting-skrining-rutin</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hFidTCUrtHAR90zYoVe4NCXEPUc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ILUSTRASI-KANKER-SERVIKS-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya Bongkar Peredaran Narkoba Lewat Ekspedisi di Jakarta Pusat, 7 Paket Sabu Disita</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:30:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menggagalkan peredaran narkotika jenis sabu yang diduga dikirim menggunakan modus paket ekspedisi di wilayah Jakarta Pusat.</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7867060/polda-metro-jaya-bongkar-peredaran-narkoba-lewat-ekspedisi-di-jakarta-pusat-7-paket-sabu-disita</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/PzAsSaUTeWBvvqRQGt7e-1rxfyA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/rilis-kasus-narkoba-polda-metro-jaya-e.jpg</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Hanya 20,14 Persen Penyandang Disabilitas Masuk Dunia Kerja, Karyanya Masih Terbatas</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:26:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>Data Kemenaker mencatat, dari sekitar 17 juta penyandang disabilitas usia produktif, hanya 20,14 persen yang masuk dalam angkatan kerja.</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867059/hanya-2014-persen-penyandang-disabilitas-masuk-dunia-kerja-karyanya-masih-terbatas</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oZltZiwirt3OEOiFCb00Np07XmY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Nurdini-Prihastiti-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Sidang Yaqut: KPK Ungkap Pengaturan Kuota Haji, USD1 Juta untuk Pansus dan Kerugian Rp622 Miliar</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:24:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>Yaqut Cholil Qoumas menyiapkan USD 1 juta untuk mempengaruhi hasil Pansus Angket Haji di DPR Tahun 2024.</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867058/sidang-yaqut-kpk-ungkap-pengaturan-kuota-haji-usd1-juta-untuk-pansus-dan-kerugian-rp622-miliar</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hQOLdcKo2PFpCgJrAjSiIBiOS6M=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Yaqut-Jalani-Sidang-Perdana-Kasus-Korupsi-Kuota-Haji_20260811_145757.jpg</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Beat Takeshi Kritik Pendaki Gunung Fuji, 2 WNI Jadi Sorotan karena Pakai Payung</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:24:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>Beat Takeshi kritik pendaki Gunung Fuji yang tak siap dan dukung aturan lebih tegas, termasuk biaya pendakian dan asuransi untuk operasi penyelamatan</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867057/beat-takeshi-kritik-pendaki-gunung-fuji-2-wni-jadi-sorotan-karena-pakai-payung</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/W80YeOER7fokSbD-Vo1YrMfQISc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/orangpayung11111.jpg</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>3 Alasan Rodri Ragu ke Real Madrid hingga Pilih Barcelona</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:24:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>Rodri dikabarkan batal ke Real Madrid setelah memiliki sejumlah keraguan. Barcelona kemudian datang dan selangkah lagi mendapatkan sang gelandang.</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867056/3-alasan-rodri-ragu-ke-real-madrid-hingga-pilih-barcelona</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/_VpOqU99lj-Oz2bEhTHowlCuKvY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Rodri-Raih-Ballon-dOr_20241029_113921.jpg</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Dana PTN dan PTS Dinilai Belum Adil, Riset Dosen Terkendala Anggaran</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:22:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>Dosen PTS menggugat aturan pendanaan pendidikan tinggi ke MK setelah anggaran riset disebut semakin terbatas.</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867055/dana-ptn-dan-pts-dinilai-belum-adil-riset-dosen-terkendala-anggaran</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oAcRRDSjQ7nHVcXmoaAOIcOmd4Q=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/sidang-uji-materi-Undang-Undang-Nomor-12-Tahun-2012-UU-Pendidikan-Tinggi-Mahkamah-Konstitusi-MK.jpg</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>KPK Buka Suara Soal Winda Lorenza, Sempat Dipanggil Untuk Telusuri Aliran Uang Korupsi Bea Cukai</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:19:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>KPK akhirnya buka suara mengenai sosok Winda Lorenza Gowasa yang tewas penuh kejanggalan di Medan, Sumatera Utara.</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867054/kpk-buka-suara-soal-winda-lorenza-sempat-dipanggil-untuk-telusuri-aliran-uang-korupsi-bea-cukai</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/E0yUvTRc5-LVa7G_JqpQdDfSl7M=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Juru-Bicara-KPK-Budi-Prasetyo-2742026.jpg</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban Matematika Kelas 5 SD Halaman 197 Kurikulum Merdeka Bab 7, Membuat Segitiga</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:19:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>Kunci jawaban Matematika Kelas 5 SD halaman 197 membahas kelompok sedotan yang bisa dan tidak bisa membentuk segitiga.</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7867053/kunci-jawaban-matematika-kelas-5-sd-halaman-197-kurikulum-merdeka-bab-7-membuat-segitiga</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1JPKJGa96_InI21Y0aEE8NCU4z4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/SISWA-SD-BELAJAR-20.jpg</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Viral Challenge Hafalan Surat Alquran Berhadiah Miras, YKMI Desak Cabut Izin Edar</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:17:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>YKMI menilai promosi tersebut melecehkan agama dan mendesak pemerintah serta aparat mengambil tindakan.</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867052/viral-challenge-hafalan-surat-alquran-berhadiah-miras-ykmi-desak-cabut-izin-edar</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/WO5gUct79rm2w14vW8VLt3rKtHQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ferry-Irawan-YMKI.jpg</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Stres hingga Depresi Gegara Skripsi? Psikolog Beri Saran untuk Mahasiswa Tingkat Akhir</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:16:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>Psikolog menyarankan mahasiswa menghadapi stres skripsi dengan fokus pada hal yang bisa dikontrol dan tidak ragu mencari bantuan.</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7867051/stres-hingga-depresi-gegara-skripsi-psikolog-beri-saran-untuk-mahasiswa-tingkat-akhir</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/om_yS8jzPPdVEHqZCFP9CIRqb1E=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PSiswa-MAN-3-Padang-Ledakkan-Bom-di-Sekolah-Gegara-Di-bully-Psikolog-Tegaskan-Dia-Bukan-Anak-Jahat.jpg</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban Matematika Kelas 5 SD Halaman 196 Kurikulum Merdeka, Eksplorasi Membuat Segitiga</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:15:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>Kunci jawaban Matematika Kelas 5 SD halaman 196 membahas cara menentukan tiga panjang sisi yang dapat membentuk segitiga.</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7867050/kunci-jawaban-matematika-kelas-5-sd-halaman-196-kurikulum-merdeka-eksplorasi-membuat-segitiga</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1JPKJGa96_InI21Y0aEE8NCU4z4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/SISWA-SD-BELAJAR-20.jpg</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Flores Besok Rabu 12 Agustus 2026: Labuan Bajo dan Ende Cerah hingga Cerah Berawan</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:15:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>Berikut detail prakiraan cuaca di beberapa kota terkenal di Flores untuk Rabu (12/8/2026) berdasarkan prakiraan BMKG:</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867049/prakiraan-cuaca-flores-besok-rabu-12-agustus-2026-labuan-bajo-dan-ende-cerah-hingga-cerah-berawan</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/L57Bkzw0Fujr2ABxB4iWPb-V7SE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/danau-tiwusora-di-kabupaten-ende-flores-ntt.jpg</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Destry Damayanti Calon Gubernur BI, Anggota DPR Eric Hermawan: Kemampuannya Tak Perlu Diragukan</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:59:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>Eric Hermawan, menilai sosok Destry Damayanti sebagai figur yang pas untuk menjabat sebagai Gubernur Bank Indonesia (BI) definitif.</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867048/destry-damayanti-calon-gubernur-bi-anggota-dpr-eric-hermawan-kemampuannya-tak-perlu-diragukan</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/gMctDY3Den6hm7aAheqS9w41TQE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Destry-Damayanti-di-Istana-32102.jpg</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Penerapan K3 ke Pekerja Sawit Berdampak Positif ke Produktivitas Industri</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:56:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>implementasi K3 harus diterapkan secara menyeluruh di seluruh rantai industri sawit mulai dari perkebunan hingga pabrik pengolahan</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7867047/penerapan-k3-ke-pekerja-sawit-berdampak-positif-ke-produktivitas-industri</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/T1sIpuSqdVF6MvUOF5E5MjDnhQE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penerapan-standar-keselamatan-dan-kesehatan-kerja-K3-di-perkebunan.jpg</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Gimik Bermuatan SARA Dinilai Bisa Picu Perpecahan, Anggota DPR Minta Polisi Bertindak Tegas</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:56:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>Abdullah menyoroti maraknya gimik di ruang publik dan media sosial yang dinilai merendahkan suku, agama, ras, dan antargolongan (SARA).</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867046/gimik-bermuatan-sara-dinilai-bisa-picu-perpecahan-anggota-dpr-minta-polisi-bertindak-tegas</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/S7niCuPoL-On6Ah57kIk9Zp3z9c=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Anggota-DPR-RI-Abdullah-Soroti-Kasus-Brimob-Lindas-Ojol.jpg</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Habis Indonesia Gantian Malaysia, Kans Vietnam Ulangi Pembantaian di Piala AFF 2026</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:55:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>Vietnam diprediksi bakal menyingkirkan Malaysia dengan cara memalukan di semifinal Piala AFF 2026.</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867045/habis-indonesia-gantian-malaysia-kans-vietnam-ulangi-pembantaian-di-piala-aff-2026</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/u8AMguqjsVPB9v5yd1u6daLPdnU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Timnas-Indonesia-Dicukur-Timnas-Vietnam-3-0_20260804_070349.jpg</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Kronologi Penyelamatan Ibu dan Bayi 6 Bulan Ditemukan Hidup di Balik Reruntuhan Gempa Cali Kolombia</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:51:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>Tim SAR menemukan ibu dan bayinya yang berusia enam bulan masih hidup di balik reruntuhan bangunan akibat gempa di Cali, Kolombia</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867044/kronologi-penyelamatan-ibu-dan-bayi-6-bulan-ditemukan-hidup-di-balik-reruntuhan-gempa-cali-kolombia</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hzWx5otJiYfuvi7E1WBaYnCcYqs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KONDISI-KOTA-PEREIRA-SETELAH-GEMPA-GUNCANG-KOLOMBIA.jpg</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Purbaya Targetkan Pembenahan Bea Cukai hingga September 2026, Djaka Budhi Minta Bantuan Masyarakat</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:50:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>Djaka mengkaui, pembenahan terhadap internal Bea Cukai akan maksimal apabila ada peran dari stakeholder lainnya.</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7867043/purbaya-targetkan-pembenahan-bea-cukai-hingga-september-2026-djaka-budhi-minta-bantuan-masyarakat</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ZtjSZdLN0na1W9fF4cZ3CaaG_X8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Dirjen-Bea-Cukai-Kemenkeu-Djaka-Budhi-Utama-saat-konpers-rokok-ilegal-di-priok.jpg</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Peringatan Dini 6 Ibu Kota Pulau Jawa Besok Rabu 12 Agustus: Jakarta Cerah, Jogja Udara Kabur</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:49:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>Peringatan dini BMKG di 6 Ibu Kota di Pulau Jawa. Mulai dari Jakarta, Bandung, hingga Semarang pada (12/8/2026).</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867042/peringatan-dini-6-ibu-kota-pulau-jawa-besok-rabu-12-agustus-jakarta-cerah-jogja-udara-kabur</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Ew22ZWpIXWs0i0Fg5jOcsd0PKDk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-cerah-sekali.jpg</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Menteri UMKM Maman Janjikan Perpres Ojol Segera Terbit</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>Novina Putri Bestari</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>Menteri UMKM Maman Abdurrahman menjanjikan Perpres Ojol akan segera terbit</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811191928-37-758413/menteri-umkm-maman-janjikan-perpres-ojol-segera-terbit</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/menteri-umkm-maman-abdurrahman-saat-doorstop-usai-acara-umkm-finance-summit-2026-dengan-tema-penguatan-akses-pembiayaan-dan-ek-1786422817800_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Petaka Baru Datang dari China, Satu Dunia Terancam Jadi Korban</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>Microsoft mengungkap kelompok peretas China, Storm-1175, yang menyebarkan ransomware baru, StormEncryptor. Simak!</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811120046-37-758220/petaka-baru-datang-dari-china-satu-dunia-terancam-jadi-korban</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/09/11/siapakah-bjorka-hacker-yang-bikin-pemerintah-ri-ketar-ketir_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Batu Dipakai Ganjal Pintu, Ternyata Harta Karun Rp 20 Miliar</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>Seorang nenek di Romania menemukan batu 3,5 kg yang ternyata adalah amber raksasa bernilai Rp 20 miliar.</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811145624-37-758308/batu-dipakai-ganjal-pintu-ternyata-harta-karun-rp-20-miliar</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/09/12/bongkahan-amber-seberat-35-kilogram-itu-merupakan-potongan-rumanit-terbesar-yang-pernah-ditemukan_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Jadi Bangunan Cerdas, RS dan Pabrik Ini Mampu Tekan Cost dan Downtime</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:57:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>Khoirul Anam</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>Indonesia menargetkan penurunan emisi gas rumah kaca hingga 43% pada 2030, salah satunya lewat penerapan Bangunan Gedung Cerdas.</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260811171626-37-758386/jadi-bangunan-cerdas-rs-dan-pabrik-ini-mampu-tekan-cost-downtime</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/smc-rumah-sakit-telogorejo-semarang-1786445781245_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>Rapat dengan Bahlil, Purbaya Janji Pembatasan Pembelian Pertalite Dilakukan Bertahap</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:09:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Menteri Energi dan Sumber Daya Mineral (ESDM) dan Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa melaksanakan pertemuan untuk membahas mekanisme penyaluran BBM bersubsidi. Purbaya mengatakan, pengendalian subsidi bahan...</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjltrs490/rapat-dengan-bahlil-purbaya-janji-pembatasan-pembelian-pertalite-dilakukan-bertahap</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/096319300-1780650844-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Bahlil Temui Purbaya Bahas Pembatasan Pembelian Pertalite</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:03:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menemui Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa. Pertemuan itu membahas penyaluran subsidi bahan bakar minyak (BBM) agar tepat...</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlti1490/bahlil-temui-purbaya-bahas-pembatasan-pembelian-pertalite</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/006092900-1760884175-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Polisi Tangkap 2 Pelaku Penyekapan Lansia Ngaku Anggota KPK</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:38:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>Polisi mengamankan dua pria yang diduga terlibat dalam tindak pidana pencurian dengan pemberatan disertai penyekapan terhadap lansia di Tangsel.</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267437/polisi-tangkap-2-pelaku-penyekapan-lansia-ngaku-anggota-kpk</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/EvCoV8tn_M-VP-PCM52zvLmQyM4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321574/original/082974800_1786451876-IMG-20260811-WA0026.jpg</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Sempat Dikira Gantung Diri, Wanita di Tangerang Ternyata Dibunuh Kekasih</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:32:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>Korban ditemukan dalam kondisi tergantung yang awalnya diduga sebagai bunuh diri.</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267431/sempat-dikira-gantung-diri-wanita-di-tangerang-ternyata-dibunuh-kekasih</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/elDNxj19Ao1xJh5eehIKyL9IihU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/849467/original/025285500_1428837125-Ilustrasi-pembunuhan-wanita-2.jpg</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Fokus Rangkul Generasi Muda, PDIP Lantik Taruna Merah Putih</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:03:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>PDI Perjuangan menegaskan fokus partai dalam merangkul generasi muda.</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267415/fokus-rangkul-generasi-muda-pdip-lantik-taruna-merah-putih</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/m48HfJYPaJEZKeA4JZOFEYcJ3b0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321561/original/095047900_1786449805-DSC02530.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Pakar Usul RUU Perampasan Aset Diubah Jadi RUU Melindungi Aset</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:51:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>RUU Perampasan Aset berpotensi memberikan kewenangan besar kepada negara untuk mengambil alih hak milik pribadi.</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267408/pakar-usul-ruu-perampasan-aset-diubah-jadi-ruu-melindungi-aset</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/P0blfdNw0Xxs6u842ruS_IXQRUQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/8137362/original/092189600_1780989441-RUU_Polri.jpeg</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Tantangan Hafalan Alquran Berhadiah Miras Dilaporkan ke Bareskrim</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:36:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>Kegiatan berupa challenge atau tantangan yang melibatkan Alquran dinilai bermasalah dari sisi etika dan moral.</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267399/tantangan-hafalan-alquran-berhadiah-miras-dilaporkan-ke-bareskrim</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/iHD_QgF-uP8FSa50xdyMeQkNYRU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321537/original/088033500_1786448173-IMG_2876.jpeg</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Harga Minyak Mentah Melonjak 2 Persen Usai Kesepakatan Damai AS-Iran Kian Buntu</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:42:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>Pada Senin kemarin, pemerintahan Trump memperpanjang penangguhan undang-undang pengiriman.</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/11/194216126/harga-minyak-mentah-melonjak-2-persen-usai-kesepakatan-damai-as-iran-kian</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/eX6M2TeyVC73j-CvAId9vaXzdrA=/0x0:1496x997/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/02/28/69a26f1c57fb7.jpg</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>Gelombang Tinggi Terjang Pesisir Kebumen, Puluhan Warung dan Kios Rusak</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:42:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>Berikut dampak gelombang tinggi di kawasan pesisir selatan Kabupaten Kebumen, Jawa Tengah, pada Selasa (11/8/2026).</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/11/192102678/gelombang-tinggi-terjang-pesisir-kebumen-puluhan-warung-dan-kios-rusak</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/jEQBgdw-vBS65LR6lKzvHD_J0oA=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7b095514f9b.jpg</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Relawan Sound Horeg Temui Jokowi di Solo, Siap Kawal Gibran di Pilpres 2029</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:42:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>'Arahan dari beliau suruh menunggu dulu. Arahannya begitu,' ungkapnya.</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/11/190029878/relawan-sound-horeg-temui-jokowi-di-solo-siap-kawal-gibran-di-pilpres-2029</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/nnUbOMKlD9faKR9GqE97AVjun5A=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7b0a34d3f3f.jpg</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1088"/>
+  <autoFilter ref="A1:I1177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1279</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1177"/>
+  <dimension ref="A1:I1279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -55758,8 +55758,4802 @@
         </is>
       </c>
     </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Gamba Osaka dan CAHN lolos ke fase liga ACL Elite</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:09:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>Gamba Osaka dan Cong An Hanoi FC (CAHN) lolos ke fase liga AFC Champions League (ACL) Elite wilayah Timur setelah ...</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689932/gamba-osaka-dan-cahn-lolos-ke-fase-liga-acl-elite</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/image-39.jpg</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Mentan percepat bantuan pompa dan sumur dangkal untuk petani di Gresik</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:09:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>Menteri Pertanian Andi Amran Sulaiman mempercepat penanganan kekeringan di Kabupaten Gresik, Jawa ...</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689929/mentan-percepat-bantuan-pompa-dan-sumur-dangkal-untuk-petani-di-gresik</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-21.01.17.jpeg</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Deltras FC datangkan dua pemain perkuat skuad di musim 2026/2027</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:05:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>Deltras FC Sidoarjo mendatangkan penjaga gawang Samuel Reimas dan gelandang senior Rizky Pellu untuk memperkuat ...</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689925/deltras-fc-datangkan-dua-pemain-perkuat-skuad-di-musim-2026-2027</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/ANTARA-2026-08-11T163721.534.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Petugas berjibaku padamkan kebakaran lahan di Kertapati Palembang</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:05:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>Api membakar lahan di Karya Jaya, Kecamatan Kertapati, Palembang, Sumatera Selatan.</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5689924/petugas-berjibaku-padamkan-kebakaran-lahan-di-kertapati-palembang</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Upaya-pemadaman-kebakaran-lahan-di-Kertapati-Palembang-110826-Lmo-5.jpg</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Manggala Agni masih berjibaku padamkan karhutla di Rohil dan Bengkalis</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:04:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>Manggala Agni Daerah Operasi Dumai, Provinsi Riau, masih berjibaku memadamkan kebakaran hutan dan lahan (karhutla) ...</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689923/manggala-agni-masih-berjibaku-padamkan-karhutla-di-rohil-dan-bengkalis</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000705378.jpg</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Menkop mendorong Agrinas bangun ekosistem sawit seperti Felda Malaysia</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:03:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>Menteri Koperasi (Menkop) Ferry Juliantono mendorong PT Agrinas Palma Nusantara (Persero) mengembangkan ekosistem ...</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689920/menkop-mendorong-agrinas-bangun-ekosistem-sawit-seperti-felda-malaysia</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/tempImageRyzPec.jpg</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>KPK ungkap konstruksi korupsi kuota Haji, negara rugi Rp622 mililar</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:01:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>ANTARA - Komisi Pemberantasan Korupsi (KPK) membeberkan konstruksi dugaan tindak pidana korupsi pengalokasian kuota ...</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689895/kpk-ungkap-konstruksi-korupsi-kuota-haji-negara-rugi-rp622-mililar</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KPK-UNGKAP-KONSTRUKSI-KORUPSI-KUOTA-HAJI-KERUGIAN-NEGARA-RP622-M.jpg</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Kementan optimalkan rumah pompa untuk 600 hektare sawah di Lamongan</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:58:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian mengoptimalkan penggunaan rumah pompa di salah satu lokasi di Kabupaten Lamongan yang ...</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689915/kementan-optimalkan-rumah-pompa-untuk-600-hektare-sawah-di-lamongan</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-20.27.36.jpeg</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Jaksa sebut Yaqut siapkan 1 juta dolar AS pengaruhi Pansus Haji</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:58:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>Jaksa Penuntut Umum Komisi Pemberantasan Korupsi (KPK) menyebut mantan Menteri Agama Yaqut Cholil Qoumas diduga ...</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689912/jaksa-sebut-yaqut-siapkan-1-juta-dolar-as-pengaruhi-pansus-haji</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/yaqut-cholil-didakwa-rugikan-negara-ratusan-miliar-2838961.jpg</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Zero ODOL mulai 2027, Kakorlantas ingatkan distribusi harus lancar</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:58:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>Kakorlantas Polri Irjen Pol. Wibowo mengingatkan jajaran bahwa distribusi barang maupun bahan pokok harus tetap lancar ...</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689911/zero-odol-mulai-2027-kakorlantas-ingatkan-distribusi-harus-lancar</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000087748.jpg</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>OJK sebut pengembangan UMKM dilakukan dengan pendekatan lebih sistemik</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:58:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>Kepala Eksekutif Pengawas Perbankan Otoritas Jasa Keuangan (OJK) Dian Ediana Rae mengatakan pengembangan usaha mikro ...</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689908/ojk-sebut-pengembangan-umkm-dilakukan-dengan-pendekatan-lebih-sistemik</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/posalia-sulteng-digifest-2026-2839153.jpeg</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>Topan Chan-hom terjang Jepang, Tokyo siaga banjir</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:57:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>Topan Chan-hom menerjang wilayah daratan Kanto di Jepang timur, yang juga mencakup kawasan Tokyo, pada ...</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689905/topan-chan-hom-terjang-jepang-tokyo-siaga-banjir</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/08/10/2023-08-10T000000Z_2137806987_MT1YOMIUR000TGJLC3_RTRMADP_3_TYPHOON-NO-6-KHANUN-STRAYS-IN-JAPAN.jpg</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>BNPB targetkan dua titik karhutla Bromo bisa padam pekan ini</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:53:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) menargetkan dua titik api yang masih belum padam di kebakaran hutan dan ...</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689904/bnpb-targetkan-dua-titik-karhutla-bromo-bisa-padam-pekan-ini</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-20.32.22.jpeg</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Juventus tutup pramusim di Australia dengan kemenangan</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:50:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>Juventus menutup laga pramusim di Australia dengan kemenangan 2-0 atas sesama klub asal Italia Palermo di ...</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689903/juventus-tutup-pramusim-di-australia-dengan-kemenangan</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/image-38.jpg</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Suriah kecam Kolombia akui "kedaulatan Israel" di Dataran Tinggi Golan</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:50:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>Suriah dengan tegas mengecam pengakuan Kolombia yang mengakui "kedaulatan Israel" di Dataran Tinggi ...</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689899/suriah-kecam-kolombia-akui-kedaulatan-israel-di-dataran-tinggi-golan</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/03/Golan.jpg</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>BPBD catat 1.077 kejadian karhutla di Sumsel hingga Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:50:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>ANTARA - Eskalasi kebakaran hutan dan lahan atau karhutla di Sumatera Selatan terus meningkat seiring memasuki puncak ...</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689693/bpbd-catat-1077-kejadian-karhutla-di-sumsel-hingga-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_BPBD-CATAT-1.077-KEJADIAN-KARHUTLA-DI-SUMSEL-HINGGA-AGUSTUS-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Hanura usul kursi pertama diberikan caleg nomor urut 1</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:48:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>Partai Hanura mengusulkan sistem pemilu legislatif dengan mekanisme kombinasi proporsional tertutup dan terbuka, yakni ...</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689891/hanura-usul-kursi-pertama-diberikan-caleg-nomor-urut-1</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000583793.jpg</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>AUM BNI Private tercatat tumbuh 21 persen hingga kuartal II 2026</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:48:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>PT Bank Negara Indonesia (Persero) Tbk atau BNI mencatat aset kelolaan (asset under management/AUM) BNI Private tumbuh ...</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689888/aum-bni-private-tercatat-tumbuh-21-persen-hingga-kuartal-ii-2026</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000675745.jpg</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Pemkab Pasuruan kerahkan 3 tangki air bantu padamkan kebakaran Bromo</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:48:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten (Pemkab) Pasuruan, Jawa Timur, mengerahkan tiga kendaraan tangki air dan satu kendaraan ...</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689884/pemkab-pasuruan-kerahkan-3-tangki-air-bantu-padamkan-kebakaran-bromo</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/ANTARA-2026-08-11T194712.702.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya tangkap pelaku pembunuhan-pemerkosaan di Tangerang</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:48:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>Ditreskrimum Polda Metro Jaya membekuk seorang pelaku pembunuhan dan pemerkosaan yang beraksi di sebuah rumah kontrakan ...</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689883/polda-metro-jaya-tangkap-pelaku-pembunuhan-pemerkosaan-di-tangerang</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000913631.jpg</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Menhan RI dan Wamenhan AS bahas penguatan kerja sama pertahanan</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:43:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Menteri Pertahanan (Menhan) RI Sjafrie Sjamsoeddin membahas rencana penguatan kerja sama bidang pertahanan dengan Wakil ...</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689879/menhan-ri-dan-wamenhan-as-bahas-penguatan-kerja-sama-pertahanan</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001569954.jpg</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Karhutla Palangka Raya meluas, pemkot perpanjang status darurat</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:42:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>ANTARA - Luas lahan terdampak kebakaran hutan dan lahan (karhutla) di Kota Palangka Raya, Kalimantan Tengah, terus ...</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689537/karhutla-palangka-raya-meluas-pemkot-perpanjang-status-darurat</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KARHUTLA-PALANGKA-RAYA-MELUAS-PEMKOT-PERPANJANG-STATUS-DARURAT.jpg</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>PBB: Hampir 5.000 rumah, 24 faskes rusak akibat gempa Kolombia</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:40:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>Gempa bumi dahsyat bermagnitudo 7,4 yang mengguncang Kolombia pada Senin (10/8) merusak hampir 5.000 rumah dan 24 ...</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689877/pbb-hampir-5000-rumah-24-faskes-rusak-akibat-gempa-kolombia</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Reruntuhan-gedung-akibat-gempa-Kolombia.jpg</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Menko Airlangga sebut calon Gubernur PFII sudah ada dari pemerintah</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:40:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Perekonomian Airlangga Hartarto menyatakan calon Gubernur Pusat Finansial Internasional ...</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689873/menko-airlangga-sebut-calon-gubernur-pfii-sudah-ada-dari-pemerintah</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/4A66028E-AC15-4B2B-BF63-6F00D047171E.jpeg</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Pemprov Kalsel dorong pesantren adaptif tanpa kehilangan jati diri</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:40:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) Kalimantan Selatan (Kalsel) mendorong pesantren mengembangkan pendekatan pendidikan yang ...</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689869/pemprov-kalsel-dorong-pesantren-adaptif-tanpa-kehilangan-jati-diri</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_1873.jpeg</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>Pemkot Semarang prioritaskan skrining kesehatan bagi perempuan</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:39:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Semarang menggelar layanan Cek Kesehatan Gratis (CKG) di Balai Kota Semarang pada 10-12 ...</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689747/pemkot-semarang-prioritaskan-skrining-kesehatan-bagi-perempuan</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_PEMKOT-SEMARANG-PRIORITASKAN-SKRINING-KESEHATAN-BAGI-PEREMPUAN_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Pemerintah berupaya tingkatkan keselamatan wisata bahari</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:39:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>Kementerian Pariwisata menjalankan program pelatihan bagi sumber daya manusia pariwisata dalam ...</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689868/pemerintah-berupaya-tingkatkan-keselamatan-wisata-bahari</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-14.10.27.jpeg</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Peneliti ingatkan ancaman gelombang panas laut bagi kesehatan manusia</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:38:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Gelombang panas laut (marine heatwaves) menimbulkan ancaman yang semakin besar terhadap kesehatan manusia, dengan ...</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689864/peneliti-ingatkan-ancaman-gelombang-panas-laut-bagi-kesehatan-manusia</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000023_20260811_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>Liga Putri Indonesia mulai kick off Oktober 2026, Erick: Kita bangkit</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:36:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>ANTARA - Liga Putri Indonesia (Indonesia Women's League) 2026/2027 resmi melaksanakan kick off pada 17 ...</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689621/liga-putri-indonesia-mulai-kick-off-oktober-2026-erick-kita-bangkit</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_46_42_02.Still488.jpg</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>ATR/BPN kuatkan integritas ASN melalui pendidikan antikorupsi</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:36:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) bekerja sama dengan Komisi Pemberantasan Korupsi ...</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689861/atr-bpn-kuatkan-integritas-asn-melalui-pendidikan-antikorupsi</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_200228.jpg</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Menag tandai pembangunan baru MIN 5 Pidie Jaya di atas tanah hibah</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:36:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>Menteri Agama (Menag) Nasaruddin Umar menandai pembangunan baru Madrasah Ibtidaiyah Negeri (MIN) 5 Pidie Jaya, Aceh ...</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689857/menag-tandai-pembangunan-baru-min-5-pidie-jaya-di-atas-tanah-hibah</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0012.jpg</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>BNN gandeng tiga kementerian siapkan penyintas masuk dunia kerja</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:36:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Badan Narkotika Nasional (BNN) bersama tiga kementerian mengintegrasikan penanganan penyintas penyalahgunaan narkotika ...</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689856/bnn-gandeng-tiga-kementerian-siapkan-penyintas-masuk-dunia-kerja</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1003330639.jpg</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>BNPB: Pemadaman api di Bromo andalkan pasokan air Danau Ranu Pani</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:35:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) menyatakan tidak ada sumber air lain yang bisa dimanfaatkan selain ...</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689852/bnpb-pemadaman-api-di-bromo-andalkan-pasokan-air-danau-ranu-pani</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0029_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Korban tewas gempa Kolombia bertambah jadi 224 orang</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:34:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Jumlah korban tewas akibat gempa bumi yang mengguncang Kolombia pada Senin (10/8) bertambah menjadi 224 orang, seperti ...</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689851/korban-tewas-gempa-kolombia-bertambah-jadi-224-orang</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/AT_LEAST_18_KILLED_AS_MAGNITUDE_74_EARTHQUAKE_HITS_COLOMBIA.jpg</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>WEGE-RDM KSO Resmi Mulai Pembangunan Gedung Poliklinik RSUD Temanggung Senilai Rp 155,4 Miliar</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:33:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA) – PT Wijaya Karya Bangunan Gedung Tbk (WEGE) yang tergabung dalam WEGE-RDM KSO secara resmi ...</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689849/wege-rdm-kso-resmi-mulai-pembangunan-gedung-poliklinik-rsud-temanggung-senilai-rp-1554-miliar</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WIKA-Ground-Breaking.jpg</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Trump berganti pesawat setelah kunjungan ke Turkiye</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:32:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat (AS) Donald Trump secara diam-diam berganti pesawat saat bertolak dari Turkiye setelah ...</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689845/trump-berganti-pesawat-setelah-kunjungan-ke-turkiye</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000025_20260811_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Bakamla RI gelar latihan gabungan dengan Malaysia dan Singapura</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:31:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Keamanan Laut Republik Indonesia  (Bakamla RI) menggelar latihan gabungan bersama ...</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689577/bakamla-ri-gelar-latihan-gabungan-dengan-malaysia-dan-singapura</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKAMLA-RI-GELAR-LATIHAN-GABUNGAN-DENGAN-MALAYSIA-DAN-SINGAPURA.jpg</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Pegadaian perkuat literasi keuangan pekerja informal di Tangerang</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:30:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>PT Pegadaian memperkuat literasi dan inklusi keuangan pekerja sektor informal melalui edukasi pengelolaan keuangan bagi ...</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689844/pegadaian-perkuat-literasi-keuangan-pekerja-informal-di-tangerang</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000179867.jpg</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Pemkot Jakbar perketat pengawasan "pak ogah" di exit tol Rawa Buaya</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:28:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>Petugas gabungan Satpol PP dan Suku Dinas Perhubungan Jakarta Barat meningkatkan pengawasan terhadap pengatur lalu ...</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689841/pemkot-jakbar-perketat-pengawasan-pak-ogah-di-exit-tol-rawa-buaya</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_200925.v1.jpg</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Pengacara Yaqut pertanyakan negara rugi Rp622 miliar kasus kuota haji</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:26:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>ANTARA - Penasihat hukum mantan Menteri Agama Yaqut Cholil Qoumas, Mellisa Anggraini, di Pengadilan Negara Jakarta ...</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689617/pengacara-yaqut-pertanyakan-negara-rugi-rp622-miliar-kasus-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PENGACARA-YAQUT-PERTANYAKAN-NEGARA-RUGI-RP622-MILIAR-KASUS-KUOTA-HAJI.jpg</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Kemenpora ajak warga mendaftar Merdeka Run 2026 dibuka 12 Agustus</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:25:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>Kementerian Pemuda dan Olahraga (Kemenpora) mengajak semua elemen warga mengikuti Merdeka Run 2026 yang ...</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689840/kemenpora-ajak-warga-mendaftar-merdeka-run-2026-dibuka-12-agustus</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/10/26/Resize_20231026_225833_3699.jpg</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Wamendagri soroti kesiapan APBD tangani kekerasan perempuan-anak</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:24:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Dalam Negeri Bima Arya Sugiarto meminta pemerintah daerah untuk memperkuat sistem pelayanan terpadu dalam ...</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689839/wamendagri-soroti-kesiapan-apbd-tangani-kekerasan-perempuan-anak</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/28/IMG_4925.jpeg</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Pemko Banjarmasin bagikan 10.000 bendera, tumbuhkan nasionalisme warga</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:20:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>ANTARA - Guna Menyemarakkan Hari Ulang Tahun Ke-81 Kemerdekaan Republik Indonesia, Pemerintah Kota Banjarmasin ...</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689751/pemko-banjarmasin-bagikan-10000-bendera-tumbuhkan-nasionalisme-warga</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_52_35_01.Still490.jpg</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Perpres Ojol masuk finalisasi, pemerintah lengkapi formula pola bisnis</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:20:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Sekretaris Negara (Mensesneg) Prasetyo Hadi, Selasa (11/8), menyebut bahwa Perpres terkait Ojek Online ...</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689252/perpres-ojol-masuk-finalisasi-pemerintah-lengkapi-formula-pola-bisnis</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PERPRES-OJOL-MASUK-FINALISASI-PEMERINTAH-LENGKAPI-FORMULA-POLA-BISNIS.jpg</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>BPK: SPKN 2026 jadi transformasi standar pemeriksaan sektor publik RI</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:20:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Badan Pemeriksa Keuangan (BPK) Budi Prijono menyatakan Standar Pemeriksaan Keuangan Negara (SPKN) 2026 ...</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689832/bpk-spkn-2026-jadi-transformasi-standar-pemeriksaan-sektor-publik-ri</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-06-at-15.29.02.jpeg</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Megawati: Partai politik perlu riset dan sains</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:19:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>Ketua Umum DPP PDI Perjuangan Megawati Soekarnoputri menekankan pentingnya riset berbasis sains dalam tubuh partai ...</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689829/megawati-partai-politik-perlu-riset-dan-sains</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000583723.jpg</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Waspadai karhutla, Banjarmasin gelar apel penanggulangan bencana</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:17:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepolisian Resor Kota Banjarmasin menggelar apel pasukan penanggulangan bencana kebakaran hutan dan lahan yang ...</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689729/waspadai-karhutla-banjarmasin-gelar-apel-penanggulangan-bencana</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_48_48_24.Still489.jpg</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>BMKG: El Nino kuat picu Sumsel makin kering hingga September</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:15:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menyebut fenomena El Nino berstatus kuat menyebabkan kondisi ...</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689827/bmkg-el-nino-kuat-picu-sumsel-makin-kering-hingga-september</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/prediksi-puncak-musim-kemarau-di-sumatera-selatan-2835887.jpg</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Pemkot Jakbar perkuat kerja sama lintas sektor turunkan stunting</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:14:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Jakarta Barat memperkuat kerja sama lintas sektor untuk intervensi percepatan penurunan kasus anak ...</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689824/pemkot-jakbar-perkuat-kerja-sama-lintas-sektor-turunkan-stunting</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/24/IMG_20260723_212803.v1.jpg</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Polisi: situasi pascaricuh di Tabang Kukar telah kondusif</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:13:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepolisian mengamankan situasi dan memastikan kondusivitas di wilayah Kecamatan Tabang, Kabupaten Kutai ...</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689172/polisi-situasi-pascaricuh-di-tabang-kukar-telah-kondusif</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/POLISI-SITUASI-PASCARICUH-DI-TABANG-KUKAR-TELAH-KONDUSIF.jpg</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Bamsoet Dorong Kampus Selaraskan Pendidikan dengan Kebutuhan Dunia Kerja</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:02:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Moch. Prima Fauzi</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>Bambang Soesatyo mengusulkan tiga program studi baru di UNPERBA untuk 2026, mendukung pendidikan tinggi yang relevan dengan kebutuhan industri.</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614374/bamsoet-dorong-kampus-selaraskan-pendidikan-dengan-kebutuhan-dunia-kerja</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/anggota-dpr-ri-bambang-soesatyo-1784547923074.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>KPK Libatkan BPKP dalam Pemeriksaan Rudy Tanoe untuk Hitung Kerugian Negara</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:57:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Adrial akbar</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>KPK memeriksa Rudy Tanoe terkait dugaan korupsi bansos 2020. Pemeriksaan melibatkan BPKP untuk menghitung kerugian negara dalam pengadaan bantuan.</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614371/kpk-libatkan-bpkp-dalam-pemeriksaan-rudy-tanoe-untuk-hitung-kerugian-negara</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/03/02/gedung-baru-kpk-7_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Pria di Bogor Diikat di Tiang Usai Kepergok Curi Uang Kotak Amal Masjid</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:48:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>M Solihin</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>Pria bernama Asmanto ditangkap setelah mencuri uang kotak amal masjid di Bogor. Ia pura-pura solat sebelum aksinya dan mengaku sudah dua kali melakukannya.</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614351/pria-di-bogor-diikat-di-tiang-usai-kepergok-curi-uang-kotak-amal-masjid</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/maling-kotak-amal-di-bogor-diikat-di-tiang-listrik-dok-istimewa-1786456096957_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Jatanras PMJ Tangkap Pelaku Pembunuhan dan Pemerkosaan di Tangerang</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:43:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>Zunita Putri</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>Seorang wanita berinisial SNA (20) ditemukan tewas di kontrakan di Tangerang, diduga korban pembunuhan dan pemerkosaan. Pelaku ditangkap dalam 24 jam.</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614346/jatanras-pmj-tangkap-pelaku-pembunuhan-dan-pemerkosaan-di-tangerang</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/tkp-pembunuhan-dan-pemerkosaan-di-tangerang-1786455813903_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Uji Coba E-voting, Kemenkum Libatkan Pegawai Pilih Kakanwil Jatim</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:36:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>Angelina Vioni</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>Kemenkum uji coba e-voting untuk pengisian jabatan, meningkatkan transparansi dan manajemen talenta. Langkah ini diharapkan memperkuat tata kelola birokrasi.</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614341/uji-coba-e-voting-kemenkum-libatkan-pegawai-pilih-kakanwil-jatim</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kemenkum-1786455205202_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Menkop Dorong Hilirisasi Sawit Berbasis Koperasi untuk Sejahterakan Petani</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:32:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>Chayyara Zulghifary</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>Program hilirisasi kelapa sawit berbasis koperasi diharapkan meningkatkan kesejahteraan petani. Dukungan dari berbagai pihak penting untuk keberhasilan ini.</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614339/menkop-dorong-hilirisasi-sawit-berbasis-koperasi-untuk-sejahterakan-petani</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kemenkop-1786455130445_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Wamendagri Ribka Haluk Sambut Anak Papua Lanjutkan Sekolah di Tangerang</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:21:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>Nada Herwando Kartika</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>Wamendagri Ribka Haluk menyambut 65 pelajar Papua di Jakarta. Mereka akan melanjutkan pendidikan di Tangerang setelah perjalanan laut tujuh hari.</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614319/wamendagri-ribka-haluk-sambut-anak-papua-lanjutkan-sekolah-di-tangerang</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kemendagri-1786454396856_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Waka MPR Dorong Penataan Ulang Sistem Pendidikan di Indonesia</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:21:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>Waka MPR Lestari Moerdijat tekankan pentingnya transformasi pendidikan untuk lahirkan lulusan yang kritis dan berkarakter, selaras dengan kebutuhan pasar kerja.</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614318/waka-mpr-dorong-penataan-ulang-sistem-pendidikan-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/02/wakil-ketua-mpr-lestari-moerdijat-1777717773159_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Empat Lembaga Teken MoU Rehabilitasi hingga Pemberdayaan Napza</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:16:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>Chayyara Zulghifary</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>Kemensos, Kemenkes, Kemenaker, dan BNN tandatangani MoU untuk penanganan terpadu korban penyalahgunaan Napza, dari rehabilitasi hingga penempatan kerja.</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614315/empat-lembaga-teken-mou-rehabilitasi-hingga-pemberdayaan-napza</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kemensos-1786453983320_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Megawati Lantik Pinka Haprani-Andi Widjajanto Pimpin Organisasi Sayap PDIP</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:10:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>Megawati Soekarnoputri melantik pimpinan organisasi sayap PDIP, termasuk Pinka Haprani dan Andi Widjajanto, untuk memperkuat konsolidasi dan riset partai.</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614312/megawati-lantik-pinka-haprani-andi-widjajanto-pimpin-organisasi-sayap-pdip</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/ketua-umum-dpp-pdi-perjuangan-pdip-megawati-soekarnoputri-melantik-pimpinan-organisasi-sayap-dan-badan-partai-dok-ist-1786453772423_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Ulah Maling di Serang Sembelih Puluhan Kambing di Pematang Sawah</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:00:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>Aksi pencurian puluhan kambing terjadi di Kabupaten Serang, Banten. Kambing-kambing itu diduga disembelih sebelum diangkut dan dibawa kabur.</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614304/ulah-maling-di-serang-sembelih-puluhan-kambing-di-pematang-sawah</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/lokasi-kandang-kambing-yang-dicuri-ariefdetikcom-1786427491486_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Ramai di Medsos, Komentar Warganet Soal Videotron 'Hujan Anggur' di Jakarta</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:00:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>Visual 'hujan anggur' di videotron Jakarta menarik perhatian warganet. Beragam respons muncul, dari ketertarikan hingga komentar tentang HiFruit.</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614286/ramai-di-medsos-komentar-warganet-soal-videotron-hujan-anggur-di-jakarta</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/viral-hujan-anggur-di-jakarta-iklan-ini-bikin-warga-berhenti-menoleh-1786451271811_43.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Banjir Bertahun-tahun di Bulak Barat Depok Kini Telah Surut</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:47:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>Banjir di Bulak Barat, Depok, yang berkepanjangan kini telah surut. Pemerintah setempat melakukan normalisasi sungai dan merencanakan pembangunan jembatan baru.</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614290/banjir-bertahun-tahun-di-bulak-barat-depok-kini-telah-surut</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/banjir-di-bulak-barat-depok-yang-berkepanjangan-kini-telah-surut-pemerintah-setempat-melakukan-normalisasi-sungai-devi-pdetikc-1786452277211_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Perwira TNI Didakwa Selundupkan Sabu di Kepri, Paket Ditulis 'Selamat Umrah'</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:44:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>Nizar Aldi</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>Mayor Laut Faisal Mulia didakwa menyelundupkan 12 paket sabu ke pesawat militer. Ia ditangkap setelah interogasi terkait pengiriman narkoba.</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614288/perwira-tni-didakwa-selundupkan-sabu-di-kepri-paket-ditulis-selamat-umrah</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/03/ilustrasi-hukum-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Muncul 'Hujan Anggur' di Jakarta, Videotron Ini Curi Perhatian Warga</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:40:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>Visual unik 'hujan anggur' menghiasi videotron Jakarta, menarik perhatian di tengah iklan. Iklan HiFruit ini menciptakan pengalaman visual yang menonjol.</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614284/muncul-hujan-anggur-di-jakarta-videotron-ini-curi-perhatian-warga</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/viral-hujan-anggur-di-jakarta-iklan-ini-bikin-warga-berhenti-menoleh-1786451271811_43.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Koalisi Sipil Kritik Pernyataan Panglima TNI Tanggung Jawab Keamanan Indonesia</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:37:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>Koalisi Masyarakat Sipil mengecam pernyataan Panglima TNI tentang tanggung jawab keamanan. Mereka khawatir akan pengaburan fungsi TNI dalam urusan sipil.</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614282/koalisi-sipil-kritik-pernyataan-panglima-tni-tanggung-jawab-keamanan-indonesia</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/09/ilustrasi-tni-1754727401560.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>4 Kesimpulan Komisi III DPR soal Kasus Tewasnya Eks Istri Polisi di Medan</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:33:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>Komisi III DPR RI mengeluarkan 4 kesimpulan terkait kematian eks istri polisi di Medan, mendesak penyidikan transparan dan akuntabel.</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614277/4-kesimpulan-komisi-iii-dpr-soal-kasus-tewasnya-eks-istri-polisi-di-medan</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/komisi-iii-dpr-ri-menggelar-rapat-dengar-pendapat-rdp-dan-rapat-dengar-pendapat-umum-rdpu-membahas-kasus-kematian-eks-istri-br-1786451602067_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Mantan Sekjen Kementerian ESDM Rida Mulyana Meninggal Dunia</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:40:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>Mantan Sekretaris Jenderal Kementerian Energi dan Sumber Daya Mineral (ESDM) Rida Mulyana meninggal dunia pada Selasa (11/8/2026).</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8614344/mantan-sekjen-kementerian-esdm-rida-mulyana-meninggal-dunia</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2018/10/04/25efc886-7cad-437b-b73e-2130e142219b_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Kata Bahlil soal Kabar Reshuffle Kabinet Usai 17 Agustus</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:22:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil Lahadalia merespons isu reshuffle kabinet yang disebut-sebut akan dilakukan Presiden Prabowo Subianto setelah 17 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8614324/kata-bahlil-soal-kabar-reshuffle-kabinet-usai-17-agustus</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/bahlil-lahadalia-1785840108228_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Sederet Capaian Kinerja BUMN di Bawah Danantara</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:04:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Program konsolidasi dan transformasi BUMN yang dijalankan Danantara sejak awal pembentukannya mulai menunjukkan hasil yang konkret.</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8614307/sederet-capaian-kinerja-bumn-di-bawah-danantara</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/01/wisma-danantara-indonesia-1751345496316_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Cegah Longsor, KemenPU Perkuat Ruas Padang Panjang-Sicincin di Lembah Anai</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:35:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Nada Herwando</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>Kementerian PU memperkuat jalan dan lereng di Padang Panjang-Sicincin untuk ketahanan infrastruktur menghadapi bencana. Proyek ini selesai pada Juli 2026.</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8614281/cegah-longsor-kemenpu-perkuat-ruas-padang-panjang-sicincin-di-lembah-anai</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kementerian-pu-1786451641619_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Rp 20,5 T Telah Mengalir ke 490 Pemda, Purbaya: Cukup untuk Bayar Gaji PPPK</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:30:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengumumkan penyaluran Rp 20,5 triliun untuk 490 Pemda, cukup untuk membayar gaji ASN dan PPPK.</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8614194/rp-20-5-t-telah-mengalir-ke-490-pemda-purbaya-cukup-untuk-bayar-gaji-pppk</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/23/menkeu-purbaya-1784785896260_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Haru dan Bahagia Ivan Gunawan Exhibition Nusanova Dapat Rekor MURI</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:02:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>Ivan Gunawan terharu Nusanova 2.0: Sekar Jagat mendapatkan rekor MURI. Dia memecahkan pameran busana imersif pertama berbasis corak batik Sekar Jagat Madura.</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8613990/haru-dan-bahagia-ivan-gunawan-exhibition-nusanova-dapat-rekor-muri</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/ivan-gunawan-1786441529083_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Satu WNI dan Dua Warga Pakistan Tewas Diserang Houthi, Akankah Islamabad Terjun ke Perang?</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:50:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>Bagi Pakistan, persoalan jadi lebih sensitif karena dua warga negaranya jadi korban. Mereka baru bergabung dalam pakta pertahanan Turki-Saudi</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867107/satu-wni-dan-dua-warga-pakistan-tewas-diserang-houthi-akankah-islamabad-terjun-ke-perang</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/sKTjW2IWme_tj-rBEFT9DF7gqhA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PAKTA-PERTAHANAN-Bendera-Arab-Saudi-Pakistan-dan-Turki.jpg</t>
+        </is>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Soal Isu Demo Agustus 2025 Berulang, Ray Rangkuti: Tak Ada Indikasi, tapi Lampu Kuning bagi Prabowo</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:47:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>Ray Rangkuti menilai, publik sudah semakin resah dengan pemerintahan Prabowo-Gibran, dan hal itu makin terlihat dari survei SMRC terbaru.</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867106/soal-isu-demo-agustus-2025-berulang-ray-rangkuti-tak-ada-indikasi-tapi-lampu-kuning-bagi-prabowo</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0iL7xMX-_zskwBZCe2XRTCl1Bzs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/prabowo-kadin-dks.jpg</t>
+        </is>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Orang Kaya Mulai Kurangi Properti, Saham dan Kripto Dinilai Lebih Menarik</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:44:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>Penjualan properti kelas atas melambat karena orang kaya mengurangi aset properti dan beralih ke saham serta kripto yang dinilai lebih…</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867105/orang-kaya-mulai-kurangi-properti-saham-dan-kripto-dinilai-lebih-menarik</t>
+        </is>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/UNKBC5WcfRV_cLsFJWHGS_vnnvE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/BDeutsche-Welle77982382_403.jpg.jpg</t>
+        </is>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Sejarah Baru CAHN FC Tembus Liga Champions Asia 2026/2027, Sepak Bola Vietnam Naik Kelas</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:44:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Sejarah baru diukir salah satu klub Vietnam yang berhasil menembus putaran final Liga Champions Asia musim 2026/2027.</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867104/sejarah-baru-cahn-fc-tembus-liga-champions-asia-20262027-sepak-bola-vietnam-naik-kelas</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/IInQZ2cgGLMiezomp6XB8qOu4_k=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pelatih-kepala-timnas-thailand-alexandre-polking_20211229_202645.jpg</t>
+        </is>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Raffi Ahmad Dorong Kolaborasi Anak Muda Jadi Penggerak Transformasi Digital</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:44:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Raffi Ahmad mendorong kolaborasi pemerintah dan pemuda diperkuat untuk memanfaatkan transformasi digital, termasuk AI, bagi pendidikan,</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867103/raffi-ahmad-dorong-kolaborasi-anak-muda-jadi-penggerak-transformasi-digital</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8G7DhYEeY8_HDZm-rOs30XeMDkU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/raffi-audiensi-dengan-dpp.jpg</t>
+        </is>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Cegah Kekerasan Terhadap Santri, Kemenag Hingga KPAI Rumuskan Pedoman Safeguarding Pesantren</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:42:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>Pedoman Safeguarding Pesantren Ramah Anak akan menjadi panduan bersama dalam memperkuat sistem pencegahan tindak kekerasan</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867102/cegah-kekerasan-terhadap-santri-kemenag-hingga-kpai-rumuskan-pedoman-safeguarding-pesantren</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/RJLgc4hbDHHbIMpg3m_gQYsPxBM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Tadarus-Santri-Ponpes-Ar-Raudlatul-Hasanah-Medan_20260221_172957.jpg</t>
+        </is>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Bukan Sekadar Hasil, Xabi Alonso Bangun Fondasi Chelsea di Tur Pramusim</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:42:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>Lebih dari sekadar hasil laga, tur pramusim menjadi momen Xabi Alonso membangun chemistry dan fondasi baru Chelsea.</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867101/bukan-sekadar-hasil-xabi-alonso-bangun-fondasi-chelsea-di-tur-pramusim</t>
+        </is>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/SIUs7kjLLjYIblFlkw_JSBUggrM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Chelsea-FC-vs-AC-Milan_20260809_140404.jpg</t>
+        </is>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu Purple Rain - Prince: I Never Meant to Cause You any Sorrow</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:40:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>Solo gitarnya di bagian akhir menjadi momen paling emosional dan menjadi penutup yang apik.</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7867100/terjemahan-lirik-lagu-purple-rain-prince-i-never-meant-to-cause-you-any-sorrow</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zLN77GXG_MWcQ27NDqNvGgp-QJs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-musik-ilustrasi-lirik-ilustrasi-terjemahan-lirik-lagu.jpg</t>
+        </is>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu Slow Dancing in a Burning Room dari John Mayer: We're Going Down</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:39:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>Slow Dancing in a Burning Room sering digunakan oleh banyak musisi muda untuk belajar teknik gitar blues modern.</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7867099/terjemahan-lirik-lagu-slow-dancing-in-a-burning-room-dari-john-mayer-were-going-down</t>
+        </is>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/iF9WIvyjtJsIYfbmSdBAvkMvzYI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/john-mayer-hibur-fansnya-di-indonesia-dalam-konser-asia-tour_20190405_213614.jpg</t>
+        </is>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu Blackout - Turnstile: Blackout in the Middle of the Light</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:39:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>Berikut ini merupakan terjemahan lirik lagu Blackout yang dipopulerkan oleh grup band asal Baltimore, Turnstile.</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7867098/terjemahan-lirik-lagu-blackout-turnstile-blackout-in-the-middle-of-the-light</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zLN77GXG_MWcQ27NDqNvGgp-QJs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-musik-ilustrasi-lirik-ilustrasi-terjemahan-lirik-lagu.jpg</t>
+        </is>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Kunci Gitar Lagu Sementara - The Paps: Ku Tak Mau Jatuh Cinta untuk Sementara</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:38:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>Berikut ini merupakan chord kunci gitar lagu Sementara yang dipopulerkan oleh grup band The Paps, dimainkan dari kunci Am.</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7867097/kunci-gitar-lagu-sementara-the-paps-ku-tak-mau-jatuh-cinta-untuk-sementara</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vZGfIQdrUWUr9aeBMAO6c3gc3O0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Potret-gitar-akustik-untuk-kunci-chord-dasar-mudah-dimainkan.jpg</t>
+        </is>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu New Generation - The SIGIT: We Are the Noodle Generation</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:37:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>Berikut ini merupakan terjemahan lirik lagu New Generation yang dipopulerkan oleh grup band The SIGIT.</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7867096/terjemahan-lirik-lagu-new-generation-the-sigit-we-are-the-noodle-generation</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/tEq9lHSi3zC8-tIEQ99J9IcoxD8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-terjemahan-lirik-lagu.jpg</t>
+        </is>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Taiwan Deteksi Pesawat dan Kapal Perang China di Sekitar Wilayahnya</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:36:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Beijing menganggap Taiwan sebagai bagian dari wilayah China dan menolak gagasan bahwa Taiwan merupakan negara yang terpisah.</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867095/taiwan-deteksi-pesawat-dan-kapal-perang-china-di-sekitar-wilayahnya</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/04b2exUAkAL41jonI7E-0LjTXnk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kapal-Perang-China-Angkatan-Laut-Tiongkok.jpg</t>
+        </is>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>‘Berkarya Lewat Lensa’ Jadi Ruang Jurnalis dan Masyarakat Bercerita Melalui Foto</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:34:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>PFI bersama Nojorono Kudus gelar “Berkarya Lewat Lensa”, ruang ekspresi visual menjaga warisan di tengah perubahan zaman.</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867094/berkarya-lewat-lensa-jadi-ruang-jurnalis-dan-masyarakat-bercerita-melalui-foto</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ctKK8KNp7E6vPwK-FrLwXXJmN9w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-fotografi-smartphone.jpg</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Abdul Muhari Dilantik Jadi Deputi Pencegahan BNPB, Ini Sosoknya</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:34:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Kepala BNPB Letjen TNI Dr Suharyanto mengambil sumpah jabatan Abdul Muhari sebagai Deputi Bidang Pencegahan BNPB</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867093/abdul-muhari-dilantik-jadi-deputi-pencegahan-bnpb-ini-sosoknya</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c5wKBOF6W6_Peb2ImbRRlDy7GTY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Abdul-Muhari-dilantik-menjadi-Deputi-Bidang-Pencegahan-BNPB.jpg</t>
+        </is>
+      </c>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik dan Makna Lagu Loser - Tame Impala: So Much for Closure, I Lost Composure</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:33:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Berikut ini terjemahan lirik dan makna lagu "Loser" karya Tame Impala lengkap dengan profil singkat sang musisi.</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7867092/terjemahan-lirik-dan-makna-lagu-loser-tame-impala-so-much-for-closure-i-lost-composure</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8ofGbaRMpqu_gFPWYkenF6qEE2Y=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Potret-ilustrasi-lirik-lagu-terjemahan-musik-mendengarkan-musik.jpg</t>
+        </is>
+      </c>
+      <c r="I1266" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban Bahasa Indonesia Kawan Seiring Kelas 3 Halaman 22 Kurikulum Merdeka: Aktivitas 6</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:29:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Soal ini terdapat pada buku Bahasa Indonesia Kawan Seiring Kelas 3 Halaman 22 Kurikulum Merdeka, tepatnya pada Aktivitas 6.</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7867091/kunci-jawaban-bahasa-indonesia-kawan-seiring-kelas-3-halaman-22-kurikulum-merdeka-aktivitas-6</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/AQ6NUlpft8TPoUd6GxuTuejfIw4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/siswa-SD-belajar-di-sekolah.jpg</t>
+        </is>
+      </c>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Laut Merah Jadi Front Baru Perang Iran, Houthi Gencarkan Serangan Kapal: Ada WNI Jadi Korban</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:28:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Sumber dari penjaga pantai Yaman dan pemerintah setempat menyebut tiga awak kapal tewas, terdiri dari dua warga Pakistan dan satu warga Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867090/laut-merah-jadi-front-baru-perang-iran-houthi-gencarkan-serangan-kapal-ada-wni-jadi-korban</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ic5AbtT--SxS2enYL-jm8r_WyyI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Houthi-serangan-kapal-kargo-di-Laut-Merah.jpg</t>
+        </is>
+      </c>
+      <c r="I1268" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Agenda Keliling Dunia Rampung, Chelsea Gantian Sambut Para Bintang</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:25:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Chelsea mulai akan menyambut para pemain bintang yang bergabung belakangan ke klub, seperti Enzo Fernandez, Morgan Rogers,dan Valentin Barco.</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867089/agenda-keliling-dunia-rampung-chelsea-gantian-sambut-para-bintang</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1TZQge9GlQD89HfEuhZSIz5D8rA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Chelsea-FC-vs-AC-Milan_20260809_140223.jpg</t>
+        </is>
+      </c>
+      <c r="I1269" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Uji Materi UU Kesehatan, Pemohon Soroti Wewenang MDP KKI: Kasus Dokter Ratna Jadi Acuan</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Kasus dokter Ratna di Pangkalpinang menjadi acuan uji UU Kesehatan soal batas kewenangan MDP KKI dan proses hukum dokter</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867088/uji-materi-uu-kesehatan-pemohon-soroti-wewenang-mdp-kki-kasus-dokter-ratna-jadi-acuan</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zAd483LFybKEViN_GUiehmzCGNY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Mahkamah-Konstitusi-menggelar-sidang-pengucapan-sejumlah-putusan.jpg</t>
+        </is>
+      </c>
+      <c r="I1270" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>KAI Diskon Tiket 17 Persen dan Tarif Rp8 untuk LRT dan KRL</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:25:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- PT Kereta Api Indonesia (Persero) atau KAI menghadirkan Promo Spesial 17-8-2026 dalam rangka menyemarakkan Hari Ulang Tahun ke-81 Kemerdekaan Republik Indonesia dengan tema “Bersatu Berdaulat, Rakyat...</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlxaq370/kai-diskon-tiket-17-persen-dan-tarif-rp8-untuk-lrt-dan-krl</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/jumlah-pengguna-lrt-jabodebek-terus-meningkat-seiring-semakin-banyak_260730175516-557.jpg</t>
+        </is>
+      </c>
+      <c r="I1271" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Harga Pakan Naik, Harga Telur Turun, Peternak Unggas Tercekik</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:57:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, SEMARANG — Para peternak yang tergabung dalam Koperasi Peternak Unggas Sejahtera (KPUS) telah menggelar demonstrasi di sejumlah kabupaten di Provinsi Jawa Tengah (Jateng) pada Senin (10/8/2026). Mereka mengeluhkan terus...</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjlw0k423/harga-pakan-naik-harga-telur-turun-peternak-unggas-tercekik</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/sejumlah-peternak-ayam-di-diy-membentangkan-spanduk-memprotes-mahalnya_260811010152-976.jpeg</t>
+        </is>
+      </c>
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Lima Pihak Dipolisikan Buntut Tantangan Hafalan Alquran Berhadiah Miras</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:06:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>Tim Hukum Muslim melaporkan perkara ini ke Polda Metro Jaya.</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267496/lima-pihak-dipolisikan-buntut-tantangan-hafalan-alquran-berhadiah-miras</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/zZCEJSPd8hO87JaYrgYkVT8aozU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321619/original/023796700_1786457189-03531120-2f6a-4f2a-b03d-ae796cbec761.jpg</t>
+        </is>
+      </c>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Gus Alex Didakwa Perkaya Diri Rp 93,6 M dari Kasus Kuota Haji</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:46:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>Uang yang diterima Gus Alex tersebut berasal dari sejumlah pihak dalam praktik pengisian kuota haji khusus</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267481/gus-alex-didakwa-perkaya-diri-rp-936-m-dari-kasus-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/w5ODo7-d0Sp1v14iaP_WyQRa58I=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5777171/original/051032100_1778679973-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1274" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Kejagung: Febrie Adriansyah Mantan Pendekar Hukum, Harus Hati-Hati</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:26:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Febrie merupakan orang yang memahami hukum sehingga penyidik perlu menyiapkan strategi dalam menangani perkara tersebut.</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267464/kejagung-febrie-adriansyah-mantan-pendekar-hukum-harus-hati-hati</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/A02PfRJ2y22nBz-jXAXGn_wIYFI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9306887/original/065864800_1784913814-jam8.jpg</t>
+        </is>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Menko PMK Ungkap Kendala Modifikasi Cuaca untuk Padamkan Kebakaran Bromo</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:54:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>Saat ini masih terdapat dua titik api di kawasan tersebut, turun dari 36 titik pada puncak kebakaran.</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267444/menko-pmk-ungkap-kendala-modifikasi-cuaca-untuk-padamkan-kebakaran-bromo</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/v7T1HIXrr1naqq66YB477MHNM78=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321359/original/040865600_1786440061-Menko_PMK_Pratikno_rakor_kebakaran_bromo.jpg</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Polisi Usut Perusakan Lahan, Direktur CV Dzarrin Dijemput Paksa di Gresik</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:14:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Direktur CV Dzarrin dijemput paksa terkait dua kasus berbeda di Pamekasan: dugaan perusakan lahan dan korupsi proyek jalan mangkrak senilai miliaran rupiah.</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>https://surabaya.kompas.com/read/2026/08/11/211405478/polisi-usut-perusakan-lahan-direktur-cv-dzarrin-dijemput-paksa-di-gresik</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/2TzBwW3DCPFeMeQ_QhMXMoq2YMU=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7b1b17f2cdc.jpg</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>Cahaya</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Surat Ad-Dhuha: Arab, Latin, Arti, Makna, dan Keutamaannya</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:14:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>Surat Ad-Dhuha merupakan surah ke-93 dalam Al-Qur’an yang terdiri dari 11 ayat. Berikut bacaan lengkap Arab, latin, arti, dan penjelasan lainnya.</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>https://cahaya.kompas.com/aktual/26H11204414090/surat-ad-dhuha-arab-latin-arti-makna-dan-keutamaannya</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/KGfNQwPTuUwSXgO6yDemkYULfrU=/733x0:5093x2906/1200x675/data/photo/2026/07/09/6a4f9394db337.jpg</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Garuda Indonesia Sediakan 170.845 Tiket Domestik Gratis Buat Wisatawan Asing</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:14:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>Garuda Indonesia (Persero) Tbk meluncurkan program free domestic flight atau penerbangan domestik gratis bagi wisatawan asing.</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/11/201836926/garuda-indonesia-sediakan-170845-tiket-domestik-gratis-buat-wisatawan-asing</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/LKqMqZcv-AbYqee3C9YXcUvcLK0=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/11/6a7b1f598854c.jpg</t>
+        </is>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1177"/>
+  <autoFilter ref="A1:I1279"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1279</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1356</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1279"/>
+  <dimension ref="A1:I1356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -60552,8 +60552,3627 @@
         </is>
       </c>
     </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>TNI hadirkan Yuke Dewa 19 pulihkan trauma warga Aceh di momen HUT RI</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:46:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>TNI AD melalui Korem (Danrem) 011/Lilawangsa menghadirkan basis grup musik legendaris Dewa 19 Yuke Sampurna untuk ...</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690031/tni-hadirkan-yuke-dewa-19-pulihkan-trauma-warga-aceh-di-momen-hut-ri</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG-20260811-WA0025.jpg</t>
+        </is>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Yaqut ajukan perlawanan atas dakwaan korupsi kuota haji</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:43:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Menteri Agama periode 2020-2024 Yaqut Cholil Qoumas, melalui tim advokatnya, mengajukan perlawanan terkait kasus dugaan ...</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690028/yaqut-ajukan-perlawanan-atas-dakwaan-korupsi-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Yaqut-Cholil-Didakwa-Rugikan-Negara-Ratusan-Miliar-110826-Bay-3.jpg</t>
+        </is>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Kemlu benarkan ABK WNI jadi korban serangan di Bab Al-Mandeb Yaman</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:42:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>Kementerian Luar Negeri (Kemlu) RI membenarkan informasi terkait tiga anak buah kapal (ABK) asal Indonesia yang menjadi ...</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690024/kemlu-benarkan-abk-wni-jadi-korban-serangan-di-bab-al-mandeb-yaman</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/06/create-antaranews-logo.jpg</t>
+        </is>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Nusron beberkan mekanisme penyelesaian konflik agraria</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:41:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid menjelaskan bahwa penyelesaian ...</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690020/nusron-beberkan-mekanisme-penyelesaian-konflik-agraria</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_223144.jpg</t>
+        </is>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>139 SPPG Surabaya tak serap telur lokal, Mentan copot Korwil</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:41:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Pertanian Andi Amran Sulaiman mencopot Koordinator Wilayah Kantor Pelayanan Pemenuhan Gizi Kota ...</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689765/139-sppg-surabaya-tak-serap-telur-lokal-mentan-copot-korwil</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_139-SPPG-SURABAYA-TAK-SERAP-TELUR-LOKAL-MENTAN-COPOT-KORWIL.jpg</t>
+        </is>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Lewat M4CR, Pelestarian Ekosistem Pesisir Jadi Kunci Ketahanan Pangan di Bulungan Kaltara</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:38:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>Hamparan tambak tradisional membentang luas mengikuti garis pantai di Desa Tanjung Buka, Kabupaten Bulungan, ...</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690016/lewat-m4cr-pelestarian-ekosistem-pesisir-jadi-kunci-ketahanan-pangan-di-bulungan-kaltara</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Program-Mangroves-for-Coastal-Resilience.jpg</t>
+        </is>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Gita Bahana Nusantara unjuk kesiapan di Pakansari jelang HUT ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:37:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Gita Bahana Nusantara (GBN) 2026 menunjukkan kesiapan menjelang peringatan HUT ke-81 Kemerdekaan Republik Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690013/gita-bahana-nusantara-unjuk-kesiapan-di-pakansari-jelang-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1003331040.jpg</t>
+        </is>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Kabut asap memburuk, sekolah di Pontianak beralih daring</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:35:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Pontianak, Kalimantan Barat, mengalihkan pembelajaran tatap muka menjadi pembelajaran daring ...</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689769/kabut-asap-memburuk-sekolah-di-pontianak-beralih-daring</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KABUT-ASAP-MEMBURUK-SEKOLAH-DI-PONTIANAK-BERALIH-DARING.jpg</t>
+        </is>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Asiana perkenalkan teknologi ubah sampah jadi bahan bakar alternatif</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:32:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>PT Asiana Technologies memperkenalkan pengolahan sampah menjadi bahan bakar alternatif berupa Refuse Derived Fuel (RDF) ...</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690012/asiana-perkenalkan-teknologi-ubah-sampah-jadi-bahan-bakar-alternatif</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_220846.jpg</t>
+        </is>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Komisi VII DPR minta Pemprov NTB benahi destinasi wisata Gili Tramena</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:28:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>Komisi VII DPR RI meminta Pemerintah Provinsi Nusa Tenggara Barat (Pemprov NTB) serius membenahi persoalan di kawasan ...</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690011/komisi-vii-dpr-minta-pemprov-ntb-benahi-destinasi-wisata-gili-tramena</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/b2ba4340-fd3c-4459-ac58-e54cf4341212.jpg</t>
+        </is>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>InJourney menyatakan Mandalika siap sambut MotoGP 2026</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:24:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>PT Aviasi Pariwisata Indonesia (Persero) atau InJourney menyatakan bahwa Sirkuit Internasional Pertamina ...</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690007/injourney-menyatakan-mandalika-siap-sambut-motogp-2026</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-20.08.05.jpeg</t>
+        </is>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Wagub Sumut: majukan kualitas pendidikan Nias Barat butuh kolaborasi</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:19:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Wakil Gubernur (Wagub) Sumatera Utara (Sumut) Surya menegaskan, bahwa memajukan kualitas pendidikan di wilayah ...</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690003/wagub-sumut-majukan-kualitas-pendidikan-nias-barat-butuh-kolaborasi</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001041644.jpg</t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Danantara: PSEL Yogyakarta diproyeksikan aliri listrik 15 ribu rumah</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:15:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>Badan Pengelola Investasi Daya Anagata Nusantara (Danantara) menyebut energi listrik yang dihasilkan dari konstruksi ...</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690000/danantara-psel-yogyakarta-diproyeksikan-aliri-listrik-15-ribu-rumah</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_220510.jpg</t>
+        </is>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Menkop: LPDB siap dukung koperasi bangun pabrik CPO</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:15:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Menteri Koperasi Ferry Juliantono mengatakan Lembaga Pengelola Dana Bergulir (LPDB) Koperasi siap mendukung pembiayaan ...</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689997/menkop-lpdb-siap-dukung-koperasi-bangun-pabrik-cpo</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/tempImagePrULuy.jpg</t>
+        </is>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Hanura: Caleg berkualitas jangan sampai kalah karena modal</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:09:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>Partai Hanura menilai sistem pemilu perlu memberikan ruang bagi calon legislatif (caleg) berkualitas agar tidak ...</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689996/hanura-caleg-berkualitas-jangan-sampai-kalah-karena-modal</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000583792.jpg</t>
+        </is>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Polisi kumpulkan barang bukti dugaan penistaan agama di festival musik</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:08:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>Polres Metro Jakarta Utara mengumpulkan barang bukti untuk menyelidiki dugaan penistaan agama yang terjadi saat ...</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689992/polisi-kumpulkan-barang-bukti-dugaan-penistaan-agama-di-festival-musik</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000913154.jpg</t>
+        </is>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>BPBD Sleman tetapkan Siaga Darurat Kekeringan antisipasi El Nino</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:02:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>BPBD Kabupaten Sleman, Daerah Istimewa Yogyakarta, menetapkan Status Siaga Darurat Kekeringan melalui Keputusan Bupati ...</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689989/bpbd-sleman-tetapkan-siaga-darurat-kekeringan-antisipasi-el-nino</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000050725.jpg</t>
+        </is>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Agrinas siapkan percontohan plasma sawit berbasis koperasi di Sumut</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:01:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>PT Agrinas Palma Nusantara (Persero) sedang menyiapkan proyek percontohan atau pilot project kemitraan pengembangan ...</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689988/agrinas-siapkan-percontohan-plasma-sawit-berbasis-koperasi-di-sumut</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-19.13.31-2.jpeg</t>
+        </is>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Polres Jakbar tahan sopir taksi online terduga pelaku pencabulan</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:59:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>Polres Metro Jakarta Barat menahan pria berinisial ARA (54), sopir taksi daring yang diduga ...</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689987/polres-jakbar-tahan-sopir-taksi-online-terduga-pelaku-pencabulan</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/24/1000684130.jpg</t>
+        </is>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Kaltara lepas 119 anggota pramuka ke Jambore Nasional Cibubur</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:59:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Provinsi Kalimantan Utara resmi melepas seratus sembilan belas anggota Pramuka Penggalang untuk ...</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689963/kaltara-lepas-119-anggota-pramuka-ke-jambore-nasional-cibubur</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.14_01_58_01.Still493.jpg</t>
+        </is>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Pertamina memasok 750 kl avtur untuk Super Garuda Shield 2026</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:59:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>PT Pertamina Patra Niaga Regional Sumatera Bagian Selatan (Sumbagsel) menyiapkan 750 kiloliter (kl) bahan bakar ...</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689985/pertamina-memasok-750-kl-avtur-untuk-super-garuda-shield-2026</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/654313.jpg</t>
+        </is>
+      </c>
+      <c r="I1300" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Komisi VII minta NTB segera tuntaskan persoalan pariwisata tiga Gili</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:57:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>ANTARA - Komisi VII DPR RI mendorong Pemerintah Provinsi Nusa Tenggara Barat segera menuntaskan persoalan status ...</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689836/komisi-vii-minta-ntb-segera-tuntaskanpersoalan-pariwisata-tiga-gili</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_KOMISI-VII-MINTA-NTB-SEGERA-TUNTASKAN-PERSOALAN-PARIWISATA-TIGA-GILI.jpg</t>
+        </is>
+      </c>
+      <c r="I1301" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Usaha telur asin Cilegon produksi 2.000  per hari, tembus pasar Banten</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:55:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>ANTARA - Selama 19 tahun, Murod mengembangkan usaha telur asin dari produksi puluhan butir menjadi 2.000 butir per ...</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689959/usaha-telur-asin-cilegon-produksi-2000-per-hari-tembus-pasar-banten</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_USAHA-TELUR-ASIN-CILEGON-PRODUKSI-2.000-PER-HARI-TEMBUS-PASAR-BANTEN.jpg</t>
+        </is>
+      </c>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>GNB sampaikan delapan poin pesan kemerdekaan jelang HUT ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:55:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>ANTARA - Gerakan Nurani Bangsa (GNB) menggelar sarasehan dan menyampaikan delapan poin pesan kemerdekaan usai sarasehan ...</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689940/gnb-sampaikan-delapan-poin-pesan-kemerdekaan-jelang-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/GNB-SAMPAIKAN-DELAPAN-POIN-PESAN-KEMERDEKAAN-JELANG-HUT-KE-81-RI.jpg</t>
+        </is>
+      </c>
+      <c r="I1303" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Garuda dan InJourney berupaya tarik wisman ke lebih banyak destinasi</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:54:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>PT Garuda Indonesia (Persero) Tbk bersama PT Aviasi Pariwisata Indonesia (Persero) atau InJourney berupaya menarik ...</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689983/garuda-dan-injourney-berupaya-tarik-wisman-ke-lebih-banyak-destinasi</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-20.07.25.jpeg</t>
+        </is>
+      </c>
+      <c r="I1304" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Wamenkop sebut penempatan manajer Kopdes masih dipersiapkan</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:54:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Koperasi (Wamenkop) Farida Farichah mengatakan penempatan manajer Koperasi Desa/Kelurahan Merah Putih ...</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689979/wamenkop-sebut-penempatan-manajer-kopdes-masih-dipersiapkan</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/c79qikca.jpg</t>
+        </is>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Yaqut klaim tak pernah terima uang dari kasus korupsi kuota haji</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:47:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>Menteri Agama periode 2020–2024 Yaqut Cholil Qoumas menyatakan tidak pernah menerima uang satu rupiah pun ...</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689975/yaqut-klaim-tak-pernah-terima-uang-dari-kasus-korupsi-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/sidang-dakwaan-yaqut-cholil-qoumas-2838672.jpg</t>
+        </is>
+      </c>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Kemenag penuhi janji bangun ulang MIN 5 Pidie Jaya dengan lebih layak</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:47:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>ANTARA - Bencana banjir bandang yang menerjang desa Mon Senong, Pidie Jaya, Aceh akhir November 2025 lalu. Tidak ...</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689933/kemenag-penuhi-janji-bangun-ulang-min-5-pidie-jaya-dengan-lebih-layak</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_58_33_17.Still492.jpg</t>
+        </is>
+      </c>
+      <c r="I1307" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Airlangga: Fundamental ekonomi RI kuat meski hadapi dinamika global</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:46:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Perekonomian Airlangga Hartarto menegaskan fundamental ekonomi Indonesia tetap kuat didukung ...</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689973/airlangga-fundamental-ekonomi-ri-kuat-meski-hadapi-dinamika-global</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/47653FDE-6B7E-4613-A53F-FD6C21364C9F.jpeg</t>
+        </is>
+      </c>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Gempa dahsyat di Kolombia akibatkan 181 orang tewas dan 1.310 terluka</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:40:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>Jumlah korban tewas akibat gempa bumi berkekuatan magnitudo 7,4 yang mengguncang Kolombia, Senin (10/8) meningkat ...</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689969/gempa-dahsyat-di-kolombia-akibatkan-181-orang-tewas-dan-1310-terluka</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/bangunan-runtuh-akibat-gempa-kuat-di-Kolombia.jpg</t>
+        </is>
+      </c>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Spanyol imbau migran tidak mempertaruhkan nyawa untuk ke Ceuta</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:39:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>Menteri Luar Negeri Spanyol, Selasa, memperingatkan para migran agar tidak mempertaruhkan nyawa dengan mencoba memasuki ...</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689968/spanyol-imbau-migran-tidak-mempertaruhkan-nyawa-untuk-ke-ceuta</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Ceuta-spanyol.jpg</t>
+        </is>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Kemendikdasmen wujudkan sekolah sebagai rumah kedua lewat SNT 09 Gowa</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:38:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Dasar dan Menengah (Kemendikdasmen) berhasil mewujudkan sekolah sebagai rumah kedua bagi para ...</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689965/kemendikdasmen-wujudkan-sekolah-sebagai-rumah-kedua-lewat-snt-09-gowa</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000233119.jpg</t>
+        </is>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Pemerintah terus kebut penanganan Karhutla di Bromo</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:29:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Pembangunan Manusia dan Kebudayaan (Menko PMK) Pratikno menyatakan bahwa pemerintah terus ...</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689961/pemerintah-terus-kebut-penanganan-karhutla-di-bromo</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1000177502.jpg</t>
+        </is>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Anggota DPR dorong pemberian insentif bagi ibu rumah tangga</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:24:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>Anggota DPR RI Viktor Bungtilu Laiskodat mendorong pemerintah memberikan insentif dan perlindungan bagi ibu rumah ...</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689956/anggota-dpr-dorong-pemberian-insentif-bagi-ibu-rumah-tangga</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1001231248.jpg</t>
+        </is>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Menteri ESDM menjamin PNBP dari minerba dan migas dapat lampaui target</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:24:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menjamin bahwa Penerimaan Negara Bukan Pajak (PNBP) ...</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689952/menteri-esdm-menjamin-pnbp-dari-minerba-dan-migas-dapat-lampaui-target</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_211723.jpg</t>
+        </is>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Aceh Selatan serap dana TKD untuk normalisasi Sungai Krueng Trumon</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:22:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>ANTARA - Melalui dana Transfer Ke Daerah atau TKD yang diberikan oleh pemerintah pusat ke wilayah terdampak bencana, ...</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5689919/aceh-selatan-serap-dana-tkd-untuk-normalisasi-sungai-krueng-trumon</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_53_55_03.Still491.jpg</t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>OJK dan Kementerian UMKM bentuk satgas perluas pembiayaan UMKM</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:22:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) dan Kementerian Usaha Mikro, Kecil, dan Menengah (UMKM) sepakat untuk membentuk satuan ...</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689951/ojk-dan-kementerian-umkm-bentuk-satgas-perluas-pembiayaan-umkm</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-15.19.39.jpeg</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Chevrolet akan menghentikan penjualan mobil baru di pasar China</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:17:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>General Motors telah mengonfirmasi bahwa Chevrolet akan berhenti menjual mobil baru di pasar China, mengakhiri ...</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5689947/chevrolet-akan-menghentikan-penjualan-mobil-baru-di-pasar-china</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2019/10/29/chevrolet.jpg</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Harga hotel di Spanyol melonjak jelang gerhana Matahari total</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:16:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>Harga hotel melonjak tajam dan akomodasi di berbagai wilayah Spanyol sudah habis terjual menjelang gerhana Matahari ...</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689943/harga-hotel-di-spanyol-melonjak-jelang-gerhana-matahari-total</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/antarafoto-gerhana-matahari-sebagian-di-bekasi-20042023-par-2.jpg</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>KKP menangani 1.286 telur penyu di Sambas, hanya 96 layak ditetaskan</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:15:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>Kementerian Kelautan dan Perikanan (KKP) menangani 1.286 butir telur penyu yang ditemukan pada dua lokasi di Kabupaten ...</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5689936/kkp-menangani-1286-telur-penyu-di-sambas-hanya-96-layak-ditetaskan</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-14.12.40.jpeg</t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Progres LRT Jakarta Fase 1B Jelang Diresmikan</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:32:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>Muhammad Azzam</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>Pembangunan LRT Jakarta Fase 1B terus dikebut jelang peresmian. Progres konstruksinya kini telah mencapai 97,99 persen.</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8614467/progres-lrt-jakarta-fase-1b-jelang-diresmikan</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/progres-lrt-jakarta-fase-1b-jelang-diresmikan-1786462097440.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Garuda Tebar 170.845 Tiket Gratis buat Wisman</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:25:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>PT Garuda Indonesia (Persero) Tbk bersama PT Aviasi Pariwisata Indonesia (Persero) atau InJourney meluncurkan program peningkatan kunjungan wisatawan.</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8614461/garuda-tebar-170-845-tiket-gratis-buat-wisman</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/06/15/769bb45d-da7c-474a-b16a-8134644cb233_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>MSCI Segera Umumkan Rebalancing Saham, OJK Harap Pembekuan Dicabut</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:33:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>OJK berharap penyedia indeks global, MSCI obyektif menilai peningkatan transparansi pasar modal Indonesia dan segera mencabut pembekuan (freeze).</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8614415/msci-segera-umumkan-rebalancing-saham-ojk-harap-pembekuan-dicabut</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/02/13/6d3c742d-cc97-4819-a6ec-77edce240296_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Harga Pertalite Dijamin Tidak Naik sampai Desember</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:05:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>Pemerintah pastikan harga BBM subsidi aman alias tidak naik, sampai Desember.</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8614377/harga-pertalite-dijamin-tidak-naik-sampai-desember</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/09/01/antrean-di-spbu-mengular-panic-buying-isu-harga-bbm-naik-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Pekerja Informal Persampahan Dapat Keringanan Iuran Jaminan Sosial</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:00:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>Rifki Afifan</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>Pemerintah memberi keringanan iuran jaminan sosial. Kebijakan ini menyasar pekerja informal sektor persampahan.</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8613599/pekerja-informal-persampahan-dapat-keringanan-iuran-jaminan-sosial</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/pekerja-informal-persampahan-dapat-keringanan-iuran-jaminan-sosial-ketenagakerjaan-1786431203285_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Produksi Tas Travel Meningkat Jelang Musim Umrah</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:50:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>Muhammad Azzam</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>UMKM pembuat perlengkapan umrah memproduksi ratusan tas travel setiap hari. Pesanan meningkat menjelang musim keberangkatan umrah.</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8614352/produksi-tas-travel-meningkat-jelang-musim-umrah</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/produksi-tas-travel-meningkat-jelang-musim-umrah-1786456066313.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Kurang dari 24 Jam, Polisi Tangkap KF Terkait Wanita Muda Tewas di Tangerang</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:33:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>Kurang dari 24 jam setelah kejadian, polisi menangkap KF. Motif dan kronologi kematian wanita muda di Tangerang masih didalami.</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7867134/kurang-dari-24-jam-polisi-tangkap-kf-terkait-wanita-muda-tewas-di-tangerang</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/DlQgAzF77lGyDqvBt6frr4f96q0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ilustrasi-penangkapan-terduga-pelaku-tindak-pidana-oleh-polisi.jpg</t>
+        </is>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Mata Anak Tampak Juling? Coba Cek Pakai Flash HP, Dokter Ungkap Pantulan Cahaya yang Perlu Dicermati</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:22:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>Mata juling atau strabismus pada anak tidak selalu muncul terus-menerus sehingga perlu pengecekan.</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7867133/mata-anak-tampak-juling-coba-cek-pakai-flash-hp-dokter-ungkap-pantulan-cahaya-yang-perlu-dicermati</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oYC7Eu25ziOyR3hKvcJU_h4-zIA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bakti-sosial-operasi-mata-juling-jec_20231015_172841.jpg</t>
+        </is>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Laporan Keuangan BSSN Raih WTP, BPK Rekomendasikan Pembenahan Aset dan Belanja</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:18:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>BSSN meraih opini WTP untuk laporan keuangan 2025, tetapi BPK masih mencatat persoalan aset dan belanja.</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867132/laporan-keuangan-bssn-raih-wtp-bpk-rekomendasikan-pembenahan-aset-dan-belanja</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/arXl4_3ql_Q1vjblzpLd5xy4cXQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-bpk-ri-badan-pemeriksa-keuangan.jpg</t>
+        </is>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Cadangan Tembus 1,4 Miliar Barel, China Bangun Kekuatan Minyak dari Sisi Pembeli, Bukan Produsen</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:15:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>China bukan merupakan salah satu produsen minyak terbesar dunia. Namun berkat kekuatan uang, mereka mampu membeli dan menstok 1,4 miliar barel minyak.</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867131/cadangan-tembus-14-miliar-barel-china-bangun-kekuatan-minyak-dari-sisi-pembeli-bukan-produsen</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Q5f1SvaqZD85DlwF31QhRJge_V0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kapal-tanker-China-di-Selat-Hormuz.jpg</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Idy Muzayyad: Banyaknya Calon Ketum PBNU Tunjukkan Demokratisasi di Internal NU</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:14:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>Bursa calon Ketum PBNU 2026-2031 makin dinamis. Muncul 7-8 kandidat, NU diingatkan menjaga marwah muktamar dari politik uang.</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867130/idy-muzayyad-banyaknya-calon-ketum-pbnu-tunjukkan-demokratisasi-di-internal-nu</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/atQNf7QsqLrIUVarl0snUrlbjIg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wawancara-Anggota-Koordinator-Muktamar-Ke-35-PBNU-Idy-Muzayyad_20260811_170744.jpg</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Perang Iran-AS Jadi Ujian AI, IRGC: Rudal Kami Berhasil Hadapi Teknologi Amerika</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:03:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>Teknologi militer Amerika Serikat, termasuk sistem berbasis AI, gagal memberikan keunggulan menentukan dalam menghadapi Iran.</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867129/perang-iran-as-jadi-ujian-ai-irgc-rudal-kami-berhasil-hadapi-teknologi-amerika</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/nm1ZuVS7uMjwQPa9tQAPPcg-ElY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Rudal-IRGC-ke-Selat-Hormuz-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Suara untuk yang Tak Bisa Bicara, Pengalaman Pahit Dhisha dan Thomas Kehilangan Hewan Kesayangan</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:02:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>Kehadiran dokter hewan sangat krusial untuk menjadi perpanjangan suara bagi satwa-satwa yang menderita</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7867128/suara-untuk-yang-tak-bisa-bicara-pengalaman-pahit-dhisha-dan-thomas-kehilangan-hewan-kesayangan</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/GNxXBETlpXzF3A6pTtcjT7exoZw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/suarahwan11111.jpg</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Dikawal Polisi, Oknum Tenaga Kesehatan yang Sempat Bully Pasien BPJS Yurizal Datang ke Bogor</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:59:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>Dua oknum nakes yang sempat membully Yurizal datang ke Bogor meminta maaf kepada keluarga almarhum. Permintaan maaf diterima.</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867127/dikawal-polisi-oknum-tenaga-kesehatan-yang-sempat-bully-pasien-bpjs-yurizal-datang-ke-bogor</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8RxfNXKwalnCup3VRnRm31keznc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/makam-yurizal-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>192 Ribu Bibit Kopi Dihibahkan, Tunas Bumi Fest 2026 Bawa Pesan Menjaga Hutan Wonosobo</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:55:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>Bibit tersebut diberikan kepada Lembaga Masyarakat Desa Hutan (LMDH) dan Kelompok Tani Hutan (KTH)</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867126/192-ribu-bibit-kopi-dihibahkan-tunas-bumi-fest-2026-bawa-pesan-menjaga-hutan-wonosobo</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/tGVKeIsZzV7MxZZgpfkj-969KM8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Jatubu-Fest111111.jpg</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Koalisi Sipil Kritik Klaim Panglima TNI Bertanggung Jawab atas Kamtibmas</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:54:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Klaim Panglima TNI soal keamanan masyarakat menuai kritik. Koalisi Sipil mengingatkan batas kewenangan TNI dan Polri.</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867125/koalisi-sipil-kritik-klaim-panglima-tni-bertanggung-jawab-atas-kamtibmas</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/E3QMa9fa3HNSU927YKwVdeDFlnM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Presiden-Prabowo-Hadiri-Upacara-Gelar-Pasukan-dan-Kehormatan-Mil_20250811_110806.jpg</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Jelang Team Launching, Persija TC di Thailand dan Tantang Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:49:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>Persija bersiap menyambut Super League 2026/2027 dengan TC di Thailand sebelum meluncurkan tim dan menghadapi Brisbane Roar di JIS.</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867124/jelang-team-launching-persija-tc-di-thailand-dan-tantang-brisbane-roar</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/crXao2yo-UjEX99RtPnK3s3JExo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pemain-Persija-Jakarta-berfoto-bersama-menjelang-laga-perdana-Grup-B-Piala-Presiden-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Pakar Ingatkan RUU Perampasan Aset Harus Cegah Kekuasaan Dipakai Bungkam Lawan Politik</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:49:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>Ia meminta agar RUU Perampasan Aset secara tegas memberikan jaminan, kewenangan negara tidak dapat disalahgunakan untuk kepentingan politik.</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867123/pakar-ingatkan-ruu-perampasan-aset-harus-cegah-kekuasaan-dipakai-bungkam-lawan-politik</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/qglOIrg4c3lXIy6rB43f30cKECI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/perampasan-aset-skjd.jpg</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Cristiano Ronaldo Sudah Rindu Al Nassr, Rekan Senegara Sudah Gabung Duluan</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:49:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>Cristiano Ronaldo akan kembali ke Al Nassr pada tengah pekan ini untuk berlatih bersama rekan-rekannya menjelang musim 2026/2027.</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867122/cristiano-ronaldo-sudah-rindu-al-nassr-rekan-senegara-sudah-gabung-duluan</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Cyib7FLfUSF10TPgO8ouC9PoF_0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Logo-klub-Liga-Arab-Saudi-Al-Nassr.jpg</t>
+        </is>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Ketahanan Air Masuk Prioritas Nasional, AHY Tekankan Pentingnya Kolaborasi</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:49:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>Pemerintah menempatkan ketahanan air atau water security sebagai salah satu prioritas utama pembangunan nasional, sejajar dengan ketahanan pangan.</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867121/ketahanan-air-masuk-prioritas-nasional-ahy-tekankan-pentingnya-kolaborasi</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/AkC4VRXFN4MZJlBqD48-39W7e_g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ahy-air-pangan-as.jpg</t>
+        </is>
+      </c>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Habis Manis Sepah Dibuang: Paul Munster Out, Bhayangkara FC Depak Juru Penyelamat</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:45:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>Kabar mengejutkan datang dari Bhayangkara FC yang resmi memutuskan untuk berpisah dengan Paul Munster sebagai pelatih.</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867120/habis-manis-sepah-dibuang-paul-munster-out-bhayangkara-fc-depak-juru-penyelamat</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vSmPHoAl2A9WDAiJstoz1nFTN1w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Potret-aksi-duel-Bhayangkara-FC-vs-Persita-Tangerang-di-pekan-ke-11-Super-League.jpg</t>
+        </is>
+      </c>
+      <c r="I1340" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>35.936 Peserta Kapolri Cup 2026, Esports dan Tantangan Literasi Finansial</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:44:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>Kompetisi yang digelar di Indonesia Arena, Gelora Bung Karno itu menghadirkan pertandingan Mobile Legends: Bang Bang (MLBB)</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/e-sport/7867119/35936-peserta-kapolri-cup-2026-esports-dan-tantangan-literasi-finansial</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/GWYK-VELKrbWWVxgCrLj_83cI1g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PENGEMBANGAN-TALENTA-Esports-Kapolri-Cup-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I1341" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Ukraina Digempur Rudal dan 120 Drone, Zelensky Tuding Rusia Pakai Senjata Korut</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:36:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>Selain rudal, Rusia juga dilaporkan mengerahkan lebih dari 120 drone dalam serangan malam hingga pagi hari.</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867118/ukraina-digempur-rudal-dan-120-drone-zelensky-tuding-rusia-pakai-senjata-korut</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/t1lTPJsAvsM7FM8Z_QMNTGn3ar0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/DIHANTAM-RUDAL-BALISTIK-Ibu-kota-Ukraina-Kiev-diserang-oleh-Rusia.jpg</t>
+        </is>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Mengubah Sampah Menjadi Bahan Bakar, Mengapa Sampah Basah Jadi Kendala?</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:34:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>Salah satu teknologi yang dikembangkan untuk menjawab persoalan tersebut adalah Refuse Derived Fuel (RDF), yakni bahan bakar yang dibuat dari sampah</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867117/mengubah-sampah-menjadi-bahan-bakar-mengapa-sampah-basah-jadi-kendala</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Xsb5OdhuvaqkqAmy-k6mese8NsY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/sampahbasah111111.jpg</t>
+        </is>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Haaland Puncaki Daftar Gaji Liga Inggris 2026/2027, Rashford Punya Keuntungan dari Klausul Lama</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:27:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>Daftar 10 pemain dengan gaji tertinggi di Liga Inggris 2026/2027, dengan Haaland teratas yang mendapatkan bayaran sekitar Rp12 miliar per pekan.</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867116/haaland-puncaki-daftar-gaji-liga-inggris-20262027-rashford-punya-keuntungan-dari-klausul-lama</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5JoIgZ4U65E-o8goXbBIyLYIWEI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Logo-kompetisi-Liga-Inggris-atau-Premier-League.jpg</t>
+        </is>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Siap Nikah Tahun Depan, Jonathan Frizzy Sebut Ririn Dwi Ariyanti Soulmate Sempurna</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:24:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>Jonathan Frizzy dan Ririn Dwi Ariyanti mantap melangkah ke jenjang pernikahan. Keduanya meminta doa agar rencana baik mereka berjalan lancar.</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867115/siap-nikah-tahun-depan-jonathan-frizzy-sebut-ririn-dwi-ariyanti-soulmate-sempurna</t>
+        </is>
+      </c>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/08xUXEebGRYmJGQUXu1SOcDzb4w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Momen-kebersamaan-Jonathan-Frizzy-dan-Ririn-Dwi-Ariyanti.jpg</t>
+        </is>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Diam-Diam Pengendali Emiten Ini Borong 204 Juta Saham di Harga Rp210</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:35:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>Pengendali emiten di bidang pengolahan singkong, PT Budi Starch dan Sweetener (BUDI), Budi Delta Swakarya memborong 204 juta saham (4,54%) perseroan.</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811172750-17-758384/diam-diam-pengendali-emiten-ini-borong-204-juta-saham-di-harga-rp210</t>
+        </is>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2019/06/21/ab14131b-0e21-4f01-adff-754949cf6ace_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1346" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>RANS Ungkap Penggunaan Dana Hasil IPO, Nagita: Buat Pelunasan Utang</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:50:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>RANS Entertainment, milik Raffi Ahmad, alokasikan dana IPO untuk pelunasan utang dan pengembangan bisnis. Kerja sama strategis dengan Mayora juga diumumkan.</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1347" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811180008-17-758395/rans-ungkap-penggunaan-dana-hasil-ipo-nagita-buat-pelunasan-utang</t>
+        </is>
+      </c>
+      <c r="H1347" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/27/pt-rans-entertainmen-indonesia-tbk-rans-1785124527605_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1347" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Emiten RI Ini Mau Caplok 1 Pabrik Gula Jumbo dan Bangun 2 Pabrik Baru</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>Romys Binekasri</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>Emiten produsen gula, PT Aman Agrindo Tbk (GULA) saat ini tengah menjalankan tiga proyek strategis.</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811171357-17-758379/emiten-ri-ini-mau-caplok-1-pabrik-gula-jumbo-dan-bangun-2-pabrik-baru</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797018492_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Video: Efek RKAB-Biaya BBM Naik, Penambang Tunda Beli Truk-Alat Berat</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:00:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>RKAB - Biaya BBM Naik Bikin Penambang Tunda Beli Alat Berat, Distributor Kena Imbasnya</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811170703-19-758376/video-efek-rkab-biaya-bbm-naik-penambang-tunda-beli-truk-alat-berat</t>
+        </is>
+      </c>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/rkab-biaya-bbm-naik-bikin-penambang-tunda-beli-alat-berat-distributor-kena-imbasnya-1786443365369_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Purbaya Ungkap Ada Ide Keuntungan Danantara Masuk APBN</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:00:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya Yudhi Sadewa menyatakan keuntungan BPI Danantara akan disalurkan ke APBN. Pendapatan Danantara melonjak 400% dalam setahun.</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260811165448-17-758362/purbaya-ungkap-ada-ide-keuntungan-danantara-masuk-apbn</t>
+        </is>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/menteri-esdm-bahlil-lahadalia-dan-menteri-keuangan-purbaya-yudhi-sadewa-usai-melakukan-pertemuan-di-kantor-kementerian-keuanga-1786439887710_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Daihatsu Catatkan 591 SPK Sepanjang GIIAS 2026, Sigra Jadi Model Terlaris</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:29:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>Israr Itah</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, TANGERANG -- Daihatsu menutup partisipasinya di Gaikindo Indonesia International Auto Show (GIIAS) 2026 dengan hasil positif. Selama 11 hari penyelenggaraan pameran di ICE BSD, Tangerang, merek otomotif asal Jepang...</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjm314348/daihatsu-catatkan-591-spk-sepanjang-giias-2026-sigra-jadi-model-terlaris</t>
+        </is>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260729232327-626.png</t>
+        </is>
+      </c>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Laba BUMN Melejit, Ada yang Naik 804 Persen dalam Enam Bulan</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:56:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Sejumlah badan usaha milik negara (BUMN) mencatat pertumbuhan laba signifikan pada semester I 2026, termasuk perusahaan yang sebelumnya mengalami tekanan kinerja. Capaian tersebut menunjukkan adanya perbaikan pada...</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjm1dc416/laba-bumn-melejit-ada-yang-naik-804-persen-dalam-enam-bulan</t>
+        </is>
+      </c>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_241119101508-198.png</t>
+        </is>
+      </c>
+      <c r="I1352" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Ditangkap, Ini Tampang Pelaku Pembunuhan dan Pemerkosaan di Tangerang</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:00:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>Polisi menangkap kurang dari 24 jam setelah pelaku melancarkan aksinya.</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267522/ditangkap-ini-tampang-pelaku-pembunuhan-dan-pemerkosaan-di-tangerang</t>
+        </is>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/PZAYEojI2eFEzzJmj0KuNbn2kMI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321632/original/052176900_1786460436-a71e799a-7631-4261-b3b3-a253ab4faad9.jpg</t>
+        </is>
+      </c>
+      <c r="I1353" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Mantan Stafsus Yaqut Didakwa Terima 5,2 Juta Dolar AS dan Rp 330 Juta dari Korupsi Kuota Haji</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:54:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>Eks staf khusus Menteri Agama Yaqut Cholil Qoumas, Ishfah Abidal Azis alias Gus Alex didakwa menerima uang sebesar 5,2 juta dolar AS dan Rp 330 juta.</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/22514641/mantan-stafsus-yaqut-didakwa-terima-52-juta-dolar-as-dan-rp-330-juta-dari</t>
+        </is>
+      </c>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/mkdPAvRjMX48rozLcZBVJ_5s3KM=/479x107:2994x1784/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/01/26/6977470578a63.jpeg</t>
+        </is>
+      </c>
+      <c r="I1354" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>Cahaya</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Contoh Teks Doa Upacara 17 Agustus 2026 pada Peringatan HUT Ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:54:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>Contoh teks doa upacara HUT ke-81 RI pada 17 Agustus 2026 untuk dibacakan saat upacara Hari Kemerdekaan Republik Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>https://cahaya.kompas.com/doa-dan-niat/26H11220103190/contoh-teks-doa-upacara-17-agustus-2026-pada-peringatan-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/uPHZcq5iiOIr4YuWHvYAi1_Pq-Y=/0x0:2048x1365/1200x675/data/photo/2025/11/24/69242af6309cc.jpg</t>
+        </is>
+      </c>
+      <c r="I1355" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Dugaan Penyebab Kecelakaan Drag Race Kotamobagu Sulut yang Tewaskan 8 Penonton</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:54:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>'Semuanya ini masih kita lengkapi, masih kita kembangkan untuk sekali lagi membuat terang perkara ini,' ujarnya.</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>https://makassar.kompas.com/read/2026/08/11/210628478/dugaan-penyebab-kecelakaan-drag-race-kotamobagu-sulut-yang-tewaskan-8</t>
+        </is>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/qJYtu36N4ZY_lhfCKp-c_wVdyI0=/46x9:1024x662/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a7952569bb7e.png</t>
+        </is>
+      </c>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1279"/>
+  <autoFilter ref="A1:I1356"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1356</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1397</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1356"/>
+  <dimension ref="A1:I1397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -64171,8 +64171,1935 @@
         </is>
       </c>
     </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>KP2MI ungkap opsi, kuota sektor kerja Program SMK Go Global tahun ini</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:42:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>Kementerian Pelindungan Pekerja Migran Indonesia (KP2MI) mengungkapkan detail jumlah kebutuhan tenaga kerja, bidang ...</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690080/kp2mi-ungkap-opsi-kuota-sektor-kerja-program-smk-go-global-tahun-ini</t>
+        </is>
+      </c>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-05-at-13.28.21.jpeg</t>
+        </is>
+      </c>
+      <c r="I1357" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>KY pastikan proses seleksi calon hakim agung-ad hoc transparan</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:31:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>Komisi Yudisial memastikan pelaksanaan seleksi calon hakim agung, calon hakim ad hoc hak asasi manusia, dan calon ...</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1358" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690069/ky-pastikan-proses-seleksi-calon-hakim-agung-ad-hoc-transparan</t>
+        </is>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1358" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Ketahanan pangan, Kowani dorong hilirisasi singkong berbasis perempuan</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:31:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>Kongres Wanita Indonesia (Kowani) mendorong pengembangan hilirisasi singkong berbasis perempuan sebagai bagian dari ...</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690065/ketahanan-pangan-kowani-dorong-hilirisasi-singkong-berbasis-perempuan</t>
+        </is>
+      </c>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-14.12.22.jpg</t>
+        </is>
+      </c>
+      <c r="I1359" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Kantor Imigrasi Mimika deportasi WNA asal PNG</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:30:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>Kantor Imigrasi Kelas II TPI Mimika mendeportasi seorang warga negara asing (WNA) asal Papua New Guinea (PNG) yang ...</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690063/kantor-imigrasi-mimika-deportasi-wna-asal-png</t>
+        </is>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Imigrasi-Timika_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1360" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>InJourney dukung “Free Add-on Domestic Flight” Garuda Indonesia</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:24:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>ANTARA - InJourney dan Garuda Indonesia berkolaborasi mendorong kedatangan turis luar negeri lewat layanan “Free ...</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1361" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5690047/injourney-dukung-free-add-on-domestic-flight-garuda-indonesia</t>
+        </is>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/INJOURNEY-DUKUNG-22FREE-ADD-ON-DOMESTIC-FLIGHT-22-GARUDA-INDONESIA.jpg</t>
+        </is>
+      </c>
+      <c r="I1361" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Kasus korupsi haji, eks Stafsus Yaqut didakwa perkaya diri Rp93 miliar</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:21:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>Mantan Staf Khusus Yaqut Cholil Qoumas, Ishfah Abidal Aziz alias Gus Alex ,didakwa memperkaya diri senilai Rp93,42 ...</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690060/kasus-korupsi-haji-eks-stafsus-yaqut-didakwa-perkaya-diri-rp93-miliar</t>
+        </is>
+      </c>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/sidang-perdana-gus-alex-2838669.jpg</t>
+        </is>
+      </c>
+      <c r="I1362" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>Olimpiade Informatika Internasional dibuka di Uzbekistan untuk kali pertama</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:16:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>Olimpiade Informatika Internasional ke-38 (IOI 2026) dibuka pada hari Senin di ibu kota Uzbekistan, Tashkent, menurut ...</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690056/olimpiade-informatika-internasional-dibuka-di-uzbekistan-untuk-kali-pertama</t>
+        </is>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000016_20260811_CBMFN0A001.jpeg</t>
+        </is>
+      </c>
+      <c r="I1363" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Kejaksaan amankan uang Rp1,98 miliar dari kasus korupsi DPRD Ponorogo</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:15:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>ANTARA - Kejaksaan Negeri (Kejari) Ponorogo mengamankan uang senilai Rp 1,24 miliar dari penanganan kasus dugaan ...</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5690043/kejaksaan-amankan-uang-rp198-miliar-dari-kasus-korupsi-dprd-ponorogo</t>
+        </is>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KEJAKSAAN-AMANKAN-UANG-RP1-98-MILIAR-DARI-KASUS-KORUPSI-DPRD-PONOROGO.jpg</t>
+        </is>
+      </c>
+      <c r="I1364" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Wuling rangkum ribuan SPK dalam pameran GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:14:42 +0700</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>Wuling melaporkan total pemesanan sebesar 3.290 unit kendaraan selama sebelas hari ajang Gaikindo Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5690053/wuling-rangkum-ribuan-spk-dalam-pameran-giias-2026</t>
+        </is>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/CjkinzN000026_20260811_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1365" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan di Gunung Bromo capai 800 Ha, Jatim prioritaskan OMC</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:04:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>ANTARA - Kebakaran hutan di Gunung Bromo telah meluas mencapai 800 hektare lebih. Wilayah Jawa Timur ditetapkan ...</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5690035/kebakaran-hutan-di-gunung-bromo-capai-800-ha-jatim-prioritaskan-omc</t>
+        </is>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KEBAKARAN-HUTAN-DI-GUNUNG-BROMO-CAPAI-800-HA-JATIM-PRIORITASKAN-OMC.jpg</t>
+        </is>
+      </c>
+      <c r="I1366" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>Grab Indonesia ajak para mitra bersinergi untuk berkembang</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:04:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>Perusahaan layanan transportasi berbasis aplikasi Grab Indonesia mengajak para mitra perusahaan, termasuk pengemudi ...</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1367" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690045/grab-indonesia-ajak-para-mitra-bersinergi-untuk-berkembang</t>
+        </is>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1c86c2d4-d489-4c69-a64c-a632a2ec8d2c.jpeg</t>
+        </is>
+      </c>
+      <c r="I1367" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>Yogyakarta tuan rumah forum kerja sama antarpemda Indonesia-Tiongkok</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:53:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Yogyakarta menjadi tuan rumah kegiatan Local Governments Dialogue China- Indonesia on Local Government ...</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690040/yogyakarta-tuan-rumah-forum-kerja-sama-antarpemda-indonesia-tiongkok</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/IMG_20260811_223146.jpg</t>
+        </is>
+      </c>
+      <c r="I1368" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>KP2MI buka pendaftaran 40 ribu peserta SMK Go Global hingga 16 Agustus</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:53:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>Kementerian Pelindungan Pekerja Migran Indonesia (KP2MI) membuka pendaftaran tahap pertama Pelatihan Peningkatan ...</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690036/kp2mi-buka-pendaftaran-40-ribu-peserta-smk-go-global-hingga-16-agustus</t>
+        </is>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/WhatsApp-Image-2026-08-11-at-18.32.14.jpeg</t>
+        </is>
+      </c>
+      <c r="I1369" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>Airlangga minta emiten perkuat kinerja demi jaga kepercayaan pasar</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:47:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator (Menko) Bidang Perekonomian Airlangga Hartarto meminta seluruh emiten memperkuat kinerja, tata ...</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690033/airlangga-minta-emiten-perkuat-kinerja-demi-jaga-kepercayaan-pasar</t>
+        </is>
+      </c>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/37E20D7A-30BB-48E5-B5C9-D38BC54BF91F.jpeg</t>
+        </is>
+      </c>
+      <c r="I1370" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Puntung Rokok Anak Picu Kebakaran Rumah di Grobogan, Sang Ibu Tewas</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:28:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>Ardian Dwi Kurnia</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>Kebakaran tragis di Grobogan akibat puntung rokok anak. Seorang ibu tewas setelah api melahap rumah. Kejadian terjadi saat suami melihat asap dari kamar.</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614496/puntung-rokok-anak-picu-kebakaran-rumah-di-grobogan-sang-ibu-tewas</t>
+        </is>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/rumah-di-geyer-grobogan-terbakar-1786462775941_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1371" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Polri Beri Ruang Gen Z dan Alpha, Ada Lomba Mobile Legends hingga Animasi AI</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:21:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>Polri merayakan Hari Bhayangkara ke-80 dengan 'Apresiasi Kreasi Polri Untuk Masyarakat', memberikan penghargaan untuk inovasi dan pengabdian masyarakat.</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614494/polri-beri-ruang-gen-z-dan-alpha-ada-lomba-mobile-legends-hingga-animasi-ai</t>
+        </is>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/polri-gelar-apresiasi-kreasi-1786465267542_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1372" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>Momen Hangat Kapolri Beri Ruang Anak untuk Berkarya, dari Dongeng hingga Cita-cita</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:59:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>Azhar Bagas Ramadhan</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>Kapolri Listyo Sigit memberikan ruang bagi anak-anak berbagi cita-cita dan bakat di malam puncak penganugerahan Apresiasi Kreasi Polri untuk Masyarakat.</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614486/momen-hangat-kapolri-beri-ruang-anak-untuk-berkarya-dari-dongeng-hingga-cita-cita</t>
+        </is>
+      </c>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kapolri-jenderal-listyo-sigit-prabowo-memberikan-ruang-kepada-tiga-anak-untuk-menunjukkan-kemampuan-sekaligus-menyampaikan-cit-1786463916538_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1373" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Simpang Hek Kramat Jati Macet Panjang Malam Ini Imbas Perbaikan Jalan</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:55:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>Kemacetan parah terjadi di Jalan Raya Bogor, Kramat Jati, akibat perbaikan jalan. Kemacetan terjadi lantaran ada perbaikan jalan.</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614485/simpang-hek-kramat-jati-macet-panjang-malam-ini-imbas-perbaikan-jalan</t>
+        </is>
+      </c>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/simpang-hek-kramat-jati-macet-panjang-malam-inii-karena-ada-perbaikan-jalan-dwidetikcom-1786463737093_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1374" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Truk Tabrak Mobil Lagi Parkir di Kemang Jaksel, Sempat Tutup Jalan</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:41:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>Azhar Bagas Ramadhan</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>Truk menabrak mobil yang terparkir di Jalan Kemang Timur, Jakarta Selatan. Proses evakuasi selesai, lalu lintas kini lancar kembali.</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614479/truk-tabrak-mobil-lagi-parkir-di-kemang-jaksel-sempat-tutup-jalan</t>
+        </is>
+      </c>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/sebuah-truk-muatan-menabrak-mobil-yang-sedang-terparkir-di-jalan-kemang-timur-jakarta-selatan-screenshot-video-viral-1786462606747_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1375" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>Respons TNI soal Panglima Dikritik Imbas Pernyataan Tanggung Jawab Keamanan RI</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:23:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>Azhar Bagas Ramadhan</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>TNI merespons kritik terhadap Panglima terkait tanggung jawab keamanan. Koalisi Masyarakat Sipil menilai pernyataan itu berisiko membingungkan fungsi TNI.</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1376" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614458/respons-tni-soal-panglima-dikritik-imbas-pernyataan-tanggung-jawab-keamanan-ri</t>
+        </is>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/09/kapupsen-tni-brigjen-muhammad-nas-dok-istimewa-1783579696895_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1376" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>Siti Fauziah Sebut Sinergi Bakohumas Perkuat Publikasi Sidang Tahunan MPR</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:15:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>Plt. Sekjen MPR Siti Fauziah menekankan pentingnya sinergi Bakohumas untuk publikasi Sidang Tahunan MPR 2026 yang informatif dan kredibel. Persiapan sudah 85%.</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1377" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614455/siti-fauziah-sebut-sinergi-bakohumas-perkuat-publikasi-sidang-tahunan-mpr</t>
+        </is>
+      </c>
+      <c r="H1377" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/mpr-1786461289407_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1377" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Neng Eem Tekankan 3 Prinsip Kehumasan Kawal Sidang Tahunan MPR</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:10:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>Angelina Vioni</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>Ketua Fraksi PKB MPR, Neng Eem, menekankan tiga prinsip kehumasan: informatif, kolaboratif, dan kredibel, untuk publikasi Sidang Tahunan MPR 2026.</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1378" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614454/neng-eem-tekankan-3-prinsip-kehumasan-kawal-sidang-tahunan-mpr</t>
+        </is>
+      </c>
+      <c r="H1378" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/mpr-1786459705861_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1378" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>Kapolri Anugerahi Pemenang Apresiasi Kreasi Polri untuk Masyarakat</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:09:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>Kapolri Jenderal Listyo Sigit menghadiri penganugerahan 'Apresiasi Kreasi Polri untuk Masyarakat', merayakan kreativitas dan kolaborasi Polri dan masyarakat.</t>
+        </is>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1379" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614453/kapolri-anugerahi-pemenang-apresiasi-kreasi-polri-untuk-masyarakat</t>
+        </is>
+      </c>
+      <c r="H1379" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kapolri-anugerahi-pemenang-apresiasi-kreasi-polri-untuk-masyarakat-1786460939313_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1379" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>Senangnya Warga Bulak Barat Depok, Banjir Bertahun-tahun Kini Surut</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:02:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>Banjir di Kampung Bulak Barat, Cipayung, Depok, akhirnya surut setelah normalisasi sungai. Warga bersyukur dan berharap perbaikan jembatan segera selesai.</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1380" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614444/senangnya-warga-bulak-barat-depok-banjir-bertahun-tahun-kini-surut</t>
+        </is>
+      </c>
+      <c r="H1380" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/banjir-bertahun-tahun-di-depok-surut-1786460487792_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1380" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>TPS Liar Cilincing Disorot, Pengelolaan Sampah Berbasis RDF Jadi Perhatian</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:50:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>Peninjauan TPS liar di Cilincing oleh polsek dan kecamatan berfokus pada pengelolaan sampah berbasis RDF.</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1381" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614436/tps-liar-cilincing-disorot-pengelolaan-sampah-berbasis-rdf-jadi-perhatian</t>
+        </is>
+      </c>
+      <c r="H1381" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/peninjauan-tps-liar-di-cilincing-oleh-polsek-dan-kecamatan-fokus-pada-pengelolaan-sampah-berbasis-rdf-dok-ist-1786459833382_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1381" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Buka Forum Bakohumas MPR, Neng Eem Dorong Sinergi Komunikasi Pemerintah</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:48:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>â Nada Herwando Kartika</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>Ketua Fraksi PKB MPR Neng Eem tekankan pentingnya kehumasan pemerintah untuk menjembatani komunikasi antara pemerintah dan masyarakat dalam Sidang Tahunan MPR.</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614434/buka-forum-bakohumas-mpr-neng-eem-dorong-sinergi-komunikasi-pemerintah</t>
+        </is>
+      </c>
+      <c r="H1382" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/mpr-1786461289321_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1382" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Tampang Pria Pembunuh dan Pemerkosa Wanita di Tangerang</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:40:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>Kadek Melda Luxiana</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>Polisi tangkap pelaku pembunuhan dan pemerkosaan wanita berinisial SNA (20) di Tangerang. Penangkapan dilakukan kurang dari 24 jam setelah kejadian.</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614426/tampang-pria-pembunuh-dan-pemerkosa-wanita-di-tangerang</t>
+        </is>
+      </c>
+      <c r="H1383" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/pelaku-pemerkosa-dan-pembunuhan-wanita-di-tangerang-dok-istimewa-1786459171206.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1383" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Lawyer Muslim Adukan Challenge Hafalan Qur'an demi Miras ke Bareskrim</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:22:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>Asosiasi Lawyer Muslim melaporkan tantangan hafalan Al-Qur'an berhadiah miras ke Bareskrim. Penyelidikan sedang dilakukan terkait dugaan penistaan agama.</t>
+        </is>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1384" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614400/lawyer-muslim-adukan-challenge-hafalan-quran-demi-miras-ke-bareskrim</t>
+        </is>
+      </c>
+      <c r="H1384" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/asosiasi-lawyer-muslim-indonesia-almi-mengadukan-tindakan-challenge-hafalan-al-quran-berhadiah-minuman-keras-miras-saat-konser-1786458081129_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1384" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>Pemerintah Bakal Bentuk Tim Lintas Kementerian Atasi Masalah Agraria</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:14:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>Mensesneg Prasetyo Hadi umumkan pembentukan tim lintas kementerian untuk menyelesaikan masalah agraria.</t>
+        </is>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1385" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614398/pemerintah-bakal-bentuk-tim-lintas-kementerian-atasi-masalah-agraria</t>
+        </is>
+      </c>
+      <c r="H1385" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/prasetyo-hadi-1784523183633_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1385" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Dahlia Poland Temukan Tambatan Hati Baru, Pria Sunda-Satu Frekuensi</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:02:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>Aktris Dahlia Poland bahagia dengan kekasih baru setelah berpisah dari Fandy Christian. Ia menikmati hubungan yang masih dalam tahap pengenalan.</t>
+        </is>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1386" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8614328/dahlia-poland-temukan-tambatan-hati-baru-pria-sunda-satu-frekuensi</t>
+        </is>
+      </c>
+      <c r="H1386" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/25/dahlia-poland-1764056150319_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1386" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Denny Sumargo Mohon Doa, Istri Jalani Program Bayi Tabung Terakhir</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:02:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>Denny Sumargo dan Olivia Allan berjuang untuk anak kedua melalui program bayi tabung. Setelah empat kegagalan, mereka berharap percobaan terakhir ini berhasil.</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8614317/denny-sumargo-mohon-doa-istri-jalani-program-bayi-tabung-terakhir</t>
+        </is>
+      </c>
+      <c r="H1387" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/denny-sumargo-1786454390420_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1387" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Kuasa Hukum Eks Menag Yaqut Jelaskan Duduk Persoalan Pembagian Kuota Haji Tambahan</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>Kuasa hukum Yaqut Cholil Qoumas menjelaskan duduk persoalan mengenai pembagian kuota haji tambahan tahun 2023-2024 yang dipersoalkan KPK.</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867140/kuasa-hukum-eks-menag-yaqut-jelaskan-duduk-persoalan-pembagian-kuota-haji-tambahan</t>
+        </is>
+      </c>
+      <c r="H1388" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1hVGgaXLegVFCnj-iNku1-8XQW0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Terdakwa-kasus-dugaan-korupsi-kuota-haji-mantan-Menag-Yaqut-Cholil.jpg</t>
+        </is>
+      </c>
+      <c r="I1388" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Kolaborasi DeadSquad Bareng Limbad Sukses Meriahkan Parti Libur 2026</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:29:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>Parti Libur 2026 mengusung konsep Caravan yang memadukan festival musik dengan wahana bermain di Batu Night Spectacular (NBS).</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867139/kolaborasi-deadsquad-bareng-limbad-sukses-meriahkan-parti-libur-2026</t>
+        </is>
+      </c>
+      <c r="H1389" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/UqrxxSV_61vei1R96OGYmz_eHJQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Limbad-1-11082026.jpg</t>
+        </is>
+      </c>
+      <c r="I1389" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Pria Beristri Bunuh Kekasih di Tangerang, Pelaku Rekayasa Kematian Korban Seolah Gantung Diri</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:04:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>Wanita usia 29 tahun berinisial R menjadi korban pembunuhan yang dilakukan kekasihnya berinisial di Pasar Kemis, Kabupaten Tangerang.</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7867138/pria-beristri-bunuh-kekasih-di-tangerang-pelaku-rekayasa-kematian-korban-seolah-gantung-diri</t>
+        </is>
+      </c>
+      <c r="H1390" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/a4cQ92m0zPGnlR7WfCm6rl1m9D0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kasus-pembunuhan-pasar-kemis.jpg</t>
+        </is>
+      </c>
+      <c r="I1390" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Yaqut Bantah Terima Uang Korupsi Kuota Haji, Pertanyakan Pihak yang Raup Keuntungan</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:52:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>Yaqut membantah menerima uang dalam perkara kuota haji dan mempertanyakan pihak yang disebut jaksa memperoleh keuntungan.</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867137/yaqut-bantah-terima-uang-korupsi-kuota-haji-pertanyakan-pihak-yang-raup-keuntungan</t>
+        </is>
+      </c>
+      <c r="H1391" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/2hk2ajvAHooPwdG2smD6r2W1zfI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Mantan-Menteri-Agama-Yaqut-Cholil-Qoumas-usai-sidang-perdana-perkara-korupsi-kuota-haji.jpg</t>
+        </is>
+      </c>
+      <c r="I1391" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>73 Ribu Hektare Sawah Masih Berstatus Kawasan Hutan, Pemerintah Bentuk Tim Agraria</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:52:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>Pemerintah mengatakan 73.000 hektare lahan yang saat ini telah berbentuk sawah masih memiliki status yang dapat masuk dalam kawasan hutan.</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867136/73-ribu-hektare-sawah-masih-berstatus-kawasan-hutan-pemerintah-bentuk-tim-agraria</t>
+        </is>
+      </c>
+      <c r="H1392" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yezKPCYXFWzwWCegljMEEYJiBKY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ILUSTRASI-PERTANIAN-SAWAH.jpg</t>
+        </is>
+      </c>
+      <c r="I1392" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Perketat Ekspor Teknologi, China Tangkap Sejumlah Pengusaha Jepang</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:37:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>Informasi itu menyebut sejumlah eksekutif perusahaan Jepang yang memiliki operasi di China menjadi sasaran penyelidikan.</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867135/perketat-ekspor-teknologi-china-tangkap-sejumlah-pengusaha-jepang</t>
+        </is>
+      </c>
+      <c r="H1393" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/rtTV6JXDL-dp4lehWhprdwo1SFQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ILUSTRASI-Bendera-China-dan-Jepang.jpg</t>
+        </is>
+      </c>
+      <c r="I1393" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Polisi Kumpulkan Barbuk Kasus Challenge Hafalan Al-Qur'an Berhadiah Miras</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>Selain rekaman video yang beredar di media sosial, petugas juga memeriksa sejumlah barang bukti lain.</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267527/polisi-kumpulkan-barbuk-kasus-challenge-hafalan-al-quran-berhadiah-miras</t>
+        </is>
+      </c>
+      <c r="H1394" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Fp5iC-vppn7dJSzwqGEBlrLz0gY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321055/original/059736500_1786425649-Jepretan_Layar_2025-08-11_pukul_12.15.34.jpg</t>
+        </is>
+      </c>
+      <c r="I1394" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>Peringatan ke Pegawai, Gus Ipul: Jangan Kebiasaan Habiskan Uang dan Belanja Sembarangan</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:48:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>Mensos Saifullah Yusuf atau Gus Ipul memperingatkan pegawainya agar meninggalkan kebiasaan menghabiskan uang dan belanja anggaran secara sembarangan.</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/23324151/peringatan-ke-pegawai-gus-ipul-jangan-kebiasaan-habiskan-uang-dan-belanja</t>
+        </is>
+      </c>
+      <c r="H1395" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/pKspNR1Miw68Cgbca6xdXgMI_PM=/425x148:3753x2367/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a73165e5e027.jpeg</t>
+        </is>
+      </c>
+      <c r="I1395" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Perang AS Temui Menhan Sjafrie, Bahas soal Kelanjutan Kerja Sama Pertahanan</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:48:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Perang Amerika Serikat (AS) bidang Kebijakan Elbridge A. Colby mengunjungi Menteri Pertahanan RI Sjafrie Sjamsoeddin di Kemenhan RI.</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/22202711/wakil-menteri-perang-as-temui-menhan-sjafrie-bahas-soal-kelanjutan-kerja</t>
+        </is>
+      </c>
+      <c r="H1396" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/d6iy2gqD10-O_Sn9zLIxhlhGQOI=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7b340b0529f.jpg</t>
+        </is>
+      </c>
+      <c r="I1396" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>Rinaldi Umar Batal Dilantik Jadi Dirdik Jampidsus, Ini Alasan Kejagung</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:48:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>Alasan Rinaldi Umar batal dilantik sebagai Direktur Penyidikan (Dirdik) pada Jaksa Agung Muda Tindak Pidana Khusus karena alasan pengalaman.</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1397" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/21262681/rinaldi-umar-batal-dilantik-jadi-dirdik-jampidsus-ini-alasan-kejagung</t>
+        </is>
+      </c>
+      <c r="H1397" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/RkjlvY0ly1nBMPQx3Rv8uJ7Vyts=/265x66:1297x754/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/03/6a70a42491bfb.jpg</t>
+        </is>
+      </c>
+      <c r="I1397" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1356"/>
+  <autoFilter ref="A1:I1397"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-11.xlsx
+++ b/data/berita_2026-08-11.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1397</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1502</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1397"/>
+  <dimension ref="A1:I1502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -66098,8 +66098,4943 @@
         </is>
       </c>
     </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>Kaltara dapat bantuan Rp10 miliar lebih dari Presiden Prabowo</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:59:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>ANTARA - Gubernur Kalimantan Utara Zainal Arifin Paliwang menyebut Kaltara mendapat bantuan anggaran lebih dari Rp10 ...</t>
+        </is>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1398" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5690051/kaltara-dapat-bantuan-rp10-miliar-lebih-dari-presiden-prabowo</t>
+        </is>
+      </c>
+      <c r="H1398" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KALTARA-DAPAT-BANTUAN-RP10-MILIAR-LEBIH-DARI-PRESIDEN-PRABOWO.jpg</t>
+        </is>
+      </c>
+      <c r="I1398" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>Bapanas: Perpanjangan SPHP jagung pakan demi bantu peternak lokal</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:54:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>Kepala Badan Pangan Nasional (Bapanas) Andi Amran Sulaiman menegaskan program Stabilisasi Pasokan dan Harga Pangan ...</t>
+        </is>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1399" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690089/bapanas-perpanjangan-sphp-jagung-pakan-demi-bantu-peternak-lokal</t>
+        </is>
+      </c>
+      <c r="H1399" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/3E7505B6-92AA-42E1-8605-933DE8346CB5.jpeg</t>
+        </is>
+      </c>
+      <c r="I1399" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>OMC malam jadi opsi perkuat penanganan karhutla di Sumsel</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:52:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>ANTARA - Operasi Modifikasi Cuaca atau OMC pada malam hari disiapkan sebagai opsi untuk mengoptimalkan penanganan ...</t>
+        </is>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1400" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5690072/omc-malam-jadi-opsi-perkuat-penanganan-karhutla-di-sumsel</t>
+        </is>
+      </c>
+      <c r="H1400" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/OMC-MALAM-JADI-OPSI-PERKUAT-PENANGANAN-KARHUTLA-DI-SUMSEL.jpg</t>
+        </is>
+      </c>
+      <c r="I1400" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>Delapan pemain jadi sorotan dalam World Tour Lausanne 2026</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:52:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>Delapan pemain menjadi sorotan utama dalam FIBA 3x3 World Tour Lausanne 2026 di Swiss, pada 14-15 Agustus, mulai dari ...</t>
+        </is>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1401" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690088/delapan-pemain-jadi-sorotan-dalam-world-tour-lausanne-2026</t>
+        </is>
+      </c>
+      <c r="H1401" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/08/Basket-3-on-3.jpg</t>
+        </is>
+      </c>
+      <c r="I1401" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Silver Media Group gaet Chris John untuk kembangkan "Dragon's Dojo"</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:46:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>Silver Media Group menggandeng legenda tinju Indonesia, Chris John, untuk mengembangkan seri animasi baru berjudul ...</t>
+        </is>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1402" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690084/silver-media-group-gaet-chris-john-untuk-kembangkan-dragons-dojo</t>
+        </is>
+      </c>
+      <c r="H1402" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/07/03/IMG_2214.jpeg</t>
+        </is>
+      </c>
+      <c r="I1402" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Kemenbud siapkan situs bersejarah Bogor jadi Cagar Budaya Nasional</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:45:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>Kementerian Kebudayaan (Kemenbud) menyiapkan sejumlah situs bersejarah di Kabupaten Bogor, Jawa Barat, untuk ditata dan ...</t>
+        </is>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1403" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690083/kemenbud-siapkan-situs-bersejarah-bogor-jadi-cagar-budaya-nasional</t>
+        </is>
+      </c>
+      <c r="H1403" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1003331109.jpg</t>
+        </is>
+      </c>
+      <c r="I1403" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>KPAI Apresiasi Polri Beri Penghargaan ke Anak: Picu Mereka Terus Berkembang</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:43:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>Ketua KPAI Aris Adi Leksono apresiasi penghargaan Polri untuk anak. Ia berharap lebih banyak ruang bagi anak untuk berkreasi dan berprestasi.</t>
+        </is>
+      </c>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1404" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614499/kpai-apresiasi-polri-beri-penghargaan-ke-anak-picu-mereka-terus-berkembang</t>
+        </is>
+      </c>
+      <c r="H1404" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/ketua-kpai-aris-adi-leksono-apresiasi-penghargaan-polri-untuk-anak-kurniawan-fdetikcom-1786466595626_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1404" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Kak Seto Puji Polri Rangkul Anak Lewat Penghargaan dan Lomba Kreativitas</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:42:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>Kak Seto apresiasi kegiatan Apresiasi Kreasi Polri untuk Masyarakat. Ia menekankan pentingnya polisi sebagai sahabat anak dan membangun karakter.</t>
+        </is>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614498/kak-seto-puji-polri-rangkul-anak-lewat-penghargaan-dan-lomba-kreativitas</t>
+        </is>
+      </c>
+      <c r="H1405" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/kak-seto-selepas-acara-apresiasi-kreasi-polri-untuk-masyarakat-1786466516186_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1405" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>Pemerintah Janji Jaga Harga Pakan, Minta Dapur MBG Serap Telur Peternak</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:50:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>Menteri Pertanian (Mentan) Andi Amran Sulaiman memastikan harga pakan tetap dijaga hingga akhir tahun</t>
+        </is>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8614483/pemerintah-janji-jaga-harga-pakan-minta-dapur-mbg-serap-telur-peternak</t>
+        </is>
+      </c>
+      <c r="H1406" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/02/harga-telur-di-temanggung-anjlok-jadi-rp17000-rp18000-per-kg-1782966898187_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1406" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>Solomon Putra Wongso Tampil di Trunk Show Wedding, Hadirkan Sentuhan Tailoring dari London</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:56:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>Solomon Puttra Wongso tampil di trunk show bersama ayahnya, Lianto, membawa perspektif tailoring London ke panggung Jakarta.</t>
+        </is>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7867141/solomon-putra-wongso-tampil-di-trunk-show-wedding-hadirkan-sentuhan-tailoring-dari-london</t>
+        </is>
+      </c>
+      <c r="H1407" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fVrRaHo0Tso1W_ZiArEurHdcf6g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Lianto-Wongso-tengah-bersama-putranya-Solomon-Putra-Wongso-kiri.jpg</t>
+        </is>
+      </c>
+      <c r="I1407" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>Perang Saudara Negara Arab, Kuburan Massal Ditemukan</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>Kuburan massal ditemukan di Kurmuk, Sudan, setelah pasukan militer merebut kota.</t>
+        </is>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811170918-4-758368/perang-saudara-negara-arab-kuburan-massal-ditemukan</t>
+        </is>
+      </c>
+      <c r="H1408" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/09/13/jenazah-korban-ditempatkan-di-kuburan-massal-setelah-badai-dahsyat-dan-hujan-lebat-di-libya-di-derna-libya-12-september-2023-4_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1408" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>Kasus Suap Miliarder Dibatalkan, Pengacaranya sama dengan Presiden</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>Hakim AS batalkan kasus suap Gautam Adani. Pengacara Adani, Robert Giuffra, merupakan pengacara pribadi Presiden AS Donald Trump.</t>
+        </is>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811164104-4-758357/kasus-suap-miliarder-dibatalkan-pengacaranya-sama-dengan-presiden</t>
+        </is>
+      </c>
+      <c r="H1409" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/20/miliarder-india-gautam-adani-reutersstringerfile-photo-1779240974007_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1409" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>Iran Rombak Struktur Keamanan, Veteran IRGC Naik ke Posisi Kunci</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>tfa</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>Iran melakukan perombakan di jajaran keamanan dengan menunjuk veteran IRGC, termasuk Mohsen Rezaee, di tengah ketegangan dengan AS dan Israel.</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811143928-4-758300/iran-rombak-struktur-keamanan-veteran-irgc-naik-ke-posisi-kunci</t>
+        </is>
+      </c>
+      <c r="H1410" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/13/seorang-wanita-memegang-bendera-iran-di-jalanan-teheran-iran-10-juni-2026-1781317439422_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1410" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>CNG 3 Kg Bakal Disubsidi, Tapi Biayanya Lebih Hemat 40% dari LPG</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>CNG 3 Kg bakal disubsidi pemerintah</t>
+        </is>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811181543-4-758404/cng-3-kg-bakal-disubsidi-tapi-biayanya-lebih-hemat-40-dari-lpg</t>
+        </is>
+      </c>
+      <c r="H1411" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/29/ilustrasi-cng-merah-putih-3kg-1782728074855_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1411" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>Banjir Surut, Potret Pantai Tetangga RI Kini Jadi Lautan Sampah</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>Sampah menumpuk di Pantai Dolomit Manila usai hujan deras akibat Habagat. Limbah terbawa banjir dari saluran air dan permukiman di sekitar kawasan.</t>
+        </is>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811180143-7-758397/banjir-surut-potret-pantai-tetangga-ri-kini-jadi-lautan-sampah</t>
+        </is>
+      </c>
+      <c r="H1412" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/seorang-pekerja-mengumpulkan-sampah-yang-terbawa-arus-ke-sungai-di-tengah-hujan-deras-akibat-angin-muson-barat-daya-di-dekat-g-1786446098324_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1412" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>Lempeng Samudra Nazca Plate Robek, Gempa Dahsyat Mw7,4 Rusak Kolombia</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>Gempa Mw7,4 mengguncang Kolombia, menewaskan 138 orang dan melukai ratusan. Daryono menjelaskan penyebab dan dampak gempa dalam-lempeng ini.</t>
+        </is>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811180341-4-758396/lempeng-samudra-nazca-plate-robek-gempa-dahsyat-mw74-rusak-kolombia</t>
+        </is>
+      </c>
+      <c r="H1413" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/suasana-setelah-gempa-bumi-di-dosquebradas-kolombia-senin-1082026-reutersjuan-david-duque-1786405982899_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1413" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>Gubernur Bank Sentral Libya Mundur di Tengah Tekanan Ekonomi</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>Pengunduran diri Gubernur Bank Sentral Libya, Naji Issa, memunculkan tantangan ekonomi besar, termasuk belanja pemerintah dan cadangan devisa.</t>
+        </is>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811161659-4-758346/gubernur-bank-sentral-libya-mundur-di-tengah-tekanan-ekonomi</t>
+        </is>
+      </c>
+      <c r="H1414" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/gubernur-bank-sentral-libya-naji-issa-1786440205574_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1414" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>Freeport Sudah Ajukan Perpanjangan Izin Tambang (IUPK), Ini Kata ESDM</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>Firda Dwi Muliawati</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM masih mereview permohonan perpanjangan IUPK PT Freeport Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811170211-4-758367/freeport-sudah-ajukan-perpanjangan-izin-tambang--iupk--ini-kata-esdm</t>
+        </is>
+      </c>
+      <c r="H1415" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/01/23/dirjen-minerba-kementerian-esdm-tri-winarno-saat-menyampaikan-paparan-dalam-program-cnbc-indonesia-mining-zone-1769160383776_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1415" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Siap-Siap China Digulung Petaka, Beijing Darurat</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>Beijing bersiap menghadapi hujan ekstrem mulai 11 Agustus 2026, dengan curah hujan diperkirakan melebihi 200 mm dalam 24 jam, meningkatkan risiko banjir.</t>
+        </is>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811143603-4-758298/siap-siap-china-digulung-petaka-beijing-darurat</t>
+        </is>
+      </c>
+      <c r="H1416" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/sebuah-truk-terguling-akibat-angin-kencang-saat-topan-dolphin-menerjang-daratan-di-wenzhou-provinsi-zhejiang-tiongkok-pada-9-a-1786355485482_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1416" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>Soal Pembatasan BBM Pertalite, Bahlil: Sesuai Jenis Kendaraannya</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil Lahadalia merumuskan kriteria yang akan dibatasi menggunakan BBM Pertalite</t>
+        </is>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811171307-4-758381/soal-pembatasan-bbm-pertalite-bahlil-sesuai-jenis-kendaraannya</t>
+        </is>
+      </c>
+      <c r="H1417" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/menteri-esdm-bahlil-lahadalia-datangi-kantor-menteri-keuangan-purbaya-yudhi-sadewa-selasa-1182026-1786432462005_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1417" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>PNBP Sektor ESDM Tahun 2026 Diramal Bisa Melebihi Target</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>Firda Dwi Muliawati</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>PNBP sektor ESDM diramal bakal melebihi target tahun 2026</t>
+        </is>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811191022-4-758412/pnbp-sektor-esdm-tahun-2026-diramal-bisa-melebihi-target</t>
+        </is>
+      </c>
+      <c r="H1418" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/07/10/gedung-kementerian-esdm-dok-esdm_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1418" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>Momen Utusan AS Datangi Menhan Sjafrie Sjamsoeddin, Ada Apa?</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>Instagram/sjafrie.sjamsoeddin</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>Menhan Sjafrie Sjamsoeddin bertemu pejabat pertahanan AS Elbridge A. Colby. Keduanya membahas penguatan kerja sama pertahanan dan keamanan kawasan.</t>
+        </is>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811174948-7-758387/momen-utusan-as-datangi-menhan-sjafrie-sjamsoeddin-ada-apa</t>
+        </is>
+      </c>
+      <c r="H1419" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/menteri-pertahanan-menhan-sjafrie-sjamsoeddin-menerima-courtesy-call-sekaligus-melaksanakan-round-table-discussion-bersama-us--1786445238426_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1419" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>Uji Sistem! Pembatasan Pengguna BBM Pertalite Bakal Dilakukan Bertahap</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>Pemerintah bakal melakukan secara bertahap pembatasan pengguanaan BBM Pertalite</t>
+        </is>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811183732-4-758407/uji-sistem-pembatasan-pengguna-bbm-pertalite-bakal-dilakukan-bertahap</t>
+        </is>
+      </c>
+      <c r="H1420" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/11/18/petugas-mengisi-bahan-bakar-minyak-bbm-jenis-pertalite-untuk-kendaraan-roda-dua-pada-salah-satu-spbu-di-jakarta-senin-18112024-8_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1420" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>KP2MI Buka Pendaftaran Pelatihan Asta Mandala SMK Go Global!</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:11:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>Pendaftaran Pelatihan Asta Mandala SMK Go Global dibuka 12-16 Agustus 2026. Program ini siapkan generasi muda Indonesia untuk pasar kerja internasional.</t>
+        </is>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811190548-4-758410/kp2mi-buka-pendaftaran-pelatihan-asta-mandala-smk-go-global</t>
+        </is>
+      </c>
+      <c r="H1421" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/dok-kementerian-pelindungan-pekerja-migran-indonesia-kp2mi-1786450231375_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1421" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>Berita Duka: Rida Mulyana Mantan Sekjen KESDM Meninggal Dunia</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:09:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>Rida Mulyana mantan Sekjen Kementerian ESDM meninggal dunia</t>
+        </is>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811185928-4-758411/berita-duka-rida-mulyana-mantan-sekjen-kesdm-meninggal-dunia</t>
+        </is>
+      </c>
+      <c r="H1422" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/01/10/fd501455-dd1c-48fd-a774-b70915471ff1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1422" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>Data Baru! Utang Pemerintah Rp10.293 T, 41% dari PDB</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 19:01:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>Direktorat Jenderal Pengelolaan Pembiayaan dan Risiko (DJPPR) merilis data terbaru total utang pemerintah pusat, per Semester I-2026.</t>
+        </is>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811185938-4-758409/data-baru-utang-pemerintah-rp10293-t-41-dari-pdb</t>
+        </is>
+      </c>
+      <c r="H1423" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/01/10/suasana-gedung-kementerian-keuangan-kemenkeu-di-jakarta-rabu-1012024-19_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1423" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>Menko PMK Pratikno Bantah Sakit dan Mundur dari Kabinet Presiden Prabowo</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:55:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>Pratikno menegaskan sedang bertugas melakukan percepatan pemadaman kebakaran hutan dan lahan (karhutla) di Taman Nasional Bromo Tengger Semeru, Jawa Timur.</t>
+        </is>
+      </c>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1424" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811182030-4-758406/menko-pmk-pratikno-bantah-sakit-mundur-dari-kabinet-presiden-prabowo</t>
+        </is>
+      </c>
+      <c r="H1424" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/12/03/menteri-koordinator-bidang-pembangunan-manusia-dan-kebudayaan-pratikno-saat-menyampaikan-keterangan-pers-perkembangan-penanggu-1764745137945_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1424" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Ini Dia Jenis Kendaraan yang Tidak Akan Kena Pembatasan BBM Pertalite</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>Ini jenis kendaraan yang tidak akan kena pembatasan BBM Pertalite</t>
+        </is>
+      </c>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1425" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811181902-4-758405/ini-dia-jenis-kendaraan-yang-tidak-akan-kena-pembatasan-bbm-pertalite</t>
+        </is>
+      </c>
+      <c r="H1425" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/menteri-esdm-bahlil-lahadalia-dan-menteri-keuangan-purbaya-yudhi-sadewa-usai-melakukan-pertemuan-di-kantor-kementerian-keuanga-1786439887620_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1425" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>Soal Rencana Pembatasan Pertalite, Bahlil: Biar Subsidi Tepat Sasaran</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil Lahadalia menekankan bahwa pembatasan BBM Pertalite supaya subsidi tepat sasaran</t>
+        </is>
+      </c>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1426" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811165958-4-758365/soal-rencana-pembatasan-pertalite-bahlil-biar-subsidi-tepat-sasaran</t>
+        </is>
+      </c>
+      <c r="H1426" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/menteri-esdm-bahlil-lahadalia-dan-menteri-keuangan-purbaya-yudhi-sadewa-usai-melakukan-pertemuan-di-kantor-kementerian-keuanga-1786439887620_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1426" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>CNG Alternatif Pengganti LPG 3 Kg Bakal Diuji Coba Pekan Depan</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>Pemerintah bakal melakukan uji coba CNG sebagai alternatif pengganti LPG 3 Kg</t>
+        </is>
+      </c>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1427" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811175616-4-758394/cng-alternatif-pengganti-lpg-3-kg-bakal-diuji-coba-pekan-depan</t>
+        </is>
+      </c>
+      <c r="H1427" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/29/ilustrasi-cng-merah-putih-3kg-1782728074855_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1427" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Pembelian Pertalite Mau Dibatasi, Purbaya: Kita Incar Kalangan Atas</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:30:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>Rencana pemerintah untuk membatasi pembelian bahan bakar minyak (BBM) bersubsidi ditujukan supaya konsumsinya tepat sasaran.</t>
+        </is>
+      </c>
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1428" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811165717-4-758364/pembelian-pertalite-mau-dibatasi-purbaya-kita-incar-kalangan-atas</t>
+        </is>
+      </c>
+      <c r="H1428" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/21/menteri-keuangan-menkeu-purbaya-yudhi-sadewa-saat-menyampaikan-pemaparan-dalam-konferensi-pers-apbn-kita-edisi-juli-2026-di-ka-1784620747563_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1428" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Integrasi Satusehat-Siak, Akte Kelahiran Terbit Setelah Bayi Lahir</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 18:15:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>Integrasi Satusehat-Siak, Akte Kelahiran Langsung Terbit Setelah Bayi Lahir</t>
+        </is>
+      </c>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1429" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811145924-8-758316/integrasi-satusehat-siak-akte-kelahiran-terbit-setelah-bayi-lahir</t>
+        </is>
+      </c>
+      <c r="H1429" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/integrasi-satusehat-siak-akte-kelahiran-langsung-terbit-setelah-bayi-lahir-1786443833062_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1429" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>Fenomena Baru, Ada Perubahan Perilaku di Pengguna Asuransi Kendaraan</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:56:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>Vincent Soegianto, CEO Oona Insurance, mengungkap perubahan perilaku pengguna asuransi kendaraan, kini fokus pada perlindungan risiko personal accident.</t>
+        </is>
+      </c>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811175135-4-758393/fenomena-baru-ada-perubahan-perilaku-di-pengguna-asuransi-kendaraan</t>
+        </is>
+      </c>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/president-director-chief-executive-officer-ceo-oona-insurance-indonesia-vincent-c-soegianto-saat-menyampaikan-pemaparan-dalam--1786417368032_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1430" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Daerah di Jabar Ini Mau Disulap Jadi Pusat Mebel dan Kerajinan RI</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>Daerah di Jabar ini berpotensi jadi pusat industri mebel dan kerajinan baru di Indonesia. Ini lokasinya.</t>
+        </is>
+      </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811164429-4-758359/daerah-di-jabar-ini-mau-disulap-jadi-pusat-mebel-dan-kerajinan-ri</t>
+        </is>
+      </c>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/02/18/pabrik-pembuatan-mebel-19_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1431" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>Konsumsi BBM Pertalite Bakal Dibatasi, Ini Penjelasan Bahlil dan Purbaya</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan dan Menteri ESDM bahas pembatasan subsidi Pertalite untuk kelompok ekonomi atas.</t>
+        </is>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811164705-4-758361/konsumsi-bbm-pertalite-bakal-dibatasi-ini-penjelasan-bahlil-purbaya</t>
+        </is>
+      </c>
+      <c r="H1432" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/menteri-esdm-bahlil-lahadalia-dan-menteri-keuangan-purbaya-yudhi-sadewa-usai-melakukan-pertemuan-di-kantor-kementerian-keuanga-1786439887620_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1432" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Industri Sepatu RI Lagi Tancap Gas-Gegara AS Jadi Dipepet 2 Negara Ini</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 17:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>Industri kulit dan alas kaki tumbuh 11,30% pada kuartal II-2026, tertinggi dalam 15 kuartal.</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260811172207-4-758382/industri-sepatu-ri-lagi-tancap-gas-gegara-as-jadi-dipepet-2-negara-ini</t>
+        </is>
+      </c>
+      <c r="H1433" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/07/10/ilustrasi-sepatu-dok-freepik-1752130339557_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1433" t="inlineStr">
+        <is>
+          <t>CNBC Indon